--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4834,16 +4834,16 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="P1">
-            <v>4166.66666666667</v>
+            <v>11166.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>1000</v>
+            <v>1800</v>
           </cell>
           <cell r="R1">
             <v>0</v>
           </cell>
           <cell r="S1">
-            <v>0</v>
+            <v>700</v>
           </cell>
           <cell r="T1">
             <v>0</v>
@@ -4861,13 +4861,13 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="P1">
-            <v>4166.66666666667</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
-            <v>2000</v>
+            <v>1000</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -4888,16 +4888,16 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="P1">
-            <v>4166.66666666667</v>
+            <v>12366.6666666667</v>
           </cell>
           <cell r="Q1">
+            <v>800</v>
+          </cell>
+          <cell r="R1">
+            <v>2000</v>
+          </cell>
+          <cell r="S1">
             <v>0</v>
-          </cell>
-          <cell r="R1">
-            <v>0</v>
-          </cell>
-          <cell r="S1">
-            <v>500</v>
           </cell>
           <cell r="T1">
             <v>0</v>
@@ -4915,16 +4915,16 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="P1">
-            <v>5833.33333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>1000</v>
+            <v>1800</v>
           </cell>
           <cell r="R1">
             <v>0</v>
           </cell>
           <cell r="S1">
-            <v>0</v>
+            <v>700</v>
           </cell>
           <cell r="T1">
             <v>0</v>
@@ -4942,10 +4942,10 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="P1">
-            <v>5833.33333333333</v>
+            <v>12966.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -4969,16 +4969,16 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="P1">
-            <v>5833.33333333333</v>
+            <v>10866.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>1800</v>
           </cell>
           <cell r="S1">
-            <v>0</v>
+            <v>500</v>
           </cell>
           <cell r="T1">
             <v>0</v>
@@ -4996,16 +4996,16 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="P1">
-            <v>5833.33333333333</v>
+            <v>12966.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>1000</v>
+            <v>1800</v>
           </cell>
           <cell r="R1">
             <v>0</v>
           </cell>
           <cell r="S1">
-            <v>0</v>
+            <v>700</v>
           </cell>
           <cell r="T1">
             <v>0</v>
@@ -5023,13 +5023,13 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="P1">
-            <v>4166.66666666667</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
-            <v>1500</v>
+            <v>3000</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -5050,10 +5050,10 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="P1">
-            <v>4166.66666666667</v>
+            <v>12366.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -5077,16 +5077,16 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="P1">
-            <v>2500</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
+            <v>1800</v>
+          </cell>
+          <cell r="R1">
             <v>1000</v>
           </cell>
-          <cell r="R1">
-            <v>0</v>
-          </cell>
           <cell r="S1">
-            <v>0</v>
+            <v>1100</v>
           </cell>
           <cell r="T1">
             <v>0</v>
@@ -5104,13 +5104,13 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="P1">
-            <v>2500</v>
+            <v>12166.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>1500</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -5131,10 +5131,10 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="P1">
-            <v>1250</v>
+            <v>10866.6666666667</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>800</v>
           </cell>
           <cell r="R1">
             <v>0</v>
@@ -5146,7 +5146,7 @@
             <v>0</v>
           </cell>
           <cell r="U1">
-            <v>333.333333333333</v>
+            <v>300</v>
           </cell>
         </row>
         <row r="1">
@@ -5194,25 +5194,25 @@
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
-            <v>1200</v>
+            <v>0</v>
           </cell>
           <cell r="U1">
-            <v>0</v>
+            <v>120</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="W1">
-            <v>300</v>
+            <v>602.25</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -5228,13 +5228,13 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>720</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>360</v>
+            <v>249</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -5246,13 +5246,13 @@
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>153</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>666</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>152</v>
           </cell>
           <cell r="Y1">
             <v>600</v>
@@ -5268,37 +5268,37 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="Q1">
-            <v>3600</v>
+            <v>5000</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="U1">
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>231</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>654</v>
           </cell>
           <cell r="X1">
-            <v>720</v>
+            <v>272</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
           </cell>
           <cell r="Z1">
-            <v>300</v>
+            <v>550</v>
           </cell>
           <cell r="AA1">
             <v>0</v>
@@ -5308,34 +5308,34 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>720</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
-            <v>1200</v>
+            <v>0</v>
           </cell>
           <cell r="U1">
-            <v>0</v>
+            <v>180</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>159</v>
           </cell>
           <cell r="W1">
-            <v>300</v>
+            <v>584.25</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>480</v>
           </cell>
           <cell r="Z1">
             <v>300</v>
@@ -5348,13 +5348,13 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>540</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="S1">
             <v>800</v>
@@ -5363,16 +5363,16 @@
             <v>0</v>
           </cell>
           <cell r="U1">
-            <v>0</v>
+            <v>240</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>602.25</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>140</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -5388,37 +5388,37 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="P1">
+            <v>240</v>
+          </cell>
+          <cell r="Q1">
             <v>0</v>
           </cell>
-          <cell r="Q1">
-            <v>2400</v>
-          </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
+            <v>300</v>
+          </cell>
+          <cell r="U1">
             <v>0</v>
           </cell>
-          <cell r="U1">
-            <v>480</v>
-          </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>147</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>708</v>
           </cell>
           <cell r="X1">
-            <v>720</v>
+            <v>92</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
           </cell>
           <cell r="Z1">
-            <v>300</v>
+            <v>1468</v>
           </cell>
           <cell r="AA1">
             <v>0</v>
@@ -5434,28 +5434,28 @@
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
-            <v>1200</v>
+            <v>0</v>
           </cell>
           <cell r="U1">
-            <v>0</v>
+            <v>96</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="W1">
-            <v>300</v>
+            <v>606.75</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>212</v>
           </cell>
           <cell r="Y1">
-            <v>0</v>
+            <v>3000</v>
           </cell>
           <cell r="Z1">
             <v>300</v>
@@ -5468,13 +5468,13 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>840</v>
           </cell>
           <cell r="Q1">
-            <v>0</v>
+            <v>3000</v>
           </cell>
           <cell r="R1">
-            <v>360</v>
+            <v>249</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -5486,13 +5486,13 @@
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>165</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>645</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>164</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -5508,37 +5508,37 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>480</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="S1">
-            <v>0</v>
+            <v>5000</v>
           </cell>
           <cell r="T1">
-            <v>0</v>
+            <v>420</v>
           </cell>
           <cell r="U1">
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>255</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>613.5</v>
           </cell>
           <cell r="X1">
-            <v>720</v>
+            <v>92</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
           </cell>
           <cell r="Z1">
-            <v>300</v>
+            <v>467</v>
           </cell>
           <cell r="AA1">
             <v>500</v>
@@ -5548,34 +5548,34 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>600</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
-            <v>1200</v>
+            <v>0</v>
           </cell>
           <cell r="U1">
-            <v>0</v>
+            <v>144</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>153</v>
           </cell>
           <cell r="W1">
-            <v>300</v>
+            <v>638.25</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>92</v>
           </cell>
           <cell r="Y1">
-            <v>600</v>
+            <v>480</v>
           </cell>
           <cell r="Z1">
             <v>300</v>
@@ -5588,13 +5588,13 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>660</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>285</v>
           </cell>
           <cell r="S1">
             <v>0</v>
@@ -5606,13 +5606,13 @@
             <v>360</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>135</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>595.5</v>
           </cell>
           <cell r="X1">
-            <v>0</v>
+            <v>368</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
@@ -5628,37 +5628,37 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="P1">
-            <v>0</v>
+            <v>300</v>
           </cell>
           <cell r="Q1">
             <v>0</v>
           </cell>
           <cell r="R1">
-            <v>0</v>
+            <v>249</v>
           </cell>
           <cell r="S1">
             <v>0</v>
           </cell>
           <cell r="T1">
-            <v>0</v>
+            <v>360</v>
           </cell>
           <cell r="U1">
             <v>0</v>
           </cell>
           <cell r="V1">
-            <v>60</v>
+            <v>159</v>
           </cell>
           <cell r="W1">
-            <v>0</v>
+            <v>682.5</v>
           </cell>
           <cell r="X1">
-            <v>720</v>
+            <v>92</v>
           </cell>
           <cell r="Y1">
             <v>0</v>
           </cell>
           <cell r="Z1">
-            <v>300</v>
+            <v>425</v>
           </cell>
           <cell r="AA1">
             <v>0</v>
@@ -10010,7 +10010,7 @@
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="str">
         <f aca="false">IF(D38&gt;67000,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
-        <v>Business income - if your annual turnover was below £90000 VAT threshold</v>
+        <v>SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £90000 VAT threshold</v>
       </c>
       <c r="B33" s="96"/>
       <c r="C33" s="96"/>
@@ -10155,7 +10155,7 @@
       </c>
       <c r="D38" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B9</f>
-        <v>58416.6666666667</v>
+        <v>169200</v>
       </c>
       <c r="E38" s="98"/>
       <c r="F38" s="98"/>
@@ -10391,7 +10391,7 @@
       </c>
       <c r="D46" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B17," ")</f>
-        <v>7800</v>
+        <v>17744</v>
       </c>
       <c r="E46" s="98"/>
       <c r="F46" s="98"/>
@@ -10413,7 +10413,7 @@
       </c>
       <c r="O46" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B28," ")</f>
-        <v>3600</v>
+        <v>5310</v>
       </c>
       <c r="P46" s="98"/>
       <c r="Q46" s="98"/>
@@ -10548,7 +10548,7 @@
       </c>
       <c r="D51" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
-        <v>4080</v>
+        <v>9458.25</v>
       </c>
       <c r="E51" s="98"/>
       <c r="F51" s="98"/>
@@ -10678,7 +10678,7 @@
       </c>
       <c r="D55" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B21," ")</f>
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="E55" s="98"/>
       <c r="F55" s="98"/>
@@ -10700,7 +10700,7 @@
       </c>
       <c r="O55" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B24," ")</f>
-        <v>720</v>
+        <v>1962</v>
       </c>
       <c r="P55" s="98"/>
       <c r="Q55" s="98"/>
@@ -10835,7 +10835,7 @@
       </c>
       <c r="D60" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B22," ")</f>
-        <v>4800</v>
+        <v>1440</v>
       </c>
       <c r="E60" s="98"/>
       <c r="F60" s="98"/>
@@ -10857,7 +10857,7 @@
       </c>
       <c r="O60" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
-        <v>1366.66666666667</v>
+        <v>4760</v>
       </c>
       <c r="P60" s="98"/>
       <c r="Q60" s="98"/>
@@ -10965,7 +10965,7 @@
       </c>
       <c r="D64" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B23," ")</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="E64" s="98"/>
       <c r="F64" s="98"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="O64" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'Profit &amp; Loss Account'!B34</f>
-        <v>24006.6666666667</v>
+        <v>47614.25</v>
       </c>
       <c r="P64" s="98"/>
       <c r="Q64" s="98"/>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="D71" s="98" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>34410</v>
+        <v>121585.75</v>
       </c>
       <c r="E71" s="98"/>
       <c r="F71" s="98"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>34410</v>
+        <v>121585.75</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -14501,7 +14501,7 @@
       </c>
       <c r="D55" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B9</f>
-        <v>58416.6666666667</v>
+        <v>169200</v>
       </c>
       <c r="E55" s="98"/>
       <c r="F55" s="98"/>
@@ -14820,7 +14820,7 @@
       </c>
       <c r="D66" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B14+'Profit &amp; Loss Account'!B16</f>
-        <v>1800</v>
+        <v>9744</v>
       </c>
       <c r="E66" s="98"/>
       <c r="F66" s="98"/>
@@ -14945,7 +14945,7 @@
       </c>
       <c r="D70" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B15</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="E70" s="98"/>
       <c r="F70" s="98"/>
@@ -15070,7 +15070,7 @@
       </c>
       <c r="D74" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B21</f>
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="E74" s="98"/>
       <c r="F74" s="98"/>
@@ -15195,7 +15195,7 @@
       </c>
       <c r="D78" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26</f>
-        <v>4080</v>
+        <v>9458.25</v>
       </c>
       <c r="E78" s="98"/>
       <c r="F78" s="98"/>
@@ -15320,7 +15320,7 @@
       </c>
       <c r="D82" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B22</f>
-        <v>4800</v>
+        <v>1440</v>
       </c>
       <c r="E82" s="98"/>
       <c r="F82" s="98"/>
@@ -15445,7 +15445,7 @@
       </c>
       <c r="D86" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B23</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="E86" s="98"/>
       <c r="F86" s="98"/>
@@ -15570,7 +15570,7 @@
       </c>
       <c r="D90" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B24</f>
-        <v>720</v>
+        <v>1962</v>
       </c>
       <c r="E90" s="98"/>
       <c r="F90" s="98"/>
@@ -15695,7 +15695,7 @@
       </c>
       <c r="D94" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B27</f>
-        <v>1200</v>
+        <v>4560</v>
       </c>
       <c r="E94" s="98"/>
       <c r="F94" s="98"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B29</f>
-        <v>-333.333333333333</v>
+        <v>-300</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -16195,7 +16195,7 @@
       </c>
       <c r="D110" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B28</f>
-        <v>3600</v>
+        <v>5310</v>
       </c>
       <c r="E110" s="98"/>
       <c r="F110" s="98"/>
@@ -16575,7 +16575,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>24006.6666666667</v>
+        <v>47614.25</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>34410</v>
+        <v>121585.75</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>34410</v>
+        <v>121585.75</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">O174</f>
-        <v>34410</v>
+        <v>121585.75</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -22875,55 +22875,55 @@
       </c>
       <c r="B5" s="170" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>50416.6666666667</v>
+        <v>141600</v>
       </c>
       <c r="C5" s="171" t="n">
         <f aca="false">[2]Apr!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>11166.6666666667</v>
       </c>
       <c r="D5" s="171" t="n">
         <f aca="false">[2]May!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="E5" s="172" t="n">
         <f aca="false">[2]Jun!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="F5" s="171" t="n">
         <f aca="false">[2]Jul!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="G5" s="171" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="H5" s="172" t="n">
         <f aca="false">[2]Sep!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="I5" s="171" t="n">
         <f aca="false">[2]Oct!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="J5" s="171" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K5" s="172" t="n">
         <f aca="false">[2]Dec!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="L5" s="171" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>2500</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="M5" s="171" t="n">
         <f aca="false">[2]Feb!$P$1</f>
-        <v>2500</v>
+        <v>12166.6666666667</v>
       </c>
       <c r="N5" s="171" t="n">
         <f aca="false">[2]Mar!$P$1</f>
-        <v>1250</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="O5" s="164"/>
     </row>
@@ -22933,55 +22933,55 @@
       </c>
       <c r="B6" s="170" t="n">
         <f aca="false">SUM(C6:N6)</f>
-        <v>4000</v>
+        <v>13600</v>
       </c>
       <c r="C6" s="171" t="n">
         <f aca="false">[2]Apr!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="D6" s="171" t="n">
         <f aca="false">[2]May!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E6" s="172" t="n">
         <f aca="false">[2]Jun!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="F6" s="171" t="n">
         <f aca="false">[2]Jul!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="G6" s="171" t="n">
         <f aca="false">[2]Aug!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H6" s="172" t="n">
         <f aca="false">[2]Sep!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I6" s="171" t="n">
         <f aca="false">[2]Oct!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="J6" s="171" t="n">
         <f aca="false">[2]Nov!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="K6" s="172" t="n">
         <f aca="false">[2]Dec!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="L6" s="171" t="n">
         <f aca="false">[2]Jan!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="M6" s="171" t="n">
         <f aca="false">[2]Feb!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="N6" s="171" t="n">
         <f aca="false">[2]Mar!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="O6" s="164"/>
     </row>
@@ -22991,7 +22991,7 @@
       </c>
       <c r="B7" s="170" t="n">
         <f aca="false">SUM(C7:N7)</f>
-        <v>3500</v>
+        <v>10300</v>
       </c>
       <c r="C7" s="171" t="n">
         <f aca="false">[2]Apr!$R$1</f>
@@ -22999,11 +22999,11 @@
       </c>
       <c r="D7" s="171" t="n">
         <f aca="false">[2]May!$R$1</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="E7" s="172" t="n">
         <f aca="false">[2]Jun!$R$1</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F7" s="171" t="n">
         <f aca="false">[2]Jul!$R$1</f>
@@ -23015,7 +23015,7 @@
       </c>
       <c r="H7" s="172" t="n">
         <f aca="false">[2]Sep!$R$1</f>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="I7" s="171" t="n">
         <f aca="false">[2]Oct!$R$1</f>
@@ -23023,7 +23023,7 @@
       </c>
       <c r="J7" s="171" t="n">
         <f aca="false">[2]Nov!$R$1</f>
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="K7" s="172" t="n">
         <f aca="false">[2]Dec!$R$1</f>
@@ -23031,11 +23031,11 @@
       </c>
       <c r="L7" s="171" t="n">
         <f aca="false">[2]Jan!$R$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="M7" s="171" t="n">
         <f aca="false">[2]Feb!$R$1</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="N7" s="171" t="n">
         <f aca="false">[2]Mar!$R$1</f>
@@ -23049,11 +23049,11 @@
       </c>
       <c r="B8" s="170" t="n">
         <f aca="false">SUM(C8:N8)</f>
-        <v>500</v>
+        <v>3700</v>
       </c>
       <c r="C8" s="171" t="n">
         <f aca="false">[2]Apr!$S$1</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="D8" s="171" t="n">
         <f aca="false">[2]May!$S$1</f>
@@ -23061,11 +23061,11 @@
       </c>
       <c r="E8" s="172" t="n">
         <f aca="false">[2]Jun!$S$1</f>
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F8" s="171" t="n">
         <f aca="false">[2]Jul!$S$1</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="G8" s="171" t="n">
         <f aca="false">[2]Aug!$S$1</f>
@@ -23073,11 +23073,11 @@
       </c>
       <c r="H8" s="172" t="n">
         <f aca="false">[2]Sep!$S$1</f>
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="I8" s="171" t="n">
         <f aca="false">[2]Oct!$S$1</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="J8" s="171" t="n">
         <f aca="false">[2]Nov!$S$1</f>
@@ -23089,7 +23089,7 @@
       </c>
       <c r="L8" s="171" t="n">
         <f aca="false">[2]Jan!$S$1</f>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="M8" s="171" t="n">
         <f aca="false">[2]Feb!$S$1</f>
@@ -23107,55 +23107,55 @@
       </c>
       <c r="B9" s="170" t="n">
         <f aca="false">SUM(B5:B8)</f>
-        <v>58416.6666666667</v>
+        <v>169200</v>
       </c>
       <c r="C9" s="170" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>5166.66666666667</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="D9" s="170" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>6166.66666666667</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="E9" s="170" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>4666.66666666667</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="F9" s="174" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>6833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="G9" s="170" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>5833.33333333333</v>
+        <v>13766.6666666667</v>
       </c>
       <c r="H9" s="170" t="n">
         <f aca="false">SUM(H5:H8)</f>
-        <v>5833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="I9" s="174" t="n">
         <f aca="false">SUM(I5:I8)</f>
-        <v>6833.33333333333</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="J9" s="170" t="n">
         <f aca="false">SUM(J5:J8)</f>
-        <v>5666.66666666667</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="K9" s="170" t="n">
         <f aca="false">SUM(K5:K8)</f>
-        <v>4166.66666666667</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="L9" s="174" t="n">
         <f aca="false">SUM(L5:L8)</f>
-        <v>3500</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="M9" s="170" t="n">
         <f aca="false">SUM(M5:M8)</f>
-        <v>2500</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="N9" s="170" t="n">
         <f aca="false">SUM(N5:N8)</f>
-        <v>1250</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="O9" s="175"/>
     </row>
@@ -23276,7 +23276,7 @@
       </c>
       <c r="B14" s="170" t="n">
         <f aca="false">SUM(C14:N14)</f>
-        <v>1080</v>
+        <v>6540</v>
       </c>
       <c r="C14" s="171" t="n">
         <f aca="false">[3]Apr!$P$1+StockControl!AB6-StockControl!AB8</f>
@@ -23284,23 +23284,23 @@
       </c>
       <c r="D14" s="171" t="n">
         <f aca="false">[3]May!$P$1+StockControl!AB8-StockControl!AB10</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E14" s="172" t="n">
         <f aca="false">[3]Jun!$P$1+StockControl!AB10-StockControl!AB12</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F14" s="171" t="n">
         <f aca="false">[3]Jul!$P$1+StockControl!AB12-StockControl!AB14</f>
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="G14" s="171" t="n">
         <f aca="false">[3]Aug!$P$1+StockControl!AB14-StockControl!AB16</f>
-        <v>0</v>
+        <v>540</v>
       </c>
       <c r="H14" s="172" t="n">
         <f aca="false">[3]Sep!$P$1+StockControl!AB16-StockControl!AB18</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="I14" s="171" t="n">
         <f aca="false">[3]Oct!$P$1+StockControl!AB18-StockControl!AB20</f>
@@ -23308,23 +23308,23 @@
       </c>
       <c r="J14" s="171" t="n">
         <f aca="false">[3]Nov!$P$1+StockControl!AB20-StockControl!AB22</f>
-        <v>0</v>
+        <v>840</v>
       </c>
       <c r="K14" s="172" t="n">
         <f aca="false">[3]Dec!$P$1+StockControl!AB22-StockControl!AB24</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="L14" s="171" t="n">
         <f aca="false">[3]Jan!$P$1+StockControl!AB24-StockControl!AB26</f>
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M14" s="171" t="n">
         <f aca="false">[3]Feb!$P$1+StockControl!AB26-StockControl!AB28</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="N14" s="171" t="n">
         <f aca="false">[3]Mar!$P$1+StockControl!AB28-StockControl!AB30</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="O14" s="164"/>
     </row>
@@ -23334,7 +23334,7 @@
       </c>
       <c r="B15" s="170" t="n">
         <f aca="false">SUM(C15:N15)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="C15" s="171" t="n">
         <f aca="false">[3]Apr!$Q$1</f>
@@ -23346,7 +23346,7 @@
       </c>
       <c r="E15" s="172" t="n">
         <f aca="false">[3]Jun!$Q$1</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="F15" s="171" t="n">
         <f aca="false">[3]Jul!$Q$1</f>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="H15" s="172" t="n">
         <f aca="false">[3]Sep!$Q$1</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="I15" s="171" t="n">
         <f aca="false">[3]Oct!$Q$1</f>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="J15" s="171" t="n">
         <f aca="false">[3]Nov!$Q$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="K15" s="172" t="n">
         <f aca="false">[3]Dec!$Q$1</f>
@@ -23392,55 +23392,55 @@
       </c>
       <c r="B16" s="170" t="n">
         <f aca="false">SUM(C16:N16)</f>
-        <v>720</v>
+        <v>3204</v>
       </c>
       <c r="C16" s="171" t="n">
         <f aca="false">[3]Apr!$R$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="D16" s="171" t="n">
         <f aca="false">[3]May!$R$1</f>
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="E16" s="172" t="n">
         <f aca="false">[3]Jun!$R$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="F16" s="171" t="n">
         <f aca="false">[3]Jul!$R$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="G16" s="171" t="n">
         <f aca="false">[3]Aug!$R$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="H16" s="172" t="n">
         <f aca="false">[3]Sep!$R$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="I16" s="171" t="n">
         <f aca="false">[3]Oct!$R$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="J16" s="171" t="n">
         <f aca="false">[3]Nov!$R$1</f>
-        <v>360</v>
+        <v>249</v>
       </c>
       <c r="K16" s="172" t="n">
         <f aca="false">[3]Dec!$R$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="L16" s="171" t="n">
         <f aca="false">[3]Jan!$R$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="M16" s="171" t="n">
         <f aca="false">[3]Feb!$R$1</f>
-        <v>0</v>
+        <v>285</v>
       </c>
       <c r="N16" s="171" t="n">
         <f aca="false">[3]Mar!$R$1</f>
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="O16" s="164"/>
     </row>
@@ -23450,55 +23450,55 @@
       </c>
       <c r="B17" s="170" t="n">
         <f aca="false">SUM(B14:B16)</f>
-        <v>7800</v>
+        <v>17744</v>
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(C14:C16)</f>
-        <v>600</v>
+        <v>885</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">SUM(D14:D16)</f>
-        <v>360</v>
+        <v>969</v>
       </c>
       <c r="E17" s="170" t="n">
         <f aca="false">SUM(E14:E16)</f>
-        <v>3600</v>
+        <v>5645</v>
       </c>
       <c r="F17" s="174" t="n">
         <f aca="false">SUM(F14:F16)</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="G17" s="170" t="n">
         <f aca="false">SUM(G14:G16)</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="H17" s="170" t="n">
         <f aca="false">SUM(H14:H16)</f>
-        <v>2400</v>
+        <v>489</v>
       </c>
       <c r="I17" s="174" t="n">
         <f aca="false">SUM(I14:I16)</f>
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="J17" s="170" t="n">
         <f aca="false">SUM(J14:J16)</f>
-        <v>360</v>
+        <v>4089</v>
       </c>
       <c r="K17" s="170" t="n">
         <f aca="false">SUM(K14:K16)</f>
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="L17" s="174" t="n">
         <f aca="false">SUM(L14:L16)</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="M17" s="170" t="n">
         <f aca="false">SUM(M14:M16)</f>
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="N17" s="170" t="n">
         <f aca="false">SUM(N14:N16)</f>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="O17" s="175"/>
     </row>
@@ -23525,55 +23525,55 @@
       </c>
       <c r="B19" s="170" t="n">
         <f aca="false">B9+B11-B17</f>
-        <v>52700</v>
+        <v>153539.333333334</v>
       </c>
       <c r="C19" s="170" t="n">
         <f aca="false">C9+C11-C17</f>
-        <v>4566.66666666667</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="D19" s="170" t="n">
         <f aca="false">D9+D11-D17</f>
-        <v>5806.66666666667</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="E19" s="170" t="n">
         <f aca="false">E9+E11-E17</f>
-        <v>1066.66666666667</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="F19" s="174" t="n">
         <f aca="false">F9+F11-F17</f>
-        <v>6833.33333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="G19" s="170" t="n">
         <f aca="false">G9+G11-G17</f>
-        <v>7916.66666666666</v>
+        <v>15025</v>
       </c>
       <c r="H19" s="170" t="n">
         <f aca="false">H9+H11-H17</f>
-        <v>3433.33333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="I19" s="174" t="n">
         <f aca="false">I9+I11-I17</f>
-        <v>6353.33333333333</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="J19" s="170" t="n">
         <f aca="false">J9+J11-J17</f>
-        <v>5306.66666666667</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="K19" s="170" t="n">
         <f aca="false">K9+K11-K17</f>
-        <v>4166.66666666667</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="L19" s="174" t="n">
         <f aca="false">L9+L11-L17</f>
-        <v>3500</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="M19" s="170" t="n">
         <f aca="false">M9+M11-M17</f>
-        <v>2500</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="N19" s="170" t="n">
         <f aca="false">N9+N11-N17</f>
-        <v>1250</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="O19" s="175"/>
     </row>
@@ -23602,7 +23602,7 @@
       </c>
       <c r="B21" s="170" t="n">
         <f aca="false">SUM(C21:N21)</f>
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="C21" s="171" t="n">
         <f aca="false">[3]Apr!$S$1+Wagesinterface!C4+Wagesinterface!H4-Wagesinterface!I4</f>
@@ -23638,7 +23638,7 @@
       </c>
       <c r="K21" s="172" t="n">
         <f aca="false">[3]Dec!$S$1+Wagesinterface!C12+Wagesinterface!H12-Wagesinterface!I12</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="L21" s="171" t="n">
         <f aca="false">[3]Jan!$S$1+Wagesinterface!C13+Wagesinterface!H13-Wagesinterface!I13</f>
@@ -23660,11 +23660,11 @@
       </c>
       <c r="B22" s="170" t="n">
         <f aca="false">SUM(C22:N22)</f>
-        <v>4800</v>
+        <v>1440</v>
       </c>
       <c r="C22" s="171" t="n">
         <f aca="false">[3]Apr!$T$1</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="D22" s="171" t="n">
         <f aca="false">[3]May!$T$1</f>
@@ -23672,11 +23672,11 @@
       </c>
       <c r="E22" s="172" t="n">
         <f aca="false">[3]Jun!$T$1</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="F22" s="171" t="n">
         <f aca="false">[3]Jul!$T$1</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="G22" s="171" t="n">
         <f aca="false">[3]Aug!$T$1</f>
@@ -23684,11 +23684,11 @@
       </c>
       <c r="H22" s="172" t="n">
         <f aca="false">[3]Sep!$T$1</f>
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="I22" s="171" t="n">
         <f aca="false">[3]Oct!$T$1</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="J22" s="171" t="n">
         <f aca="false">[3]Nov!$T$1</f>
@@ -23696,11 +23696,11 @@
       </c>
       <c r="K22" s="172" t="n">
         <f aca="false">[3]Dec!$T$1</f>
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="L22" s="171" t="n">
         <f aca="false">[3]Jan!$T$1</f>
-        <v>1200</v>
+        <v>0</v>
       </c>
       <c r="M22" s="171" t="n">
         <f aca="false">[3]Feb!$T$1</f>
@@ -23708,7 +23708,7 @@
       </c>
       <c r="N22" s="171" t="n">
         <f aca="false">[3]Mar!$T$1</f>
-        <v>0</v>
+        <v>360</v>
       </c>
       <c r="O22" s="164"/>
     </row>
@@ -23718,11 +23718,11 @@
       </c>
       <c r="B23" s="170" t="n">
         <f aca="false">SUM(C23:N23)</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="C23" s="171" t="n">
         <f aca="false">[3]Apr!$U$1</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D23" s="171" t="n">
         <f aca="false">[3]May!$U$1</f>
@@ -23734,19 +23734,19 @@
       </c>
       <c r="F23" s="171" t="n">
         <f aca="false">[3]Jul!$U$1</f>
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G23" s="171" t="n">
         <f aca="false">[3]Aug!$U$1</f>
-        <v>0</v>
+        <v>240</v>
       </c>
       <c r="H23" s="172" t="n">
         <f aca="false">[3]Sep!$U$1</f>
-        <v>480</v>
+        <v>0</v>
       </c>
       <c r="I23" s="171" t="n">
         <f aca="false">[3]Oct!$U$1</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="J23" s="171" t="n">
         <f aca="false">[3]Nov!$U$1</f>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="L23" s="171" t="n">
         <f aca="false">[3]Jan!$U$1</f>
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="M23" s="171" t="n">
         <f aca="false">[3]Feb!$U$1</f>
@@ -23776,55 +23776,55 @@
       </c>
       <c r="B24" s="170" t="n">
         <f aca="false">SUM(C24:N24)</f>
-        <v>720</v>
+        <v>1962</v>
       </c>
       <c r="C24" s="171" t="n">
         <f aca="false">[3]Apr!$V$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="D24" s="171" t="n">
         <f aca="false">[3]May!$V$1</f>
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="E24" s="172" t="n">
         <f aca="false">[3]Jun!$V$1</f>
-        <v>60</v>
+        <v>231</v>
       </c>
       <c r="F24" s="171" t="n">
         <f aca="false">[3]Jul!$V$1</f>
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="G24" s="171" t="n">
         <f aca="false">[3]Aug!$V$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="H24" s="172" t="n">
         <f aca="false">[3]Sep!$V$1</f>
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="I24" s="171" t="n">
         <f aca="false">[3]Oct!$V$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="J24" s="171" t="n">
         <f aca="false">[3]Nov!$V$1</f>
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="K24" s="172" t="n">
         <f aca="false">[3]Dec!$V$1</f>
-        <v>60</v>
+        <v>255</v>
       </c>
       <c r="L24" s="171" t="n">
         <f aca="false">[3]Jan!$V$1</f>
-        <v>60</v>
+        <v>153</v>
       </c>
       <c r="M24" s="171" t="n">
         <f aca="false">[3]Feb!$V$1</f>
-        <v>60</v>
+        <v>135</v>
       </c>
       <c r="N24" s="171" t="n">
         <f aca="false">[3]Mar!$V$1</f>
-        <v>60</v>
+        <v>159</v>
       </c>
       <c r="O24" s="164"/>
     </row>
@@ -23834,55 +23834,55 @@
       </c>
       <c r="B25" s="170" t="n">
         <f aca="false">SUM(C25:N25)</f>
-        <v>1200</v>
+        <v>7598.25</v>
       </c>
       <c r="C25" s="171" t="n">
         <f aca="false">[3]Apr!$W$1</f>
-        <v>300</v>
+        <v>602.25</v>
       </c>
       <c r="D25" s="171" t="n">
         <f aca="false">[3]May!$W$1</f>
-        <v>0</v>
+        <v>666</v>
       </c>
       <c r="E25" s="172" t="n">
         <f aca="false">[3]Jun!$W$1</f>
-        <v>0</v>
+        <v>654</v>
       </c>
       <c r="F25" s="171" t="n">
         <f aca="false">[3]Jul!$W$1</f>
-        <v>300</v>
+        <v>584.25</v>
       </c>
       <c r="G25" s="171" t="n">
         <f aca="false">[3]Aug!$W$1</f>
-        <v>0</v>
+        <v>602.25</v>
       </c>
       <c r="H25" s="172" t="n">
         <f aca="false">[3]Sep!$W$1</f>
-        <v>0</v>
+        <v>708</v>
       </c>
       <c r="I25" s="171" t="n">
         <f aca="false">[3]Oct!$W$1</f>
-        <v>300</v>
+        <v>606.75</v>
       </c>
       <c r="J25" s="171" t="n">
         <f aca="false">[3]Nov!$W$1</f>
-        <v>0</v>
+        <v>645</v>
       </c>
       <c r="K25" s="172" t="n">
         <f aca="false">[3]Dec!$W$1</f>
-        <v>0</v>
+        <v>613.5</v>
       </c>
       <c r="L25" s="171" t="n">
         <f aca="false">[3]Jan!$W$1</f>
-        <v>300</v>
+        <v>638.25</v>
       </c>
       <c r="M25" s="171" t="n">
         <f aca="false">[3]Feb!$W$1</f>
-        <v>0</v>
+        <v>595.5</v>
       </c>
       <c r="N25" s="171" t="n">
         <f aca="false">[3]Mar!$W$1</f>
-        <v>0</v>
+        <v>682.5</v>
       </c>
       <c r="O25" s="164"/>
     </row>
@@ -23892,55 +23892,55 @@
       </c>
       <c r="B26" s="170" t="n">
         <f aca="false">SUM(C26:N26)</f>
-        <v>2880</v>
+        <v>1860</v>
       </c>
       <c r="C26" s="171" t="n">
         <f aca="false">[3]Apr!$X$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="D26" s="171" t="n">
         <f aca="false">[3]May!$X$1</f>
-        <v>0</v>
+        <v>152</v>
       </c>
       <c r="E26" s="172" t="n">
         <f aca="false">[3]Jun!$X$1</f>
-        <v>720</v>
+        <v>272</v>
       </c>
       <c r="F26" s="171" t="n">
         <f aca="false">[3]Jul!$X$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="G26" s="171" t="n">
         <f aca="false">[3]Aug!$X$1</f>
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="H26" s="172" t="n">
         <f aca="false">[3]Sep!$X$1</f>
-        <v>720</v>
+        <v>92</v>
       </c>
       <c r="I26" s="171" t="n">
         <f aca="false">[3]Oct!$X$1</f>
-        <v>0</v>
+        <v>212</v>
       </c>
       <c r="J26" s="171" t="n">
         <f aca="false">[3]Nov!$X$1</f>
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="K26" s="172" t="n">
         <f aca="false">[3]Dec!$X$1</f>
-        <v>720</v>
+        <v>92</v>
       </c>
       <c r="L26" s="171" t="n">
         <f aca="false">[3]Jan!$X$1</f>
-        <v>0</v>
+        <v>92</v>
       </c>
       <c r="M26" s="171" t="n">
         <f aca="false">[3]Feb!$X$1</f>
-        <v>0</v>
+        <v>368</v>
       </c>
       <c r="N26" s="171" t="n">
         <f aca="false">[3]Mar!$X$1</f>
-        <v>720</v>
+        <v>92</v>
       </c>
       <c r="O26" s="164"/>
     </row>
@@ -23950,7 +23950,7 @@
       </c>
       <c r="B27" s="170" t="n">
         <f aca="false">SUM(C27:N27)</f>
-        <v>1200</v>
+        <v>4560</v>
       </c>
       <c r="C27" s="171" t="n">
         <f aca="false">[3]Apr!$Y$1</f>
@@ -23966,7 +23966,7 @@
       </c>
       <c r="F27" s="171" t="n">
         <f aca="false">[3]Jul!$Y$1</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="G27" s="171" t="n">
         <f aca="false">[3]Aug!$Y$1</f>
@@ -23978,7 +23978,7 @@
       </c>
       <c r="I27" s="171" t="n">
         <f aca="false">[3]Oct!$Y$1</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="J27" s="171" t="n">
         <f aca="false">[3]Nov!$Y$1</f>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="L27" s="171" t="n">
         <f aca="false">[3]Jan!$Y$1</f>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="M27" s="171" t="n">
         <f aca="false">[3]Feb!$Y$1</f>
@@ -24008,7 +24008,7 @@
       </c>
       <c r="B28" s="170" t="n">
         <f aca="false">SUM(C28:N28)</f>
-        <v>3600</v>
+        <v>5310</v>
       </c>
       <c r="C28" s="171" t="n">
         <f aca="false">[3]Apr!$Z$1</f>
@@ -24020,7 +24020,7 @@
       </c>
       <c r="E28" s="172" t="n">
         <f aca="false">[3]Jun!$Z$1</f>
-        <v>300</v>
+        <v>550</v>
       </c>
       <c r="F28" s="171" t="n">
         <f aca="false">[3]Jul!$Z$1</f>
@@ -24032,7 +24032,7 @@
       </c>
       <c r="H28" s="172" t="n">
         <f aca="false">[3]Sep!$Z$1</f>
-        <v>300</v>
+        <v>1468</v>
       </c>
       <c r="I28" s="171" t="n">
         <f aca="false">[3]Oct!$Z$1</f>
@@ -24044,7 +24044,7 @@
       </c>
       <c r="K28" s="172" t="n">
         <f aca="false">[3]Dec!$Z$1</f>
-        <v>300</v>
+        <v>467</v>
       </c>
       <c r="L28" s="171" t="n">
         <f aca="false">[3]Jan!$Z$1</f>
@@ -24056,7 +24056,7 @@
       </c>
       <c r="N28" s="171" t="n">
         <f aca="false">[3]Mar!$Z$1</f>
-        <v>300</v>
+        <v>425</v>
       </c>
       <c r="O28" s="164"/>
     </row>
@@ -24066,7 +24066,7 @@
       </c>
       <c r="B29" s="170" t="n">
         <f aca="false">SUM(C29:N29)</f>
-        <v>-333.333333333333</v>
+        <v>-300</v>
       </c>
       <c r="C29" s="171" t="n">
         <f aca="false">-[2]Apr!$U$1</f>
@@ -24114,7 +24114,7 @@
       </c>
       <c r="N29" s="171" t="n">
         <f aca="false">-[2]Mar!$U$1</f>
-        <v>-333.333333333333</v>
+        <v>-300</v>
       </c>
       <c r="O29" s="164"/>
     </row>
@@ -24414,55 +24414,55 @@
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>16206.6666666667</v>
+        <v>29870.25</v>
       </c>
       <c r="C35" s="170" t="n">
         <f aca="false">SUM(C21:C34)</f>
-        <v>1860</v>
+        <v>1249.25</v>
       </c>
       <c r="D35" s="170" t="n">
         <f aca="false">SUM(D21:D34)</f>
-        <v>960</v>
+        <v>1871</v>
       </c>
       <c r="E35" s="170" t="n">
         <f aca="false">SUM(E21:E34)</f>
-        <v>1080</v>
+        <v>2067</v>
       </c>
       <c r="F35" s="174" t="n">
         <f aca="false">SUM(F21:F34)</f>
-        <v>1860</v>
+        <v>1795.25</v>
       </c>
       <c r="G35" s="170" t="n">
         <f aca="false">SUM(G21:G34)</f>
-        <v>1160</v>
+        <v>2217.25</v>
       </c>
       <c r="H35" s="170" t="n">
         <f aca="false">SUM(H21:H34)</f>
-        <v>1560</v>
+        <v>2715</v>
       </c>
       <c r="I35" s="174" t="n">
         <f aca="false">SUM(I21:I34)</f>
-        <v>1860</v>
+        <v>4349.75</v>
       </c>
       <c r="J35" s="170" t="n">
         <f aca="false">SUM(J21:J34)</f>
-        <v>360</v>
+        <v>1274</v>
       </c>
       <c r="K35" s="170" t="n">
         <f aca="false">SUM(K21:K34)</f>
-        <v>1580</v>
+        <v>7347.5</v>
       </c>
       <c r="L35" s="174" t="n">
         <f aca="false">SUM(L21:L34)</f>
-        <v>2460</v>
+        <v>1807.25</v>
       </c>
       <c r="M35" s="170" t="n">
         <f aca="false">SUM(M21:M34)</f>
-        <v>720</v>
+        <v>1758.5</v>
       </c>
       <c r="N35" s="170" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>746.666666666667</v>
+        <v>1418.5</v>
       </c>
       <c r="O35" s="164"/>
     </row>
@@ -24489,55 +24489,55 @@
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="C37" s="170" t="n">
         <f aca="false">C19-C35</f>
-        <v>2706.66666666667</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="D37" s="170" t="n">
         <f aca="false">D19-D35</f>
-        <v>4846.66666666667</v>
+        <v>10426.6666666667</v>
       </c>
       <c r="E37" s="170" t="n">
         <f aca="false">E19-E35</f>
-        <v>-13.3333333333303</v>
+        <v>7454.6666666667</v>
       </c>
       <c r="F37" s="174" t="n">
         <f aca="false">F19-F35</f>
-        <v>4973.33333333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="G37" s="170" t="n">
         <f aca="false">G19-G35</f>
-        <v>6756.66666666666</v>
+        <v>12807.75</v>
       </c>
       <c r="H37" s="170" t="n">
         <f aca="false">H19-H35</f>
-        <v>1873.33333333333</v>
+        <v>10762.6666666667</v>
       </c>
       <c r="I37" s="174" t="n">
         <f aca="false">I19-I35</f>
-        <v>4493.33333333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="J37" s="170" t="n">
         <f aca="false">J19-J35</f>
-        <v>4946.66666666667</v>
+        <v>9903.6666666667</v>
       </c>
       <c r="K37" s="170" t="n">
         <f aca="false">K19-K35</f>
-        <v>2586.66666666667</v>
+        <v>5054.1666666667</v>
       </c>
       <c r="L37" s="174" t="n">
         <f aca="false">L19-L35</f>
-        <v>1040</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="M37" s="170" t="n">
         <f aca="false">M19-M35</f>
-        <v>1780</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="N37" s="170" t="n">
         <f aca="false">N19-N35</f>
-        <v>503.333333333333</v>
+        <v>9699.1666666667</v>
       </c>
       <c r="O37" s="164"/>
     </row>
@@ -24605,55 +24605,55 @@
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="C39" s="170" t="n">
         <f aca="false">C37+C38</f>
-        <v>2706.66666666667</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="D39" s="170" t="n">
         <f aca="false">D37+D38</f>
-        <v>4846.66666666667</v>
+        <v>10426.6666666667</v>
       </c>
       <c r="E39" s="170" t="n">
         <f aca="false">E37+E38</f>
-        <v>-13.3333333333303</v>
+        <v>7454.6666666667</v>
       </c>
       <c r="F39" s="174" t="n">
         <f aca="false">F37+F38</f>
-        <v>4973.33333333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="G39" s="170" t="n">
         <f aca="false">G37+G38</f>
-        <v>6756.66666666666</v>
+        <v>12807.75</v>
       </c>
       <c r="H39" s="170" t="n">
         <f aca="false">H37+H38</f>
-        <v>1873.33333333333</v>
+        <v>10762.6666666667</v>
       </c>
       <c r="I39" s="174" t="n">
         <f aca="false">I37+I38</f>
-        <v>4493.33333333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="J39" s="170" t="n">
         <f aca="false">J37+J38</f>
-        <v>4946.66666666667</v>
+        <v>9903.6666666667</v>
       </c>
       <c r="K39" s="170" t="n">
         <f aca="false">K37+K38</f>
-        <v>2586.66666666667</v>
+        <v>5054.1666666667</v>
       </c>
       <c r="L39" s="174" t="n">
         <f aca="false">L37+L38</f>
-        <v>1040</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="M39" s="170" t="n">
         <f aca="false">M37+M38</f>
-        <v>1780</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="N39" s="170" t="n">
         <f aca="false">N37+N38</f>
-        <v>503.333333333333</v>
+        <v>9699.1666666667</v>
       </c>
       <c r="O39" s="164"/>
     </row>
@@ -24815,55 +24815,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>6220.06666666667</v>
+        <v>40629.4550000002</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>518.338888888889</v>
+        <v>3385.78791666668</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24873,55 +24873,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>30273.2666666667</v>
+        <v>83039.6283333336</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>2188.32777777778</v>
+        <v>8146.62875000002</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>4328.32777777778</v>
+        <v>7040.87875000002</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>-531.672222222219</v>
+        <v>4068.87875000002</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>4454.99444444444</v>
+        <v>7816.62875000002</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>6238.32777777777</v>
+        <v>9421.96208333335</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>1354.99444444444</v>
+        <v>7376.87875000002</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>3974.99444444444</v>
+        <v>6966.12875000002</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>4428.32777777778</v>
+        <v>6517.87875000002</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>2068.32777777778</v>
+        <v>1668.37875000002</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>521.661111111111</v>
+        <v>9324.62875000002</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>1261.66111111111</v>
+        <v>8377.37875000002</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-15.0055555555559</v>
+        <v>6313.37875000002</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -25110,23 +25110,23 @@
       </c>
       <c r="C5" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
-        <v>15500</v>
+        <v>41400.0000000001</v>
       </c>
       <c r="D5" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F5:H7)</f>
-        <v>18500</v>
+        <v>40500.0000000001</v>
       </c>
       <c r="E5" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I5:K7)</f>
-        <v>16666.6666666667</v>
+        <v>43200.0000000001</v>
       </c>
       <c r="F5" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L5:N7)</f>
-        <v>7250</v>
+        <v>40400.0000000001</v>
       </c>
       <c r="G5" s="200" t="n">
         <f aca="false">SUM(C5:F5)</f>
-        <v>57916.6666666667</v>
+        <v>165500</v>
       </c>
       <c r="H5" s="195"/>
       <c r="I5" s="195"/>
@@ -25138,23 +25138,23 @@
       </c>
       <c r="C6" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="D6" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F8:H8)+SUM('Profit &amp; Loss Account'!F11:H11)+SUM('Profit &amp; Loss Account'!F38:H38)</f>
-        <v>2083.33333333333</v>
+        <v>3283.33333333333</v>
       </c>
       <c r="E6" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I8:K8)+SUM('Profit &amp; Loss Account'!I11:K11)+SUM('Profit &amp; Loss Account'!I38:K38)</f>
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F6" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L8:N8)+SUM('Profit &amp; Loss Account'!L11:N11)+SUM('Profit &amp; Loss Account'!L38:N38)</f>
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="G6" s="200" t="n">
         <f aca="false">SUM(C6:F6)</f>
-        <v>2583.33333333333</v>
+        <v>5783.33333333333</v>
       </c>
       <c r="H6" s="195"/>
       <c r="I6" s="195"/>
@@ -25166,23 +25166,23 @@
       </c>
       <c r="C7" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
-        <v>960</v>
+        <v>2499</v>
       </c>
       <c r="D7" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F14:H14)+SUM('Profit &amp; Loss Account'!F16:H16)</f>
-        <v>0</v>
+        <v>2283</v>
       </c>
       <c r="E7" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I14:K14)+SUM('Profit &amp; Loss Account'!I16:K16)</f>
-        <v>840</v>
+        <v>2619</v>
       </c>
       <c r="F7" s="199" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L14:N14)+SUM('Profit &amp; Loss Account'!L16:N16)</f>
-        <v>0</v>
+        <v>2343</v>
       </c>
       <c r="G7" s="200" t="n">
         <f aca="false">SUM(C7:F7)</f>
-        <v>1800</v>
+        <v>9744</v>
       </c>
       <c r="H7" s="195"/>
       <c r="I7" s="195"/>
@@ -25248,7 +25248,7 @@
       </c>
       <c r="E12" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I21:K21)</f>
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="F12" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L21:N21)</f>
@@ -25256,7 +25256,7 @@
       </c>
       <c r="G12" s="200" t="n">
         <f aca="false">SUM(C12:F12)</f>
-        <v>800</v>
+        <v>5800</v>
       </c>
       <c r="H12" s="195"/>
       <c r="I12" s="195"/>
@@ -25268,23 +25268,23 @@
       </c>
       <c r="C13" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
-        <v>1200</v>
+        <v>360</v>
       </c>
       <c r="D13" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F22:H22)</f>
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="E13" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I22:K22)</f>
-        <v>1200</v>
+        <v>420</v>
       </c>
       <c r="F13" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L22:N22)</f>
-        <v>1200</v>
+        <v>360</v>
       </c>
       <c r="G13" s="200" t="n">
         <f aca="false">SUM(C13:F13)</f>
-        <v>4800</v>
+        <v>1440</v>
       </c>
       <c r="H13" s="195"/>
       <c r="I13" s="195"/>
@@ -25296,23 +25296,23 @@
       </c>
       <c r="C14" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="D14" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F23:H23)</f>
-        <v>480</v>
+        <v>420</v>
       </c>
       <c r="E14" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I23:K23)</f>
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="F14" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L23:N23)</f>
-        <v>360</v>
+        <v>504</v>
       </c>
       <c r="G14" s="200" t="n">
         <f aca="false">SUM(C14:F14)</f>
-        <v>840</v>
+        <v>1140</v>
       </c>
       <c r="H14" s="195"/>
       <c r="I14" s="195"/>
@@ -25324,23 +25324,23 @@
       </c>
       <c r="C15" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
-        <v>180</v>
+        <v>519</v>
       </c>
       <c r="D15" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F24:H24)</f>
-        <v>180</v>
+        <v>441</v>
       </c>
       <c r="E15" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I24:K24)</f>
-        <v>180</v>
+        <v>555</v>
       </c>
       <c r="F15" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L24:N24)</f>
-        <v>180</v>
+        <v>447</v>
       </c>
       <c r="G15" s="200" t="n">
         <f aca="false">SUM(C15:F15)</f>
-        <v>720</v>
+        <v>1962</v>
       </c>
       <c r="H15" s="195"/>
       <c r="I15" s="195"/>
@@ -25380,23 +25380,23 @@
       </c>
       <c r="C17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
-        <v>1020</v>
+        <v>2438.25</v>
       </c>
       <c r="D17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F25:H26)</f>
-        <v>1020</v>
+        <v>2218.5</v>
       </c>
       <c r="E17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I25:K26)</f>
-        <v>1020</v>
+        <v>2333.25</v>
       </c>
       <c r="F17" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L25:N26)</f>
-        <v>1020</v>
+        <v>2468.25</v>
       </c>
       <c r="G17" s="200" t="n">
         <f aca="false">SUM(C17:F17)</f>
-        <v>4080</v>
+        <v>9458.25</v>
       </c>
       <c r="H17" s="195"/>
       <c r="I17" s="195"/>
@@ -25412,19 +25412,19 @@
       </c>
       <c r="D18" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F27:H27)</f>
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="E18" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I27:K27)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F18" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L27:N27)</f>
-        <v>600</v>
+        <v>480</v>
       </c>
       <c r="G18" s="200" t="n">
         <f aca="false">SUM(C18:F18)</f>
-        <v>1200</v>
+        <v>4560</v>
       </c>
       <c r="H18" s="195"/>
       <c r="I18" s="195"/>
@@ -25436,23 +25436,23 @@
       </c>
       <c r="C19" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
-        <v>900</v>
+        <v>1150</v>
       </c>
       <c r="D19" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F28:H28)</f>
-        <v>900</v>
+        <v>2068</v>
       </c>
       <c r="E19" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I28:K28)</f>
-        <v>900</v>
+        <v>1067</v>
       </c>
       <c r="F19" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L28:N28)</f>
-        <v>900</v>
+        <v>1025</v>
       </c>
       <c r="G19" s="200" t="n">
         <f aca="false">SUM(C19:F19)</f>
-        <v>3600</v>
+        <v>5310</v>
       </c>
       <c r="H19" s="195"/>
       <c r="I19" s="195"/>
@@ -25476,11 +25476,11 @@
       </c>
       <c r="F20" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L29:N29)</f>
-        <v>-333.333333333333</v>
+        <v>-300</v>
       </c>
       <c r="G20" s="200" t="n">
         <f aca="false">SUM(C20:F20)</f>
-        <v>-333.333333333333</v>
+        <v>-300</v>
       </c>
       <c r="H20" s="195"/>
       <c r="I20" s="195"/>
@@ -25559,15 +25559,15 @@
       </c>
       <c r="C24" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="D24" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F15:H15)</f>
-        <v>2400</v>
+        <v>0</v>
       </c>
       <c r="E24" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I15:K15)</f>
-        <v>0</v>
+        <v>3000</v>
       </c>
       <c r="F24" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L15:N15)</f>
@@ -25575,7 +25575,7 @@
       </c>
       <c r="G24" s="200" t="n">
         <f aca="false">SUM(C24:F24)</f>
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="H24" s="195"/>
       <c r="I24" s="195"/>
@@ -25663,23 +25663,23 @@
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
-        <v>8460</v>
+        <v>12686.25</v>
       </c>
       <c r="D29" s="203" t="n">
         <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D25,D26)</f>
-        <v>6980</v>
+        <v>9010.5</v>
       </c>
       <c r="E29" s="203" t="n">
         <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E25,E26)</f>
-        <v>4640</v>
+        <v>18590.25</v>
       </c>
       <c r="F29" s="203" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F25,F26)</f>
-        <v>3926.66666666667</v>
+        <v>7327.25</v>
       </c>
       <c r="G29" s="203" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G25,G26)</f>
-        <v>24006.6666666667</v>
+        <v>47614.25</v>
       </c>
       <c r="H29" s="204"/>
       <c r="I29" s="195"/>
@@ -26249,7 +26249,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -26282,7 +26282,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>23923.3333333333</v>
+        <v>111099.083333334</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -26303,7 +26303,7 @@
       </c>
       <c r="E8" s="213" t="n">
         <f aca="false">IF((E7&gt;0),(IF((E7&lt;C9),E7*D8,C9*D8)),0)</f>
-        <v>4784.66666666667</v>
+        <v>7540.2</v>
       </c>
       <c r="F8" s="214"/>
       <c r="G8" s="218"/>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="E9" s="213" t="n">
         <f aca="false">IF((E7&gt;C9),((E7-C9)*D9),0)</f>
-        <v>0</v>
+        <v>29359.2333333335</v>
       </c>
       <c r="F9" s="214"/>
       <c r="G9" s="218"/>
@@ -26340,7 +26340,7 @@
       <c r="D10" s="230"/>
       <c r="E10" s="231" t="n">
         <f aca="false">SUM(E8:E9)</f>
-        <v>4784.66666666667</v>
+        <v>36899.4333333335</v>
       </c>
       <c r="F10" s="214"/>
       <c r="G10" s="218"/>
@@ -26408,7 +26408,7 @@
       </c>
       <c r="E15" s="240" t="n">
         <f aca="false">IF(E5&gt;Admin!N20,IF(E5&lt;Admin!N$23,(E5-Admin!N20)*D15,(Admin!N$23-Admin!N20)*D15),0)</f>
-        <v>1435.4</v>
+        <v>2262</v>
       </c>
       <c r="F15" s="214"/>
       <c r="G15" s="234"/>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="E16" s="240" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>0</v>
+        <v>1467.98166666667</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="234"/>
@@ -26451,7 +26451,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E10:E17)</f>
-        <v>6220.06666666667</v>
+        <v>40629.4150000002</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -26533,7 +26533,7 @@
       </c>
       <c r="E25" s="240" t="n">
         <f aca="false">E18</f>
-        <v>6220.06666666667</v>
+        <v>40629.4150000002</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -26550,7 +26550,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>3110.03333333333</v>
+        <v>20314.7075000001</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -26567,7 +26567,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>3110.03333333333</v>
+        <v>20314.7075000001</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -27631,7 +27631,7 @@
       <c r="I8" s="177"/>
       <c r="J8" s="177" t="n">
         <f aca="false">[2]Apr!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>11166.6666666667</v>
       </c>
       <c r="K8" s="177"/>
       <c r="L8" s="179" t="n">
@@ -27646,7 +27646,7 @@
       <c r="O8" s="177"/>
       <c r="P8" s="177" t="n">
         <f aca="false">[2]Apr!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q8" s="177"/>
       <c r="R8" s="179" t="n">
@@ -27745,7 +27745,7 @@
       <c r="I10" s="177"/>
       <c r="J10" s="177" t="n">
         <f aca="false">[2]May!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K10" s="177"/>
       <c r="L10" s="179" t="n">
@@ -27760,7 +27760,7 @@
       <c r="O10" s="177"/>
       <c r="P10" s="177" t="n">
         <f aca="false">[2]May!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q10" s="177"/>
       <c r="R10" s="179" t="n">
@@ -27775,7 +27775,7 @@
       <c r="U10" s="177"/>
       <c r="V10" s="177" t="n">
         <f aca="false">[2]May!$R$1</f>
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="W10" s="177"/>
       <c r="X10" s="177" t="n">
@@ -27861,7 +27861,7 @@
       <c r="I12" s="177"/>
       <c r="J12" s="177" t="n">
         <f aca="false">[2]Jun!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="K12" s="177"/>
       <c r="L12" s="179" t="n">
@@ -27876,7 +27876,7 @@
       <c r="O12" s="177"/>
       <c r="P12" s="177" t="n">
         <f aca="false">[2]Jun!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q12" s="177"/>
       <c r="R12" s="179" t="n">
@@ -27891,7 +27891,7 @@
       <c r="U12" s="177"/>
       <c r="V12" s="177" t="n">
         <f aca="false">[2]Jun!$R$1</f>
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="W12" s="177"/>
       <c r="X12" s="177" t="n">
@@ -27975,7 +27975,7 @@
       <c r="I14" s="177"/>
       <c r="J14" s="177" t="n">
         <f aca="false">[2]Jul!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K14" s="177"/>
       <c r="L14" s="179" t="n">
@@ -27990,7 +27990,7 @@
       <c r="O14" s="177"/>
       <c r="P14" s="177" t="n">
         <f aca="false">[2]Jul!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q14" s="177"/>
       <c r="R14" s="179" t="n">
@@ -28091,7 +28091,7 @@
       <c r="I16" s="177"/>
       <c r="J16" s="177" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="K16" s="177"/>
       <c r="L16" s="179" t="n">
@@ -28106,7 +28106,7 @@
       <c r="O16" s="177"/>
       <c r="P16" s="177" t="n">
         <f aca="false">[2]Aug!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q16" s="177"/>
       <c r="R16" s="179" t="n">
@@ -28205,7 +28205,7 @@
       <c r="I18" s="177"/>
       <c r="J18" s="177" t="n">
         <f aca="false">[2]Sep!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="K18" s="177"/>
       <c r="L18" s="179" t="n">
@@ -28220,7 +28220,7 @@
       <c r="O18" s="177"/>
       <c r="P18" s="177" t="n">
         <f aca="false">[2]Sep!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q18" s="177"/>
       <c r="R18" s="179" t="n">
@@ -28235,7 +28235,7 @@
       <c r="U18" s="177"/>
       <c r="V18" s="177" t="n">
         <f aca="false">[2]Sep!$R$1</f>
-        <v>0</v>
+        <v>1800</v>
       </c>
       <c r="W18" s="177"/>
       <c r="X18" s="177" t="n">
@@ -28321,7 +28321,7 @@
       <c r="I20" s="177"/>
       <c r="J20" s="177" t="n">
         <f aca="false">[2]Oct!$P$1</f>
-        <v>5833.33333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="K20" s="177"/>
       <c r="L20" s="179" t="n">
@@ -28336,7 +28336,7 @@
       <c r="O20" s="177"/>
       <c r="P20" s="177" t="n">
         <f aca="false">[2]Oct!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q20" s="177"/>
       <c r="R20" s="179" t="n">
@@ -28435,7 +28435,7 @@
       <c r="I22" s="177"/>
       <c r="J22" s="177" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K22" s="177"/>
       <c r="L22" s="179" t="n">
@@ -28450,7 +28450,7 @@
       <c r="O22" s="177"/>
       <c r="P22" s="177" t="n">
         <f aca="false">[2]Nov!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q22" s="177"/>
       <c r="R22" s="179" t="n">
@@ -28465,7 +28465,7 @@
       <c r="U22" s="177"/>
       <c r="V22" s="177" t="n">
         <f aca="false">[2]Nov!$R$1</f>
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="W22" s="177"/>
       <c r="X22" s="177" t="n">
@@ -28551,7 +28551,7 @@
       <c r="I24" s="177"/>
       <c r="J24" s="177" t="n">
         <f aca="false">[2]Dec!$P$1</f>
-        <v>4166.66666666667</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="K24" s="177"/>
       <c r="L24" s="179" t="n">
@@ -28566,7 +28566,7 @@
       <c r="O24" s="177"/>
       <c r="P24" s="177" t="n">
         <f aca="false">[2]Dec!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q24" s="177"/>
       <c r="R24" s="179" t="n">
@@ -28665,7 +28665,7 @@
       <c r="I26" s="177"/>
       <c r="J26" s="177" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>2500</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K26" s="177"/>
       <c r="L26" s="179" t="n">
@@ -28680,7 +28680,7 @@
       <c r="O26" s="177"/>
       <c r="P26" s="177" t="n">
         <f aca="false">[2]Jan!$Q$1</f>
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="Q26" s="177"/>
       <c r="R26" s="179" t="n">
@@ -28695,7 +28695,7 @@
       <c r="U26" s="177"/>
       <c r="V26" s="177" t="n">
         <f aca="false">[2]Jan!$R$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="W26" s="177"/>
       <c r="X26" s="177" t="n">
@@ -28779,7 +28779,7 @@
       <c r="I28" s="177"/>
       <c r="J28" s="177" t="n">
         <f aca="false">[2]Feb!$P$1</f>
-        <v>2500</v>
+        <v>12166.6666666667</v>
       </c>
       <c r="K28" s="177"/>
       <c r="L28" s="179" t="n">
@@ -28794,7 +28794,7 @@
       <c r="O28" s="177"/>
       <c r="P28" s="177" t="n">
         <f aca="false">[2]Feb!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q28" s="177"/>
       <c r="R28" s="179" t="n">
@@ -28809,7 +28809,7 @@
       <c r="U28" s="177"/>
       <c r="V28" s="177" t="n">
         <f aca="false">[2]Feb!$R$1</f>
-        <v>0</v>
+        <v>1500</v>
       </c>
       <c r="W28" s="177"/>
       <c r="X28" s="177" t="n">
@@ -28895,7 +28895,7 @@
       <c r="I30" s="177"/>
       <c r="J30" s="177" t="n">
         <f aca="false">[2]Mar!$P$1</f>
-        <v>1250</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="K30" s="177"/>
       <c r="L30" s="179" t="n">
@@ -28910,7 +28910,7 @@
       <c r="O30" s="177"/>
       <c r="P30" s="177" t="n">
         <f aca="false">[2]Mar!$Q$1</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="Q30" s="177"/>
       <c r="R30" s="179" t="n">
@@ -29174,55 +29174,55 @@
       </c>
       <c r="C5" s="170" t="n">
         <f aca="false">SUM(D5:O5)</f>
-        <v>58416.6666666667</v>
+        <v>169200</v>
       </c>
       <c r="D5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C9</f>
-        <v>5166.66666666667</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="E5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D9</f>
-        <v>6166.66666666667</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="F5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E9</f>
-        <v>4666.66666666667</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="G5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F9</f>
-        <v>6833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="H5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G9</f>
-        <v>5833.33333333333</v>
+        <v>13766.6666666667</v>
       </c>
       <c r="I5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H9</f>
-        <v>5833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="J5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I9</f>
-        <v>6833.33333333333</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="K5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J9</f>
-        <v>5666.66666666667</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="L5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K9</f>
-        <v>4166.66666666667</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="M5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L9</f>
-        <v>3500</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="N5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M9</f>
-        <v>2500</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="O5" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N9</f>
-        <v>1250</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="P5" s="178"/>
     </row>
@@ -29328,55 +29328,55 @@
       </c>
       <c r="C9" s="170" t="n">
         <f aca="false">SUM(D9:O9)</f>
-        <v>7800</v>
+        <v>17744</v>
       </c>
       <c r="D9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C17</f>
-        <v>600</v>
+        <v>885</v>
       </c>
       <c r="E9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D17</f>
-        <v>360</v>
+        <v>969</v>
       </c>
       <c r="F9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E17</f>
-        <v>3600</v>
+        <v>5645</v>
       </c>
       <c r="G9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F17</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="H9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G17</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="I9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H17</f>
-        <v>2400</v>
+        <v>489</v>
       </c>
       <c r="J9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I17</f>
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="K9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J17</f>
-        <v>360</v>
+        <v>4089</v>
       </c>
       <c r="L9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K17</f>
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="M9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L17</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="N9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M17</f>
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="O9" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N17</f>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="P9" s="178"/>
     </row>
@@ -29405,55 +29405,55 @@
       </c>
       <c r="C11" s="170" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>52700</v>
+        <v>153539.333333334</v>
       </c>
       <c r="D11" s="170" t="n">
         <f aca="false">D5+D7-D9</f>
-        <v>4566.66666666667</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="E11" s="170" t="n">
         <f aca="false">E5+E7-E9</f>
-        <v>5806.66666666667</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="F11" s="170" t="n">
         <f aca="false">F5+F7-F9</f>
-        <v>1066.66666666667</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="G11" s="170" t="n">
         <f aca="false">G5+G7-G9</f>
-        <v>6833.33333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="H11" s="170" t="n">
         <f aca="false">H5+H7-H9</f>
-        <v>7916.66666666666</v>
+        <v>15025</v>
       </c>
       <c r="I11" s="170" t="n">
         <f aca="false">I5+I7-I9</f>
-        <v>3433.33333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="J11" s="170" t="n">
         <f aca="false">J5+J7-J9</f>
-        <v>6353.33333333333</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="K11" s="170" t="n">
         <f aca="false">K5+K7-K9</f>
-        <v>5306.66666666667</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="L11" s="170" t="n">
         <f aca="false">L5+L7-L9</f>
-        <v>4166.66666666667</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="M11" s="170" t="n">
         <f aca="false">M5+M7-M9</f>
-        <v>3500</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="N11" s="170" t="n">
         <f aca="false">N5+N7-N9</f>
-        <v>2500</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="O11" s="170" t="n">
         <f aca="false">O5+O7-O9</f>
-        <v>1250</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="P11" s="178"/>
     </row>
@@ -29482,55 +29482,55 @@
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>16206.6666666667</v>
+        <v>29870.25</v>
       </c>
       <c r="D13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
-        <v>1860</v>
+        <v>1249.25</v>
       </c>
       <c r="E13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D35</f>
-        <v>960</v>
+        <v>1871</v>
       </c>
       <c r="F13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E35</f>
-        <v>1080</v>
+        <v>2067</v>
       </c>
       <c r="G13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F35</f>
-        <v>1860</v>
+        <v>1795.25</v>
       </c>
       <c r="H13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G35</f>
-        <v>1160</v>
+        <v>2217.25</v>
       </c>
       <c r="I13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
-        <v>1560</v>
+        <v>2715</v>
       </c>
       <c r="J13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I35</f>
-        <v>1860</v>
+        <v>4349.75</v>
       </c>
       <c r="K13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J35</f>
-        <v>360</v>
+        <v>1274</v>
       </c>
       <c r="L13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K35</f>
-        <v>1580</v>
+        <v>7347.5</v>
       </c>
       <c r="M13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L35</f>
-        <v>2460</v>
+        <v>1807.25</v>
       </c>
       <c r="N13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M35</f>
-        <v>720</v>
+        <v>1758.5</v>
       </c>
       <c r="O13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>746.666666666667</v>
+        <v>1418.5</v>
       </c>
       <c r="P13" s="158"/>
     </row>
@@ -29559,55 +29559,55 @@
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="D15" s="170" t="n">
         <f aca="false">D11-D13</f>
-        <v>2706.66666666667</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E15" s="170" t="n">
         <f aca="false">E11-E13</f>
-        <v>4846.66666666667</v>
+        <v>10426.6666666667</v>
       </c>
       <c r="F15" s="170" t="n">
         <f aca="false">F11-F13</f>
-        <v>-13.3333333333303</v>
+        <v>7454.6666666667</v>
       </c>
       <c r="G15" s="170" t="n">
         <f aca="false">G11-G13</f>
-        <v>4973.33333333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H15" s="170" t="n">
         <f aca="false">H11-H13</f>
-        <v>6756.66666666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I15" s="170" t="n">
         <f aca="false">I11-I13</f>
-        <v>1873.33333333333</v>
+        <v>10762.6666666667</v>
       </c>
       <c r="J15" s="170" t="n">
         <f aca="false">J11-J13</f>
-        <v>4493.33333333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K15" s="170" t="n">
         <f aca="false">K11-K13</f>
-        <v>4946.66666666667</v>
+        <v>9903.6666666667</v>
       </c>
       <c r="L15" s="170" t="n">
         <f aca="false">L11-L13</f>
-        <v>2586.66666666667</v>
+        <v>5054.1666666667</v>
       </c>
       <c r="M15" s="170" t="n">
         <f aca="false">M11-M13</f>
-        <v>1040</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N15" s="170" t="n">
         <f aca="false">N11-N13</f>
-        <v>1780</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O15" s="170" t="n">
         <f aca="false">O11-O13</f>
-        <v>503.333333333333</v>
+        <v>9699.1666666667</v>
       </c>
       <c r="P15" s="158"/>
     </row>
@@ -29677,55 +29677,55 @@
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">D15+D16</f>
-        <v>2706.66666666667</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E17" s="170" t="n">
         <f aca="false">E15+E16</f>
-        <v>4846.66666666667</v>
+        <v>10426.6666666667</v>
       </c>
       <c r="F17" s="170" t="n">
         <f aca="false">F15+F16</f>
-        <v>-13.3333333333303</v>
+        <v>7454.6666666667</v>
       </c>
       <c r="G17" s="170" t="n">
         <f aca="false">G15+G16</f>
-        <v>4973.33333333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H17" s="170" t="n">
         <f aca="false">H15+H16</f>
-        <v>6756.66666666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I17" s="170" t="n">
         <f aca="false">I15+I16</f>
-        <v>1873.33333333333</v>
+        <v>10762.6666666667</v>
       </c>
       <c r="J17" s="170" t="n">
         <f aca="false">J15+J16</f>
-        <v>4493.33333333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K17" s="170" t="n">
         <f aca="false">K15+K16</f>
-        <v>4946.66666666667</v>
+        <v>9903.6666666667</v>
       </c>
       <c r="L17" s="170" t="n">
         <f aca="false">L15+L16</f>
-        <v>2586.66666666667</v>
+        <v>5054.1666666667</v>
       </c>
       <c r="M17" s="170" t="n">
         <f aca="false">M15+M16</f>
-        <v>1040</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N17" s="170" t="n">
         <f aca="false">N15+N16</f>
-        <v>1780</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O17" s="170" t="n">
         <f aca="false">O15+O16</f>
-        <v>503.333333333333</v>
+        <v>9699.1666666667</v>
       </c>
       <c r="P17" s="158"/>
     </row>
@@ -29890,55 +29890,55 @@
       </c>
       <c r="C22" s="170" t="n">
         <f aca="false">SUM(D22:O22)</f>
-        <v>58416.6666666667</v>
+        <v>169200</v>
       </c>
       <c r="D22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D5,C5/C21),0)</f>
-        <v>5166.66666666667</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="E22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E5,C5/C21),0)</f>
-        <v>6166.66666666667</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="F22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F5,C5/C21),0)</f>
-        <v>4666.66666666667</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="G22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G5,C5/C21),0)</f>
-        <v>6833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="H22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H5,C5/C21),0)</f>
-        <v>5833.33333333333</v>
+        <v>13766.6666666667</v>
       </c>
       <c r="I22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I5,C5/C21),0)</f>
-        <v>5833.33333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="J22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J5,C5/C21),0)</f>
-        <v>6833.33333333333</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="K22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K5,C5/C21),0)</f>
-        <v>5666.66666666667</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="L22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L5,C5/C21),0)</f>
-        <v>4166.66666666667</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="M22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M5,C5/C21),0)</f>
-        <v>3500</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="N22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N5,C5/C21),0)</f>
-        <v>2500</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="O22" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O5,C5/C21),0)</f>
-        <v>1250</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="P22" s="178"/>
     </row>
@@ -30044,55 +30044,55 @@
       </c>
       <c r="C26" s="170" t="n">
         <f aca="false">SUM(D26:O26)</f>
-        <v>7800</v>
+        <v>17744</v>
       </c>
       <c r="D26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D9,C9/C21),0)</f>
-        <v>600</v>
+        <v>885</v>
       </c>
       <c r="E26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E9,C9/C21),0)</f>
-        <v>360</v>
+        <v>969</v>
       </c>
       <c r="F26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F9,C9/C21),0)</f>
-        <v>3600</v>
+        <v>5645</v>
       </c>
       <c r="G26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G9,C9/C21),0)</f>
-        <v>0</v>
+        <v>969</v>
       </c>
       <c r="H26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H9,C9/C21),0)</f>
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="I26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I9,C9/C21),0)</f>
-        <v>2400</v>
+        <v>489</v>
       </c>
       <c r="J26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J9,C9/C21),0)</f>
-        <v>480</v>
+        <v>765</v>
       </c>
       <c r="K26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K9,C9/C21),0)</f>
-        <v>360</v>
+        <v>4089</v>
       </c>
       <c r="L26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L9,C9/C21),0)</f>
-        <v>0</v>
+        <v>765</v>
       </c>
       <c r="M26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M9,C9/C21),0)</f>
-        <v>0</v>
+        <v>849</v>
       </c>
       <c r="N26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N9,C9/C21),0)</f>
-        <v>0</v>
+        <v>945</v>
       </c>
       <c r="O26" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O9,C9/C21),0)</f>
-        <v>0</v>
+        <v>549</v>
       </c>
       <c r="P26" s="178"/>
     </row>
@@ -30121,55 +30121,55 @@
       </c>
       <c r="C28" s="170" t="n">
         <f aca="false">SUM(D28:O28)</f>
-        <v>52700</v>
+        <v>153539.333333334</v>
       </c>
       <c r="D28" s="170" t="n">
         <f aca="false">D22+D24-D26</f>
-        <v>4566.66666666667</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="E28" s="170" t="n">
         <f aca="false">E22+E24-E26</f>
-        <v>5806.66666666667</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="F28" s="170" t="n">
         <f aca="false">F22+F24-F26</f>
-        <v>1066.66666666667</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="G28" s="170" t="n">
         <f aca="false">G22+G24-G26</f>
-        <v>6833.33333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="H28" s="170" t="n">
         <f aca="false">H22+H24-H26</f>
-        <v>7916.66666666666</v>
+        <v>15025</v>
       </c>
       <c r="I28" s="170" t="n">
         <f aca="false">I22+I24-I26</f>
-        <v>3433.33333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="J28" s="170" t="n">
         <f aca="false">J22+J24-J26</f>
-        <v>6353.33333333333</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="K28" s="170" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>5306.66666666667</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="L28" s="170" t="n">
         <f aca="false">L22+L24-L26</f>
-        <v>4166.66666666667</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="M28" s="170" t="n">
         <f aca="false">M22+M24-M26</f>
-        <v>3500</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="N28" s="170" t="n">
         <f aca="false">N22+N24-N26</f>
-        <v>2500</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="O28" s="170" t="n">
         <f aca="false">O22+O24-O26</f>
-        <v>1250</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="P28" s="178"/>
     </row>
@@ -30198,55 +30198,55 @@
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>16206.6666666667</v>
+        <v>29870.25</v>
       </c>
       <c r="D30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
-        <v>1860</v>
+        <v>1249.25</v>
       </c>
       <c r="E30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E13,C13/C21),0)</f>
-        <v>960</v>
+        <v>1871</v>
       </c>
       <c r="F30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F13,C13/C21),0)</f>
-        <v>1080</v>
+        <v>2067</v>
       </c>
       <c r="G30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G13,C13/C21),0)</f>
-        <v>1860</v>
+        <v>1795.25</v>
       </c>
       <c r="H30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H13,C13/C21),0)</f>
-        <v>1160</v>
+        <v>2217.25</v>
       </c>
       <c r="I30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
-        <v>1560</v>
+        <v>2715</v>
       </c>
       <c r="J30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J13,C13/C21),0)</f>
-        <v>1860</v>
+        <v>4349.75</v>
       </c>
       <c r="K30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K13,C13/C21),0)</f>
-        <v>360</v>
+        <v>1274</v>
       </c>
       <c r="L30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L13,C13/C21),0)</f>
-        <v>1580</v>
+        <v>7347.5</v>
       </c>
       <c r="M30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M13,C13/C21),0)</f>
-        <v>2460</v>
+        <v>1807.25</v>
       </c>
       <c r="N30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N13,C13/C21),0)</f>
-        <v>720</v>
+        <v>1758.5</v>
       </c>
       <c r="O30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>746.666666666667</v>
+        <v>1418.5</v>
       </c>
       <c r="P30" s="158"/>
     </row>
@@ -30275,55 +30275,55 @@
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="D32" s="170" t="n">
         <f aca="false">D28-D30</f>
-        <v>2706.66666666667</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E32" s="170" t="n">
         <f aca="false">E28-E30</f>
-        <v>4846.66666666667</v>
+        <v>10426.6666666667</v>
       </c>
       <c r="F32" s="170" t="n">
         <f aca="false">F28-F30</f>
-        <v>-13.3333333333303</v>
+        <v>7454.6666666667</v>
       </c>
       <c r="G32" s="170" t="n">
         <f aca="false">G28-G30</f>
-        <v>4973.33333333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H32" s="170" t="n">
         <f aca="false">H28-H30</f>
-        <v>6756.66666666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I32" s="170" t="n">
         <f aca="false">I28-I30</f>
-        <v>1873.33333333333</v>
+        <v>10762.6666666667</v>
       </c>
       <c r="J32" s="170" t="n">
         <f aca="false">J28-J30</f>
-        <v>4493.33333333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K32" s="170" t="n">
         <f aca="false">K28-K30</f>
-        <v>4946.66666666667</v>
+        <v>9903.6666666667</v>
       </c>
       <c r="L32" s="170" t="n">
         <f aca="false">L28-L30</f>
-        <v>2586.66666666667</v>
+        <v>5054.1666666667</v>
       </c>
       <c r="M32" s="170" t="n">
         <f aca="false">M28-M30</f>
-        <v>1040</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N32" s="170" t="n">
         <f aca="false">N28-N30</f>
-        <v>1780</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O32" s="170" t="n">
         <f aca="false">O28-O30</f>
-        <v>503.333333333333</v>
+        <v>9699.1666666667</v>
       </c>
       <c r="P32" s="158"/>
     </row>
@@ -30393,55 +30393,55 @@
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="D34" s="170" t="n">
         <f aca="false">D32+D33</f>
-        <v>2706.66666666667</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E34" s="170" t="n">
         <f aca="false">E32+E33</f>
-        <v>4846.66666666667</v>
+        <v>10426.6666666667</v>
       </c>
       <c r="F34" s="170" t="n">
         <f aca="false">F32+F33</f>
-        <v>-13.3333333333303</v>
+        <v>7454.6666666667</v>
       </c>
       <c r="G34" s="170" t="n">
         <f aca="false">G32+G33</f>
-        <v>4973.33333333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H34" s="170" t="n">
         <f aca="false">H32+H33</f>
-        <v>6756.66666666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I34" s="170" t="n">
         <f aca="false">I32+I33</f>
-        <v>1873.33333333333</v>
+        <v>10762.6666666667</v>
       </c>
       <c r="J34" s="170" t="n">
         <f aca="false">J32+J33</f>
-        <v>4493.33333333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K34" s="170" t="n">
         <f aca="false">K32+K33</f>
-        <v>4946.66666666667</v>
+        <v>9903.6666666667</v>
       </c>
       <c r="L34" s="170" t="n">
         <f aca="false">L32+L33</f>
-        <v>2586.66666666667</v>
+        <v>5054.1666666667</v>
       </c>
       <c r="M34" s="170" t="n">
         <f aca="false">M32+M33</f>
-        <v>1040</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N34" s="170" t="n">
         <f aca="false">N32+N33</f>
-        <v>1780</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O34" s="170" t="n">
         <f aca="false">O32+O33</f>
-        <v>503.333333333333</v>
+        <v>9699.1666666667</v>
       </c>
       <c r="P34" s="158"/>
     </row>
@@ -30536,7 +30536,7 @@
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>36493.3333333333</v>
+        <v>123669.083333334</v>
       </c>
       <c r="D39" s="158"/>
       <c r="E39" s="158"/>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>23923.3333333333</v>
+        <v>111099.083333334</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30605,7 +30605,7 @@
       </c>
       <c r="C42" s="339" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!N$12),C41*Admin!N$6,Admin!N$12*Admin!N$6)),0)</f>
-        <v>4784.66666666667</v>
+        <v>7540.2</v>
       </c>
       <c r="D42" s="340"/>
       <c r="E42" s="158"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>0</v>
+        <v>29359.2333333335</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="C44" s="339" t="n">
         <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>1435.4</v>
+        <v>3730.02166666667</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30692,7 +30692,7 @@
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44</f>
-        <v>6220.06666666667</v>
+        <v>40629.4550000002</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -5697,7 +5697,7 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
@@ -5722,12 +5722,12 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>0</v>
+            <v>25</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5747,12 +5747,12 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>0</v>
+            <v>250</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5772,7 +5772,7 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
@@ -5797,7 +5797,7 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
@@ -5822,12 +5822,12 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>0</v>
+            <v>208</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5847,7 +5847,7 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
@@ -5872,12 +5872,12 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>0</v>
+            <v>25</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5897,12 +5897,12 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>0</v>
+            <v>167</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5922,7 +5922,7 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>6000</v>
           </cell>
         </row>
         <row r="1">
@@ -5947,7 +5947,7 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
@@ -5972,12 +5972,12 @@
         </row>
         <row r="1">
           <cell r="L1">
-            <v>0</v>
+            <v>1000</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>0</v>
+            <v>125</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -10570,7 +10570,7 @@
       </c>
       <c r="O51" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="P51" s="98"/>
       <c r="Q51" s="98"/>
@@ -10987,7 +10987,7 @@
       </c>
       <c r="O64" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'Profit &amp; Loss Account'!B34</f>
-        <v>47614.25</v>
+        <v>48414.25</v>
       </c>
       <c r="P64" s="98"/>
       <c r="Q64" s="98"/>
@@ -11176,7 +11176,7 @@
       </c>
       <c r="D71" s="98" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>121585.75</v>
+        <v>120785.75</v>
       </c>
       <c r="E71" s="98"/>
       <c r="F71" s="98"/>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>121585.75</v>
+        <v>120785.75</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -12241,7 +12241,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -15945,7 +15945,7 @@
       </c>
       <c r="D102" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B31</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="E102" s="98"/>
       <c r="F102" s="98"/>
@@ -16575,7 +16575,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>47614.25</v>
+        <v>48414.25</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -16786,7 +16786,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>121585.75</v>
+        <v>120785.75</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -18194,7 +18194,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>121585.75</v>
+        <v>120785.75</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -18791,7 +18791,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">O174</f>
-        <v>121585.75</v>
+        <v>120785.75</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -19298,7 +19298,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="B31" s="170" t="n">
         <f aca="false">SUM(C31:N31)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="C31" s="171" t="n">
         <f aca="false">[5]Apr!$V$1+[4]Apr!$Y$1</f>
@@ -24190,11 +24190,11 @@
       </c>
       <c r="D31" s="171" t="n">
         <f aca="false">[5]May!$V$1+[4]May!$Y$1</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="E31" s="172" t="n">
         <f aca="false">[5]Jun!$V$1+[4]Jun!$Y$1</f>
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F31" s="171" t="n">
         <f aca="false">[5]Jul!$V$1+[4]Jul!$Y$1</f>
@@ -24206,7 +24206,7 @@
       </c>
       <c r="H31" s="172" t="n">
         <f aca="false">[5]Sep!$V$1+[4]Sep!$Y$1</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="I31" s="171" t="n">
         <f aca="false">[5]Oct!$V$1+[4]Oct!$Y$1</f>
@@ -24214,11 +24214,11 @@
       </c>
       <c r="J31" s="171" t="n">
         <f aca="false">[5]Nov!$V$1+[4]Nov!$Y$1</f>
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="K31" s="172" t="n">
         <f aca="false">[5]Dec!$V$1+[4]Dec!$Y$1</f>
-        <v>0</v>
+        <v>167</v>
       </c>
       <c r="L31" s="171" t="n">
         <f aca="false">[5]Jan!$V$1+[4]Jan!$Y$1</f>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="N31" s="171" t="n">
         <f aca="false">[5]Mar!$V$1+[4]Mar!$Y$1</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="O31" s="164"/>
     </row>
@@ -24414,7 +24414,7 @@
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>29870.25</v>
+        <v>30670.25</v>
       </c>
       <c r="C35" s="170" t="n">
         <f aca="false">SUM(C21:C34)</f>
@@ -24422,11 +24422,11 @@
       </c>
       <c r="D35" s="170" t="n">
         <f aca="false">SUM(D21:D34)</f>
-        <v>1871</v>
+        <v>1896</v>
       </c>
       <c r="E35" s="170" t="n">
         <f aca="false">SUM(E21:E34)</f>
-        <v>2067</v>
+        <v>2317</v>
       </c>
       <c r="F35" s="174" t="n">
         <f aca="false">SUM(F21:F34)</f>
@@ -24438,7 +24438,7 @@
       </c>
       <c r="H35" s="170" t="n">
         <f aca="false">SUM(H21:H34)</f>
-        <v>2715</v>
+        <v>2923</v>
       </c>
       <c r="I35" s="174" t="n">
         <f aca="false">SUM(I21:I34)</f>
@@ -24446,11 +24446,11 @@
       </c>
       <c r="J35" s="170" t="n">
         <f aca="false">SUM(J21:J34)</f>
-        <v>1274</v>
+        <v>1299</v>
       </c>
       <c r="K35" s="170" t="n">
         <f aca="false">SUM(K21:K34)</f>
-        <v>7347.5</v>
+        <v>7514.5</v>
       </c>
       <c r="L35" s="174" t="n">
         <f aca="false">SUM(L21:L34)</f>
@@ -24462,7 +24462,7 @@
       </c>
       <c r="N35" s="170" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>1418.5</v>
+        <v>1543.5</v>
       </c>
       <c r="O35" s="164"/>
     </row>
@@ -24489,7 +24489,7 @@
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="C37" s="170" t="n">
         <f aca="false">C19-C35</f>
@@ -24497,11 +24497,11 @@
       </c>
       <c r="D37" s="170" t="n">
         <f aca="false">D19-D35</f>
-        <v>10426.6666666667</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="E37" s="170" t="n">
         <f aca="false">E19-E35</f>
-        <v>7454.6666666667</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="F37" s="174" t="n">
         <f aca="false">F19-F35</f>
@@ -24513,7 +24513,7 @@
       </c>
       <c r="H37" s="170" t="n">
         <f aca="false">H19-H35</f>
-        <v>10762.6666666667</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="I37" s="174" t="n">
         <f aca="false">I19-I35</f>
@@ -24521,11 +24521,11 @@
       </c>
       <c r="J37" s="170" t="n">
         <f aca="false">J19-J35</f>
-        <v>9903.6666666667</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="K37" s="170" t="n">
         <f aca="false">K19-K35</f>
-        <v>5054.1666666667</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="L37" s="174" t="n">
         <f aca="false">L19-L35</f>
@@ -24537,7 +24537,7 @@
       </c>
       <c r="N37" s="170" t="n">
         <f aca="false">N19-N35</f>
-        <v>9699.1666666667</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="O37" s="164"/>
     </row>
@@ -24605,7 +24605,7 @@
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="C39" s="170" t="n">
         <f aca="false">C37+C38</f>
@@ -24613,11 +24613,11 @@
       </c>
       <c r="D39" s="170" t="n">
         <f aca="false">D37+D38</f>
-        <v>10426.6666666667</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="E39" s="170" t="n">
         <f aca="false">E37+E38</f>
-        <v>7454.6666666667</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="F39" s="174" t="n">
         <f aca="false">F37+F38</f>
@@ -24629,7 +24629,7 @@
       </c>
       <c r="H39" s="170" t="n">
         <f aca="false">H37+H38</f>
-        <v>10762.6666666667</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="I39" s="174" t="n">
         <f aca="false">I37+I38</f>
@@ -24637,11 +24637,11 @@
       </c>
       <c r="J39" s="170" t="n">
         <f aca="false">J37+J38</f>
-        <v>9903.6666666667</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="K39" s="170" t="n">
         <f aca="false">K37+K38</f>
-        <v>5054.1666666667</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="L39" s="174" t="n">
         <f aca="false">L37+L38</f>
@@ -24653,7 +24653,7 @@
       </c>
       <c r="N39" s="170" t="n">
         <f aca="false">N37+N38</f>
-        <v>9699.1666666667</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="O39" s="164"/>
     </row>
@@ -24815,55 +24815,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>40629.4550000002</v>
+        <v>40293.4550000002</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3385.78791666668</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24873,55 +24873,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>83039.6283333336</v>
+        <v>82575.6283333336</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>8146.62875000002</v>
+        <v>8174.62875000002</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>7040.87875000002</v>
+        <v>7043.87875000002</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>4068.87875000002</v>
+        <v>3846.87875000002</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>7816.62875000002</v>
+        <v>7844.62875000002</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>9421.96208333335</v>
+        <v>9449.96208333335</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>7376.87875000002</v>
+        <v>7196.87875000002</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>6966.12875000002</v>
+        <v>6994.12875000002</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>6517.87875000002</v>
+        <v>6520.87875000002</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>1668.37875000002</v>
+        <v>1529.37875000002</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9324.62875000002</v>
+        <v>9352.62875000002</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>8377.37875000002</v>
+        <v>8405.37875000002</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>6313.37875000002</v>
+        <v>6216.37875000002</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -24931,55 +24931,55 @@
       </c>
       <c r="B46" s="177" t="n">
         <f aca="false">SUM(C46:N46)</f>
-        <v>0</v>
+        <v>17000</v>
       </c>
       <c r="C46" s="177" t="n">
         <f aca="false">[5]Apr!$J$1+[4]Apr!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="D46" s="177" t="n">
         <f aca="false">[5]May!$J$1+[4]May!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="E46" s="177" t="n">
         <f aca="false">[5]Jun!$J$1+[4]Jun!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="F46" s="177" t="n">
         <f aca="false">[5]Jul!$J$1+[4]Jul!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="G46" s="177" t="n">
         <f aca="false">[5]Aug!$J$1+[4]Aug!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="H46" s="177" t="n">
         <f aca="false">[5]Sep!$J$1+[4]Sep!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="I46" s="177" t="n">
         <f aca="false">[5]Oct!$J$1+[4]Oct!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="J46" s="177" t="n">
         <f aca="false">[5]Nov!$J$1+[4]Nov!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="K46" s="177" t="n">
         <f aca="false">[5]Dec!$J$1+[4]Dec!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="L46" s="177" t="n">
         <f aca="false">[5]Jan!$J$1+[4]Jan!$L$1</f>
-        <v>0</v>
+        <v>6000</v>
       </c>
       <c r="M46" s="177" t="n">
         <f aca="false">[5]Feb!$J$1+[4]Feb!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="N46" s="177" t="n">
         <f aca="false">[5]Mar!$J$1+[4]Mar!$L$1</f>
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="O46" s="164"/>
     </row>
@@ -25352,23 +25352,23 @@
       </c>
       <c r="C16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
-        <v>0</v>
+        <v>275</v>
       </c>
       <c r="D16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F31:H31)</f>
-        <v>0</v>
+        <v>208</v>
       </c>
       <c r="E16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I31:K31)</f>
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="F16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L31:N31)</f>
-        <v>0</v>
+        <v>125</v>
       </c>
       <c r="G16" s="200" t="n">
         <f aca="false">SUM(C16:F16)</f>
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="H16" s="195"/>
       <c r="I16" s="195"/>
@@ -25663,23 +25663,23 @@
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
-        <v>12686.25</v>
+        <v>12961.25</v>
       </c>
       <c r="D29" s="203" t="n">
         <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D25,D26)</f>
-        <v>9010.5</v>
+        <v>9218.5</v>
       </c>
       <c r="E29" s="203" t="n">
         <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E25,E26)</f>
-        <v>18590.25</v>
+        <v>18782.25</v>
       </c>
       <c r="F29" s="203" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F25,F26)</f>
-        <v>7327.25</v>
+        <v>7452.25</v>
       </c>
       <c r="G29" s="203" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G25,G26)</f>
-        <v>47614.25</v>
+        <v>48414.25</v>
       </c>
       <c r="H29" s="204"/>
       <c r="I29" s="195"/>
@@ -26249,7 +26249,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -26282,7 +26282,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>111099.083333334</v>
+        <v>110299.083333334</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="E9" s="213" t="n">
         <f aca="false">IF((E7&gt;C9),((E7-C9)*D9),0)</f>
-        <v>29359.2333333335</v>
+        <v>29039.2333333335</v>
       </c>
       <c r="F9" s="214"/>
       <c r="G9" s="218"/>
@@ -26340,7 +26340,7 @@
       <c r="D10" s="230"/>
       <c r="E10" s="231" t="n">
         <f aca="false">SUM(E8:E9)</f>
-        <v>36899.4333333335</v>
+        <v>36579.4333333335</v>
       </c>
       <c r="F10" s="214"/>
       <c r="G10" s="218"/>
@@ -26426,7 +26426,7 @@
       </c>
       <c r="E16" s="240" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1467.98166666667</v>
+        <v>1451.98166666667</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="234"/>
@@ -26451,7 +26451,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E10:E17)</f>
-        <v>40629.4150000002</v>
+        <v>40293.4150000002</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -26533,7 +26533,7 @@
       </c>
       <c r="E25" s="240" t="n">
         <f aca="false">E18</f>
-        <v>40629.4150000002</v>
+        <v>40293.4150000002</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -26550,7 +26550,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>20314.7075000001</v>
+        <v>20146.7075000001</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -26567,7 +26567,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>20314.7075000001</v>
+        <v>20146.7075000001</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -29482,7 +29482,7 @@
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>29870.25</v>
+        <v>30670.25</v>
       </c>
       <c r="D13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
@@ -29490,11 +29490,11 @@
       </c>
       <c r="E13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D35</f>
-        <v>1871</v>
+        <v>1896</v>
       </c>
       <c r="F13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E35</f>
-        <v>2067</v>
+        <v>2317</v>
       </c>
       <c r="G13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F35</f>
@@ -29506,7 +29506,7 @@
       </c>
       <c r="I13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
-        <v>2715</v>
+        <v>2923</v>
       </c>
       <c r="J13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I35</f>
@@ -29514,11 +29514,11 @@
       </c>
       <c r="K13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J35</f>
-        <v>1274</v>
+        <v>1299</v>
       </c>
       <c r="L13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K35</f>
-        <v>7347.5</v>
+        <v>7514.5</v>
       </c>
       <c r="M13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L35</f>
@@ -29530,7 +29530,7 @@
       </c>
       <c r="O13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>1418.5</v>
+        <v>1543.5</v>
       </c>
       <c r="P13" s="158"/>
     </row>
@@ -29559,7 +29559,7 @@
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D15" s="170" t="n">
         <f aca="false">D11-D13</f>
@@ -29567,11 +29567,11 @@
       </c>
       <c r="E15" s="170" t="n">
         <f aca="false">E11-E13</f>
-        <v>10426.6666666667</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F15" s="170" t="n">
         <f aca="false">F11-F13</f>
-        <v>7454.6666666667</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G15" s="170" t="n">
         <f aca="false">G11-G13</f>
@@ -29583,7 +29583,7 @@
       </c>
       <c r="I15" s="170" t="n">
         <f aca="false">I11-I13</f>
-        <v>10762.6666666667</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J15" s="170" t="n">
         <f aca="false">J11-J13</f>
@@ -29591,11 +29591,11 @@
       </c>
       <c r="K15" s="170" t="n">
         <f aca="false">K11-K13</f>
-        <v>9903.6666666667</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L15" s="170" t="n">
         <f aca="false">L11-L13</f>
-        <v>5054.1666666667</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M15" s="170" t="n">
         <f aca="false">M11-M13</f>
@@ -29607,7 +29607,7 @@
       </c>
       <c r="O15" s="170" t="n">
         <f aca="false">O11-O13</f>
-        <v>9699.1666666667</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P15" s="158"/>
     </row>
@@ -29677,7 +29677,7 @@
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">D15+D16</f>
@@ -29685,11 +29685,11 @@
       </c>
       <c r="E17" s="170" t="n">
         <f aca="false">E15+E16</f>
-        <v>10426.6666666667</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F17" s="170" t="n">
         <f aca="false">F15+F16</f>
-        <v>7454.6666666667</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G17" s="170" t="n">
         <f aca="false">G15+G16</f>
@@ -29701,7 +29701,7 @@
       </c>
       <c r="I17" s="170" t="n">
         <f aca="false">I15+I16</f>
-        <v>10762.6666666667</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J17" s="170" t="n">
         <f aca="false">J15+J16</f>
@@ -29709,11 +29709,11 @@
       </c>
       <c r="K17" s="170" t="n">
         <f aca="false">K15+K16</f>
-        <v>9903.6666666667</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L17" s="170" t="n">
         <f aca="false">L15+L16</f>
-        <v>5054.1666666667</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M17" s="170" t="n">
         <f aca="false">M15+M16</f>
@@ -29725,7 +29725,7 @@
       </c>
       <c r="O17" s="170" t="n">
         <f aca="false">O15+O16</f>
-        <v>9699.1666666667</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P17" s="158"/>
     </row>
@@ -30198,7 +30198,7 @@
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>29870.25</v>
+        <v>30670.25</v>
       </c>
       <c r="D30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
@@ -30206,11 +30206,11 @@
       </c>
       <c r="E30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E13,C13/C21),0)</f>
-        <v>1871</v>
+        <v>1896</v>
       </c>
       <c r="F30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F13,C13/C21),0)</f>
-        <v>2067</v>
+        <v>2317</v>
       </c>
       <c r="G30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G13,C13/C21),0)</f>
@@ -30222,7 +30222,7 @@
       </c>
       <c r="I30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
-        <v>2715</v>
+        <v>2923</v>
       </c>
       <c r="J30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J13,C13/C21),0)</f>
@@ -30230,11 +30230,11 @@
       </c>
       <c r="K30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K13,C13/C21),0)</f>
-        <v>1274</v>
+        <v>1299</v>
       </c>
       <c r="L30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L13,C13/C21),0)</f>
-        <v>7347.5</v>
+        <v>7514.5</v>
       </c>
       <c r="M30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M13,C13/C21),0)</f>
@@ -30246,7 +30246,7 @@
       </c>
       <c r="O30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>1418.5</v>
+        <v>1543.5</v>
       </c>
       <c r="P30" s="158"/>
     </row>
@@ -30275,7 +30275,7 @@
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D32" s="170" t="n">
         <f aca="false">D28-D30</f>
@@ -30283,11 +30283,11 @@
       </c>
       <c r="E32" s="170" t="n">
         <f aca="false">E28-E30</f>
-        <v>10426.6666666667</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F32" s="170" t="n">
         <f aca="false">F28-F30</f>
-        <v>7454.6666666667</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G32" s="170" t="n">
         <f aca="false">G28-G30</f>
@@ -30299,7 +30299,7 @@
       </c>
       <c r="I32" s="170" t="n">
         <f aca="false">I28-I30</f>
-        <v>10762.6666666667</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J32" s="170" t="n">
         <f aca="false">J28-J30</f>
@@ -30307,11 +30307,11 @@
       </c>
       <c r="K32" s="170" t="n">
         <f aca="false">K28-K30</f>
-        <v>9903.6666666667</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L32" s="170" t="n">
         <f aca="false">L28-L30</f>
-        <v>5054.1666666667</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M32" s="170" t="n">
         <f aca="false">M28-M30</f>
@@ -30323,7 +30323,7 @@
       </c>
       <c r="O32" s="170" t="n">
         <f aca="false">O28-O30</f>
-        <v>9699.1666666667</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P32" s="158"/>
     </row>
@@ -30393,7 +30393,7 @@
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D34" s="170" t="n">
         <f aca="false">D32+D33</f>
@@ -30401,11 +30401,11 @@
       </c>
       <c r="E34" s="170" t="n">
         <f aca="false">E32+E33</f>
-        <v>10426.6666666667</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F34" s="170" t="n">
         <f aca="false">F32+F33</f>
-        <v>7454.6666666667</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G34" s="170" t="n">
         <f aca="false">G32+G33</f>
@@ -30417,7 +30417,7 @@
       </c>
       <c r="I34" s="170" t="n">
         <f aca="false">I32+I33</f>
-        <v>10762.6666666667</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J34" s="170" t="n">
         <f aca="false">J32+J33</f>
@@ -30425,11 +30425,11 @@
       </c>
       <c r="K34" s="170" t="n">
         <f aca="false">K32+K33</f>
-        <v>9903.6666666667</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L34" s="170" t="n">
         <f aca="false">L32+L33</f>
-        <v>5054.1666666667</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M34" s="170" t="n">
         <f aca="false">M32+M33</f>
@@ -30441,7 +30441,7 @@
       </c>
       <c r="O34" s="170" t="n">
         <f aca="false">O32+O33</f>
-        <v>9699.1666666667</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P34" s="158"/>
     </row>
@@ -30536,7 +30536,7 @@
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>123669.083333334</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D39" s="158"/>
       <c r="E39" s="158"/>
@@ -30582,7 +30582,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>111099.083333334</v>
+        <v>110299.083333334</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30628,7 +30628,7 @@
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>29359.2333333335</v>
+        <v>29039.2333333335</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30651,7 +30651,7 @@
       </c>
       <c r="C44" s="339" t="n">
         <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>3730.02166666667</v>
+        <v>3714.02166666667</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30692,7 +30692,7 @@
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44</f>
-        <v>40629.4550000002</v>
+        <v>40293.4550000002</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4829,7 +4829,7 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="P1">
-            <v>11166.6666666667</v>
+            <v>25333.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -4856,7 +4856,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="P1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4883,7 +4883,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="P1">
-            <v>12366.6666666667</v>
+            <v>26533.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4910,7 +4910,7 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="P1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -4937,7 +4937,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="P1">
-            <v>12966.6666666667</v>
+            <v>27133.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4964,7 +4964,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="P1">
-            <v>10866.6666666667</v>
+            <v>25033.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4991,7 +4991,7 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="P1">
-            <v>12966.6666666667</v>
+            <v>27133.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -5018,7 +5018,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="P1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -5045,7 +5045,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="P1">
-            <v>12366.6666666667</v>
+            <v>26533.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -5072,7 +5072,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="P1">
-            <v>11466.6666666667</v>
+            <v>25633.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -5099,7 +5099,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="P1">
-            <v>12166.6666666667</v>
+            <v>26333.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -5126,7 +5126,7 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="P1">
-            <v>10866.6666666667</v>
+            <v>25033.3333333333</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="D38" s="96" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B9</f>
-        <v>169200</v>
+        <v>339200</v>
       </c>
       <c r="E38" s="96"/>
       <c r="F38" s="96"/>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="D71" s="96" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>120785.75</v>
+        <v>290785.75</v>
       </c>
       <c r="E71" s="96"/>
       <c r="F71" s="96"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="D99" s="96" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>120785.75</v>
+        <v>290785.75</v>
       </c>
       <c r="E99" s="96"/>
       <c r="F99" s="96"/>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="D106" s="96" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="E106" s="96"/>
       <c r="F106" s="96"/>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="D55" s="96" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B9</f>
-        <v>169200</v>
+        <v>339200</v>
       </c>
       <c r="E55" s="96"/>
       <c r="F55" s="96"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="D129" s="96" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>120785.75</v>
+        <v>290785.75</v>
       </c>
       <c r="E129" s="96"/>
       <c r="F129" s="96"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="O174" s="96" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>120785.75</v>
+        <v>290785.75</v>
       </c>
       <c r="P174" s="96"/>
       <c r="Q174" s="96"/>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="O194" s="96" t="n">
         <f aca="false">O174</f>
-        <v>120785.75</v>
+        <v>290785.75</v>
       </c>
       <c r="P194" s="96"/>
       <c r="Q194" s="96"/>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="O210" s="96" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="P210" s="96"/>
       <c r="Q210" s="96"/>
@@ -22798,55 +22798,55 @@
       </c>
       <c r="B5" s="168" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>141600</v>
+        <v>311600</v>
       </c>
       <c r="C5" s="169" t="n">
         <f aca="false">[2]Apr!$P$1</f>
-        <v>11166.6666666667</v>
+        <v>25333.3333333333</v>
       </c>
       <c r="D5" s="169" t="n">
         <f aca="false">[2]May!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="E5" s="170" t="n">
         <f aca="false">[2]Jun!$P$1</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="F5" s="169" t="n">
         <f aca="false">[2]Jul!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="G5" s="169" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="H5" s="170" t="n">
         <f aca="false">[2]Sep!$P$1</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="I5" s="169" t="n">
         <f aca="false">[2]Oct!$P$1</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="J5" s="169" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K5" s="170" t="n">
         <f aca="false">[2]Dec!$P$1</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="L5" s="169" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="M5" s="169" t="n">
         <f aca="false">[2]Feb!$P$1</f>
-        <v>12166.6666666667</v>
+        <v>26333.3333333333</v>
       </c>
       <c r="N5" s="169" t="n">
         <f aca="false">[2]Mar!$P$1</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="O5" s="162"/>
     </row>
@@ -23030,55 +23030,55 @@
       </c>
       <c r="B9" s="168" t="n">
         <f aca="false">SUM(B5:B8)</f>
-        <v>169200</v>
+        <v>339200</v>
       </c>
       <c r="C9" s="168" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>13666.6666666667</v>
+        <v>27833.3333333333</v>
       </c>
       <c r="D9" s="168" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>13266.6666666667</v>
+        <v>27433.3333333333</v>
       </c>
       <c r="E9" s="168" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>15166.6666666667</v>
+        <v>29333.3333333333</v>
       </c>
       <c r="F9" s="172" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="G9" s="168" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>13766.6666666667</v>
+        <v>27933.3333333333</v>
       </c>
       <c r="H9" s="168" t="n">
         <f aca="false">SUM(H5:H8)</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="I9" s="172" t="n">
         <f aca="false">SUM(I5:I8)</f>
-        <v>15466.6666666667</v>
+        <v>29633.3333333333</v>
       </c>
       <c r="J9" s="168" t="n">
         <f aca="false">SUM(J5:J8)</f>
-        <v>15266.6666666667</v>
+        <v>29433.3333333333</v>
       </c>
       <c r="K9" s="168" t="n">
         <f aca="false">SUM(K5:K8)</f>
-        <v>13166.6666666667</v>
+        <v>27333.3333333333</v>
       </c>
       <c r="L9" s="172" t="n">
         <f aca="false">SUM(L5:L8)</f>
-        <v>15366.6666666667</v>
+        <v>29533.3333333333</v>
       </c>
       <c r="M9" s="168" t="n">
         <f aca="false">SUM(M5:M8)</f>
-        <v>14466.6666666667</v>
+        <v>28633.3333333333</v>
       </c>
       <c r="N9" s="168" t="n">
         <f aca="false">SUM(N5:N8)</f>
-        <v>11666.6666666667</v>
+        <v>25833.3333333333</v>
       </c>
       <c r="O9" s="173"/>
     </row>
@@ -23448,55 +23448,55 @@
       </c>
       <c r="B19" s="168" t="n">
         <f aca="false">B9+B11-B17</f>
-        <v>153539.333333334</v>
+        <v>323539.333333333</v>
       </c>
       <c r="C19" s="168" t="n">
         <f aca="false">C9+C11-C17</f>
-        <v>12781.6666666667</v>
+        <v>26948.3333333333</v>
       </c>
       <c r="D19" s="168" t="n">
         <f aca="false">D9+D11-D17</f>
-        <v>12297.6666666667</v>
+        <v>26464.3333333333</v>
       </c>
       <c r="E19" s="168" t="n">
         <f aca="false">E9+E11-E17</f>
-        <v>9521.6666666667</v>
+        <v>23688.3333333333</v>
       </c>
       <c r="F19" s="172" t="n">
         <f aca="false">F9+F11-F17</f>
-        <v>12997.6666666667</v>
+        <v>27164.3333333333</v>
       </c>
       <c r="G19" s="168" t="n">
         <f aca="false">G9+G11-G17</f>
-        <v>15025</v>
+        <v>29191.6666666666</v>
       </c>
       <c r="H19" s="168" t="n">
         <f aca="false">H9+H11-H17</f>
-        <v>13477.6666666667</v>
+        <v>27644.3333333333</v>
       </c>
       <c r="I19" s="172" t="n">
         <f aca="false">I9+I11-I17</f>
-        <v>14701.6666666667</v>
+        <v>28868.3333333333</v>
       </c>
       <c r="J19" s="168" t="n">
         <f aca="false">J9+J11-J17</f>
-        <v>11177.6666666667</v>
+        <v>25344.3333333333</v>
       </c>
       <c r="K19" s="168" t="n">
         <f aca="false">K9+K11-K17</f>
-        <v>12401.6666666667</v>
+        <v>26568.3333333333</v>
       </c>
       <c r="L19" s="172" t="n">
         <f aca="false">L9+L11-L17</f>
-        <v>14517.6666666667</v>
+        <v>28684.3333333333</v>
       </c>
       <c r="M19" s="168" t="n">
         <f aca="false">M9+M11-M17</f>
-        <v>13521.6666666667</v>
+        <v>27688.3333333333</v>
       </c>
       <c r="N19" s="168" t="n">
         <f aca="false">N9+N11-N17</f>
-        <v>11117.6666666667</v>
+        <v>25284.3333333333</v>
       </c>
       <c r="O19" s="173"/>
     </row>
@@ -24412,55 +24412,55 @@
       </c>
       <c r="B37" s="168" t="n">
         <f aca="false">B19-B35</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="C37" s="168" t="n">
         <f aca="false">C19-C35</f>
-        <v>11532.4166666667</v>
+        <v>25699.0833333333</v>
       </c>
       <c r="D37" s="168" t="n">
         <f aca="false">D19-D35</f>
-        <v>10401.6666666667</v>
+        <v>24568.3333333333</v>
       </c>
       <c r="E37" s="168" t="n">
         <f aca="false">E19-E35</f>
-        <v>7204.6666666667</v>
+        <v>21371.3333333333</v>
       </c>
       <c r="F37" s="172" t="n">
         <f aca="false">F19-F35</f>
-        <v>11202.4166666667</v>
+        <v>25369.0833333333</v>
       </c>
       <c r="G37" s="168" t="n">
         <f aca="false">G19-G35</f>
-        <v>12807.75</v>
+        <v>26974.4166666666</v>
       </c>
       <c r="H37" s="168" t="n">
         <f aca="false">H19-H35</f>
-        <v>10554.6666666667</v>
+        <v>24721.3333333333</v>
       </c>
       <c r="I37" s="172" t="n">
         <f aca="false">I19-I35</f>
-        <v>10351.9166666667</v>
+        <v>24518.5833333333</v>
       </c>
       <c r="J37" s="168" t="n">
         <f aca="false">J19-J35</f>
-        <v>9878.6666666667</v>
+        <v>24045.3333333333</v>
       </c>
       <c r="K37" s="168" t="n">
         <f aca="false">K19-K35</f>
-        <v>4887.1666666667</v>
+        <v>19053.8333333333</v>
       </c>
       <c r="L37" s="172" t="n">
         <f aca="false">L19-L35</f>
-        <v>12710.4166666667</v>
+        <v>26877.0833333333</v>
       </c>
       <c r="M37" s="168" t="n">
         <f aca="false">M19-M35</f>
-        <v>11763.1666666667</v>
+        <v>25929.8333333333</v>
       </c>
       <c r="N37" s="168" t="n">
         <f aca="false">N19-N35</f>
-        <v>9574.1666666667</v>
+        <v>23740.8333333333</v>
       </c>
       <c r="O37" s="162"/>
     </row>
@@ -24528,55 +24528,55 @@
       </c>
       <c r="B39" s="168" t="n">
         <f aca="false">B37+B38</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="C39" s="168" t="n">
         <f aca="false">C37+C38</f>
-        <v>11532.4166666667</v>
+        <v>25699.0833333333</v>
       </c>
       <c r="D39" s="168" t="n">
         <f aca="false">D37+D38</f>
-        <v>10401.6666666667</v>
+        <v>24568.3333333333</v>
       </c>
       <c r="E39" s="168" t="n">
         <f aca="false">E37+E38</f>
-        <v>7204.6666666667</v>
+        <v>21371.3333333333</v>
       </c>
       <c r="F39" s="172" t="n">
         <f aca="false">F37+F38</f>
-        <v>11202.4166666667</v>
+        <v>25369.0833333333</v>
       </c>
       <c r="G39" s="168" t="n">
         <f aca="false">G37+G38</f>
-        <v>12807.75</v>
+        <v>26974.4166666666</v>
       </c>
       <c r="H39" s="168" t="n">
         <f aca="false">H37+H38</f>
-        <v>10554.6666666667</v>
+        <v>24721.3333333333</v>
       </c>
       <c r="I39" s="172" t="n">
         <f aca="false">I37+I38</f>
-        <v>10351.9166666667</v>
+        <v>24518.5833333333</v>
       </c>
       <c r="J39" s="168" t="n">
         <f aca="false">J37+J38</f>
-        <v>9878.6666666667</v>
+        <v>24045.3333333333</v>
       </c>
       <c r="K39" s="168" t="n">
         <f aca="false">K37+K38</f>
-        <v>4887.1666666667</v>
+        <v>19053.8333333333</v>
       </c>
       <c r="L39" s="172" t="n">
         <f aca="false">L37+L38</f>
-        <v>12710.4166666667</v>
+        <v>26877.0833333333</v>
       </c>
       <c r="M39" s="168" t="n">
         <f aca="false">M37+M38</f>
-        <v>11763.1666666667</v>
+        <v>25929.8333333333</v>
       </c>
       <c r="N39" s="168" t="n">
         <f aca="false">N37+N38</f>
-        <v>9574.1666666667</v>
+        <v>23740.8333333333</v>
       </c>
       <c r="O39" s="162"/>
     </row>
@@ -24738,55 +24738,55 @@
       </c>
       <c r="B44" s="175" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>40293.4550000002</v>
+        <v>111693.455</v>
       </c>
       <c r="C44" s="175" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="D44" s="175" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="E44" s="175" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="F44" s="175" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="G44" s="175" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="H44" s="175" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="I44" s="175" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="J44" s="175" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="K44" s="175" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="L44" s="175" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="M44" s="175" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="N44" s="175" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3357.78791666668</v>
+        <v>9307.78791666665</v>
       </c>
       <c r="O44" s="162"/>
     </row>
@@ -24796,55 +24796,55 @@
       </c>
       <c r="B45" s="187" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>82575.6283333336</v>
+        <v>181175.628333333</v>
       </c>
       <c r="C45" s="188" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>8174.62875000002</v>
+        <v>16391.2954166666</v>
       </c>
       <c r="D45" s="189" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>7043.87875000002</v>
+        <v>15260.5454166666</v>
       </c>
       <c r="E45" s="189" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>3846.87875000002</v>
+        <v>12063.5454166666</v>
       </c>
       <c r="F45" s="189" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>7844.62875000002</v>
+        <v>16061.2954166666</v>
       </c>
       <c r="G45" s="189" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>9449.96208333335</v>
+        <v>17666.62875</v>
       </c>
       <c r="H45" s="189" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>7196.87875000002</v>
+        <v>15413.5454166666</v>
       </c>
       <c r="I45" s="189" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>6994.12875000002</v>
+        <v>15210.7954166666</v>
       </c>
       <c r="J45" s="189" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>6520.87875000002</v>
+        <v>14737.5454166666</v>
       </c>
       <c r="K45" s="189" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>1529.37875000002</v>
+        <v>9746.04541666665</v>
       </c>
       <c r="L45" s="189" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9352.62875000002</v>
+        <v>17569.2954166666</v>
       </c>
       <c r="M45" s="189" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>8405.37875000002</v>
+        <v>16622.0454166666</v>
       </c>
       <c r="N45" s="189" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>6216.37875000002</v>
+        <v>14433.0454166666</v>
       </c>
       <c r="O45" s="162"/>
     </row>
@@ -25033,23 +25033,23 @@
       </c>
       <c r="C5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
-        <v>41400.0000000001</v>
+        <v>83899.9999999999</v>
       </c>
       <c r="D5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F5:H7)</f>
-        <v>40500.0000000001</v>
+        <v>82999.9999999999</v>
       </c>
       <c r="E5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I5:K7)</f>
-        <v>43200.0000000001</v>
+        <v>85699.9999999999</v>
       </c>
       <c r="F5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L5:N7)</f>
-        <v>40400.0000000001</v>
+        <v>82899.9999999999</v>
       </c>
       <c r="G5" s="198" t="n">
         <f aca="false">SUM(C5:F5)</f>
-        <v>165500</v>
+        <v>335500</v>
       </c>
       <c r="H5" s="193"/>
       <c r="I5" s="193"/>
@@ -26172,7 +26172,7 @@
       <c r="D5" s="220"/>
       <c r="E5" s="221" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="F5" s="212"/>
       <c r="G5" s="216"/>
@@ -26205,7 +26205,7 @@
       <c r="D7" s="220"/>
       <c r="E7" s="221" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>110299.083333334</v>
+        <v>280299.083333333</v>
       </c>
       <c r="F7" s="212"/>
       <c r="G7" s="216"/>
@@ -26248,7 +26248,7 @@
       </c>
       <c r="E9" s="211" t="n">
         <f aca="false">IF((E7&gt;C9),((E7-C9)*D9),0)</f>
-        <v>29039.2333333335</v>
+        <v>97039.2333333332</v>
       </c>
       <c r="F9" s="212"/>
       <c r="G9" s="216"/>
@@ -26263,7 +26263,7 @@
       <c r="D10" s="228"/>
       <c r="E10" s="229" t="n">
         <f aca="false">SUM(E8:E9)</f>
-        <v>36579.4333333335</v>
+        <v>104579.433333333</v>
       </c>
       <c r="F10" s="212"/>
       <c r="G10" s="216"/>
@@ -26349,7 +26349,7 @@
       </c>
       <c r="E16" s="238" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1451.98166666667</v>
+        <v>4851.98166666666</v>
       </c>
       <c r="F16" s="212"/>
       <c r="G16" s="232"/>
@@ -26374,7 +26374,7 @@
       <c r="D18" s="235"/>
       <c r="E18" s="229" t="n">
         <f aca="false">SUM(E10:E17)</f>
-        <v>40293.4150000002</v>
+        <v>111693.415</v>
       </c>
       <c r="F18" s="212"/>
       <c r="G18" s="216"/>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="E25" s="238" t="n">
         <f aca="false">E18</f>
-        <v>40293.4150000002</v>
+        <v>111693.415</v>
       </c>
       <c r="F25" s="212"/>
       <c r="G25" s="216"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="E26" s="221" t="n">
         <f aca="false">E25/2</f>
-        <v>20146.7075000001</v>
+        <v>55846.7074999999</v>
       </c>
       <c r="F26" s="212"/>
       <c r="G26" s="216"/>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="E27" s="221" t="n">
         <f aca="false">E25/2</f>
-        <v>20146.7075000001</v>
+        <v>55846.7074999999</v>
       </c>
       <c r="F27" s="212"/>
       <c r="G27" s="216"/>
@@ -27554,7 +27554,7 @@
       <c r="I8" s="175"/>
       <c r="J8" s="175" t="n">
         <f aca="false">[2]Apr!$P$1</f>
-        <v>11166.6666666667</v>
+        <v>25333.3333333333</v>
       </c>
       <c r="K8" s="175"/>
       <c r="L8" s="177" t="n">
@@ -27668,7 +27668,7 @@
       <c r="I10" s="175"/>
       <c r="J10" s="175" t="n">
         <f aca="false">[2]May!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K10" s="175"/>
       <c r="L10" s="177" t="n">
@@ -27784,7 +27784,7 @@
       <c r="I12" s="175"/>
       <c r="J12" s="175" t="n">
         <f aca="false">[2]Jun!$P$1</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="K12" s="175"/>
       <c r="L12" s="177" t="n">
@@ -27898,7 +27898,7 @@
       <c r="I14" s="175"/>
       <c r="J14" s="175" t="n">
         <f aca="false">[2]Jul!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K14" s="175"/>
       <c r="L14" s="177" t="n">
@@ -28014,7 +28014,7 @@
       <c r="I16" s="175"/>
       <c r="J16" s="175" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="K16" s="175"/>
       <c r="L16" s="177" t="n">
@@ -28128,7 +28128,7 @@
       <c r="I18" s="175"/>
       <c r="J18" s="175" t="n">
         <f aca="false">[2]Sep!$P$1</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="K18" s="175"/>
       <c r="L18" s="177" t="n">
@@ -28244,7 +28244,7 @@
       <c r="I20" s="175"/>
       <c r="J20" s="175" t="n">
         <f aca="false">[2]Oct!$P$1</f>
-        <v>12966.6666666667</v>
+        <v>27133.3333333333</v>
       </c>
       <c r="K20" s="175"/>
       <c r="L20" s="177" t="n">
@@ -28358,7 +28358,7 @@
       <c r="I22" s="175"/>
       <c r="J22" s="175" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K22" s="175"/>
       <c r="L22" s="177" t="n">
@@ -28474,7 +28474,7 @@
       <c r="I24" s="175"/>
       <c r="J24" s="175" t="n">
         <f aca="false">[2]Dec!$P$1</f>
-        <v>12366.6666666667</v>
+        <v>26533.3333333333</v>
       </c>
       <c r="K24" s="175"/>
       <c r="L24" s="177" t="n">
@@ -28588,7 +28588,7 @@
       <c r="I26" s="175"/>
       <c r="J26" s="175" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>11466.6666666667</v>
+        <v>25633.3333333333</v>
       </c>
       <c r="K26" s="175"/>
       <c r="L26" s="177" t="n">
@@ -28702,7 +28702,7 @@
       <c r="I28" s="175"/>
       <c r="J28" s="175" t="n">
         <f aca="false">[2]Feb!$P$1</f>
-        <v>12166.6666666667</v>
+        <v>26333.3333333333</v>
       </c>
       <c r="K28" s="175"/>
       <c r="L28" s="177" t="n">
@@ -28818,7 +28818,7 @@
       <c r="I30" s="175"/>
       <c r="J30" s="175" t="n">
         <f aca="false">[2]Mar!$P$1</f>
-        <v>10866.6666666667</v>
+        <v>25033.3333333333</v>
       </c>
       <c r="K30" s="175"/>
       <c r="L30" s="177" t="n">
@@ -29097,55 +29097,55 @@
       </c>
       <c r="C5" s="168" t="n">
         <f aca="false">SUM(D5:O5)</f>
-        <v>169200</v>
+        <v>339200</v>
       </c>
       <c r="D5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C9</f>
-        <v>13666.6666666667</v>
+        <v>27833.3333333333</v>
       </c>
       <c r="E5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D9</f>
-        <v>13266.6666666667</v>
+        <v>27433.3333333333</v>
       </c>
       <c r="F5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E9</f>
-        <v>15166.6666666667</v>
+        <v>29333.3333333333</v>
       </c>
       <c r="G5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F9</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="H5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G9</f>
-        <v>13766.6666666667</v>
+        <v>27933.3333333333</v>
       </c>
       <c r="I5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H9</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="J5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I9</f>
-        <v>15466.6666666667</v>
+        <v>29633.3333333333</v>
       </c>
       <c r="K5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J9</f>
-        <v>15266.6666666667</v>
+        <v>29433.3333333333</v>
       </c>
       <c r="L5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K9</f>
-        <v>13166.6666666667</v>
+        <v>27333.3333333333</v>
       </c>
       <c r="M5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L9</f>
-        <v>15366.6666666667</v>
+        <v>29533.3333333333</v>
       </c>
       <c r="N5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M9</f>
-        <v>14466.6666666667</v>
+        <v>28633.3333333333</v>
       </c>
       <c r="O5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N9</f>
-        <v>11666.6666666667</v>
+        <v>25833.3333333333</v>
       </c>
       <c r="P5" s="176"/>
     </row>
@@ -29328,55 +29328,55 @@
       </c>
       <c r="C11" s="168" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>153539.333333334</v>
+        <v>323539.333333333</v>
       </c>
       <c r="D11" s="168" t="n">
         <f aca="false">D5+D7-D9</f>
-        <v>12781.6666666667</v>
+        <v>26948.3333333333</v>
       </c>
       <c r="E11" s="168" t="n">
         <f aca="false">E5+E7-E9</f>
-        <v>12297.6666666667</v>
+        <v>26464.3333333333</v>
       </c>
       <c r="F11" s="168" t="n">
         <f aca="false">F5+F7-F9</f>
-        <v>9521.6666666667</v>
+        <v>23688.3333333333</v>
       </c>
       <c r="G11" s="168" t="n">
         <f aca="false">G5+G7-G9</f>
-        <v>12997.6666666667</v>
+        <v>27164.3333333333</v>
       </c>
       <c r="H11" s="168" t="n">
         <f aca="false">H5+H7-H9</f>
-        <v>15025</v>
+        <v>29191.6666666666</v>
       </c>
       <c r="I11" s="168" t="n">
         <f aca="false">I5+I7-I9</f>
-        <v>13477.6666666667</v>
+        <v>27644.3333333333</v>
       </c>
       <c r="J11" s="168" t="n">
         <f aca="false">J5+J7-J9</f>
-        <v>14701.6666666667</v>
+        <v>28868.3333333333</v>
       </c>
       <c r="K11" s="168" t="n">
         <f aca="false">K5+K7-K9</f>
-        <v>11177.6666666667</v>
+        <v>25344.3333333333</v>
       </c>
       <c r="L11" s="168" t="n">
         <f aca="false">L5+L7-L9</f>
-        <v>12401.6666666667</v>
+        <v>26568.3333333333</v>
       </c>
       <c r="M11" s="168" t="n">
         <f aca="false">M5+M7-M9</f>
-        <v>14517.6666666667</v>
+        <v>28684.3333333333</v>
       </c>
       <c r="N11" s="168" t="n">
         <f aca="false">N5+N7-N9</f>
-        <v>13521.6666666667</v>
+        <v>27688.3333333333</v>
       </c>
       <c r="O11" s="168" t="n">
         <f aca="false">O5+O7-O9</f>
-        <v>11117.6666666667</v>
+        <v>25284.3333333333</v>
       </c>
       <c r="P11" s="176"/>
     </row>
@@ -29482,55 +29482,55 @@
       </c>
       <c r="C15" s="168" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="D15" s="168" t="n">
         <f aca="false">D11-D13</f>
-        <v>11532.4166666667</v>
+        <v>25699.0833333333</v>
       </c>
       <c r="E15" s="168" t="n">
         <f aca="false">E11-E13</f>
-        <v>10401.6666666667</v>
+        <v>24568.3333333333</v>
       </c>
       <c r="F15" s="168" t="n">
         <f aca="false">F11-F13</f>
-        <v>7204.6666666667</v>
+        <v>21371.3333333333</v>
       </c>
       <c r="G15" s="168" t="n">
         <f aca="false">G11-G13</f>
-        <v>11202.4166666667</v>
+        <v>25369.0833333333</v>
       </c>
       <c r="H15" s="168" t="n">
         <f aca="false">H11-H13</f>
-        <v>12807.75</v>
+        <v>26974.4166666666</v>
       </c>
       <c r="I15" s="168" t="n">
         <f aca="false">I11-I13</f>
-        <v>10554.6666666667</v>
+        <v>24721.3333333333</v>
       </c>
       <c r="J15" s="168" t="n">
         <f aca="false">J11-J13</f>
-        <v>10351.9166666667</v>
+        <v>24518.5833333333</v>
       </c>
       <c r="K15" s="168" t="n">
         <f aca="false">K11-K13</f>
-        <v>9878.6666666667</v>
+        <v>24045.3333333333</v>
       </c>
       <c r="L15" s="168" t="n">
         <f aca="false">L11-L13</f>
-        <v>4887.1666666667</v>
+        <v>19053.8333333333</v>
       </c>
       <c r="M15" s="168" t="n">
         <f aca="false">M11-M13</f>
-        <v>12710.4166666667</v>
+        <v>26877.0833333333</v>
       </c>
       <c r="N15" s="168" t="n">
         <f aca="false">N11-N13</f>
-        <v>11763.1666666667</v>
+        <v>25929.8333333333</v>
       </c>
       <c r="O15" s="168" t="n">
         <f aca="false">O11-O13</f>
-        <v>9574.1666666667</v>
+        <v>23740.8333333333</v>
       </c>
       <c r="P15" s="156"/>
     </row>
@@ -29600,55 +29600,55 @@
       </c>
       <c r="C17" s="168" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="D17" s="168" t="n">
         <f aca="false">D15+D16</f>
-        <v>11532.4166666667</v>
+        <v>25699.0833333333</v>
       </c>
       <c r="E17" s="168" t="n">
         <f aca="false">E15+E16</f>
-        <v>10401.6666666667</v>
+        <v>24568.3333333333</v>
       </c>
       <c r="F17" s="168" t="n">
         <f aca="false">F15+F16</f>
-        <v>7204.6666666667</v>
+        <v>21371.3333333333</v>
       </c>
       <c r="G17" s="168" t="n">
         <f aca="false">G15+G16</f>
-        <v>11202.4166666667</v>
+        <v>25369.0833333333</v>
       </c>
       <c r="H17" s="168" t="n">
         <f aca="false">H15+H16</f>
-        <v>12807.75</v>
+        <v>26974.4166666666</v>
       </c>
       <c r="I17" s="168" t="n">
         <f aca="false">I15+I16</f>
-        <v>10554.6666666667</v>
+        <v>24721.3333333333</v>
       </c>
       <c r="J17" s="168" t="n">
         <f aca="false">J15+J16</f>
-        <v>10351.9166666667</v>
+        <v>24518.5833333333</v>
       </c>
       <c r="K17" s="168" t="n">
         <f aca="false">K15+K16</f>
-        <v>9878.6666666667</v>
+        <v>24045.3333333333</v>
       </c>
       <c r="L17" s="168" t="n">
         <f aca="false">L15+L16</f>
-        <v>4887.1666666667</v>
+        <v>19053.8333333333</v>
       </c>
       <c r="M17" s="168" t="n">
         <f aca="false">M15+M16</f>
-        <v>12710.4166666667</v>
+        <v>26877.0833333333</v>
       </c>
       <c r="N17" s="168" t="n">
         <f aca="false">N15+N16</f>
-        <v>11763.1666666667</v>
+        <v>25929.8333333333</v>
       </c>
       <c r="O17" s="168" t="n">
         <f aca="false">O15+O16</f>
-        <v>9574.1666666667</v>
+        <v>23740.8333333333</v>
       </c>
       <c r="P17" s="156"/>
     </row>
@@ -29813,55 +29813,55 @@
       </c>
       <c r="C22" s="168" t="n">
         <f aca="false">SUM(D22:O22)</f>
-        <v>169200</v>
+        <v>339200</v>
       </c>
       <c r="D22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D5,C5/C21),0)</f>
-        <v>13666.6666666667</v>
+        <v>27833.3333333333</v>
       </c>
       <c r="E22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E5,C5/C21),0)</f>
-        <v>13266.6666666667</v>
+        <v>27433.3333333333</v>
       </c>
       <c r="F22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F5,C5/C21),0)</f>
-        <v>15166.6666666667</v>
+        <v>29333.3333333333</v>
       </c>
       <c r="G22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G5,C5/C21),0)</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="H22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H5,C5/C21),0)</f>
-        <v>13766.6666666667</v>
+        <v>27933.3333333333</v>
       </c>
       <c r="I22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I5,C5/C21),0)</f>
-        <v>13966.6666666667</v>
+        <v>28133.3333333333</v>
       </c>
       <c r="J22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J5,C5/C21),0)</f>
-        <v>15466.6666666667</v>
+        <v>29633.3333333333</v>
       </c>
       <c r="K22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K5,C5/C21),0)</f>
-        <v>15266.6666666667</v>
+        <v>29433.3333333333</v>
       </c>
       <c r="L22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L5,C5/C21),0)</f>
-        <v>13166.6666666667</v>
+        <v>27333.3333333333</v>
       </c>
       <c r="M22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M5,C5/C21),0)</f>
-        <v>15366.6666666667</v>
+        <v>29533.3333333333</v>
       </c>
       <c r="N22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N5,C5/C21),0)</f>
-        <v>14466.6666666667</v>
+        <v>28633.3333333333</v>
       </c>
       <c r="O22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O5,C5/C21),0)</f>
-        <v>11666.6666666667</v>
+        <v>25833.3333333333</v>
       </c>
       <c r="P22" s="176"/>
     </row>
@@ -30044,55 +30044,55 @@
       </c>
       <c r="C28" s="168" t="n">
         <f aca="false">SUM(D28:O28)</f>
-        <v>153539.333333334</v>
+        <v>323539.333333333</v>
       </c>
       <c r="D28" s="168" t="n">
         <f aca="false">D22+D24-D26</f>
-        <v>12781.6666666667</v>
+        <v>26948.3333333333</v>
       </c>
       <c r="E28" s="168" t="n">
         <f aca="false">E22+E24-E26</f>
-        <v>12297.6666666667</v>
+        <v>26464.3333333333</v>
       </c>
       <c r="F28" s="168" t="n">
         <f aca="false">F22+F24-F26</f>
-        <v>9521.6666666667</v>
+        <v>23688.3333333333</v>
       </c>
       <c r="G28" s="168" t="n">
         <f aca="false">G22+G24-G26</f>
-        <v>12997.6666666667</v>
+        <v>27164.3333333333</v>
       </c>
       <c r="H28" s="168" t="n">
         <f aca="false">H22+H24-H26</f>
-        <v>15025</v>
+        <v>29191.6666666666</v>
       </c>
       <c r="I28" s="168" t="n">
         <f aca="false">I22+I24-I26</f>
-        <v>13477.6666666667</v>
+        <v>27644.3333333333</v>
       </c>
       <c r="J28" s="168" t="n">
         <f aca="false">J22+J24-J26</f>
-        <v>14701.6666666667</v>
+        <v>28868.3333333333</v>
       </c>
       <c r="K28" s="168" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>11177.6666666667</v>
+        <v>25344.3333333333</v>
       </c>
       <c r="L28" s="168" t="n">
         <f aca="false">L22+L24-L26</f>
-        <v>12401.6666666667</v>
+        <v>26568.3333333333</v>
       </c>
       <c r="M28" s="168" t="n">
         <f aca="false">M22+M24-M26</f>
-        <v>14517.6666666667</v>
+        <v>28684.3333333333</v>
       </c>
       <c r="N28" s="168" t="n">
         <f aca="false">N22+N24-N26</f>
-        <v>13521.6666666667</v>
+        <v>27688.3333333333</v>
       </c>
       <c r="O28" s="168" t="n">
         <f aca="false">O22+O24-O26</f>
-        <v>11117.6666666667</v>
+        <v>25284.3333333333</v>
       </c>
       <c r="P28" s="176"/>
     </row>
@@ -30198,55 +30198,55 @@
       </c>
       <c r="C32" s="168" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="D32" s="168" t="n">
         <f aca="false">D28-D30</f>
-        <v>11532.4166666667</v>
+        <v>25699.0833333333</v>
       </c>
       <c r="E32" s="168" t="n">
         <f aca="false">E28-E30</f>
-        <v>10401.6666666667</v>
+        <v>24568.3333333333</v>
       </c>
       <c r="F32" s="168" t="n">
         <f aca="false">F28-F30</f>
-        <v>7204.6666666667</v>
+        <v>21371.3333333333</v>
       </c>
       <c r="G32" s="168" t="n">
         <f aca="false">G28-G30</f>
-        <v>11202.4166666667</v>
+        <v>25369.0833333333</v>
       </c>
       <c r="H32" s="168" t="n">
         <f aca="false">H28-H30</f>
-        <v>12807.75</v>
+        <v>26974.4166666666</v>
       </c>
       <c r="I32" s="168" t="n">
         <f aca="false">I28-I30</f>
-        <v>10554.6666666667</v>
+        <v>24721.3333333333</v>
       </c>
       <c r="J32" s="168" t="n">
         <f aca="false">J28-J30</f>
-        <v>10351.9166666667</v>
+        <v>24518.5833333333</v>
       </c>
       <c r="K32" s="168" t="n">
         <f aca="false">K28-K30</f>
-        <v>9878.6666666667</v>
+        <v>24045.3333333333</v>
       </c>
       <c r="L32" s="168" t="n">
         <f aca="false">L28-L30</f>
-        <v>4887.1666666667</v>
+        <v>19053.8333333333</v>
       </c>
       <c r="M32" s="168" t="n">
         <f aca="false">M28-M30</f>
-        <v>12710.4166666667</v>
+        <v>26877.0833333333</v>
       </c>
       <c r="N32" s="168" t="n">
         <f aca="false">N28-N30</f>
-        <v>11763.1666666667</v>
+        <v>25929.8333333333</v>
       </c>
       <c r="O32" s="168" t="n">
         <f aca="false">O28-O30</f>
-        <v>9574.1666666667</v>
+        <v>23740.8333333333</v>
       </c>
       <c r="P32" s="156"/>
     </row>
@@ -30316,55 +30316,55 @@
       </c>
       <c r="C34" s="168" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="D34" s="168" t="n">
         <f aca="false">D32+D33</f>
-        <v>11532.4166666667</v>
+        <v>25699.0833333333</v>
       </c>
       <c r="E34" s="168" t="n">
         <f aca="false">E32+E33</f>
-        <v>10401.6666666667</v>
+        <v>24568.3333333333</v>
       </c>
       <c r="F34" s="168" t="n">
         <f aca="false">F32+F33</f>
-        <v>7204.6666666667</v>
+        <v>21371.3333333333</v>
       </c>
       <c r="G34" s="168" t="n">
         <f aca="false">G32+G33</f>
-        <v>11202.4166666667</v>
+        <v>25369.0833333333</v>
       </c>
       <c r="H34" s="168" t="n">
         <f aca="false">H32+H33</f>
-        <v>12807.75</v>
+        <v>26974.4166666666</v>
       </c>
       <c r="I34" s="168" t="n">
         <f aca="false">I32+I33</f>
-        <v>10554.6666666667</v>
+        <v>24721.3333333333</v>
       </c>
       <c r="J34" s="168" t="n">
         <f aca="false">J32+J33</f>
-        <v>10351.9166666667</v>
+        <v>24518.5833333333</v>
       </c>
       <c r="K34" s="168" t="n">
         <f aca="false">K32+K33</f>
-        <v>9878.6666666667</v>
+        <v>24045.3333333333</v>
       </c>
       <c r="L34" s="168" t="n">
         <f aca="false">L32+L33</f>
-        <v>4887.1666666667</v>
+        <v>19053.8333333333</v>
       </c>
       <c r="M34" s="168" t="n">
         <f aca="false">M32+M33</f>
-        <v>12710.4166666667</v>
+        <v>26877.0833333333</v>
       </c>
       <c r="N34" s="168" t="n">
         <f aca="false">N32+N33</f>
-        <v>11763.1666666667</v>
+        <v>25929.8333333333</v>
       </c>
       <c r="O34" s="168" t="n">
         <f aca="false">O32+O33</f>
-        <v>9574.1666666667</v>
+        <v>23740.8333333333</v>
       </c>
       <c r="P34" s="156"/>
     </row>
@@ -30459,7 +30459,7 @@
       </c>
       <c r="C39" s="337" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>122869.083333334</v>
+        <v>292869.083333333</v>
       </c>
       <c r="D39" s="156"/>
       <c r="E39" s="156"/>
@@ -30505,7 +30505,7 @@
       </c>
       <c r="C41" s="337" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>110299.083333334</v>
+        <v>280299.083333333</v>
       </c>
       <c r="D41" s="156"/>
       <c r="E41" s="156"/>
@@ -30551,7 +30551,7 @@
       </c>
       <c r="C43" s="337" t="n">
         <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>29039.2333333335</v>
+        <v>97039.2333333332</v>
       </c>
       <c r="D43" s="156"/>
       <c r="E43" s="156"/>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="C44" s="337" t="n">
         <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>3714.02166666667</v>
+        <v>7114.02166666666</v>
       </c>
       <c r="D44" s="156"/>
       <c r="E44" s="156"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="C46" s="339" t="n">
         <f aca="false">C42+C43+C44</f>
-        <v>40293.4550000002</v>
+        <v>111693.455</v>
       </c>
       <c r="D46" s="156"/>
       <c r="E46" s="156"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4829,7 +4829,7 @@
       <sheetData sheetId="1">
         <row r="1">
           <cell r="P1">
-            <v>25333.3333333333</v>
+            <v>11166.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -4856,7 +4856,7 @@
       <sheetData sheetId="2">
         <row r="1">
           <cell r="P1">
-            <v>25633.3333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4883,7 +4883,7 @@
       <sheetData sheetId="3">
         <row r="1">
           <cell r="P1">
-            <v>26533.3333333333</v>
+            <v>12366.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4910,7 +4910,7 @@
       <sheetData sheetId="4">
         <row r="1">
           <cell r="P1">
-            <v>25633.3333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -4937,7 +4937,7 @@
       <sheetData sheetId="5">
         <row r="1">
           <cell r="P1">
-            <v>27133.3333333333</v>
+            <v>12966.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4964,7 +4964,7 @@
       <sheetData sheetId="6">
         <row r="1">
           <cell r="P1">
-            <v>25033.3333333333</v>
+            <v>10866.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -4991,7 +4991,7 @@
       <sheetData sheetId="7">
         <row r="1">
           <cell r="P1">
-            <v>27133.3333333333</v>
+            <v>12966.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -5018,7 +5018,7 @@
       <sheetData sheetId="8">
         <row r="1">
           <cell r="P1">
-            <v>25633.3333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -5045,7 +5045,7 @@
       <sheetData sheetId="9">
         <row r="1">
           <cell r="P1">
-            <v>26533.3333333333</v>
+            <v>12366.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -5072,7 +5072,7 @@
       <sheetData sheetId="10">
         <row r="1">
           <cell r="P1">
-            <v>25633.3333333333</v>
+            <v>11466.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>1800</v>
@@ -5099,7 +5099,7 @@
       <sheetData sheetId="11">
         <row r="1">
           <cell r="P1">
-            <v>26333.3333333333</v>
+            <v>12166.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -5126,7 +5126,7 @@
       <sheetData sheetId="12">
         <row r="1">
           <cell r="P1">
-            <v>25033.3333333333</v>
+            <v>10866.6666666667</v>
           </cell>
           <cell r="Q1">
             <v>800</v>
@@ -10078,7 +10078,7 @@
       </c>
       <c r="D38" s="96" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B9</f>
-        <v>339200</v>
+        <v>169200</v>
       </c>
       <c r="E38" s="96"/>
       <c r="F38" s="96"/>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="D71" s="96" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>290785.75</v>
+        <v>120785.75</v>
       </c>
       <c r="E71" s="96"/>
       <c r="F71" s="96"/>
@@ -11951,7 +11951,7 @@
       </c>
       <c r="D99" s="96" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>290785.75</v>
+        <v>120785.75</v>
       </c>
       <c r="E99" s="96"/>
       <c r="F99" s="96"/>
@@ -12164,7 +12164,7 @@
       </c>
       <c r="D106" s="96" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="E106" s="96"/>
       <c r="F106" s="96"/>
@@ -14424,7 +14424,7 @@
       </c>
       <c r="D55" s="96" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B9</f>
-        <v>339200</v>
+        <v>169200</v>
       </c>
       <c r="E55" s="96"/>
       <c r="F55" s="96"/>
@@ -16709,7 +16709,7 @@
       </c>
       <c r="D129" s="96" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>290785.75</v>
+        <v>120785.75</v>
       </c>
       <c r="E129" s="96"/>
       <c r="F129" s="96"/>
@@ -18117,7 +18117,7 @@
       </c>
       <c r="O174" s="96" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>290785.75</v>
+        <v>120785.75</v>
       </c>
       <c r="P174" s="96"/>
       <c r="Q174" s="96"/>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="O194" s="96" t="n">
         <f aca="false">O174</f>
-        <v>290785.75</v>
+        <v>120785.75</v>
       </c>
       <c r="P194" s="96"/>
       <c r="Q194" s="96"/>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="O210" s="96" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="P210" s="96"/>
       <c r="Q210" s="96"/>
@@ -22798,55 +22798,55 @@
       </c>
       <c r="B5" s="168" t="n">
         <f aca="false">SUM(C5:N5)</f>
-        <v>311600</v>
+        <v>141600</v>
       </c>
       <c r="C5" s="169" t="n">
         <f aca="false">[2]Apr!$P$1</f>
-        <v>25333.3333333333</v>
+        <v>11166.6666666667</v>
       </c>
       <c r="D5" s="169" t="n">
         <f aca="false">[2]May!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="E5" s="170" t="n">
         <f aca="false">[2]Jun!$P$1</f>
-        <v>26533.3333333333</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="F5" s="169" t="n">
         <f aca="false">[2]Jul!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="G5" s="169" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>27133.3333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="H5" s="170" t="n">
         <f aca="false">[2]Sep!$P$1</f>
-        <v>25033.3333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="I5" s="169" t="n">
         <f aca="false">[2]Oct!$P$1</f>
-        <v>27133.3333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="J5" s="169" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K5" s="170" t="n">
         <f aca="false">[2]Dec!$P$1</f>
-        <v>26533.3333333333</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="L5" s="169" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="M5" s="169" t="n">
         <f aca="false">[2]Feb!$P$1</f>
-        <v>26333.3333333333</v>
+        <v>12166.6666666667</v>
       </c>
       <c r="N5" s="169" t="n">
         <f aca="false">[2]Mar!$P$1</f>
-        <v>25033.3333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="O5" s="162"/>
     </row>
@@ -23030,55 +23030,55 @@
       </c>
       <c r="B9" s="168" t="n">
         <f aca="false">SUM(B5:B8)</f>
-        <v>339200</v>
+        <v>169200</v>
       </c>
       <c r="C9" s="168" t="n">
         <f aca="false">SUM(C5:C8)</f>
-        <v>27833.3333333333</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="D9" s="168" t="n">
         <f aca="false">SUM(D5:D8)</f>
-        <v>27433.3333333333</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="E9" s="168" t="n">
         <f aca="false">SUM(E5:E8)</f>
-        <v>29333.3333333333</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="F9" s="172" t="n">
         <f aca="false">SUM(F5:F8)</f>
-        <v>28133.3333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="G9" s="168" t="n">
         <f aca="false">SUM(G5:G8)</f>
-        <v>27933.3333333333</v>
+        <v>13766.6666666667</v>
       </c>
       <c r="H9" s="168" t="n">
         <f aca="false">SUM(H5:H8)</f>
-        <v>28133.3333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="I9" s="172" t="n">
         <f aca="false">SUM(I5:I8)</f>
-        <v>29633.3333333333</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="J9" s="168" t="n">
         <f aca="false">SUM(J5:J8)</f>
-        <v>29433.3333333333</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="K9" s="168" t="n">
         <f aca="false">SUM(K5:K8)</f>
-        <v>27333.3333333333</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="L9" s="172" t="n">
         <f aca="false">SUM(L5:L8)</f>
-        <v>29533.3333333333</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="M9" s="168" t="n">
         <f aca="false">SUM(M5:M8)</f>
-        <v>28633.3333333333</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="N9" s="168" t="n">
         <f aca="false">SUM(N5:N8)</f>
-        <v>25833.3333333333</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="O9" s="173"/>
     </row>
@@ -23448,55 +23448,55 @@
       </c>
       <c r="B19" s="168" t="n">
         <f aca="false">B9+B11-B17</f>
-        <v>323539.333333333</v>
+        <v>153539.333333334</v>
       </c>
       <c r="C19" s="168" t="n">
         <f aca="false">C9+C11-C17</f>
-        <v>26948.3333333333</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="D19" s="168" t="n">
         <f aca="false">D9+D11-D17</f>
-        <v>26464.3333333333</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="E19" s="168" t="n">
         <f aca="false">E9+E11-E17</f>
-        <v>23688.3333333333</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="F19" s="172" t="n">
         <f aca="false">F9+F11-F17</f>
-        <v>27164.3333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="G19" s="168" t="n">
         <f aca="false">G9+G11-G17</f>
-        <v>29191.6666666666</v>
+        <v>15025</v>
       </c>
       <c r="H19" s="168" t="n">
         <f aca="false">H9+H11-H17</f>
-        <v>27644.3333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="I19" s="172" t="n">
         <f aca="false">I9+I11-I17</f>
-        <v>28868.3333333333</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="J19" s="168" t="n">
         <f aca="false">J9+J11-J17</f>
-        <v>25344.3333333333</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="K19" s="168" t="n">
         <f aca="false">K9+K11-K17</f>
-        <v>26568.3333333333</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="L19" s="172" t="n">
         <f aca="false">L9+L11-L17</f>
-        <v>28684.3333333333</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="M19" s="168" t="n">
         <f aca="false">M9+M11-M17</f>
-        <v>27688.3333333333</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="N19" s="168" t="n">
         <f aca="false">N9+N11-N17</f>
-        <v>25284.3333333333</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="O19" s="173"/>
     </row>
@@ -24412,55 +24412,55 @@
       </c>
       <c r="B37" s="168" t="n">
         <f aca="false">B19-B35</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="C37" s="168" t="n">
         <f aca="false">C19-C35</f>
-        <v>25699.0833333333</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="D37" s="168" t="n">
         <f aca="false">D19-D35</f>
-        <v>24568.3333333333</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="E37" s="168" t="n">
         <f aca="false">E19-E35</f>
-        <v>21371.3333333333</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="F37" s="172" t="n">
         <f aca="false">F19-F35</f>
-        <v>25369.0833333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="G37" s="168" t="n">
         <f aca="false">G19-G35</f>
-        <v>26974.4166666666</v>
+        <v>12807.75</v>
       </c>
       <c r="H37" s="168" t="n">
         <f aca="false">H19-H35</f>
-        <v>24721.3333333333</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="I37" s="172" t="n">
         <f aca="false">I19-I35</f>
-        <v>24518.5833333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="J37" s="168" t="n">
         <f aca="false">J19-J35</f>
-        <v>24045.3333333333</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="K37" s="168" t="n">
         <f aca="false">K19-K35</f>
-        <v>19053.8333333333</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="L37" s="172" t="n">
         <f aca="false">L19-L35</f>
-        <v>26877.0833333333</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="M37" s="168" t="n">
         <f aca="false">M19-M35</f>
-        <v>25929.8333333333</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="N37" s="168" t="n">
         <f aca="false">N19-N35</f>
-        <v>23740.8333333333</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="O37" s="162"/>
     </row>
@@ -24528,55 +24528,55 @@
       </c>
       <c r="B39" s="168" t="n">
         <f aca="false">B37+B38</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="C39" s="168" t="n">
         <f aca="false">C37+C38</f>
-        <v>25699.0833333333</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="D39" s="168" t="n">
         <f aca="false">D37+D38</f>
-        <v>24568.3333333333</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="E39" s="168" t="n">
         <f aca="false">E37+E38</f>
-        <v>21371.3333333333</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="F39" s="172" t="n">
         <f aca="false">F37+F38</f>
-        <v>25369.0833333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="G39" s="168" t="n">
         <f aca="false">G37+G38</f>
-        <v>26974.4166666666</v>
+        <v>12807.75</v>
       </c>
       <c r="H39" s="168" t="n">
         <f aca="false">H37+H38</f>
-        <v>24721.3333333333</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="I39" s="172" t="n">
         <f aca="false">I37+I38</f>
-        <v>24518.5833333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="J39" s="168" t="n">
         <f aca="false">J37+J38</f>
-        <v>24045.3333333333</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="K39" s="168" t="n">
         <f aca="false">K37+K38</f>
-        <v>19053.8333333333</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="L39" s="172" t="n">
         <f aca="false">L37+L38</f>
-        <v>26877.0833333333</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="M39" s="168" t="n">
         <f aca="false">M37+M38</f>
-        <v>25929.8333333333</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="N39" s="168" t="n">
         <f aca="false">N37+N38</f>
-        <v>23740.8333333333</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="O39" s="162"/>
     </row>
@@ -24738,55 +24738,55 @@
       </c>
       <c r="B44" s="175" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>111693.455</v>
+        <v>40293.4550000002</v>
       </c>
       <c r="C44" s="175" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="D44" s="175" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="E44" s="175" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="F44" s="175" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="G44" s="175" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="H44" s="175" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="I44" s="175" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="J44" s="175" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="K44" s="175" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="L44" s="175" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="M44" s="175" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="N44" s="175" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>9307.78791666665</v>
+        <v>3357.78791666668</v>
       </c>
       <c r="O44" s="162"/>
     </row>
@@ -24796,55 +24796,55 @@
       </c>
       <c r="B45" s="187" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>181175.628333333</v>
+        <v>82575.6283333336</v>
       </c>
       <c r="C45" s="188" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>16391.2954166666</v>
+        <v>8174.62875000002</v>
       </c>
       <c r="D45" s="189" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>15260.5454166666</v>
+        <v>7043.87875000002</v>
       </c>
       <c r="E45" s="189" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>12063.5454166666</v>
+        <v>3846.87875000002</v>
       </c>
       <c r="F45" s="189" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>16061.2954166666</v>
+        <v>7844.62875000002</v>
       </c>
       <c r="G45" s="189" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>17666.62875</v>
+        <v>9449.96208333335</v>
       </c>
       <c r="H45" s="189" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>15413.5454166666</v>
+        <v>7196.87875000002</v>
       </c>
       <c r="I45" s="189" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>15210.7954166666</v>
+        <v>6994.12875000002</v>
       </c>
       <c r="J45" s="189" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>14737.5454166666</v>
+        <v>6520.87875000002</v>
       </c>
       <c r="K45" s="189" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>9746.04541666665</v>
+        <v>1529.37875000002</v>
       </c>
       <c r="L45" s="189" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>17569.2954166666</v>
+        <v>9352.62875000002</v>
       </c>
       <c r="M45" s="189" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>16622.0454166666</v>
+        <v>8405.37875000002</v>
       </c>
       <c r="N45" s="189" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>14433.0454166666</v>
+        <v>6216.37875000002</v>
       </c>
       <c r="O45" s="162"/>
     </row>
@@ -25033,23 +25033,23 @@
       </c>
       <c r="C5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
-        <v>83899.9999999999</v>
+        <v>41400.0000000001</v>
       </c>
       <c r="D5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F5:H7)</f>
-        <v>82999.9999999999</v>
+        <v>40500.0000000001</v>
       </c>
       <c r="E5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I5:K7)</f>
-        <v>85699.9999999999</v>
+        <v>43200.0000000001</v>
       </c>
       <c r="F5" s="197" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L5:N7)</f>
-        <v>82899.9999999999</v>
+        <v>40400.0000000001</v>
       </c>
       <c r="G5" s="198" t="n">
         <f aca="false">SUM(C5:F5)</f>
-        <v>335500</v>
+        <v>165500</v>
       </c>
       <c r="H5" s="193"/>
       <c r="I5" s="193"/>
@@ -26172,7 +26172,7 @@
       <c r="D5" s="220"/>
       <c r="E5" s="221" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="F5" s="212"/>
       <c r="G5" s="216"/>
@@ -26205,7 +26205,7 @@
       <c r="D7" s="220"/>
       <c r="E7" s="221" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>280299.083333333</v>
+        <v>110299.083333334</v>
       </c>
       <c r="F7" s="212"/>
       <c r="G7" s="216"/>
@@ -26248,7 +26248,7 @@
       </c>
       <c r="E9" s="211" t="n">
         <f aca="false">IF((E7&gt;C9),((E7-C9)*D9),0)</f>
-        <v>97039.2333333332</v>
+        <v>29039.2333333335</v>
       </c>
       <c r="F9" s="212"/>
       <c r="G9" s="216"/>
@@ -26263,7 +26263,7 @@
       <c r="D10" s="228"/>
       <c r="E10" s="229" t="n">
         <f aca="false">SUM(E8:E9)</f>
-        <v>104579.433333333</v>
+        <v>36579.4333333335</v>
       </c>
       <c r="F10" s="212"/>
       <c r="G10" s="216"/>
@@ -26349,7 +26349,7 @@
       </c>
       <c r="E16" s="238" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>4851.98166666666</v>
+        <v>1451.98166666667</v>
       </c>
       <c r="F16" s="212"/>
       <c r="G16" s="232"/>
@@ -26374,7 +26374,7 @@
       <c r="D18" s="235"/>
       <c r="E18" s="229" t="n">
         <f aca="false">SUM(E10:E17)</f>
-        <v>111693.415</v>
+        <v>40293.4150000002</v>
       </c>
       <c r="F18" s="212"/>
       <c r="G18" s="216"/>
@@ -26456,7 +26456,7 @@
       </c>
       <c r="E25" s="238" t="n">
         <f aca="false">E18</f>
-        <v>111693.415</v>
+        <v>40293.4150000002</v>
       </c>
       <c r="F25" s="212"/>
       <c r="G25" s="216"/>
@@ -26473,7 +26473,7 @@
       </c>
       <c r="E26" s="221" t="n">
         <f aca="false">E25/2</f>
-        <v>55846.7074999999</v>
+        <v>20146.7075000001</v>
       </c>
       <c r="F26" s="212"/>
       <c r="G26" s="216"/>
@@ -26490,7 +26490,7 @@
       </c>
       <c r="E27" s="221" t="n">
         <f aca="false">E25/2</f>
-        <v>55846.7074999999</v>
+        <v>20146.7075000001</v>
       </c>
       <c r="F27" s="212"/>
       <c r="G27" s="216"/>
@@ -27554,7 +27554,7 @@
       <c r="I8" s="175"/>
       <c r="J8" s="175" t="n">
         <f aca="false">[2]Apr!$P$1</f>
-        <v>25333.3333333333</v>
+        <v>11166.6666666667</v>
       </c>
       <c r="K8" s="175"/>
       <c r="L8" s="177" t="n">
@@ -27668,7 +27668,7 @@
       <c r="I10" s="175"/>
       <c r="J10" s="175" t="n">
         <f aca="false">[2]May!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K10" s="175"/>
       <c r="L10" s="177" t="n">
@@ -27784,7 +27784,7 @@
       <c r="I12" s="175"/>
       <c r="J12" s="175" t="n">
         <f aca="false">[2]Jun!$P$1</f>
-        <v>26533.3333333333</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="K12" s="175"/>
       <c r="L12" s="177" t="n">
@@ -27898,7 +27898,7 @@
       <c r="I14" s="175"/>
       <c r="J14" s="175" t="n">
         <f aca="false">[2]Jul!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K14" s="175"/>
       <c r="L14" s="177" t="n">
@@ -28014,7 +28014,7 @@
       <c r="I16" s="175"/>
       <c r="J16" s="175" t="n">
         <f aca="false">[2]Aug!$P$1</f>
-        <v>27133.3333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="K16" s="175"/>
       <c r="L16" s="177" t="n">
@@ -28128,7 +28128,7 @@
       <c r="I18" s="175"/>
       <c r="J18" s="175" t="n">
         <f aca="false">[2]Sep!$P$1</f>
-        <v>25033.3333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="K18" s="175"/>
       <c r="L18" s="177" t="n">
@@ -28244,7 +28244,7 @@
       <c r="I20" s="175"/>
       <c r="J20" s="175" t="n">
         <f aca="false">[2]Oct!$P$1</f>
-        <v>27133.3333333333</v>
+        <v>12966.6666666667</v>
       </c>
       <c r="K20" s="175"/>
       <c r="L20" s="177" t="n">
@@ -28358,7 +28358,7 @@
       <c r="I22" s="175"/>
       <c r="J22" s="175" t="n">
         <f aca="false">[2]Nov!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K22" s="175"/>
       <c r="L22" s="177" t="n">
@@ -28474,7 +28474,7 @@
       <c r="I24" s="175"/>
       <c r="J24" s="175" t="n">
         <f aca="false">[2]Dec!$P$1</f>
-        <v>26533.3333333333</v>
+        <v>12366.6666666667</v>
       </c>
       <c r="K24" s="175"/>
       <c r="L24" s="177" t="n">
@@ -28588,7 +28588,7 @@
       <c r="I26" s="175"/>
       <c r="J26" s="175" t="n">
         <f aca="false">[2]Jan!$P$1</f>
-        <v>25633.3333333333</v>
+        <v>11466.6666666667</v>
       </c>
       <c r="K26" s="175"/>
       <c r="L26" s="177" t="n">
@@ -28702,7 +28702,7 @@
       <c r="I28" s="175"/>
       <c r="J28" s="175" t="n">
         <f aca="false">[2]Feb!$P$1</f>
-        <v>26333.3333333333</v>
+        <v>12166.6666666667</v>
       </c>
       <c r="K28" s="175"/>
       <c r="L28" s="177" t="n">
@@ -28818,7 +28818,7 @@
       <c r="I30" s="175"/>
       <c r="J30" s="175" t="n">
         <f aca="false">[2]Mar!$P$1</f>
-        <v>25033.3333333333</v>
+        <v>10866.6666666667</v>
       </c>
       <c r="K30" s="175"/>
       <c r="L30" s="177" t="n">
@@ -29097,55 +29097,55 @@
       </c>
       <c r="C5" s="168" t="n">
         <f aca="false">SUM(D5:O5)</f>
-        <v>339200</v>
+        <v>169200</v>
       </c>
       <c r="D5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C9</f>
-        <v>27833.3333333333</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="E5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D9</f>
-        <v>27433.3333333333</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="F5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E9</f>
-        <v>29333.3333333333</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="G5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F9</f>
-        <v>28133.3333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="H5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G9</f>
-        <v>27933.3333333333</v>
+        <v>13766.6666666667</v>
       </c>
       <c r="I5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H9</f>
-        <v>28133.3333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="J5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I9</f>
-        <v>29633.3333333333</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="K5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J9</f>
-        <v>29433.3333333333</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="L5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K9</f>
-        <v>27333.3333333333</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="M5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L9</f>
-        <v>29533.3333333333</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="N5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M9</f>
-        <v>28633.3333333333</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="O5" s="168" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N9</f>
-        <v>25833.3333333333</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="P5" s="176"/>
     </row>
@@ -29328,55 +29328,55 @@
       </c>
       <c r="C11" s="168" t="n">
         <f aca="false">SUM(D11:O11)</f>
-        <v>323539.333333333</v>
+        <v>153539.333333334</v>
       </c>
       <c r="D11" s="168" t="n">
         <f aca="false">D5+D7-D9</f>
-        <v>26948.3333333333</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="E11" s="168" t="n">
         <f aca="false">E5+E7-E9</f>
-        <v>26464.3333333333</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="F11" s="168" t="n">
         <f aca="false">F5+F7-F9</f>
-        <v>23688.3333333333</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="G11" s="168" t="n">
         <f aca="false">G5+G7-G9</f>
-        <v>27164.3333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="H11" s="168" t="n">
         <f aca="false">H5+H7-H9</f>
-        <v>29191.6666666666</v>
+        <v>15025</v>
       </c>
       <c r="I11" s="168" t="n">
         <f aca="false">I5+I7-I9</f>
-        <v>27644.3333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="J11" s="168" t="n">
         <f aca="false">J5+J7-J9</f>
-        <v>28868.3333333333</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="K11" s="168" t="n">
         <f aca="false">K5+K7-K9</f>
-        <v>25344.3333333333</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="L11" s="168" t="n">
         <f aca="false">L5+L7-L9</f>
-        <v>26568.3333333333</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="M11" s="168" t="n">
         <f aca="false">M5+M7-M9</f>
-        <v>28684.3333333333</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="N11" s="168" t="n">
         <f aca="false">N5+N7-N9</f>
-        <v>27688.3333333333</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="O11" s="168" t="n">
         <f aca="false">O5+O7-O9</f>
-        <v>25284.3333333333</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="P11" s="176"/>
     </row>
@@ -29482,55 +29482,55 @@
       </c>
       <c r="C15" s="168" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D15" s="168" t="n">
         <f aca="false">D11-D13</f>
-        <v>25699.0833333333</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E15" s="168" t="n">
         <f aca="false">E11-E13</f>
-        <v>24568.3333333333</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F15" s="168" t="n">
         <f aca="false">F11-F13</f>
-        <v>21371.3333333333</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G15" s="168" t="n">
         <f aca="false">G11-G13</f>
-        <v>25369.0833333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H15" s="168" t="n">
         <f aca="false">H11-H13</f>
-        <v>26974.4166666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I15" s="168" t="n">
         <f aca="false">I11-I13</f>
-        <v>24721.3333333333</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J15" s="168" t="n">
         <f aca="false">J11-J13</f>
-        <v>24518.5833333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K15" s="168" t="n">
         <f aca="false">K11-K13</f>
-        <v>24045.3333333333</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L15" s="168" t="n">
         <f aca="false">L11-L13</f>
-        <v>19053.8333333333</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M15" s="168" t="n">
         <f aca="false">M11-M13</f>
-        <v>26877.0833333333</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N15" s="168" t="n">
         <f aca="false">N11-N13</f>
-        <v>25929.8333333333</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O15" s="168" t="n">
         <f aca="false">O11-O13</f>
-        <v>23740.8333333333</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P15" s="156"/>
     </row>
@@ -29600,55 +29600,55 @@
       </c>
       <c r="C17" s="168" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D17" s="168" t="n">
         <f aca="false">D15+D16</f>
-        <v>25699.0833333333</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E17" s="168" t="n">
         <f aca="false">E15+E16</f>
-        <v>24568.3333333333</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F17" s="168" t="n">
         <f aca="false">F15+F16</f>
-        <v>21371.3333333333</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G17" s="168" t="n">
         <f aca="false">G15+G16</f>
-        <v>25369.0833333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H17" s="168" t="n">
         <f aca="false">H15+H16</f>
-        <v>26974.4166666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I17" s="168" t="n">
         <f aca="false">I15+I16</f>
-        <v>24721.3333333333</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J17" s="168" t="n">
         <f aca="false">J15+J16</f>
-        <v>24518.5833333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K17" s="168" t="n">
         <f aca="false">K15+K16</f>
-        <v>24045.3333333333</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L17" s="168" t="n">
         <f aca="false">L15+L16</f>
-        <v>19053.8333333333</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M17" s="168" t="n">
         <f aca="false">M15+M16</f>
-        <v>26877.0833333333</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N17" s="168" t="n">
         <f aca="false">N15+N16</f>
-        <v>25929.8333333333</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O17" s="168" t="n">
         <f aca="false">O15+O16</f>
-        <v>23740.8333333333</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P17" s="156"/>
     </row>
@@ -29813,55 +29813,55 @@
       </c>
       <c r="C22" s="168" t="n">
         <f aca="false">SUM(D22:O22)</f>
-        <v>339200</v>
+        <v>169200</v>
       </c>
       <c r="D22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D5,C5/C21),0)</f>
-        <v>27833.3333333333</v>
+        <v>13666.6666666667</v>
       </c>
       <c r="E22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E5,C5/C21),0)</f>
-        <v>27433.3333333333</v>
+        <v>13266.6666666667</v>
       </c>
       <c r="F22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F5,C5/C21),0)</f>
-        <v>29333.3333333333</v>
+        <v>15166.6666666667</v>
       </c>
       <c r="G22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G5,C5/C21),0)</f>
-        <v>28133.3333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="H22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H5,C5/C21),0)</f>
-        <v>27933.3333333333</v>
+        <v>13766.6666666667</v>
       </c>
       <c r="I22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I5,C5/C21),0)</f>
-        <v>28133.3333333333</v>
+        <v>13966.6666666667</v>
       </c>
       <c r="J22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J5,C5/C21),0)</f>
-        <v>29633.3333333333</v>
+        <v>15466.6666666667</v>
       </c>
       <c r="K22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K5,C5/C21),0)</f>
-        <v>29433.3333333333</v>
+        <v>15266.6666666667</v>
       </c>
       <c r="L22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L5,C5/C21),0)</f>
-        <v>27333.3333333333</v>
+        <v>13166.6666666667</v>
       </c>
       <c r="M22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M5,C5/C21),0)</f>
-        <v>29533.3333333333</v>
+        <v>15366.6666666667</v>
       </c>
       <c r="N22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N5,C5/C21),0)</f>
-        <v>28633.3333333333</v>
+        <v>14466.6666666667</v>
       </c>
       <c r="O22" s="168" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O5,C5/C21),0)</f>
-        <v>25833.3333333333</v>
+        <v>11666.6666666667</v>
       </c>
       <c r="P22" s="176"/>
     </row>
@@ -30044,55 +30044,55 @@
       </c>
       <c r="C28" s="168" t="n">
         <f aca="false">SUM(D28:O28)</f>
-        <v>323539.333333333</v>
+        <v>153539.333333334</v>
       </c>
       <c r="D28" s="168" t="n">
         <f aca="false">D22+D24-D26</f>
-        <v>26948.3333333333</v>
+        <v>12781.6666666667</v>
       </c>
       <c r="E28" s="168" t="n">
         <f aca="false">E22+E24-E26</f>
-        <v>26464.3333333333</v>
+        <v>12297.6666666667</v>
       </c>
       <c r="F28" s="168" t="n">
         <f aca="false">F22+F24-F26</f>
-        <v>23688.3333333333</v>
+        <v>9521.6666666667</v>
       </c>
       <c r="G28" s="168" t="n">
         <f aca="false">G22+G24-G26</f>
-        <v>27164.3333333333</v>
+        <v>12997.6666666667</v>
       </c>
       <c r="H28" s="168" t="n">
         <f aca="false">H22+H24-H26</f>
-        <v>29191.6666666666</v>
+        <v>15025</v>
       </c>
       <c r="I28" s="168" t="n">
         <f aca="false">I22+I24-I26</f>
-        <v>27644.3333333333</v>
+        <v>13477.6666666667</v>
       </c>
       <c r="J28" s="168" t="n">
         <f aca="false">J22+J24-J26</f>
-        <v>28868.3333333333</v>
+        <v>14701.6666666667</v>
       </c>
       <c r="K28" s="168" t="n">
         <f aca="false">K22+K24-K26</f>
-        <v>25344.3333333333</v>
+        <v>11177.6666666667</v>
       </c>
       <c r="L28" s="168" t="n">
         <f aca="false">L22+L24-L26</f>
-        <v>26568.3333333333</v>
+        <v>12401.6666666667</v>
       </c>
       <c r="M28" s="168" t="n">
         <f aca="false">M22+M24-M26</f>
-        <v>28684.3333333333</v>
+        <v>14517.6666666667</v>
       </c>
       <c r="N28" s="168" t="n">
         <f aca="false">N22+N24-N26</f>
-        <v>27688.3333333333</v>
+        <v>13521.6666666667</v>
       </c>
       <c r="O28" s="168" t="n">
         <f aca="false">O22+O24-O26</f>
-        <v>25284.3333333333</v>
+        <v>11117.6666666667</v>
       </c>
       <c r="P28" s="176"/>
     </row>
@@ -30198,55 +30198,55 @@
       </c>
       <c r="C32" s="168" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D32" s="168" t="n">
         <f aca="false">D28-D30</f>
-        <v>25699.0833333333</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E32" s="168" t="n">
         <f aca="false">E28-E30</f>
-        <v>24568.3333333333</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F32" s="168" t="n">
         <f aca="false">F28-F30</f>
-        <v>21371.3333333333</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G32" s="168" t="n">
         <f aca="false">G28-G30</f>
-        <v>25369.0833333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H32" s="168" t="n">
         <f aca="false">H28-H30</f>
-        <v>26974.4166666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I32" s="168" t="n">
         <f aca="false">I28-I30</f>
-        <v>24721.3333333333</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J32" s="168" t="n">
         <f aca="false">J28-J30</f>
-        <v>24518.5833333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K32" s="168" t="n">
         <f aca="false">K28-K30</f>
-        <v>24045.3333333333</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L32" s="168" t="n">
         <f aca="false">L28-L30</f>
-        <v>19053.8333333333</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M32" s="168" t="n">
         <f aca="false">M28-M30</f>
-        <v>26877.0833333333</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N32" s="168" t="n">
         <f aca="false">N28-N30</f>
-        <v>25929.8333333333</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O32" s="168" t="n">
         <f aca="false">O28-O30</f>
-        <v>23740.8333333333</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P32" s="156"/>
     </row>
@@ -30316,55 +30316,55 @@
       </c>
       <c r="C34" s="168" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D34" s="168" t="n">
         <f aca="false">D32+D33</f>
-        <v>25699.0833333333</v>
+        <v>11532.4166666667</v>
       </c>
       <c r="E34" s="168" t="n">
         <f aca="false">E32+E33</f>
-        <v>24568.3333333333</v>
+        <v>10401.6666666667</v>
       </c>
       <c r="F34" s="168" t="n">
         <f aca="false">F32+F33</f>
-        <v>21371.3333333333</v>
+        <v>7204.6666666667</v>
       </c>
       <c r="G34" s="168" t="n">
         <f aca="false">G32+G33</f>
-        <v>25369.0833333333</v>
+        <v>11202.4166666667</v>
       </c>
       <c r="H34" s="168" t="n">
         <f aca="false">H32+H33</f>
-        <v>26974.4166666666</v>
+        <v>12807.75</v>
       </c>
       <c r="I34" s="168" t="n">
         <f aca="false">I32+I33</f>
-        <v>24721.3333333333</v>
+        <v>10554.6666666667</v>
       </c>
       <c r="J34" s="168" t="n">
         <f aca="false">J32+J33</f>
-        <v>24518.5833333333</v>
+        <v>10351.9166666667</v>
       </c>
       <c r="K34" s="168" t="n">
         <f aca="false">K32+K33</f>
-        <v>24045.3333333333</v>
+        <v>9878.6666666667</v>
       </c>
       <c r="L34" s="168" t="n">
         <f aca="false">L32+L33</f>
-        <v>19053.8333333333</v>
+        <v>4887.1666666667</v>
       </c>
       <c r="M34" s="168" t="n">
         <f aca="false">M32+M33</f>
-        <v>26877.0833333333</v>
+        <v>12710.4166666667</v>
       </c>
       <c r="N34" s="168" t="n">
         <f aca="false">N32+N33</f>
-        <v>25929.8333333333</v>
+        <v>11763.1666666667</v>
       </c>
       <c r="O34" s="168" t="n">
         <f aca="false">O32+O33</f>
-        <v>23740.8333333333</v>
+        <v>9574.1666666667</v>
       </c>
       <c r="P34" s="156"/>
     </row>
@@ -30459,7 +30459,7 @@
       </c>
       <c r="C39" s="337" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>292869.083333333</v>
+        <v>122869.083333334</v>
       </c>
       <c r="D39" s="156"/>
       <c r="E39" s="156"/>
@@ -30505,7 +30505,7 @@
       </c>
       <c r="C41" s="337" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>280299.083333333</v>
+        <v>110299.083333334</v>
       </c>
       <c r="D41" s="156"/>
       <c r="E41" s="156"/>
@@ -30551,7 +30551,7 @@
       </c>
       <c r="C43" s="337" t="n">
         <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>97039.2333333332</v>
+        <v>29039.2333333335</v>
       </c>
       <c r="D43" s="156"/>
       <c r="E43" s="156"/>
@@ -30574,7 +30574,7 @@
       </c>
       <c r="C44" s="337" t="n">
         <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>7114.02166666666</v>
+        <v>3714.02166666667</v>
       </c>
       <c r="D44" s="156"/>
       <c r="E44" s="156"/>
@@ -30615,7 +30615,7 @@
       </c>
       <c r="C46" s="339" t="n">
         <f aca="false">C42+C43+C44</f>
-        <v>111693.455</v>
+        <v>40293.4550000002</v>
       </c>
       <c r="D46" s="156"/>
       <c r="E46" s="156"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -4736,12 +4736,12 @@
       <sheetData sheetId="0">
         <row r="1">
           <cell r="I1">
-            <v>11740</v>
+            <v>13740</v>
           </cell>
         </row>
         <row r="1">
           <cell r="Q1">
-            <v>32500</v>
+            <v>52500</v>
           </cell>
           <cell r="R1">
             <v>3000</v>
@@ -5722,7 +5722,7 @@
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>250</v>
+            <v>2250</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -5797,7 +5797,7 @@
         </row>
         <row r="1">
           <cell r="Y1">
-            <v>208</v>
+            <v>1308</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -8950,7 +8950,9 @@
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="63"/>
-      <c r="B25" s="368"/>
+      <c r="B25" s="347" t="n">
+        <v>46599</v>
+      </c>
       <c r="C25" s="63"/>
       <c r="D25" s="63"/>
       <c r="E25" s="63"/>
@@ -10564,7 +10566,7 @@
       </c>
       <c r="O51" s="98" t="n">
         <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
-        <v>800</v>
+        <v>3900</v>
       </c>
       <c r="P51" s="98"/>
       <c r="Q51" s="98"/>
@@ -10981,7 +10983,7 @@
       </c>
       <c r="O64" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'Profit &amp; Loss Account'!B34</f>
-        <v>152567.941666667</v>
+        <v>155667.941666667</v>
       </c>
       <c r="P64" s="98"/>
       <c r="Q64" s="98"/>
@@ -11170,7 +11172,7 @@
       </c>
       <c r="D71" s="98" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>186632.058333333</v>
+        <v>183532.058333333</v>
       </c>
       <c r="E71" s="98"/>
       <c r="F71" s="98"/>
@@ -11439,7 +11441,7 @@
       </c>
       <c r="D80" s="98" t="n">
         <f aca="false">IF(([1]Schedule!$Q$1)&gt;0,[1]Schedule!$Q$1,0)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="E80" s="98"/>
       <c r="F80" s="98"/>
@@ -12022,7 +12024,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>142632.058333333</v>
+        <v>119532.058333333</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -12235,7 +12237,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>144715.391666666</v>
+        <v>121615.391666666</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -15939,7 +15941,7 @@
       </c>
       <c r="D102" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B31</f>
-        <v>800</v>
+        <v>3900</v>
       </c>
       <c r="E102" s="98"/>
       <c r="F102" s="98"/>
@@ -16314,7 +16316,7 @@
       </c>
       <c r="D114" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
-        <v>11912</v>
+        <v>13912</v>
       </c>
       <c r="E114" s="98"/>
       <c r="F114" s="98"/>
@@ -16336,7 +16338,7 @@
       </c>
       <c r="O114" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B34</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="P114" s="98"/>
       <c r="Q114" s="98"/>
@@ -16569,7 +16571,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>164307.941666667</v>
+        <v>169407.941666667</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -16591,7 +16593,7 @@
       </c>
       <c r="O122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B34</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="P122" s="98"/>
       <c r="Q122" s="98"/>
@@ -16780,7 +16782,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>174892.058333333</v>
+        <v>169792.058333333</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -17073,7 +17075,7 @@
       </c>
       <c r="D139" s="98" t="n">
         <f aca="false">IF([1]Schedule!$Q$1&gt;0,[1]Schedule!$Q$1,0)</f>
-        <v>32500</v>
+        <v>52500</v>
       </c>
       <c r="E139" s="98"/>
       <c r="F139" s="98"/>
@@ -17417,7 +17419,7 @@
       </c>
       <c r="O149" s="98" t="n">
         <f aca="false">D139+D144+D147+D152+D156+D160+O139+O144</f>
-        <v>44000</v>
+        <v>64000</v>
       </c>
       <c r="P149" s="98"/>
       <c r="Q149" s="98"/>
@@ -18029,7 +18031,7 @@
       </c>
       <c r="O169" s="98" t="n">
         <f aca="false">O149+D179</f>
-        <v>44000</v>
+        <v>64000</v>
       </c>
       <c r="P169" s="98"/>
       <c r="Q169" s="98"/>
@@ -18166,7 +18168,7 @@
       </c>
       <c r="D174" s="98" t="n">
         <f aca="false">O122+O154+O160+D169</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="E174" s="98"/>
       <c r="F174" s="98"/>
@@ -18188,7 +18190,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>142632.058333333</v>
+        <v>119532.058333333</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -18785,7 +18787,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">O174</f>
-        <v>142632.058333333</v>
+        <v>119532.058333333</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -19292,7 +19294,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>144715.391666666</v>
+        <v>121615.391666666</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -24176,7 +24178,7 @@
       </c>
       <c r="B31" s="170" t="n">
         <f aca="false">SUM(C31:N31)</f>
-        <v>800</v>
+        <v>3900</v>
       </c>
       <c r="C31" s="171" t="n">
         <f aca="false">[5]Apr!$V$1+[4]Apr!$Y$1</f>
@@ -24188,7 +24190,7 @@
       </c>
       <c r="E31" s="172" t="n">
         <f aca="false">[5]Jun!$V$1+[4]Jun!$Y$1</f>
-        <v>250</v>
+        <v>2250</v>
       </c>
       <c r="F31" s="171" t="n">
         <f aca="false">[5]Jul!$V$1+[4]Jul!$Y$1</f>
@@ -24200,7 +24202,7 @@
       </c>
       <c r="H31" s="172" t="n">
         <f aca="false">[5]Sep!$V$1+[4]Sep!$Y$1</f>
-        <v>208</v>
+        <v>1308</v>
       </c>
       <c r="I31" s="171" t="n">
         <f aca="false">[5]Oct!$V$1+[4]Oct!$Y$1</f>
@@ -24350,55 +24352,55 @@
       </c>
       <c r="B34" s="170" t="n">
         <f aca="false">SUM(C34:N34)</f>
-        <v>11740</v>
+        <v>13740</v>
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="D34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="E34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="F34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="G34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="H34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="I34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="J34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="K34" s="172" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="L34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="M34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="N34" s="171" t="n">
         <f aca="false">([1]Schedule!$I$1)/12</f>
-        <v>978.333333333333</v>
+        <v>1145</v>
       </c>
       <c r="O34" s="164"/>
     </row>
@@ -24408,55 +24410,55 @@
       </c>
       <c r="B35" s="170" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>144171.275</v>
+        <v>149271.275</v>
       </c>
       <c r="C35" s="170" t="n">
         <f aca="false">SUM(C21:C34)</f>
-        <v>11839.7416666667</v>
+        <v>12006.4083333333</v>
       </c>
       <c r="D35" s="170" t="n">
         <f aca="false">SUM(D21:D34)</f>
-        <v>11147.8666666667</v>
+        <v>11314.5333333333</v>
       </c>
       <c r="E35" s="170" t="n">
         <f aca="false">SUM(E21:E34)</f>
-        <v>11411.2</v>
+        <v>13577.8666666667</v>
       </c>
       <c r="F35" s="174" t="n">
         <f aca="false">SUM(F21:F34)</f>
-        <v>13659.7416666667</v>
+        <v>13826.4083333333</v>
       </c>
       <c r="G35" s="170" t="n">
         <f aca="false">SUM(G21:G34)</f>
-        <v>11301.4083333333</v>
+        <v>11468.075</v>
       </c>
       <c r="H35" s="170" t="n">
         <f aca="false">SUM(H21:H34)</f>
-        <v>11964.2</v>
+        <v>13230.8666666667</v>
       </c>
       <c r="I35" s="174" t="n">
         <f aca="false">SUM(I21:I34)</f>
-        <v>13518.4916666667</v>
+        <v>13685.1583333333</v>
       </c>
       <c r="J35" s="170" t="n">
         <f aca="false">SUM(J21:J34)</f>
-        <v>10700.3666666667</v>
+        <v>10867.0333333333</v>
       </c>
       <c r="K35" s="170" t="n">
         <f aca="false">SUM(K21:K34)</f>
-        <v>15723.6166666667</v>
+        <v>15890.2833333333</v>
       </c>
       <c r="L35" s="174" t="n">
         <f aca="false">SUM(L21:L34)</f>
-        <v>11219.7416666667</v>
+        <v>11386.4083333333</v>
       </c>
       <c r="M35" s="170" t="n">
         <f aca="false">SUM(M21:M34)</f>
-        <v>10894.1166666667</v>
+        <v>11060.7833333333</v>
       </c>
       <c r="N35" s="170" t="n">
         <f aca="false">SUM(N21:N34)</f>
-        <v>10790.7833333333</v>
+        <v>10957.45</v>
       </c>
       <c r="O35" s="164"/>
     </row>
@@ -24483,55 +24485,55 @@
       </c>
       <c r="B37" s="170" t="n">
         <f aca="false">B19-B35</f>
-        <v>176975.391666666</v>
+        <v>171875.391666666</v>
       </c>
       <c r="C37" s="170" t="n">
         <f aca="false">C19-C35</f>
-        <v>15256.0916666666</v>
+        <v>15089.425</v>
       </c>
       <c r="D37" s="170" t="n">
         <f aca="false">D19-D35</f>
-        <v>15277.9666666666</v>
+        <v>15111.3</v>
       </c>
       <c r="E37" s="170" t="n">
         <f aca="false">E19-E35</f>
-        <v>13217.9666666666</v>
+        <v>11051.3</v>
       </c>
       <c r="F37" s="174" t="n">
         <f aca="false">F19-F35</f>
-        <v>13266.0916666666</v>
+        <v>13099.425</v>
       </c>
       <c r="G37" s="170" t="n">
         <f aca="false">G19-G35</f>
-        <v>18027.7583333333</v>
+        <v>17861.0916666666</v>
       </c>
       <c r="H37" s="170" t="n">
         <f aca="false">H19-H35</f>
-        <v>15461.6333333333</v>
+        <v>14194.9666666666</v>
       </c>
       <c r="I37" s="174" t="n">
         <f aca="false">I19-I35</f>
-        <v>15477.3416666666</v>
+        <v>15310.675</v>
       </c>
       <c r="J37" s="170" t="n">
         <f aca="false">J19-J35</f>
-        <v>15325.4666666666</v>
+        <v>15158.8</v>
       </c>
       <c r="K37" s="170" t="n">
         <f aca="false">K19-K35</f>
-        <v>10972.2166666666</v>
+        <v>10805.55</v>
       </c>
       <c r="L37" s="174" t="n">
         <f aca="false">L19-L35</f>
-        <v>17456.0916666666</v>
+        <v>17289.425</v>
       </c>
       <c r="M37" s="170" t="n">
         <f aca="false">M19-M35</f>
-        <v>16651.7166666666</v>
+        <v>16485.05</v>
       </c>
       <c r="N37" s="170" t="n">
         <f aca="false">N19-N35</f>
-        <v>10585.05</v>
+        <v>10418.3833333333</v>
       </c>
       <c r="O37" s="164"/>
     </row>
@@ -24599,55 +24601,55 @@
       </c>
       <c r="B39" s="170" t="n">
         <f aca="false">B37+B38</f>
-        <v>176975.391666666</v>
+        <v>171875.391666666</v>
       </c>
       <c r="C39" s="170" t="n">
         <f aca="false">C37+C38</f>
-        <v>15256.0916666666</v>
+        <v>15089.425</v>
       </c>
       <c r="D39" s="170" t="n">
         <f aca="false">D37+D38</f>
-        <v>15277.9666666666</v>
+        <v>15111.3</v>
       </c>
       <c r="E39" s="170" t="n">
         <f aca="false">E37+E38</f>
-        <v>13217.9666666666</v>
+        <v>11051.3</v>
       </c>
       <c r="F39" s="174" t="n">
         <f aca="false">F37+F38</f>
-        <v>13266.0916666666</v>
+        <v>13099.425</v>
       </c>
       <c r="G39" s="170" t="n">
         <f aca="false">G37+G38</f>
-        <v>18027.7583333333</v>
+        <v>17861.0916666666</v>
       </c>
       <c r="H39" s="170" t="n">
         <f aca="false">H37+H38</f>
-        <v>15461.6333333333</v>
+        <v>14194.9666666666</v>
       </c>
       <c r="I39" s="174" t="n">
         <f aca="false">I37+I38</f>
-        <v>15477.3416666666</v>
+        <v>15310.675</v>
       </c>
       <c r="J39" s="170" t="n">
         <f aca="false">J37+J38</f>
-        <v>15325.4666666666</v>
+        <v>15158.8</v>
       </c>
       <c r="K39" s="170" t="n">
         <f aca="false">K37+K38</f>
-        <v>10972.2166666666</v>
+        <v>10805.55</v>
       </c>
       <c r="L39" s="174" t="n">
         <f aca="false">L37+L38</f>
-        <v>17456.0916666666</v>
+        <v>17289.425</v>
       </c>
       <c r="M39" s="170" t="n">
         <f aca="false">M37+M38</f>
-        <v>16651.7166666666</v>
+        <v>16485.05</v>
       </c>
       <c r="N39" s="170" t="n">
         <f aca="false">N37+N38</f>
-        <v>10585.05</v>
+        <v>10418.3833333333</v>
       </c>
       <c r="O39" s="164"/>
     </row>
@@ -24809,55 +24811,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>49541.1444999998</v>
+        <v>39839.1444999998</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>4128.42870833332</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24867,55 +24869,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>100434.247166666</v>
+        <v>105036.247166666</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10127.6629583333</v>
+        <v>10769.4962916667</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10149.5379583333</v>
+        <v>10791.3712916666</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>8089.53795833331</v>
+        <v>6731.37129166664</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5137.66295833331</v>
+        <v>5779.49629166665</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>12899.329625</v>
+        <v>13541.1629583333</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>10333.204625</v>
+        <v>9875.03795833332</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7348.91295833331</v>
+        <v>7990.74629166665</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10197.0379583333</v>
+        <v>10838.8712916666</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>5843.78795833331</v>
+        <v>6485.62129166664</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9327.66295833331</v>
+        <v>9969.49629166665</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11523.2879583333</v>
+        <v>12165.1212916666</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-543.378708333354</v>
+        <v>98.4546249999789</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -25346,11 +25348,11 @@
       </c>
       <c r="C16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
-        <v>275</v>
+        <v>2275</v>
       </c>
       <c r="D16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F31:H31)</f>
-        <v>208</v>
+        <v>1308</v>
       </c>
       <c r="E16" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I31:K31)</f>
@@ -25362,7 +25364,7 @@
       </c>
       <c r="G16" s="200" t="n">
         <f aca="false">SUM(C16:F16)</f>
-        <v>800</v>
+        <v>3900</v>
       </c>
       <c r="H16" s="195"/>
       <c r="I16" s="195"/>
@@ -25607,23 +25609,23 @@
       </c>
       <c r="C26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
-        <v>2978</v>
+        <v>3478</v>
       </c>
       <c r="D26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F33:H34)</f>
-        <v>2978</v>
+        <v>3478</v>
       </c>
       <c r="E26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I33:K34)</f>
-        <v>2978</v>
+        <v>3478</v>
       </c>
       <c r="F26" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!L33:N34)</f>
-        <v>2978</v>
+        <v>3478</v>
       </c>
       <c r="G26" s="200" t="n">
         <f aca="false">SUM(C26:F26)</f>
-        <v>11912</v>
+        <v>13912</v>
       </c>
       <c r="H26" s="195"/>
       <c r="I26" s="195"/>
@@ -25657,23 +25659,23 @@
       </c>
       <c r="C29" s="203" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
-        <v>40847.975</v>
+        <v>43347.975</v>
       </c>
       <c r="D29" s="203" t="n">
         <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D25,D26)</f>
-        <v>39527.85</v>
+        <v>41127.85</v>
       </c>
       <c r="E29" s="203" t="n">
         <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E25,E26)</f>
-        <v>44624.975</v>
+        <v>45124.975</v>
       </c>
       <c r="F29" s="203" t="n">
         <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F25,F26)</f>
-        <v>39307.1416666667</v>
+        <v>39807.1416666667</v>
       </c>
       <c r="G29" s="203" t="n">
         <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G25,G26)</f>
-        <v>164307.941666667</v>
+        <v>169407.941666667</v>
       </c>
       <c r="H29" s="204"/>
       <c r="I29" s="195"/>
@@ -26243,7 +26245,7 @@
       <c r="D5" s="222"/>
       <c r="E5" s="223" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>144715.391666666</v>
+        <v>121615.391666666</v>
       </c>
       <c r="F5" s="214"/>
       <c r="G5" s="218"/>
@@ -26261,7 +26263,7 @@
       <c r="D6" s="225"/>
       <c r="E6" s="218" t="n">
         <f aca="false">IF(E5&lt;=0,0,MAX(0,Admin!N$4-MAX(0,E5-Admin!N$5)/2))</f>
-        <v>0</v>
+        <v>1762.30416666687</v>
       </c>
       <c r="F6" s="214"/>
       <c r="G6" s="218"/>
@@ -26276,7 +26278,7 @@
       <c r="D7" s="222"/>
       <c r="E7" s="223" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>144715.391666666</v>
+        <v>119853.087499999</v>
       </c>
       <c r="F7" s="214"/>
       <c r="G7" s="218"/>
@@ -26319,7 +26321,7 @@
       </c>
       <c r="E9" s="213" t="n">
         <f aca="false">IF(E7&gt;C9,(MIN(E7,C10)-C9)*D9,0)</f>
-        <v>34976</v>
+        <v>32861.2349999998</v>
       </c>
       <c r="F9" s="214"/>
       <c r="G9" s="218"/>
@@ -26340,7 +26342,7 @@
       </c>
       <c r="E10" s="213" t="n">
         <f aca="false">IF(E7&gt;C10,(E7-C10)*D10,0)</f>
-        <v>8808.92624999983</v>
+        <v>0</v>
       </c>
       <c r="F10" s="214"/>
       <c r="G10" s="218"/>
@@ -26355,7 +26357,7 @@
       <c r="D11" s="230"/>
       <c r="E11" s="231" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>51324.9262499998</v>
+        <v>40401.2349999998</v>
       </c>
       <c r="F11" s="232"/>
       <c r="G11" s="233"/>
@@ -26431,7 +26433,7 @@
       </c>
       <c r="E16" s="240" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1888.90783333333</v>
+        <v>1426.90783333333</v>
       </c>
       <c r="F16" s="214"/>
       <c r="G16" s="233"/>
@@ -26456,7 +26458,7 @@
       <c r="D18" s="237"/>
       <c r="E18" s="231" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>55475.8340833332</v>
+        <v>44090.1428333331</v>
       </c>
       <c r="F18" s="214"/>
       <c r="G18" s="218"/>
@@ -26538,7 +26540,7 @@
       </c>
       <c r="E25" s="240" t="n">
         <f aca="false">E18</f>
-        <v>55475.8340833332</v>
+        <v>44090.1428333331</v>
       </c>
       <c r="F25" s="214"/>
       <c r="G25" s="218"/>
@@ -26555,7 +26557,7 @@
       </c>
       <c r="E26" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>27737.9170416666</v>
+        <v>22045.0714166665</v>
       </c>
       <c r="F26" s="214"/>
       <c r="G26" s="218"/>
@@ -26572,7 +26574,7 @@
       </c>
       <c r="E27" s="223" t="n">
         <f aca="false">E25/2</f>
-        <v>27737.9170416666</v>
+        <v>22045.0714166665</v>
       </c>
       <c r="F27" s="214"/>
       <c r="G27" s="218"/>
@@ -29488,55 +29490,55 @@
       </c>
       <c r="C13" s="170" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>144171.275</v>
+        <v>149271.275</v>
       </c>
       <c r="D13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
-        <v>11839.7416666667</v>
+        <v>12006.4083333333</v>
       </c>
       <c r="E13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!D35</f>
-        <v>11147.8666666667</v>
+        <v>11314.5333333333</v>
       </c>
       <c r="F13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!E35</f>
-        <v>11411.2</v>
+        <v>13577.8666666667</v>
       </c>
       <c r="G13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!F35</f>
-        <v>13659.7416666667</v>
+        <v>13826.4083333333</v>
       </c>
       <c r="H13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G35</f>
-        <v>11301.4083333333</v>
+        <v>11468.075</v>
       </c>
       <c r="I13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
-        <v>11964.2</v>
+        <v>13230.8666666667</v>
       </c>
       <c r="J13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!I35</f>
-        <v>13518.4916666667</v>
+        <v>13685.1583333333</v>
       </c>
       <c r="K13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!J35</f>
-        <v>10700.3666666667</v>
+        <v>10867.0333333333</v>
       </c>
       <c r="L13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!K35</f>
-        <v>15723.6166666667</v>
+        <v>15890.2833333333</v>
       </c>
       <c r="M13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!L35</f>
-        <v>11219.7416666667</v>
+        <v>11386.4083333333</v>
       </c>
       <c r="N13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!M35</f>
-        <v>10894.1166666667</v>
+        <v>11060.7833333333</v>
       </c>
       <c r="O13" s="170" t="n">
         <f aca="false">'Profit &amp; Loss Account'!N35</f>
-        <v>10790.7833333333</v>
+        <v>10957.45</v>
       </c>
       <c r="P13" s="158"/>
     </row>
@@ -29565,55 +29567,55 @@
       </c>
       <c r="C15" s="170" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>176975.391666666</v>
+        <v>171875.391666666</v>
       </c>
       <c r="D15" s="170" t="n">
         <f aca="false">D11-D13</f>
-        <v>15256.0916666666</v>
+        <v>15089.425</v>
       </c>
       <c r="E15" s="170" t="n">
         <f aca="false">E11-E13</f>
-        <v>15277.9666666666</v>
+        <v>15111.3</v>
       </c>
       <c r="F15" s="170" t="n">
         <f aca="false">F11-F13</f>
-        <v>13217.9666666666</v>
+        <v>11051.3</v>
       </c>
       <c r="G15" s="170" t="n">
         <f aca="false">G11-G13</f>
-        <v>13266.0916666666</v>
+        <v>13099.425</v>
       </c>
       <c r="H15" s="170" t="n">
         <f aca="false">H11-H13</f>
-        <v>18027.7583333333</v>
+        <v>17861.0916666666</v>
       </c>
       <c r="I15" s="170" t="n">
         <f aca="false">I11-I13</f>
-        <v>15461.6333333333</v>
+        <v>14194.9666666666</v>
       </c>
       <c r="J15" s="170" t="n">
         <f aca="false">J11-J13</f>
-        <v>15477.3416666666</v>
+        <v>15310.675</v>
       </c>
       <c r="K15" s="170" t="n">
         <f aca="false">K11-K13</f>
-        <v>15325.4666666666</v>
+        <v>15158.8</v>
       </c>
       <c r="L15" s="170" t="n">
         <f aca="false">L11-L13</f>
-        <v>10972.2166666666</v>
+        <v>10805.55</v>
       </c>
       <c r="M15" s="170" t="n">
         <f aca="false">M11-M13</f>
-        <v>17456.0916666666</v>
+        <v>17289.425</v>
       </c>
       <c r="N15" s="170" t="n">
         <f aca="false">N11-N13</f>
-        <v>16651.7166666666</v>
+        <v>16485.05</v>
       </c>
       <c r="O15" s="170" t="n">
         <f aca="false">O11-O13</f>
-        <v>10585.05</v>
+        <v>10418.3833333333</v>
       </c>
       <c r="P15" s="158"/>
     </row>
@@ -29683,55 +29685,55 @@
       </c>
       <c r="C17" s="170" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>176975.391666666</v>
+        <v>171875.391666666</v>
       </c>
       <c r="D17" s="170" t="n">
         <f aca="false">D15+D16</f>
-        <v>15256.0916666666</v>
+        <v>15089.425</v>
       </c>
       <c r="E17" s="170" t="n">
         <f aca="false">E15+E16</f>
-        <v>15277.9666666666</v>
+        <v>15111.3</v>
       </c>
       <c r="F17" s="170" t="n">
         <f aca="false">F15+F16</f>
-        <v>13217.9666666666</v>
+        <v>11051.3</v>
       </c>
       <c r="G17" s="170" t="n">
         <f aca="false">G15+G16</f>
-        <v>13266.0916666666</v>
+        <v>13099.425</v>
       </c>
       <c r="H17" s="170" t="n">
         <f aca="false">H15+H16</f>
-        <v>18027.7583333333</v>
+        <v>17861.0916666666</v>
       </c>
       <c r="I17" s="170" t="n">
         <f aca="false">I15+I16</f>
-        <v>15461.6333333333</v>
+        <v>14194.9666666666</v>
       </c>
       <c r="J17" s="170" t="n">
         <f aca="false">J15+J16</f>
-        <v>15477.3416666666</v>
+        <v>15310.675</v>
       </c>
       <c r="K17" s="170" t="n">
         <f aca="false">K15+K16</f>
-        <v>15325.4666666666</v>
+        <v>15158.8</v>
       </c>
       <c r="L17" s="170" t="n">
         <f aca="false">L15+L16</f>
-        <v>10972.2166666666</v>
+        <v>10805.55</v>
       </c>
       <c r="M17" s="170" t="n">
         <f aca="false">M15+M16</f>
-        <v>17456.0916666666</v>
+        <v>17289.425</v>
       </c>
       <c r="N17" s="170" t="n">
         <f aca="false">N15+N16</f>
-        <v>16651.7166666666</v>
+        <v>16485.05</v>
       </c>
       <c r="O17" s="170" t="n">
         <f aca="false">O15+O16</f>
-        <v>10585.05</v>
+        <v>10418.3833333333</v>
       </c>
       <c r="P17" s="158"/>
     </row>
@@ -30204,55 +30206,55 @@
       </c>
       <c r="C30" s="170" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>144171.275</v>
+        <v>149271.275</v>
       </c>
       <c r="D30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
-        <v>11839.7416666667</v>
+        <v>12006.4083333333</v>
       </c>
       <c r="E30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(E5&gt;0,E13,C13/C21),0)</f>
-        <v>11147.8666666667</v>
+        <v>11314.5333333333</v>
       </c>
       <c r="F30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(F5&gt;0,F13,C13/C21),0)</f>
-        <v>11411.2</v>
+        <v>13577.8666666667</v>
       </c>
       <c r="G30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(G5&gt;0,G13,C13/C21),0)</f>
-        <v>13659.7416666667</v>
+        <v>13826.4083333333</v>
       </c>
       <c r="H30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H13,C13/C21),0)</f>
-        <v>11301.4083333333</v>
+        <v>11468.075</v>
       </c>
       <c r="I30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
-        <v>11964.2</v>
+        <v>13230.8666666667</v>
       </c>
       <c r="J30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(J5&gt;0,J13,C13/C21),0)</f>
-        <v>13518.4916666667</v>
+        <v>13685.1583333333</v>
       </c>
       <c r="K30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(K5&gt;0,K13,C13/C21),0)</f>
-        <v>10700.3666666667</v>
+        <v>10867.0333333333</v>
       </c>
       <c r="L30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(L5&gt;0,L13,C13/C21),0)</f>
-        <v>15723.6166666667</v>
+        <v>15890.2833333333</v>
       </c>
       <c r="M30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(M5&gt;0,M13,C13/C21),0)</f>
-        <v>11219.7416666667</v>
+        <v>11386.4083333333</v>
       </c>
       <c r="N30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(N5&gt;0,N13,C13/C21),0)</f>
-        <v>10894.1166666667</v>
+        <v>11060.7833333333</v>
       </c>
       <c r="O30" s="170" t="n">
         <f aca="false">IF(C5&gt;0,IF(O5&gt;0,O13,C13/C21),0)</f>
-        <v>10790.7833333333</v>
+        <v>10957.45</v>
       </c>
       <c r="P30" s="158"/>
     </row>
@@ -30281,55 +30283,55 @@
       </c>
       <c r="C32" s="170" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>176975.391666666</v>
+        <v>171875.391666666</v>
       </c>
       <c r="D32" s="170" t="n">
         <f aca="false">D28-D30</f>
-        <v>15256.0916666666</v>
+        <v>15089.425</v>
       </c>
       <c r="E32" s="170" t="n">
         <f aca="false">E28-E30</f>
-        <v>15277.9666666666</v>
+        <v>15111.3</v>
       </c>
       <c r="F32" s="170" t="n">
         <f aca="false">F28-F30</f>
-        <v>13217.9666666666</v>
+        <v>11051.3</v>
       </c>
       <c r="G32" s="170" t="n">
         <f aca="false">G28-G30</f>
-        <v>13266.0916666666</v>
+        <v>13099.425</v>
       </c>
       <c r="H32" s="170" t="n">
         <f aca="false">H28-H30</f>
-        <v>18027.7583333333</v>
+        <v>17861.0916666666</v>
       </c>
       <c r="I32" s="170" t="n">
         <f aca="false">I28-I30</f>
-        <v>15461.6333333333</v>
+        <v>14194.9666666666</v>
       </c>
       <c r="J32" s="170" t="n">
         <f aca="false">J28-J30</f>
-        <v>15477.3416666666</v>
+        <v>15310.675</v>
       </c>
       <c r="K32" s="170" t="n">
         <f aca="false">K28-K30</f>
-        <v>15325.4666666666</v>
+        <v>15158.8</v>
       </c>
       <c r="L32" s="170" t="n">
         <f aca="false">L28-L30</f>
-        <v>10972.2166666666</v>
+        <v>10805.55</v>
       </c>
       <c r="M32" s="170" t="n">
         <f aca="false">M28-M30</f>
-        <v>17456.0916666666</v>
+        <v>17289.425</v>
       </c>
       <c r="N32" s="170" t="n">
         <f aca="false">N28-N30</f>
-        <v>16651.7166666666</v>
+        <v>16485.05</v>
       </c>
       <c r="O32" s="170" t="n">
         <f aca="false">O28-O30</f>
-        <v>10585.05</v>
+        <v>10418.3833333333</v>
       </c>
       <c r="P32" s="158"/>
     </row>
@@ -30399,55 +30401,55 @@
       </c>
       <c r="C34" s="170" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>176975.391666666</v>
+        <v>171875.391666666</v>
       </c>
       <c r="D34" s="170" t="n">
         <f aca="false">D32+D33</f>
-        <v>15256.0916666666</v>
+        <v>15089.425</v>
       </c>
       <c r="E34" s="170" t="n">
         <f aca="false">E32+E33</f>
-        <v>15277.9666666666</v>
+        <v>15111.3</v>
       </c>
       <c r="F34" s="170" t="n">
         <f aca="false">F32+F33</f>
-        <v>13217.9666666666</v>
+        <v>11051.3</v>
       </c>
       <c r="G34" s="170" t="n">
         <f aca="false">G32+G33</f>
-        <v>13266.0916666666</v>
+        <v>13099.425</v>
       </c>
       <c r="H34" s="170" t="n">
         <f aca="false">H32+H33</f>
-        <v>18027.7583333333</v>
+        <v>17861.0916666666</v>
       </c>
       <c r="I34" s="170" t="n">
         <f aca="false">I32+I33</f>
-        <v>15461.6333333333</v>
+        <v>14194.9666666666</v>
       </c>
       <c r="J34" s="170" t="n">
         <f aca="false">J32+J33</f>
-        <v>15477.3416666666</v>
+        <v>15310.675</v>
       </c>
       <c r="K34" s="170" t="n">
         <f aca="false">K32+K33</f>
-        <v>15325.4666666666</v>
+        <v>15158.8</v>
       </c>
       <c r="L34" s="170" t="n">
         <f aca="false">L32+L33</f>
-        <v>10972.2166666666</v>
+        <v>10805.55</v>
       </c>
       <c r="M34" s="170" t="n">
         <f aca="false">M32+M33</f>
-        <v>17456.0916666666</v>
+        <v>17289.425</v>
       </c>
       <c r="N34" s="170" t="n">
         <f aca="false">N32+N33</f>
-        <v>16651.7166666666</v>
+        <v>16485.05</v>
       </c>
       <c r="O34" s="170" t="n">
         <f aca="false">O32+O33</f>
-        <v>10585.05</v>
+        <v>10418.3833333333</v>
       </c>
       <c r="P34" s="158"/>
     </row>
@@ -30496,7 +30498,7 @@
       </c>
       <c r="C37" s="339" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
-        <v>11912</v>
+        <v>13912</v>
       </c>
       <c r="D37" s="158"/>
       <c r="E37" s="158"/>
@@ -30519,7 +30521,7 @@
       </c>
       <c r="C38" s="339" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
-        <v>44000</v>
+        <v>64000</v>
       </c>
       <c r="D38" s="158"/>
       <c r="E38" s="158"/>
@@ -30542,7 +30544,7 @@
       </c>
       <c r="C39" s="339" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>144887.391666666</v>
+        <v>121787.391666666</v>
       </c>
       <c r="D39" s="158"/>
       <c r="E39" s="158"/>
@@ -30588,7 +30590,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>132317.391666666</v>
+        <v>109217.391666666</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30634,7 +30636,7 @@
       </c>
       <c r="C43" s="339" t="n">
         <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>37846.5566666665</v>
+        <v>28606.5566666665</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30657,7 +30659,7 @@
       </c>
       <c r="C44" s="339" t="n">
         <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>4154.38783333333</v>
+        <v>3692.38783333333</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30698,7 +30700,7 @@
       </c>
       <c r="C46" s="341" t="n">
         <f aca="false">C42+C43+C44</f>
-        <v>49541.1444999998</v>
+        <v>39839.1444999998</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="445">
   <si>
     <r>
       <rPr>
@@ -2302,6 +2302,9 @@
   </si>
   <si>
     <t xml:space="preserve">Tax at higher rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tax at additional rate</t>
   </si>
   <si>
     <t xml:space="preserve">National Insurance</t>
@@ -8327,7 +8330,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="344" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="345"/>
@@ -8350,7 +8353,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="348" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E2" s="348"/>
       <c r="F2" s="348"/>
@@ -8361,7 +8364,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="350" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K2" s="350"/>
       <c r="L2" s="351" t="str">
@@ -8407,7 +8410,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="355" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J4" s="355"/>
       <c r="K4" s="355"/>
@@ -8427,7 +8430,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="355" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E5" s="355"/>
       <c r="F5" s="355"/>
@@ -8436,7 +8439,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="355" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J5" s="355"/>
       <c r="K5" s="355"/>
@@ -8461,7 +8464,7 @@
       <c r="G6" s="352"/>
       <c r="H6" s="63"/>
       <c r="I6" s="355" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J6" s="355"/>
       <c r="K6" s="355"/>
@@ -8471,7 +8474,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8481,14 +8484,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="355" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E7" s="355"/>
       <c r="F7" s="355"/>
       <c r="G7" s="352"/>
       <c r="H7" s="63"/>
       <c r="I7" s="355" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J7" s="355"/>
       <c r="K7" s="355"/>
@@ -8498,7 +8501,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8508,20 +8511,20 @@
       </c>
       <c r="C8" s="63"/>
       <c r="D8" s="63" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E8" s="358" t="n">
         <v>12000</v>
       </c>
       <c r="F8" s="63" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="G8" s="358" t="n">
         <v>3000</v>
       </c>
       <c r="H8" s="63"/>
       <c r="I8" s="355" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J8" s="355"/>
       <c r="K8" s="355"/>
@@ -8531,7 +8534,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8546,18 +8549,18 @@
       <c r="G9" s="352"/>
       <c r="H9" s="63"/>
       <c r="I9" s="355" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J9" s="355"/>
       <c r="K9" s="355"/>
       <c r="L9" s="359" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M9" s="359" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N9" s="360" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="O9" s="352"/>
     </row>
@@ -8587,16 +8590,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="348" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E11" s="348"/>
       <c r="F11" s="348"/>
       <c r="G11" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="361" t="n">
@@ -8626,7 +8629,7 @@
       <c r="G12" s="352"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="361" t="n">
@@ -8648,7 +8651,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="355" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E13" s="355"/>
       <c r="F13" s="355"/>
@@ -8657,7 +8660,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="361" t="n">
@@ -8679,7 +8682,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="355" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="E14" s="355"/>
       <c r="F14" s="355"/>
@@ -8688,7 +8691,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="348" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J14" s="348"/>
       <c r="K14" s="348"/>
@@ -8707,7 +8710,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="355" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E15" s="355"/>
       <c r="F15" s="355"/>
@@ -8730,7 +8733,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="355" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="E16" s="355"/>
       <c r="F16" s="355"/>
@@ -8739,7 +8742,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="355" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J16" s="355"/>
       <c r="K16" s="355"/>
@@ -8747,7 +8750,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N16" s="63"/>
       <c r="O16" s="63"/>
@@ -8759,7 +8762,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="355" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E17" s="355"/>
       <c r="F17" s="355"/>
@@ -8801,24 +8804,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="348" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E19" s="348"/>
       <c r="F19" s="352" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="G19" s="352" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="364" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J19" s="364"/>
       <c r="K19" s="364"/>
       <c r="L19" s="63"/>
       <c r="M19" s="365" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8855,7 +8858,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="355" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E21" s="355"/>
       <c r="F21" s="358" t="n">
@@ -8880,7 +8883,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="358" t="n">
@@ -8891,13 +8894,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="364" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="J22" s="364"/>
       <c r="K22" s="364"/>
       <c r="L22" s="63"/>
       <c r="M22" s="365" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8905,7 +8908,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="354" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8930,11 +8933,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="354" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="348" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="E24" s="348"/>
       <c r="F24" s="63"/>
@@ -8972,7 +8975,7 @@
       <c r="B26" s="368"/>
       <c r="C26" s="63"/>
       <c r="D26" s="355" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E26" s="355"/>
       <c r="F26" s="358" t="n">
@@ -8993,7 +8996,7 @@
       <c r="B27" s="368"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="356" t="n">
@@ -24811,55 +24814,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>39839.1444999998</v>
+        <v>44196.7828333331</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24869,55 +24872,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>105036.247166666</v>
+        <v>100678.608833333</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10769.4962916667</v>
+        <v>10406.3597638889</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10791.3712916666</v>
+        <v>10428.2347638889</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6731.37129166664</v>
+        <v>6368.23476388887</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5779.49629166665</v>
+        <v>5416.35976388888</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>13541.1629583333</v>
+        <v>13178.0264305555</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9875.03795833332</v>
+        <v>9511.90143055555</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7990.74629166665</v>
+        <v>7627.60976388888</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10838.8712916666</v>
+        <v>10475.7347638889</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>6485.62129166664</v>
+        <v>6122.48476388887</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9969.49629166665</v>
+        <v>9606.35976388888</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>12165.1212916666</v>
+        <v>11801.9847638889</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>98.4546249999789</v>
+        <v>-264.681902777792</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -30566,8 +30569,8 @@
         <v>396</v>
       </c>
       <c r="C40" s="339" t="n">
-        <f aca="false">Admin!N$4</f>
-        <v>12570</v>
+        <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
+        <v>1676.30416666687</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -30590,7 +30593,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>109217.391666666</v>
+        <v>120111.087499999</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30612,8 +30615,8 @@
         <v>398</v>
       </c>
       <c r="C42" s="339" t="n">
-        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!N$12),C41*Admin!N$6,Admin!N$12*Admin!N$6)),0)</f>
-        <v>7540.2</v>
+        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
+        <v>7540</v>
       </c>
       <c r="D42" s="340"/>
       <c r="E42" s="158"/>
@@ -30635,8 +30638,8 @@
         <v>399</v>
       </c>
       <c r="C43" s="339" t="n">
-        <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>28606.5566666665</v>
+        <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
+        <v>32964.4349999998</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30658,8 +30661,8 @@
         <v>400</v>
       </c>
       <c r="C44" s="339" t="n">
-        <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>3692.38783333333</v>
+        <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
+        <v>0</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30675,10 +30678,15 @@
       <c r="O44" s="158"/>
       <c r="P44" s="158"/>
     </row>
-    <row r="45" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="158"/>
-      <c r="B45" s="182"/>
-      <c r="C45" s="339"/>
+      <c r="B45" s="182" t="s">
+        <v>401</v>
+      </c>
+      <c r="C45" s="339" t="n">
+        <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
+        <v>3692.34783333333</v>
+      </c>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
       <c r="F45" s="158"/>
@@ -30696,11 +30704,11 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="158"/>
       <c r="B46" s="182" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C46" s="341" t="n">
-        <f aca="false">C42+C43+C44</f>
-        <v>39839.1444999998</v>
+        <f aca="false">C42+C43+C44+C45</f>
+        <v>44196.7828333331</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="827" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="444">
   <si>
     <r>
       <rPr>
@@ -2302,9 +2302,6 @@
   </si>
   <si>
     <t xml:space="preserve">Tax at higher rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tax at additional rate</t>
   </si>
   <si>
     <t xml:space="preserve">National Insurance</t>
@@ -8330,7 +8327,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="344" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="345"/>
@@ -8353,7 +8350,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="348" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E2" s="348"/>
       <c r="F2" s="348"/>
@@ -8364,7 +8361,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="350" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K2" s="350"/>
       <c r="L2" s="351" t="str">
@@ -8410,7 +8407,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="355" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J4" s="355"/>
       <c r="K4" s="355"/>
@@ -8430,7 +8427,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="355" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E5" s="355"/>
       <c r="F5" s="355"/>
@@ -8439,7 +8436,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="355" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J5" s="355"/>
       <c r="K5" s="355"/>
@@ -8464,7 +8461,7 @@
       <c r="G6" s="352"/>
       <c r="H6" s="63"/>
       <c r="I6" s="355" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J6" s="355"/>
       <c r="K6" s="355"/>
@@ -8474,7 +8471,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8484,14 +8481,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="355" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E7" s="355"/>
       <c r="F7" s="355"/>
       <c r="G7" s="352"/>
       <c r="H7" s="63"/>
       <c r="I7" s="355" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J7" s="355"/>
       <c r="K7" s="355"/>
@@ -8501,7 +8498,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8511,20 +8508,20 @@
       </c>
       <c r="C8" s="63"/>
       <c r="D8" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="E8" s="358" t="n">
         <v>12000</v>
       </c>
       <c r="F8" s="63" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G8" s="358" t="n">
         <v>3000</v>
       </c>
       <c r="H8" s="63"/>
       <c r="I8" s="355" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J8" s="355"/>
       <c r="K8" s="355"/>
@@ -8534,7 +8531,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8549,18 +8546,18 @@
       <c r="G9" s="352"/>
       <c r="H9" s="63"/>
       <c r="I9" s="355" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="J9" s="355"/>
       <c r="K9" s="355"/>
       <c r="L9" s="359" t="s">
+        <v>416</v>
+      </c>
+      <c r="M9" s="359" t="s">
         <v>417</v>
       </c>
-      <c r="M9" s="359" t="s">
+      <c r="N9" s="360" t="s">
         <v>418</v>
-      </c>
-      <c r="N9" s="360" t="s">
-        <v>419</v>
       </c>
       <c r="O9" s="352"/>
     </row>
@@ -8590,16 +8587,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="348" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E11" s="348"/>
       <c r="F11" s="348"/>
       <c r="G11" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="361" t="n">
@@ -8629,7 +8626,7 @@
       <c r="G12" s="352"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="361" t="n">
@@ -8651,7 +8648,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="355" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E13" s="355"/>
       <c r="F13" s="355"/>
@@ -8660,7 +8657,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="361" t="n">
@@ -8682,7 +8679,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="355" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E14" s="355"/>
       <c r="F14" s="355"/>
@@ -8691,7 +8688,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="348" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="J14" s="348"/>
       <c r="K14" s="348"/>
@@ -8710,7 +8707,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="355" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E15" s="355"/>
       <c r="F15" s="355"/>
@@ -8733,7 +8730,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="355" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="E16" s="355"/>
       <c r="F16" s="355"/>
@@ -8742,7 +8739,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="355" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="J16" s="355"/>
       <c r="K16" s="355"/>
@@ -8750,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="N16" s="63"/>
       <c r="O16" s="63"/>
@@ -8762,7 +8759,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="355" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E17" s="355"/>
       <c r="F17" s="355"/>
@@ -8804,24 +8801,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="348" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E19" s="348"/>
       <c r="F19" s="352" t="s">
+        <v>432</v>
+      </c>
+      <c r="G19" s="352" t="s">
         <v>433</v>
-      </c>
-      <c r="G19" s="352" t="s">
-        <v>434</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="364" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="J19" s="364"/>
       <c r="K19" s="364"/>
       <c r="L19" s="63"/>
       <c r="M19" s="365" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8858,7 +8855,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="355" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E21" s="355"/>
       <c r="F21" s="358" t="n">
@@ -8883,7 +8880,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="358" t="n">
@@ -8894,13 +8891,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="364" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="J22" s="364"/>
       <c r="K22" s="364"/>
       <c r="L22" s="63"/>
       <c r="M22" s="365" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8908,7 +8905,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="354" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8933,11 +8930,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="354" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="348" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E24" s="348"/>
       <c r="F24" s="63"/>
@@ -8975,7 +8972,7 @@
       <c r="B26" s="368"/>
       <c r="C26" s="63"/>
       <c r="D26" s="355" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E26" s="355"/>
       <c r="F26" s="358" t="n">
@@ -8996,7 +8993,7 @@
       <c r="B27" s="368"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="356" t="n">
@@ -24814,55 +24811,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>44196.7828333331</v>
+        <v>39839.1444999998</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24872,55 +24869,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>100678.608833333</v>
+        <v>105036.247166666</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10406.3597638889</v>
+        <v>10769.4962916667</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10428.2347638889</v>
+        <v>10791.3712916666</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6368.23476388887</v>
+        <v>6731.37129166664</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5416.35976388888</v>
+        <v>5779.49629166665</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>13178.0264305555</v>
+        <v>13541.1629583333</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9511.90143055555</v>
+        <v>9875.03795833332</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7627.60976388888</v>
+        <v>7990.74629166665</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10475.7347638889</v>
+        <v>10838.8712916666</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>6122.48476388887</v>
+        <v>6485.62129166664</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9606.35976388888</v>
+        <v>9969.49629166665</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11801.9847638889</v>
+        <v>12165.1212916666</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-264.681902777792</v>
+        <v>98.4546249999789</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -30569,8 +30566,8 @@
         <v>396</v>
       </c>
       <c r="C40" s="339" t="n">
-        <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>1676.30416666687</v>
+        <f aca="false">Admin!N$4</f>
+        <v>12570</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -30593,7 +30590,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>120111.087499999</v>
+        <v>109217.391666666</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30615,8 +30612,8 @@
         <v>398</v>
       </c>
       <c r="C42" s="339" t="n">
-        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
-        <v>7540</v>
+        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!N$12),C41*Admin!N$6,Admin!N$12*Admin!N$6)),0)</f>
+        <v>7540.2</v>
       </c>
       <c r="D42" s="340"/>
       <c r="E42" s="158"/>
@@ -30638,8 +30635,8 @@
         <v>399</v>
       </c>
       <c r="C43" s="339" t="n">
-        <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>32964.4349999998</v>
+        <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
+        <v>28606.5566666665</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30661,8 +30658,8 @@
         <v>400</v>
       </c>
       <c r="C44" s="339" t="n">
-        <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
-        <v>0</v>
+        <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
+        <v>3692.38783333333</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30678,15 +30675,10 @@
       <c r="O44" s="158"/>
       <c r="P44" s="158"/>
     </row>
-    <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="158"/>
-      <c r="B45" s="182" t="s">
-        <v>401</v>
-      </c>
-      <c r="C45" s="339" t="n">
-        <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3692.34783333333</v>
-      </c>
+      <c r="B45" s="182"/>
+      <c r="C45" s="339"/>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
       <c r="F45" s="158"/>
@@ -30704,11 +30696,11 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="158"/>
       <c r="B46" s="182" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C46" s="341" t="n">
-        <f aca="false">C42+C43+C44+C45</f>
-        <v>44196.7828333331</v>
+        <f aca="false">C42+C43+C44</f>
+        <v>39839.1444999998</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="444">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="443">
   <si>
     <r>
       <rPr>
@@ -2304,6 +2304,9 @@
     <t xml:space="preserve">Tax at higher rate</t>
   </si>
   <si>
+    <t xml:space="preserve">Tax at additional rate</t>
+  </si>
+  <si>
     <t xml:space="preserve">National Insurance</t>
   </si>
   <si>
@@ -2338,12 +2341,6 @@
   </si>
   <si>
     <t xml:space="preserve">Higher rate applicable on taxable income over higher rate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Costing over </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restricted to</t>
   </si>
   <si>
     <t xml:space="preserve">Additional rate applicable above the higher rate limit</t>
@@ -4744,10 +4741,10 @@
             <v>52500</v>
           </cell>
           <cell r="R1">
-            <v>3000</v>
+            <v>3360</v>
           </cell>
           <cell r="S1">
-            <v>21000</v>
+            <v>20640</v>
           </cell>
         </row>
         <row r="1">
@@ -4761,7 +4758,7 @@
             <v>17328</v>
           </cell>
           <cell r="Y1">
-            <v>8500</v>
+            <v>8140</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -4769,7 +4766,7 @@
         </row>
         <row r="38">
           <cell r="R38">
-            <v>3000</v>
+            <v>3360</v>
           </cell>
         </row>
       </sheetData>
@@ -8327,7 +8324,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="344" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="345"/>
@@ -8350,7 +8347,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="348" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E2" s="348"/>
       <c r="F2" s="348"/>
@@ -8361,7 +8358,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="350" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="K2" s="350"/>
       <c r="L2" s="351" t="str">
@@ -8407,7 +8404,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="355" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="J4" s="355"/>
       <c r="K4" s="355"/>
@@ -8427,7 +8424,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="355" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E5" s="355"/>
       <c r="F5" s="355"/>
@@ -8436,7 +8433,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="355" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J5" s="355"/>
       <c r="K5" s="355"/>
@@ -8461,7 +8458,7 @@
       <c r="G6" s="352"/>
       <c r="H6" s="63"/>
       <c r="I6" s="355" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="J6" s="355"/>
       <c r="K6" s="355"/>
@@ -8471,7 +8468,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8481,14 +8478,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="355" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E7" s="355"/>
       <c r="F7" s="355"/>
       <c r="G7" s="352"/>
       <c r="H7" s="63"/>
       <c r="I7" s="355" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="J7" s="355"/>
       <c r="K7" s="355"/>
@@ -8498,7 +8495,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8507,21 +8504,13 @@
         <v>46234</v>
       </c>
       <c r="C8" s="63"/>
-      <c r="D8" s="63" t="s">
-        <v>412</v>
-      </c>
-      <c r="E8" s="358" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F8" s="63" t="s">
-        <v>413</v>
-      </c>
-      <c r="G8" s="358" t="n">
-        <v>3000</v>
-      </c>
+      <c r="D8" s="63"/>
+      <c r="E8" s="358"/>
+      <c r="F8" s="63"/>
+      <c r="G8" s="358"/>
       <c r="H8" s="63"/>
       <c r="I8" s="355" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J8" s="355"/>
       <c r="K8" s="355"/>
@@ -8531,7 +8520,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8546,18 +8535,18 @@
       <c r="G9" s="352"/>
       <c r="H9" s="63"/>
       <c r="I9" s="355" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="J9" s="355"/>
       <c r="K9" s="355"/>
       <c r="L9" s="359" t="s">
+        <v>415</v>
+      </c>
+      <c r="M9" s="359" t="s">
         <v>416</v>
       </c>
-      <c r="M9" s="359" t="s">
+      <c r="N9" s="360" t="s">
         <v>417</v>
-      </c>
-      <c r="N9" s="360" t="s">
-        <v>418</v>
       </c>
       <c r="O9" s="352"/>
     </row>
@@ -8587,16 +8576,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="348" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E11" s="348"/>
       <c r="F11" s="348"/>
       <c r="G11" s="352" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="361" t="n">
@@ -8626,7 +8615,7 @@
       <c r="G12" s="352"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="361" t="n">
@@ -8648,7 +8637,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="355" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E13" s="355"/>
       <c r="F13" s="355"/>
@@ -8657,7 +8646,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="361" t="n">
@@ -8679,7 +8668,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="355" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E14" s="355"/>
       <c r="F14" s="355"/>
@@ -8688,7 +8677,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="348" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="J14" s="348"/>
       <c r="K14" s="348"/>
@@ -8707,7 +8696,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="355" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E15" s="355"/>
       <c r="F15" s="355"/>
@@ -8730,7 +8719,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="355" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E16" s="355"/>
       <c r="F16" s="355"/>
@@ -8739,7 +8728,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="355" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="J16" s="355"/>
       <c r="K16" s="355"/>
@@ -8747,7 +8736,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="N16" s="63"/>
       <c r="O16" s="63"/>
@@ -8759,7 +8748,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="355" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="E17" s="355"/>
       <c r="F17" s="355"/>
@@ -8801,24 +8790,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="348" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E19" s="348"/>
       <c r="F19" s="352" t="s">
+        <v>431</v>
+      </c>
+      <c r="G19" s="352" t="s">
         <v>432</v>
-      </c>
-      <c r="G19" s="352" t="s">
-        <v>433</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="364" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="J19" s="364"/>
       <c r="K19" s="364"/>
       <c r="L19" s="63"/>
       <c r="M19" s="365" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8855,7 +8844,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="355" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E21" s="355"/>
       <c r="F21" s="358" t="n">
@@ -8880,7 +8869,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="358" t="n">
@@ -8891,13 +8880,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="364" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="J22" s="364"/>
       <c r="K22" s="364"/>
       <c r="L22" s="63"/>
       <c r="M22" s="365" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8905,7 +8894,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="354" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8930,11 +8919,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="354" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="348" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="E24" s="348"/>
       <c r="F24" s="63"/>
@@ -8972,7 +8961,7 @@
       <c r="B26" s="368"/>
       <c r="C26" s="63"/>
       <c r="D26" s="355" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E26" s="355"/>
       <c r="F26" s="358" t="n">
@@ -8993,7 +8982,7 @@
       <c r="B27" s="368"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="356" t="n">
@@ -17261,7 +17250,7 @@
       </c>
       <c r="O144" s="98" t="n">
         <f aca="false">[1]Schedule!$Y$1</f>
-        <v>8500</v>
+        <v>8140</v>
       </c>
       <c r="P144" s="98"/>
       <c r="Q144" s="98"/>
@@ -17500,7 +17489,7 @@
       </c>
       <c r="D152" s="98" t="n">
         <f aca="false">SUM([1]Schedule!$R$38:$R$42)+SUM([1]Schedule!$R$91:$R$95)</f>
-        <v>3000</v>
+        <v>3360</v>
       </c>
       <c r="E152" s="98"/>
       <c r="F152" s="98"/>
@@ -24811,55 +24800,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>39839.1444999998</v>
+        <v>44196.7828333331</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3319.92870833332</v>
+        <v>3683.06523611109</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24869,55 +24858,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>105036.247166666</v>
+        <v>100678.608833333</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10769.4962916667</v>
+        <v>10406.3597638889</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10791.3712916666</v>
+        <v>10428.2347638889</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6731.37129166664</v>
+        <v>6368.23476388887</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5779.49629166665</v>
+        <v>5416.35976388888</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>13541.1629583333</v>
+        <v>13178.0264305555</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9875.03795833332</v>
+        <v>9511.90143055555</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7990.74629166665</v>
+        <v>7627.60976388888</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10838.8712916666</v>
+        <v>10475.7347638889</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>6485.62129166664</v>
+        <v>6122.48476388887</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9969.49629166665</v>
+        <v>9606.35976388888</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>12165.1212916666</v>
+        <v>11801.9847638889</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>98.4546249999789</v>
+        <v>-264.681902777792</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -30566,8 +30555,8 @@
         <v>396</v>
       </c>
       <c r="C40" s="339" t="n">
-        <f aca="false">Admin!N$4</f>
-        <v>12570</v>
+        <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
+        <v>1676.30416666687</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -30590,7 +30579,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>109217.391666666</v>
+        <v>120111.087499999</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30612,8 +30601,8 @@
         <v>398</v>
       </c>
       <c r="C42" s="339" t="n">
-        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!N$12),C41*Admin!N$6,Admin!N$12*Admin!N$6)),0)</f>
-        <v>7540.2</v>
+        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
+        <v>7540</v>
       </c>
       <c r="D42" s="340"/>
       <c r="E42" s="158"/>
@@ -30635,8 +30624,8 @@
         <v>399</v>
       </c>
       <c r="C43" s="339" t="n">
-        <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
-        <v>28606.5566666665</v>
+        <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
+        <v>32964.4349999998</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30658,8 +30647,8 @@
         <v>400</v>
       </c>
       <c r="C44" s="339" t="n">
-        <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
-        <v>3692.38783333333</v>
+        <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
+        <v>0</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30675,10 +30664,15 @@
       <c r="O44" s="158"/>
       <c r="P44" s="158"/>
     </row>
-    <row r="45" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="158"/>
-      <c r="B45" s="182"/>
-      <c r="C45" s="339"/>
+      <c r="B45" s="182" t="s">
+        <v>401</v>
+      </c>
+      <c r="C45" s="339" t="n">
+        <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
+        <v>3692.34783333333</v>
+      </c>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
       <c r="F45" s="158"/>
@@ -30696,11 +30690,11 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="158"/>
       <c r="B46" s="182" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C46" s="341" t="n">
-        <f aca="false">C42+C43+C44</f>
-        <v>39839.1444999998</v>
+        <f aca="false">C42+C43+C44+C45</f>
+        <v>44196.7828333331</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="825" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="826" uniqueCount="444">
   <si>
     <r>
       <rPr>
@@ -2304,9 +2304,6 @@
     <t xml:space="preserve">Tax at higher rate</t>
   </si>
   <si>
-    <t xml:space="preserve">Tax at additional rate</t>
-  </si>
-  <si>
     <t xml:space="preserve">National Insurance</t>
   </si>
   <si>
@@ -2341,6 +2338,12 @@
   </si>
   <si>
     <t xml:space="preserve">Higher rate applicable on taxable income over higher rate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Costing over </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restricted to</t>
   </si>
   <si>
     <t xml:space="preserve">Additional rate applicable above the higher rate limit</t>
@@ -4741,10 +4744,10 @@
             <v>52500</v>
           </cell>
           <cell r="R1">
-            <v>3360</v>
+            <v>3000</v>
           </cell>
           <cell r="S1">
-            <v>20640</v>
+            <v>21000</v>
           </cell>
         </row>
         <row r="1">
@@ -4758,7 +4761,7 @@
             <v>17328</v>
           </cell>
           <cell r="Y1">
-            <v>8140</v>
+            <v>8500</v>
           </cell>
           <cell r="Z1">
             <v>0</v>
@@ -4766,7 +4769,7 @@
         </row>
         <row r="38">
           <cell r="R38">
-            <v>3360</v>
+            <v>3000</v>
           </cell>
         </row>
       </sheetData>
@@ -8324,7 +8327,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="344" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="345"/>
@@ -8347,7 +8350,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="348" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="E2" s="348"/>
       <c r="F2" s="348"/>
@@ -8358,7 +8361,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="350" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="K2" s="350"/>
       <c r="L2" s="351" t="str">
@@ -8404,7 +8407,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="355" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="J4" s="355"/>
       <c r="K4" s="355"/>
@@ -8424,7 +8427,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="355" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E5" s="355"/>
       <c r="F5" s="355"/>
@@ -8433,7 +8436,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="355" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J5" s="355"/>
       <c r="K5" s="355"/>
@@ -8458,7 +8461,7 @@
       <c r="G6" s="352"/>
       <c r="H6" s="63"/>
       <c r="I6" s="355" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J6" s="355"/>
       <c r="K6" s="355"/>
@@ -8468,7 +8471,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8478,14 +8481,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="355" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="E7" s="355"/>
       <c r="F7" s="355"/>
       <c r="G7" s="352"/>
       <c r="H7" s="63"/>
       <c r="I7" s="355" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J7" s="355"/>
       <c r="K7" s="355"/>
@@ -8495,7 +8498,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8504,13 +8507,21 @@
         <v>46234</v>
       </c>
       <c r="C8" s="63"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="358"/>
-      <c r="F8" s="63"/>
-      <c r="G8" s="358"/>
+      <c r="D8" s="63" t="s">
+        <v>412</v>
+      </c>
+      <c r="E8" s="358" t="n">
+        <v>12000</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>413</v>
+      </c>
+      <c r="G8" s="358" t="n">
+        <v>3000</v>
+      </c>
       <c r="H8" s="63"/>
       <c r="I8" s="355" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J8" s="355"/>
       <c r="K8" s="355"/>
@@ -8520,7 +8531,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8535,18 +8546,18 @@
       <c r="G9" s="352"/>
       <c r="H9" s="63"/>
       <c r="I9" s="355" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="J9" s="355"/>
       <c r="K9" s="355"/>
       <c r="L9" s="359" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M9" s="359" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N9" s="360" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="O9" s="352"/>
     </row>
@@ -8576,16 +8587,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="348" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E11" s="348"/>
       <c r="F11" s="348"/>
       <c r="G11" s="352" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="361" t="n">
@@ -8615,7 +8626,7 @@
       <c r="G12" s="352"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="361" t="n">
@@ -8637,7 +8648,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="355" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E13" s="355"/>
       <c r="F13" s="355"/>
@@ -8646,7 +8657,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="361" t="n">
@@ -8668,7 +8679,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="355" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E14" s="355"/>
       <c r="F14" s="355"/>
@@ -8677,7 +8688,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="348" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J14" s="348"/>
       <c r="K14" s="348"/>
@@ -8696,7 +8707,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="355" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E15" s="355"/>
       <c r="F15" s="355"/>
@@ -8719,7 +8730,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="355" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E16" s="355"/>
       <c r="F16" s="355"/>
@@ -8728,7 +8739,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="355" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J16" s="355"/>
       <c r="K16" s="355"/>
@@ -8736,7 +8747,7 @@
         <v>0</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N16" s="63"/>
       <c r="O16" s="63"/>
@@ -8748,7 +8759,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="355" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E17" s="355"/>
       <c r="F17" s="355"/>
@@ -8790,24 +8801,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="348" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E19" s="348"/>
       <c r="F19" s="352" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="G19" s="352" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="364" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="J19" s="364"/>
       <c r="K19" s="364"/>
       <c r="L19" s="63"/>
       <c r="M19" s="365" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8844,7 +8855,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="355" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E21" s="355"/>
       <c r="F21" s="358" t="n">
@@ -8869,7 +8880,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="358" t="n">
@@ -8880,13 +8891,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="364" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J22" s="364"/>
       <c r="K22" s="364"/>
       <c r="L22" s="63"/>
       <c r="M22" s="365" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8894,7 +8905,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="354" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8919,11 +8930,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="354" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="348" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="E24" s="348"/>
       <c r="F24" s="63"/>
@@ -8961,7 +8972,7 @@
       <c r="B26" s="368"/>
       <c r="C26" s="63"/>
       <c r="D26" s="355" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E26" s="355"/>
       <c r="F26" s="358" t="n">
@@ -8982,7 +8993,7 @@
       <c r="B27" s="368"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="356" t="n">
@@ -17250,7 +17261,7 @@
       </c>
       <c r="O144" s="98" t="n">
         <f aca="false">[1]Schedule!$Y$1</f>
-        <v>8140</v>
+        <v>8500</v>
       </c>
       <c r="P144" s="98"/>
       <c r="Q144" s="98"/>
@@ -17489,7 +17500,7 @@
       </c>
       <c r="D152" s="98" t="n">
         <f aca="false">SUM([1]Schedule!$R$38:$R$42)+SUM([1]Schedule!$R$91:$R$95)</f>
-        <v>3360</v>
+        <v>3000</v>
       </c>
       <c r="E152" s="98"/>
       <c r="F152" s="98"/>
@@ -24800,55 +24811,55 @@
       </c>
       <c r="B44" s="177" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>44196.7828333331</v>
+        <v>39839.1444999998</v>
       </c>
       <c r="C44" s="177" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="D44" s="177" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="E44" s="177" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="F44" s="177" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="G44" s="177" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="H44" s="177" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="I44" s="177" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="J44" s="177" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="K44" s="177" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="L44" s="177" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="M44" s="177" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="N44" s="177" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3683.06523611109</v>
+        <v>3319.92870833332</v>
       </c>
       <c r="O44" s="164"/>
     </row>
@@ -24858,55 +24869,55 @@
       </c>
       <c r="B45" s="189" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>100678.608833333</v>
+        <v>105036.247166666</v>
       </c>
       <c r="C45" s="190" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10406.3597638889</v>
+        <v>10769.4962916667</v>
       </c>
       <c r="D45" s="191" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10428.2347638889</v>
+        <v>10791.3712916666</v>
       </c>
       <c r="E45" s="191" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6368.23476388887</v>
+        <v>6731.37129166664</v>
       </c>
       <c r="F45" s="191" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5416.35976388888</v>
+        <v>5779.49629166665</v>
       </c>
       <c r="G45" s="191" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>13178.0264305555</v>
+        <v>13541.1629583333</v>
       </c>
       <c r="H45" s="191" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9511.90143055555</v>
+        <v>9875.03795833332</v>
       </c>
       <c r="I45" s="191" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7627.60976388888</v>
+        <v>7990.74629166665</v>
       </c>
       <c r="J45" s="191" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10475.7347638889</v>
+        <v>10838.8712916666</v>
       </c>
       <c r="K45" s="191" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>6122.48476388887</v>
+        <v>6485.62129166664</v>
       </c>
       <c r="L45" s="191" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9606.35976388888</v>
+        <v>9969.49629166665</v>
       </c>
       <c r="M45" s="191" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11801.9847638889</v>
+        <v>12165.1212916666</v>
       </c>
       <c r="N45" s="191" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-264.681902777792</v>
+        <v>98.4546249999789</v>
       </c>
       <c r="O45" s="164"/>
     </row>
@@ -30555,8 +30566,8 @@
         <v>396</v>
       </c>
       <c r="C40" s="339" t="n">
-        <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>1676.30416666687</v>
+        <f aca="false">Admin!N$4</f>
+        <v>12570</v>
       </c>
       <c r="D40" s="158"/>
       <c r="E40" s="158"/>
@@ -30579,7 +30590,7 @@
       </c>
       <c r="C41" s="339" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>120111.087499999</v>
+        <v>109217.391666666</v>
       </c>
       <c r="D41" s="158"/>
       <c r="E41" s="158"/>
@@ -30601,8 +30612,8 @@
         <v>398</v>
       </c>
       <c r="C42" s="339" t="n">
-        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
-        <v>7540</v>
+        <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!N$12),C41*Admin!N$6,Admin!N$12*Admin!N$6)),0)</f>
+        <v>7540.2</v>
       </c>
       <c r="D42" s="340"/>
       <c r="E42" s="158"/>
@@ -30624,8 +30635,8 @@
         <v>399</v>
       </c>
       <c r="C43" s="339" t="n">
-        <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>32964.4349999998</v>
+        <f aca="false">IF((C41&gt;Admin!N$12),((C41-Admin!N$12)*Admin!N$7),0)</f>
+        <v>28606.5566666665</v>
       </c>
       <c r="D43" s="158"/>
       <c r="E43" s="158"/>
@@ -30647,8 +30658,8 @@
         <v>400</v>
       </c>
       <c r="C44" s="339" t="n">
-        <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
-        <v>0</v>
+        <f aca="false">IF((C41&gt;0),IF(C41&gt;Admin!N12,Admin!N12*Admin!L20+(C41-Admin!N12)*Admin!L23,C41*Admin!L$20),0)</f>
+        <v>3692.38783333333</v>
       </c>
       <c r="D44" s="158"/>
       <c r="E44" s="158"/>
@@ -30664,15 +30675,10 @@
       <c r="O44" s="158"/>
       <c r="P44" s="158"/>
     </row>
-    <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="158"/>
-      <c r="B45" s="182" t="s">
-        <v>401</v>
-      </c>
-      <c r="C45" s="339" t="n">
-        <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3692.34783333333</v>
-      </c>
+      <c r="B45" s="182"/>
+      <c r="C45" s="339"/>
       <c r="D45" s="158"/>
       <c r="E45" s="158"/>
       <c r="F45" s="158"/>
@@ -30690,11 +30696,11 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="158"/>
       <c r="B46" s="182" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="C46" s="341" t="n">
-        <f aca="false">C42+C43+C44+C45</f>
-        <v>44196.7828333331</v>
+        <f aca="false">C42+C43+C44</f>
+        <v>39839.1444999998</v>
       </c>
       <c r="D46" s="158"/>
       <c r="E46" s="158"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="437">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="434">
   <si>
     <r>
       <rPr>
@@ -592,7 +592,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Any other business income not included in box 8</t>
+    <t xml:space="preserve">Any other business income not included in box 9</t>
   </si>
   <si>
     <t xml:space="preserve">by your business</t>
@@ -630,11 +630,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> to see which expenses are allowed for tax purposes. If your annual turnover was below £30,000</t>
+      <t xml:space="preserve"> to see which expenses are allowed for tax purposes. If your annual turnover was below the VAT threshold shown above</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">you may just put your total expenses in box 19, rather than filling in the whole section.</t>
+    <t xml:space="preserve">you may just put your total expenses in box 20, rather than filling in the whole section.</t>
   </si>
   <si>
     <t xml:space="preserve">Cost of goods bought for re-sale or goods used</t>
@@ -723,7 +723,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">total of boxes 10 to 18</t>
+      <t xml:space="preserve">total of boxes 11 to 19</t>
     </r>
   </si>
   <si>
@@ -772,10 +772,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">expenses (box 8 + box 9 minus box 19)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income (box 8 + box 9 minus box 19 is negative)</t>
+    <t xml:space="preserve">expenses (box 9 + box 10 minus box 20)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income (box 9 + box 10 minus box 20 is negative)</t>
   </si>
   <si>
     <t xml:space="preserve">Tax allowances for vehicles and equipment (capital allowances)</t>
@@ -915,17 +915,17 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">up to the amount in box 27</t>
+      <t xml:space="preserve">up to the amount in box 28</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Net business profit for tax purposes (if box 20 + box 25 +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any other business income not included in boxes 8 or 9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">box 26 minus boxes 21 to 24) is positive)</t>
+    <t xml:space="preserve">Net business profit for tax purposes (if box 21 + box 26 +</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any other business income not included in boxes 9 or 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box 27 minus boxes 22 to 25) is positive)</t>
   </si>
   <si>
     <t xml:space="preserve"> - for example, Business Start-up Allowance</t>
@@ -937,13 +937,13 @@
     <t xml:space="preserve">Total taxable profits from this business</t>
   </si>
   <si>
-    <t xml:space="preserve">Net business loss for tax purposes (if boxes 21 to 24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if box 27 + box 29 minus box 28 is positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">minus (box 20 + box 25 + box 26) is positive)</t>
+    <t xml:space="preserve">Net business loss for tax purposes (if boxes 22 to 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if box 28 + box 30 minus box 29 is positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minus (box 21 + box 26 + box 27) is positive)</t>
   </si>
   <si>
     <t xml:space="preserve">Losses, Class 4 NICs and deductions</t>
@@ -956,7 +956,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">If you have made a loss for tax purposes (box 29), read page SESN 7 of the </t>
+      <t xml:space="preserve">If you have made a loss for tax purposes (box 32), read page SESN 7 of the </t>
     </r>
     <r>
       <rPr>
@@ -975,17 +975,26 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> and fill in boxes 30 to 32 as appropriate.</t>
+      <t xml:space="preserve"> and fill in boxes 33 to 35 as appropriate.</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">Loss from this tax year set-off against other income</t>
   </si>
   <si>
+    <t xml:space="preserve">for </t>
+  </si>
+  <si>
+    <t xml:space="preserve">choose to pay Class 2 NICs voluntarily, put 'X' in the box</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss to be carried back to previous year(s) and set-off</t>
+  </si>
+  <si>
     <t xml:space="preserve">If you are exempt from paying Class 4 NICs, put 'X' in the</t>
   </si>
   <si>
-    <t xml:space="preserve">for </t>
+    <t xml:space="preserve">against income (or capital gains)</t>
   </si>
   <si>
     <r>
@@ -1007,42 +1016,6 @@
       </rPr>
       <t xml:space="preserve">read page SESN 10 of the notes</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Loss to be carried back to previous year(s) and set-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you have been given a </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Class 4 NICs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">against income (or capital gains)</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">deferment certificate, put 'X' in the box - </t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">read page SESN 10</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">of the notes</t>
   </si>
   <si>
     <t xml:space="preserve">Total loss to carry forward after all other set-offs</t>
@@ -7986,7 +7959,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="345" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="346"/>
@@ -8009,7 +7982,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="349" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E2" s="349"/>
       <c r="F2" s="349"/>
@@ -8020,7 +7993,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="351" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="K2" s="351"/>
       <c r="L2" s="352" t="str">
@@ -8066,7 +8039,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="356" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J4" s="356"/>
       <c r="K4" s="356"/>
@@ -8086,7 +8059,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="356" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E5" s="356"/>
       <c r="F5" s="356"/>
@@ -8095,7 +8068,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="356" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="J5" s="356"/>
       <c r="K5" s="356"/>
@@ -8120,7 +8093,7 @@
       <c r="G6" s="353"/>
       <c r="H6" s="63"/>
       <c r="I6" s="356" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J6" s="356"/>
       <c r="K6" s="356"/>
@@ -8130,7 +8103,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="353" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8140,14 +8113,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="356" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E7" s="356"/>
       <c r="F7" s="356"/>
       <c r="G7" s="353"/>
       <c r="H7" s="63"/>
       <c r="I7" s="356" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J7" s="356"/>
       <c r="K7" s="356"/>
@@ -8157,7 +8130,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="353" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8172,7 +8145,7 @@
       <c r="G8" s="359"/>
       <c r="H8" s="63"/>
       <c r="I8" s="356" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="J8" s="356"/>
       <c r="K8" s="356"/>
@@ -8182,7 +8155,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="353" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8197,18 +8170,18 @@
       <c r="G9" s="353"/>
       <c r="H9" s="63"/>
       <c r="I9" s="356" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="J9" s="356"/>
       <c r="K9" s="356"/>
       <c r="L9" s="360" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="M9" s="360" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="N9" s="361" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="O9" s="353"/>
     </row>
@@ -8238,16 +8211,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="349" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="E11" s="349"/>
       <c r="F11" s="349"/>
       <c r="G11" s="353" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="362" t="n">
@@ -8277,7 +8250,7 @@
       <c r="G12" s="353"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="362" t="n">
@@ -8299,7 +8272,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="356" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="E13" s="356"/>
       <c r="F13" s="356"/>
@@ -8308,7 +8281,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="362" t="n">
@@ -8330,7 +8303,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="356" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -8339,7 +8312,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="349" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J14" s="349"/>
       <c r="K14" s="349"/>
@@ -8358,7 +8331,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="356" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E15" s="356"/>
       <c r="F15" s="356"/>
@@ -8381,7 +8354,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="356" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="E16" s="356"/>
       <c r="F16" s="356"/>
@@ -8390,18 +8363,22 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="356" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J16" s="356"/>
       <c r="K16" s="356"/>
       <c r="L16" s="363" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>422</v>
-      </c>
-      <c r="N16" s="63"/>
-      <c r="O16" s="63"/>
+        <v>419</v>
+      </c>
+      <c r="N16" s="359" t="n">
+        <v>6845</v>
+      </c>
+      <c r="O16" s="353" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="63"/>
@@ -8410,7 +8387,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="356" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="E17" s="356"/>
       <c r="F17" s="356"/>
@@ -8452,24 +8429,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="349" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E19" s="349"/>
       <c r="F19" s="353" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="G19" s="353" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="365" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J19" s="365"/>
       <c r="K19" s="365"/>
       <c r="L19" s="63"/>
       <c r="M19" s="366" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8506,7 +8483,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="356" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E21" s="356"/>
       <c r="F21" s="359" t="n">
@@ -8531,7 +8508,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="359" t="n">
@@ -8542,13 +8519,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="365" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="J22" s="365"/>
       <c r="K22" s="365"/>
       <c r="L22" s="63"/>
       <c r="M22" s="366" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8556,7 +8533,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="355" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8581,11 +8558,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="355" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="349" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="E24" s="349"/>
       <c r="F24" s="63"/>
@@ -8623,7 +8600,7 @@
       <c r="B26" s="369"/>
       <c r="C26" s="63"/>
       <c r="D26" s="356" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="E26" s="356"/>
       <c r="F26" s="359" t="n">
@@ -8644,7 +8621,7 @@
       <c r="B27" s="369"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="357" t="n">
@@ -9656,7 +9633,7 @@
     </row>
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="str">
-        <f aca="false">IF(D38&gt;67000,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
+        <f aca="false">IF(D38&gt;Admin!F26,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
         <v>SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £90000 VAT threshold</v>
       </c>
       <c r="B33" s="96"/>
@@ -9709,7 +9686,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="75" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B35" s="63"/>
       <c r="C35" s="64" t="s">
@@ -9724,7 +9701,7 @@
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
       <c r="L35" s="75" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M35" s="63"/>
       <c r="N35" s="64" t="s">
@@ -9974,7 +9951,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="75" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B44" s="63"/>
       <c r="C44" s="64" t="s">
@@ -9989,7 +9966,7 @@
       <c r="J44" s="64"/>
       <c r="K44" s="64"/>
       <c r="L44" s="75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M44" s="63"/>
       <c r="N44" s="64" t="s">
@@ -10037,7 +10014,7 @@
         <v>33</v>
       </c>
       <c r="D46" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B17," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17," ")</f>
         <v>20136.6666666667</v>
       </c>
       <c r="E46" s="98"/>
@@ -10059,7 +10036,7 @@
         <v>33</v>
       </c>
       <c r="O46" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B28," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28," ")</f>
         <v>6925</v>
       </c>
       <c r="P46" s="98"/>
@@ -10104,7 +10081,7 @@
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="75" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B48" s="63"/>
       <c r="C48" s="64" t="s">
@@ -10119,7 +10096,7 @@
       <c r="J48" s="64"/>
       <c r="K48" s="64"/>
       <c r="L48" s="75" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M48" s="63"/>
       <c r="N48" s="64" t="s">
@@ -10194,7 +10171,7 @@
         <v>33</v>
       </c>
       <c r="D51" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
         <v>7984.25</v>
       </c>
       <c r="E51" s="98"/>
@@ -10216,7 +10193,7 @@
         <v>33</v>
       </c>
       <c r="O51" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
         <v>3900</v>
       </c>
       <c r="P51" s="98"/>
@@ -10261,7 +10238,7 @@
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="75" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
@@ -10276,7 +10253,7 @@
       <c r="J53" s="64"/>
       <c r="K53" s="64"/>
       <c r="L53" s="75" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M53" s="63"/>
       <c r="N53" s="64" t="s">
@@ -10324,7 +10301,7 @@
         <v>33</v>
       </c>
       <c r="D55" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B21," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21," ")</f>
         <v>92735.7333333333</v>
       </c>
       <c r="E55" s="98"/>
@@ -10346,7 +10323,7 @@
         <v>33</v>
       </c>
       <c r="O55" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B24," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24," ")</f>
         <v>3035</v>
       </c>
       <c r="P55" s="98"/>
@@ -10391,7 +10368,7 @@
     </row>
     <row r="57" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="75" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B57" s="63"/>
       <c r="C57" s="64" t="s">
@@ -10406,7 +10383,7 @@
       <c r="J57" s="64"/>
       <c r="K57" s="64"/>
       <c r="L57" s="75" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M57" s="63"/>
       <c r="N57" s="64" t="s">
@@ -10481,7 +10458,7 @@
         <v>33</v>
       </c>
       <c r="D60" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B22," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22," ")</f>
         <v>13200</v>
       </c>
       <c r="E60" s="98"/>
@@ -10503,7 +10480,7 @@
         <v>33</v>
       </c>
       <c r="O60" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
         <v>6903.66666666666</v>
       </c>
       <c r="P60" s="98"/>
@@ -10548,7 +10525,7 @@
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="75" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
@@ -10563,7 +10540,7 @@
       <c r="J62" s="64"/>
       <c r="K62" s="64"/>
       <c r="L62" s="75" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M62" s="63"/>
       <c r="N62" s="64" t="s">
@@ -10611,7 +10588,7 @@
         <v>33</v>
       </c>
       <c r="D64" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B23," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23," ")</f>
         <v>950</v>
       </c>
       <c r="E64" s="98"/>
@@ -10730,7 +10707,7 @@
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="75" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
@@ -10745,7 +10722,7 @@
       <c r="J68" s="64"/>
       <c r="K68" s="64"/>
       <c r="L68" s="75" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M68" s="63"/>
       <c r="N68" s="64" t="s">
@@ -11028,7 +11005,7 @@
     </row>
     <row r="78" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="75" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B78" s="63"/>
       <c r="C78" s="64" t="s">
@@ -11043,7 +11020,7 @@
       <c r="J78" s="64"/>
       <c r="K78" s="64"/>
       <c r="L78" s="75" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M78" s="63"/>
       <c r="N78" s="64" t="s">
@@ -11158,7 +11135,7 @@
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B82" s="63"/>
       <c r="C82" s="64" t="s">
@@ -11173,7 +11150,7 @@
       <c r="J82" s="63"/>
       <c r="K82" s="63"/>
       <c r="L82" s="75" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M82" s="63"/>
       <c r="N82" s="64" t="s">
@@ -11423,7 +11400,7 @@
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="75" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B91" s="63"/>
       <c r="C91" s="64" t="s">
@@ -11438,7 +11415,7 @@
       <c r="J91" s="64"/>
       <c r="K91" s="64"/>
       <c r="L91" s="75" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M91" s="63"/>
       <c r="N91" s="64" t="s">
@@ -11582,7 +11559,7 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="75" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
@@ -11597,7 +11574,7 @@
       <c r="J96" s="64"/>
       <c r="K96" s="64"/>
       <c r="L96" s="75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M96" s="63"/>
       <c r="N96" s="64" t="s">
@@ -11795,7 +11772,7 @@
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="75" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B103" s="63"/>
       <c r="C103" s="64" t="s">
@@ -11810,7 +11787,7 @@
       <c r="J103" s="64"/>
       <c r="K103" s="64"/>
       <c r="L103" s="75" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M103" s="63"/>
       <c r="N103" s="64" t="s">
@@ -12033,7 +12010,7 @@
     </row>
     <row r="111" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="75" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B111" s="63"/>
       <c r="C111" s="64" t="s">
@@ -12048,11 +12025,12 @@
       <c r="J111" s="64"/>
       <c r="K111" s="64"/>
       <c r="L111" s="75" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="M111" s="63"/>
-      <c r="N111" s="64" t="s">
-        <v>107</v>
+      <c r="N111" s="64" t="str">
+        <f aca="false">"If your total profits for "&amp;Admin!G2&amp;" are less than £"&amp;TEXT(Admin!N16,"#,##0")&amp;" and you"</f>
+        <v>If your total profits for 2026-27 are less than £6,845 and you</v>
       </c>
       <c r="O111" s="63"/>
       <c r="P111" s="63"/>
@@ -12068,7 +12046,7 @@
       <c r="A112" s="106"/>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D112" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -12084,7 +12062,7 @@
       <c r="L112" s="64"/>
       <c r="M112" s="63"/>
       <c r="N112" s="64" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="O112" s="110"/>
       <c r="P112" s="110"/>
@@ -12181,11 +12159,11 @@
     </row>
     <row r="116" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="75" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -12196,24 +12174,19 @@
       <c r="J116" s="64"/>
       <c r="K116" s="64"/>
       <c r="L116" s="75" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="M116" s="63"/>
       <c r="N116" s="64" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O116" s="63"/>
       <c r="P116" s="63"/>
       <c r="Q116" s="63"/>
-      <c r="R116" s="115" t="str">
-        <f aca="false">Admin!G2</f>
-        <v>2026-27</v>
-      </c>
+      <c r="R116" s="115"/>
       <c r="S116" s="115"/>
       <c r="T116" s="115"/>
-      <c r="U116" s="64" t="s">
-        <v>112</v>
-      </c>
+      <c r="U116" s="64"/>
       <c r="V116" s="63"/>
       <c r="W116" s="82"/>
     </row>
@@ -12221,7 +12194,7 @@
       <c r="A117" s="106"/>
       <c r="B117" s="63"/>
       <c r="C117" s="64" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D117" s="64"/>
       <c r="E117" s="64"/>
@@ -12234,7 +12207,7 @@
       <c r="L117" s="64"/>
       <c r="M117" s="63"/>
       <c r="N117" s="64" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="O117" s="63"/>
       <c r="P117" s="63"/>
@@ -12260,9 +12233,7 @@
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
       <c r="M118" s="63"/>
-      <c r="N118" s="92" t="s">
-        <v>115</v>
-      </c>
+      <c r="N118" s="92"/>
       <c r="O118" s="63"/>
       <c r="P118" s="63"/>
       <c r="Q118" s="63"/>
@@ -12333,11 +12304,11 @@
     </row>
     <row r="121" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="75" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B121" s="63"/>
       <c r="C121" s="64" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D121" s="64"/>
       <c r="E121" s="64"/>
@@ -12348,11 +12319,11 @@
       <c r="J121" s="64"/>
       <c r="K121" s="64"/>
       <c r="L121" s="75" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M121" s="63"/>
       <c r="N121" s="64" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="O121" s="63"/>
       <c r="P121" s="63"/>
@@ -12368,7 +12339,7 @@
       <c r="A122" s="106"/>
       <c r="B122" s="63"/>
       <c r="C122" s="90" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D122" s="64"/>
       <c r="E122" s="64"/>
@@ -12381,7 +12352,7 @@
       <c r="L122" s="64"/>
       <c r="M122" s="63"/>
       <c r="N122" s="64" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="O122" s="63"/>
       <c r="P122" s="63"/>
@@ -12604,7 +12575,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -12622,7 +12593,7 @@
       <c r="L1" s="121"/>
       <c r="M1" s="121"/>
       <c r="N1" s="122" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="O1" s="122"/>
       <c r="P1" s="122"/>
@@ -12983,7 +12954,7 @@
       </c>
       <c r="M14" s="63"/>
       <c r="N14" s="64" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="O14" s="64"/>
       <c r="P14" s="64"/>
@@ -13013,7 +12984,7 @@
       <c r="L15" s="63"/>
       <c r="M15" s="63"/>
       <c r="N15" s="80" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="O15" s="64"/>
       <c r="P15" s="64"/>
@@ -13040,7 +13011,7 @@
       <c r="L16" s="63"/>
       <c r="M16" s="63"/>
       <c r="N16" s="64" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="O16" s="64"/>
       <c r="P16" s="64"/>
@@ -13497,7 +13468,7 @@
       </c>
       <c r="B32" s="63"/>
       <c r="C32" s="80" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -13545,7 +13516,7 @@
       <c r="L33" s="63"/>
       <c r="M33" s="63"/>
       <c r="N33" s="64" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="O33" s="64"/>
       <c r="P33" s="64"/>
@@ -13572,7 +13543,7 @@
       <c r="L34" s="63"/>
       <c r="M34" s="63"/>
       <c r="N34" s="90" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="O34" s="90"/>
       <c r="P34" s="64"/>
@@ -13879,7 +13850,7 @@
       <c r="L45" s="63"/>
       <c r="M45" s="63"/>
       <c r="N45" s="64" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="O45" s="64"/>
       <c r="P45" s="64"/>
@@ -13996,7 +13967,7 @@
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="103" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B50" s="103"/>
       <c r="C50" s="103"/>
@@ -14067,7 +14038,7 @@
       </c>
       <c r="M52" s="63"/>
       <c r="N52" s="64" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="64"/>
@@ -14205,7 +14176,7 @@
     </row>
     <row r="57" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="103" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="B57" s="103"/>
       <c r="C57" s="103"/>
@@ -14232,7 +14203,7 @@
     </row>
     <row r="58" s="105" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="104" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B58" s="104"/>
       <c r="C58" s="104"/>
@@ -14286,7 +14257,7 @@
       <c r="A60" s="79"/>
       <c r="B60" s="63"/>
       <c r="C60" s="130" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D60" s="63"/>
       <c r="E60" s="63"/>
@@ -14299,7 +14270,7 @@
       <c r="L60" s="63"/>
       <c r="M60" s="63"/>
       <c r="N60" s="130" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="O60" s="63"/>
       <c r="P60" s="63"/>
@@ -14315,7 +14286,7 @@
       <c r="A61" s="79"/>
       <c r="B61" s="63"/>
       <c r="C61" s="64" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D61" s="64"/>
       <c r="E61" s="64"/>
@@ -14328,7 +14299,7 @@
       <c r="L61" s="64"/>
       <c r="M61" s="64"/>
       <c r="N61" s="64" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="O61" s="64"/>
       <c r="P61" s="64"/>
@@ -14344,7 +14315,7 @@
       <c r="A62" s="79"/>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D62" s="64"/>
       <c r="E62" s="64"/>
@@ -14357,7 +14328,7 @@
       <c r="L62" s="64"/>
       <c r="M62" s="64"/>
       <c r="N62" s="64" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="O62" s="64"/>
       <c r="P62" s="64"/>
@@ -14400,7 +14371,7 @@
       </c>
       <c r="B64" s="63"/>
       <c r="C64" s="64" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D64" s="64"/>
       <c r="E64" s="64"/>
@@ -14525,7 +14496,7 @@
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D68" s="64"/>
       <c r="E68" s="64"/>
@@ -14775,7 +14746,7 @@
       </c>
       <c r="B76" s="63"/>
       <c r="C76" s="64" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D76" s="64"/>
       <c r="E76" s="64"/>
@@ -15025,7 +14996,7 @@
       </c>
       <c r="B84" s="63"/>
       <c r="C84" s="64" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D84" s="64"/>
       <c r="E84" s="64"/>
@@ -15150,7 +15121,7 @@
       </c>
       <c r="B88" s="63"/>
       <c r="C88" s="64" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D88" s="64"/>
       <c r="E88" s="64"/>
@@ -15275,7 +15246,7 @@
       </c>
       <c r="B92" s="63"/>
       <c r="C92" s="64" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D92" s="64"/>
       <c r="E92" s="64"/>
@@ -15400,7 +15371,7 @@
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D96" s="64"/>
       <c r="E96" s="64"/>
@@ -15525,7 +15496,7 @@
       </c>
       <c r="B100" s="63"/>
       <c r="C100" s="64" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D100" s="64"/>
       <c r="E100" s="64"/>
@@ -15650,7 +15621,7 @@
       </c>
       <c r="B104" s="63"/>
       <c r="C104" s="64" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D104" s="64"/>
       <c r="E104" s="64"/>
@@ -15900,7 +15871,7 @@
       </c>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D112" s="64"/>
       <c r="E112" s="64"/>
@@ -16028,7 +15999,7 @@
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -16153,7 +16124,7 @@
       </c>
       <c r="B120" s="63"/>
       <c r="C120" s="64" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D120" s="64"/>
       <c r="E120" s="64"/>
@@ -16168,7 +16139,7 @@
       </c>
       <c r="M120" s="63"/>
       <c r="N120" s="64" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="O120" s="63"/>
       <c r="P120" s="63"/>
@@ -16335,7 +16306,7 @@
       </c>
       <c r="B126" s="63"/>
       <c r="C126" s="64" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D126" s="64"/>
       <c r="E126" s="64"/>
@@ -16350,7 +16321,7 @@
       </c>
       <c r="M126" s="63"/>
       <c r="N126" s="64" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="O126" s="63"/>
       <c r="P126" s="63"/>
@@ -16366,7 +16337,7 @@
       <c r="A127" s="79"/>
       <c r="B127" s="63"/>
       <c r="C127" s="90" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D127" s="64"/>
       <c r="E127" s="64"/>
@@ -16379,7 +16350,7 @@
       <c r="L127" s="63"/>
       <c r="M127" s="63"/>
       <c r="N127" s="64" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="O127" s="63"/>
       <c r="P127" s="63"/>
@@ -16517,7 +16488,7 @@
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="104" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B132" s="104"/>
       <c r="C132" s="104"/>
@@ -16544,7 +16515,7 @@
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="104" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="B133" s="104"/>
       <c r="C133" s="104"/>
@@ -16571,7 +16542,7 @@
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="104" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B134" s="104"/>
       <c r="C134" s="104"/>
@@ -16642,7 +16613,7 @@
       </c>
       <c r="M136" s="63"/>
       <c r="N136" s="64" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O136" s="63"/>
       <c r="P136" s="63"/>
@@ -16779,7 +16750,7 @@
       </c>
       <c r="B141" s="63"/>
       <c r="C141" s="64" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D141" s="64"/>
       <c r="E141" s="64"/>
@@ -16790,7 +16761,7 @@
       </c>
       <c r="H141" s="132"/>
       <c r="I141" s="64" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J141" s="64"/>
       <c r="K141" s="64"/>
@@ -16799,7 +16770,7 @@
       </c>
       <c r="M141" s="63"/>
       <c r="N141" s="64" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O141" s="63"/>
       <c r="P141" s="63"/>
@@ -16815,7 +16786,7 @@
       <c r="A142" s="106"/>
       <c r="B142" s="63"/>
       <c r="C142" s="64" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D142" s="64"/>
       <c r="E142" s="64"/>
@@ -16941,7 +16912,7 @@
       </c>
       <c r="B146" s="63"/>
       <c r="C146" s="131" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D146" s="64"/>
       <c r="E146" s="64"/>
@@ -16989,7 +16960,7 @@
       </c>
       <c r="M147" s="63"/>
       <c r="N147" s="64" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="O147" s="63"/>
       <c r="P147" s="63"/>
@@ -17016,7 +16987,7 @@
       <c r="L148" s="64"/>
       <c r="M148" s="63"/>
       <c r="N148" s="64" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="O148" s="63"/>
       <c r="P148" s="63"/>
@@ -17034,7 +17005,7 @@
       </c>
       <c r="B149" s="63"/>
       <c r="C149" s="64" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="D149" s="64"/>
       <c r="E149" s="64"/>
@@ -17110,7 +17081,7 @@
       </c>
       <c r="M151" s="63"/>
       <c r="N151" s="64" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="O151" s="63"/>
       <c r="P151" s="63"/>
@@ -17186,7 +17157,7 @@
       </c>
       <c r="B154" s="63"/>
       <c r="C154" s="64" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D154" s="64"/>
       <c r="E154" s="64"/>
@@ -17270,7 +17241,7 @@
       </c>
       <c r="M156" s="63"/>
       <c r="N156" s="64" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="O156" s="63"/>
       <c r="P156" s="63"/>
@@ -17288,7 +17259,7 @@
       </c>
       <c r="B157" s="63"/>
       <c r="C157" s="64" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D157" s="64"/>
       <c r="E157" s="64"/>
@@ -17301,7 +17272,7 @@
       <c r="L157" s="63"/>
       <c r="M157" s="63"/>
       <c r="N157" s="64" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="O157" s="63"/>
       <c r="P157" s="63"/>
@@ -17328,7 +17299,7 @@
       <c r="L158" s="63"/>
       <c r="M158" s="63"/>
       <c r="N158" s="64" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O158" s="63"/>
       <c r="P158" s="63"/>
@@ -17436,7 +17407,7 @@
     </row>
     <row r="162" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="103" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B162" s="103"/>
       <c r="C162" s="103"/>
@@ -17463,7 +17434,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="104" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="B163" s="104"/>
       <c r="C163" s="104"/>
@@ -17490,7 +17461,7 @@
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="104" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="B164" s="104"/>
       <c r="C164" s="104"/>
@@ -17546,7 +17517,7 @@
       </c>
       <c r="B166" s="63"/>
       <c r="C166" s="64" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D166" s="64"/>
       <c r="E166" s="64"/>
@@ -17561,7 +17532,7 @@
       </c>
       <c r="M166" s="63"/>
       <c r="N166" s="64" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="O166" s="63"/>
       <c r="P166" s="63"/>
@@ -17588,7 +17559,7 @@
       <c r="L167" s="64"/>
       <c r="M167" s="63"/>
       <c r="N167" s="64" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="O167" s="110"/>
       <c r="P167" s="110"/>
@@ -17703,7 +17674,7 @@
       </c>
       <c r="B171" s="63"/>
       <c r="C171" s="64" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D171" s="64"/>
       <c r="E171" s="64"/>
@@ -17718,7 +17689,7 @@
       </c>
       <c r="M171" s="63"/>
       <c r="N171" s="64" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="O171" s="63"/>
       <c r="P171" s="63"/>
@@ -17734,7 +17705,7 @@
       <c r="A172" s="106"/>
       <c r="B172" s="63"/>
       <c r="C172" s="64" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D172" s="64"/>
       <c r="E172" s="64"/>
@@ -17747,7 +17718,7 @@
       <c r="L172" s="64"/>
       <c r="M172" s="63"/>
       <c r="N172" s="64" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="O172" s="63"/>
       <c r="P172" s="63"/>
@@ -17862,7 +17833,7 @@
       </c>
       <c r="B176" s="63"/>
       <c r="C176" s="64" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="D176" s="64"/>
       <c r="E176" s="64"/>
@@ -17877,7 +17848,7 @@
       </c>
       <c r="M176" s="63"/>
       <c r="N176" s="64" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="O176" s="63"/>
       <c r="P176" s="63"/>
@@ -17893,7 +17864,7 @@
       <c r="A177" s="79"/>
       <c r="B177" s="63"/>
       <c r="C177" s="64" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D177" s="63"/>
       <c r="E177" s="63"/>
@@ -17906,7 +17877,7 @@
       <c r="L177" s="63"/>
       <c r="M177" s="63"/>
       <c r="N177" s="64" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="O177" s="63"/>
       <c r="P177" s="63"/>
@@ -18014,7 +17985,7 @@
     </row>
     <row r="181" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="103" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B181" s="103"/>
       <c r="C181" s="103"/>
@@ -18041,7 +18012,7 @@
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="104" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="B182" s="104"/>
       <c r="C182" s="104"/>
@@ -18068,7 +18039,7 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="104" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B183" s="104"/>
       <c r="C183" s="104"/>
@@ -18095,7 +18066,7 @@
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="134" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="B184" s="134"/>
       <c r="C184" s="134"/>
@@ -18149,7 +18120,7 @@
       <c r="A186" s="75"/>
       <c r="B186" s="63"/>
       <c r="C186" s="64" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D186" s="64"/>
       <c r="E186" s="64"/>
@@ -18164,7 +18135,7 @@
       </c>
       <c r="M186" s="63"/>
       <c r="N186" s="64" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="O186" s="63"/>
       <c r="P186" s="63"/>
@@ -18191,7 +18162,7 @@
       <c r="L187" s="64"/>
       <c r="M187" s="63"/>
       <c r="N187" s="80" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="O187" s="63"/>
       <c r="P187" s="63"/>
@@ -18218,7 +18189,7 @@
       <c r="L188" s="64"/>
       <c r="M188" s="63"/>
       <c r="N188" s="92" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="O188" s="63"/>
       <c r="P188" s="63"/>
@@ -18245,7 +18216,7 @@
       <c r="L189" s="64"/>
       <c r="M189" s="63"/>
       <c r="N189" s="92" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="O189" s="110"/>
       <c r="P189" s="110"/>
@@ -18275,7 +18246,7 @@
         <v>33</v>
       </c>
       <c r="O190" s="137" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P190" s="138"/>
       <c r="Q190" s="138"/>
@@ -18323,7 +18294,7 @@
       </c>
       <c r="B192" s="63"/>
       <c r="C192" s="64" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D192" s="112"/>
       <c r="E192" s="112"/>
@@ -18338,7 +18309,7 @@
       </c>
       <c r="M192" s="63"/>
       <c r="N192" s="64" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="O192" s="63"/>
       <c r="P192" s="63"/>
@@ -18357,7 +18328,7 @@
       <c r="A193" s="79"/>
       <c r="B193" s="63"/>
       <c r="C193" s="64" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D193" s="64"/>
       <c r="E193" s="64"/>
@@ -18370,7 +18341,7 @@
       <c r="L193" s="64"/>
       <c r="M193" s="64"/>
       <c r="N193" s="80" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O193" s="112"/>
       <c r="P193" s="112"/>
@@ -18386,7 +18357,7 @@
       <c r="A194" s="79"/>
       <c r="B194" s="63"/>
       <c r="C194" s="80" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D194" s="64"/>
       <c r="E194" s="64"/>
@@ -18462,7 +18433,7 @@
       </c>
       <c r="M196" s="63"/>
       <c r="N196" s="64" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="O196" s="63"/>
       <c r="P196" s="63"/>
@@ -18481,7 +18452,7 @@
         <v>33</v>
       </c>
       <c r="D197" s="137" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="E197" s="138"/>
       <c r="F197" s="138"/>
@@ -18499,7 +18470,7 @@
       <c r="L197" s="63"/>
       <c r="M197" s="63"/>
       <c r="N197" s="80" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="O197" s="63"/>
       <c r="P197" s="63"/>
@@ -18540,7 +18511,7 @@
       <c r="A199" s="75"/>
       <c r="B199" s="63"/>
       <c r="C199" s="64" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D199" s="63"/>
       <c r="E199" s="63"/>
@@ -18616,7 +18587,7 @@
       </c>
       <c r="M201" s="63"/>
       <c r="N201" s="64" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="O201" s="63"/>
       <c r="P201" s="63"/>
@@ -18643,7 +18614,7 @@
       <c r="L202" s="63"/>
       <c r="M202" s="63"/>
       <c r="N202" s="64" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="O202" s="63"/>
       <c r="P202" s="63"/>
@@ -18785,7 +18756,7 @@
       <c r="L207" s="63"/>
       <c r="M207" s="63"/>
       <c r="N207" s="64" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="O207" s="63"/>
       <c r="P207" s="63"/>
@@ -18803,7 +18774,7 @@
       </c>
       <c r="B208" s="63"/>
       <c r="C208" s="64" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D208" s="64"/>
       <c r="E208" s="64"/>
@@ -18922,7 +18893,7 @@
     </row>
     <row r="212" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="111" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B212" s="111"/>
       <c r="C212" s="111"/>
@@ -18949,7 +18920,7 @@
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="104" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="B213" s="104"/>
       <c r="C213" s="104"/>
@@ -18976,7 +18947,7 @@
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="104" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B214" s="104"/>
       <c r="C214" s="104"/>
@@ -19032,7 +19003,7 @@
       </c>
       <c r="B216" s="63"/>
       <c r="C216" s="64" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="D216" s="64"/>
       <c r="E216" s="64"/>
@@ -19041,7 +19012,7 @@
         <v>2026-27</v>
       </c>
       <c r="G216" s="64" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H216" s="64"/>
       <c r="I216" s="64"/>
@@ -19052,7 +19023,7 @@
       </c>
       <c r="M216" s="63"/>
       <c r="N216" s="64" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="O216" s="63"/>
       <c r="P216" s="63"/>
@@ -19079,7 +19050,7 @@
       <c r="L217" s="64"/>
       <c r="M217" s="63"/>
       <c r="N217" s="64" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="O217" s="63"/>
       <c r="P217" s="63"/>
@@ -19191,7 +19162,7 @@
       </c>
       <c r="B221" s="63"/>
       <c r="C221" s="64" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="D221" s="64"/>
       <c r="E221" s="64"/>
@@ -19206,7 +19177,7 @@
       </c>
       <c r="M221" s="63"/>
       <c r="N221" s="64" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="O221" s="63"/>
       <c r="P221" s="63"/>
@@ -19222,7 +19193,7 @@
       <c r="A222" s="79"/>
       <c r="B222" s="63"/>
       <c r="C222" s="64" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D222" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -19238,7 +19209,7 @@
       <c r="L222" s="63"/>
       <c r="M222" s="63"/>
       <c r="N222" s="90" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="O222" s="63"/>
       <c r="P222" s="63"/>
@@ -19346,7 +19317,7 @@
     </row>
     <row r="226" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="148" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B226" s="148"/>
       <c r="C226" s="148"/>
@@ -19402,7 +19373,7 @@
       </c>
       <c r="B228" s="63"/>
       <c r="C228" s="64" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D228" s="64"/>
       <c r="E228" s="64"/>
@@ -19417,7 +19388,7 @@
       </c>
       <c r="M228" s="63"/>
       <c r="N228" s="64" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="O228" s="63"/>
       <c r="P228" s="63"/>
@@ -19433,7 +19404,7 @@
       <c r="A229" s="106"/>
       <c r="B229" s="63"/>
       <c r="C229" s="64" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="D229" s="64"/>
       <c r="E229" s="64"/>
@@ -19552,7 +19523,7 @@
     </row>
     <row r="233" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="103" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B233" s="103"/>
       <c r="C233" s="103"/>
@@ -19579,7 +19550,7 @@
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="104" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="B234" s="104"/>
       <c r="C234" s="104"/>
@@ -19606,7 +19577,7 @@
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="104" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="B235" s="104"/>
       <c r="C235" s="104"/>
@@ -19660,7 +19631,7 @@
       <c r="A237" s="79"/>
       <c r="B237" s="63"/>
       <c r="C237" s="130" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D237" s="63"/>
       <c r="E237" s="63"/>
@@ -19673,7 +19644,7 @@
       <c r="L237" s="63"/>
       <c r="M237" s="63"/>
       <c r="N237" s="130" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="O237" s="63"/>
       <c r="P237" s="63"/>
@@ -19716,7 +19687,7 @@
       </c>
       <c r="B239" s="63"/>
       <c r="C239" s="64" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D239" s="64"/>
       <c r="E239" s="64"/>
@@ -19731,7 +19702,7 @@
       </c>
       <c r="M239" s="63"/>
       <c r="N239" s="64" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="O239" s="63"/>
       <c r="P239" s="63"/>
@@ -19840,7 +19811,7 @@
       </c>
       <c r="B243" s="63"/>
       <c r="C243" s="64" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D243" s="64"/>
       <c r="E243" s="64"/>
@@ -19855,7 +19826,7 @@
       </c>
       <c r="M243" s="63"/>
       <c r="N243" s="64" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="O243" s="63"/>
       <c r="P243" s="63"/>
@@ -19964,7 +19935,7 @@
       </c>
       <c r="B247" s="63"/>
       <c r="C247" s="64" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D247" s="64"/>
       <c r="E247" s="64"/>
@@ -19979,7 +19950,7 @@
       </c>
       <c r="M247" s="63"/>
       <c r="N247" s="64" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="O247" s="63"/>
       <c r="P247" s="63"/>
@@ -20088,7 +20059,7 @@
       </c>
       <c r="B251" s="63"/>
       <c r="C251" s="64" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D251" s="64"/>
       <c r="E251" s="64"/>
@@ -20101,7 +20072,7 @@
       <c r="L251" s="63"/>
       <c r="M251" s="63"/>
       <c r="N251" s="130" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="O251" s="112"/>
       <c r="P251" s="112"/>
@@ -20163,7 +20134,7 @@
       </c>
       <c r="M253" s="63"/>
       <c r="N253" s="64" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="O253" s="63"/>
       <c r="P253" s="63"/>
@@ -20206,7 +20177,7 @@
       </c>
       <c r="B255" s="63"/>
       <c r="C255" s="64" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D255" s="64"/>
       <c r="E255" s="64"/>
@@ -20222,7 +20193,7 @@
         <v>33</v>
       </c>
       <c r="O255" s="150" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P255" s="98"/>
       <c r="Q255" s="98"/>
@@ -20287,7 +20258,7 @@
       <c r="L257" s="63"/>
       <c r="M257" s="63"/>
       <c r="N257" s="130" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="O257" s="63"/>
       <c r="P257" s="63"/>
@@ -20330,7 +20301,7 @@
       </c>
       <c r="B259" s="63"/>
       <c r="C259" s="64" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D259" s="64"/>
       <c r="E259" s="64"/>
@@ -20345,7 +20316,7 @@
       </c>
       <c r="M259" s="63"/>
       <c r="N259" s="64" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="O259" s="63"/>
       <c r="P259" s="63"/>
@@ -20408,7 +20379,7 @@
         <v>33</v>
       </c>
       <c r="O261" s="137" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P261" s="98"/>
       <c r="Q261" s="98"/>
@@ -20456,7 +20427,7 @@
       </c>
       <c r="B263" s="63"/>
       <c r="C263" s="64" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D263" s="64"/>
       <c r="E263" s="64"/>
@@ -20471,7 +20442,7 @@
       </c>
       <c r="M263" s="63"/>
       <c r="N263" s="64" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="O263" s="63"/>
       <c r="P263" s="63"/>
@@ -20534,7 +20505,7 @@
         <v>33</v>
       </c>
       <c r="O265" s="137" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P265" s="98"/>
       <c r="Q265" s="98"/>
@@ -20582,7 +20553,7 @@
       </c>
       <c r="B267" s="63"/>
       <c r="C267" s="64" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D267" s="64"/>
       <c r="E267" s="64"/>
@@ -20597,7 +20568,7 @@
       </c>
       <c r="M267" s="63"/>
       <c r="N267" s="64" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="O267" s="63"/>
       <c r="P267" s="63"/>
@@ -20717,7 +20688,7 @@
       </c>
       <c r="M271" s="63"/>
       <c r="N271" s="64" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="O271" s="63"/>
       <c r="P271" s="63"/>
@@ -20829,7 +20800,7 @@
       </c>
       <c r="M275" s="63"/>
       <c r="N275" s="64" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="O275" s="63"/>
       <c r="P275" s="63"/>
@@ -20884,7 +20855,7 @@
         <v>33</v>
       </c>
       <c r="O277" s="137" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="P277" s="98"/>
       <c r="Q277" s="98"/>
@@ -20928,7 +20899,7 @@
     </row>
     <row r="279" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="111" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="B279" s="111"/>
       <c r="C279" s="111"/>
@@ -20955,7 +20926,7 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="104" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="B280" s="104"/>
       <c r="C280" s="104"/>
@@ -20970,7 +20941,7 @@
         <v>12570</v>
       </c>
       <c r="K280" s="104" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="L280" s="104"/>
       <c r="M280" s="104"/>
@@ -20987,7 +20958,7 @@
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="152" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B281" s="152"/>
       <c r="C281" s="152"/>
@@ -21043,7 +21014,7 @@
       </c>
       <c r="B283" s="63"/>
       <c r="C283" s="64" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D283" s="63"/>
       <c r="E283" s="63"/>
@@ -21058,7 +21029,7 @@
       </c>
       <c r="M283" s="63"/>
       <c r="N283" s="64" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="O283" s="63"/>
       <c r="P283" s="63"/>
@@ -21074,7 +21045,7 @@
       <c r="A284" s="79"/>
       <c r="B284" s="63"/>
       <c r="C284" s="64" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D284" s="63"/>
       <c r="E284" s="63"/>
@@ -21087,7 +21058,7 @@
       <c r="L284" s="63"/>
       <c r="M284" s="63"/>
       <c r="N284" s="90" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="O284" s="63"/>
       <c r="P284" s="63"/>
@@ -21188,7 +21159,7 @@
       </c>
       <c r="B288" s="63"/>
       <c r="C288" s="64" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D288" s="63"/>
       <c r="E288" s="63"/>
@@ -21215,7 +21186,7 @@
       <c r="A289" s="79"/>
       <c r="B289" s="63"/>
       <c r="C289" s="64" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="D289" s="63"/>
       <c r="E289" s="63"/>
@@ -21340,7 +21311,7 @@
     </row>
     <row r="294" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="103" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="B294" s="103"/>
       <c r="C294" s="103"/>
@@ -21396,7 +21367,7 @@
       </c>
       <c r="B296" s="63"/>
       <c r="C296" s="64" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D296" s="63"/>
       <c r="E296" s="63"/>
@@ -22322,10 +22293,10 @@
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="161" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="B2" s="162" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C2" s="163" t="n">
         <f aca="false">Admin!B5</f>
@@ -22442,7 +22413,7 @@
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="170" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="B5" s="171" t="n">
         <f aca="false">SUM(C5:N5)</f>
@@ -22500,7 +22471,7 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="170" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="B6" s="171" t="n">
         <f aca="false">SUM(C6:N6)</f>
@@ -22558,7 +22529,7 @@
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="170" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="B7" s="171" t="n">
         <f aca="false">SUM(C7:N7)</f>
@@ -22616,7 +22587,7 @@
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="170" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="B8" s="171" t="n">
         <f aca="false">SUM(C8:N8)</f>
@@ -22674,7 +22645,7 @@
     </row>
     <row r="9" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="174" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B9" s="171" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -22749,7 +22720,7 @@
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="B11" s="171" t="n">
         <f aca="false">SUM(C11:N11)</f>
@@ -22824,7 +22795,7 @@
     </row>
     <row r="13" s="177" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="181" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B13" s="178"/>
       <c r="C13" s="178"/>
@@ -22843,7 +22814,7 @@
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="170" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B14" s="171" t="n">
         <f aca="false">SUM(C14:N14)</f>
@@ -22901,7 +22872,7 @@
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="170" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="B15" s="171" t="n">
         <f aca="false">SUM(C15:N15)</f>
@@ -22959,7 +22930,7 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="170" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="B16" s="171" t="n">
         <f aca="false">SUM(C16:N16)</f>
@@ -23017,7 +22988,7 @@
     </row>
     <row r="17" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="174" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="B17" s="171" t="n">
         <f aca="false">SUM(B14:B16)</f>
@@ -23092,7 +23063,7 @@
     </row>
     <row r="19" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="174" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="B19" s="171" t="n">
         <f aca="false">B9+B11-B17</f>
@@ -23150,7 +23121,7 @@
     </row>
     <row r="20" s="177" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="181" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B20" s="178"/>
       <c r="C20" s="182"/>
@@ -23169,7 +23140,7 @@
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="170" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B21" s="171" t="n">
         <f aca="false">SUM(C21:N21)</f>
@@ -23227,7 +23198,7 @@
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="183" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B22" s="171" t="n">
         <f aca="false">SUM(C22:N22)</f>
@@ -23285,7 +23256,7 @@
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="183" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B23" s="171" t="n">
         <f aca="false">SUM(C23:N23)</f>
@@ -23343,7 +23314,7 @@
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="183" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B24" s="171" t="n">
         <f aca="false">SUM(C24:N24)</f>
@@ -23401,7 +23372,7 @@
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="183" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B25" s="171" t="n">
         <f aca="false">SUM(C25:N25)</f>
@@ -23459,7 +23430,7 @@
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="183" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B26" s="171" t="n">
         <f aca="false">SUM(C26:N26)</f>
@@ -23517,7 +23488,7 @@
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="183" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B27" s="171" t="n">
         <f aca="false">SUM(C27:N27)</f>
@@ -23575,7 +23546,7 @@
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="183" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B28" s="171" t="n">
         <f aca="false">SUM(C28:N28)</f>
@@ -23633,7 +23604,7 @@
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="183" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="B29" s="171" t="n">
         <f aca="false">SUM(C29:N29)</f>
@@ -23691,7 +23662,7 @@
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="183" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B30" s="171" t="n">
         <f aca="false">SUM(C30:N30)</f>
@@ -23749,7 +23720,7 @@
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="183" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B31" s="171" t="n">
         <f aca="false">SUM(C31:N31)</f>
@@ -23807,7 +23778,7 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="183" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B32" s="171" t="n">
         <f aca="false">SUM(C32:N32)</f>
@@ -23865,7 +23836,7 @@
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="170" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B33" s="171" t="n">
         <f aca="false">SUM(C33:N33)</f>
@@ -23923,7 +23894,7 @@
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="170" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B34" s="171" t="n">
         <f aca="false">SUM(C34:N34)</f>
@@ -23981,7 +23952,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="174" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B35" s="171" t="n">
         <f aca="false">SUM(B21:B34)</f>
@@ -24056,7 +24027,7 @@
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="174" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B37" s="171" t="n">
         <f aca="false">B19-B35</f>
@@ -24114,7 +24085,7 @@
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="170" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B38" s="171" t="n">
         <f aca="false">SUM(C38:N38)</f>
@@ -24172,7 +24143,7 @@
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="174" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B39" s="171" t="n">
         <f aca="false">B37+B38</f>
@@ -24247,7 +24218,7 @@
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="188" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B41" s="157"/>
       <c r="C41" s="158"/>
@@ -24266,7 +24237,7 @@
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="183" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B42" s="178" t="n">
         <f aca="false">SUM(C42:N42)</f>
@@ -24324,7 +24295,7 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="183" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="B43" s="178" t="n">
         <f aca="false">SUM(C43:N43)</f>
@@ -24382,7 +24353,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="183" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="B44" s="178" t="n">
         <f aca="false">SUM(C44:N44)</f>
@@ -24440,7 +24411,7 @@
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="189" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B45" s="190" t="n">
         <f aca="false">SUM(C45:N45)</f>
@@ -24498,7 +24469,7 @@
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="183" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="B46" s="178" t="n">
         <f aca="false">SUM(C46:N46)</f>
@@ -24630,25 +24601,25 @@
     <row r="2" s="197" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="196"/>
       <c r="B2" s="198" t="s">
+        <v>289</v>
+      </c>
+      <c r="C2" s="198" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="198" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" s="198" t="s">
         <v>292</v>
       </c>
-      <c r="C2" s="198" t="s">
+      <c r="F2" s="198" t="s">
         <v>293</v>
       </c>
-      <c r="D2" s="198" t="s">
+      <c r="G2" s="198" t="s">
         <v>294</v>
       </c>
-      <c r="E2" s="198" t="s">
+      <c r="H2" s="198" t="s">
         <v>295</v>
-      </c>
-      <c r="F2" s="198" t="s">
-        <v>296</v>
-      </c>
-      <c r="G2" s="198" t="s">
-        <v>297</v>
-      </c>
-      <c r="H2" s="198" t="s">
-        <v>298</v>
       </c>
       <c r="I2" s="196"/>
     </row>
@@ -24677,7 +24648,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="196"/>
       <c r="B5" s="196" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C5" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -24705,7 +24676,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="196"/>
       <c r="B6" s="196" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="C6" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -24733,7 +24704,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="196"/>
       <c r="B7" s="196" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C7" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -24783,7 +24754,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="196"/>
       <c r="B10" s="203" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C10" s="196"/>
       <c r="D10" s="196"/>
@@ -24807,7 +24778,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="196"/>
       <c r="B12" s="196" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C12" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -24835,7 +24806,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="196"/>
       <c r="B13" s="196" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C13" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -24863,7 +24834,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="196"/>
       <c r="B14" s="196" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C14" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -24891,7 +24862,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="196"/>
       <c r="B15" s="196" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C15" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -24919,7 +24890,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="196"/>
       <c r="B16" s="196" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C16" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -24947,7 +24918,7 @@
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="196"/>
       <c r="B17" s="196" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C17" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -24975,7 +24946,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="196"/>
       <c r="B18" s="196" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C18" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -25003,7 +24974,7 @@
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="196"/>
       <c r="B19" s="196" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C19" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -25031,7 +25002,7 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="196"/>
       <c r="B20" s="196" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="C20" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -25059,7 +25030,7 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="196"/>
       <c r="B21" s="196" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C21" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -25087,7 +25058,7 @@
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="196"/>
       <c r="B22" s="196" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C22" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -25126,7 +25097,7 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="196"/>
       <c r="B24" s="196" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C24" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -25154,7 +25125,7 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="196"/>
       <c r="B25" s="196" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C25" s="201" t="n">
         <v>0</v>
@@ -25173,14 +25144,14 @@
         <v>0</v>
       </c>
       <c r="H25" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I25" s="196"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="196"/>
       <c r="B26" s="196" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
@@ -25230,7 +25201,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="196"/>
       <c r="B29" s="203" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="C29" s="204" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
@@ -25302,7 +25273,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="196"/>
       <c r="B34" s="203" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="C34" s="196"/>
       <c r="D34" s="196"/>
@@ -25326,7 +25297,7 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="196"/>
       <c r="B36" s="196" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C36" s="201" t="n">
         <v>0</v>
@@ -25345,14 +25316,14 @@
         <v>0</v>
       </c>
       <c r="H36" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I36" s="196"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="196"/>
       <c r="B37" s="196" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="C37" s="201" t="n">
         <v>0</v>
@@ -25371,14 +25342,14 @@
         <v>0</v>
       </c>
       <c r="H37" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I37" s="196"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="196"/>
       <c r="B38" s="196" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C38" s="201" t="n">
         <v>0</v>
@@ -25397,14 +25368,14 @@
         <v>0</v>
       </c>
       <c r="H38" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I38" s="196"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="196"/>
       <c r="B39" s="196" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="C39" s="201" t="n">
         <v>0</v>
@@ -25423,14 +25394,14 @@
         <v>0</v>
       </c>
       <c r="H39" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I39" s="196"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="196"/>
       <c r="B40" s="196" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C40" s="201" t="n">
         <v>0</v>
@@ -25449,14 +25420,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I40" s="196"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="196"/>
       <c r="B41" s="196" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C41" s="201" t="n">
         <v>0</v>
@@ -25475,14 +25446,14 @@
         <v>0</v>
       </c>
       <c r="H41" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I41" s="196"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="196"/>
       <c r="B42" s="196" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C42" s="201" t="n">
         <v>0</v>
@@ -25501,14 +25472,14 @@
         <v>0</v>
       </c>
       <c r="H42" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I42" s="196"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="196"/>
       <c r="B43" s="196" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C43" s="201" t="n">
         <v>0</v>
@@ -25527,14 +25498,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I43" s="196"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="196"/>
       <c r="B44" s="196" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C44" s="201" t="n">
         <v>0</v>
@@ -25553,14 +25524,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I44" s="196"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="196"/>
       <c r="B45" s="196" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="C45" s="201" t="n">
         <v>0</v>
@@ -25579,14 +25550,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I45" s="196"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="196"/>
       <c r="B46" s="196" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="C46" s="201" t="n">
         <v>0</v>
@@ -25605,14 +25576,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I46" s="196"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="196"/>
       <c r="B47" s="196" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C47" s="201" t="n">
         <v>0</v>
@@ -25631,14 +25602,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I47" s="196"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="196"/>
       <c r="B48" s="196" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C48" s="201" t="n">
         <v>0</v>
@@ -25657,14 +25628,14 @@
         <v>0</v>
       </c>
       <c r="H48" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I48" s="196"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="196"/>
       <c r="B49" s="196" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C49" s="201" t="n">
         <v>0</v>
@@ -25683,14 +25654,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I49" s="196"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="196"/>
       <c r="B50" s="196" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="C50" s="201" t="n">
         <v>0</v>
@@ -25709,7 +25680,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="196" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="I50" s="196"/>
     </row>
@@ -25780,14 +25751,14 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="212"/>
       <c r="B2" s="216" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="C2" s="217" t="str">
         <f aca="false">Admin!L2</f>
         <v>2026-27</v>
       </c>
       <c r="D2" s="218" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E2" s="218"/>
       <c r="F2" s="218"/>
@@ -25814,7 +25785,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="212"/>
       <c r="B5" s="223" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C5" s="223"/>
       <c r="D5" s="223"/>
@@ -25829,7 +25800,7 @@
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="212"/>
       <c r="B6" s="221" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C6" s="221" t="str">
         <f aca="false">C2</f>
@@ -25847,7 +25818,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="212"/>
       <c r="B7" s="223" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="C7" s="223"/>
       <c r="D7" s="223"/>
@@ -25862,7 +25833,7 @@
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="212"/>
       <c r="B8" s="221" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="C8" s="221" t="n">
         <f aca="false">Admin!N$11</f>
@@ -25884,7 +25855,7 @@
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="212"/>
       <c r="B9" s="221" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="C9" s="221" t="n">
         <f aca="false">Admin!M$11</f>
@@ -25905,7 +25876,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="212"/>
       <c r="B10" s="221" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="C10" s="221" t="n">
         <f aca="false">Admin!N$13</f>
@@ -25926,7 +25897,7 @@
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="212"/>
       <c r="B11" s="229" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="C11" s="230"/>
       <c r="D11" s="231"/>
@@ -25941,7 +25912,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="212"/>
       <c r="B12" s="221" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C12" s="221"/>
       <c r="D12" s="235"/>
@@ -25956,7 +25927,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="212"/>
       <c r="B13" s="236" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C13" s="237" t="n">
         <f aca="false">Admin!B21</f>
@@ -25981,7 +25952,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="212"/>
       <c r="B15" s="240" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C15" s="240"/>
       <c r="D15" s="227" t="n">
@@ -25999,7 +25970,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="212"/>
       <c r="B16" s="240" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="C16" s="240"/>
       <c r="D16" s="227" t="n">
@@ -26027,7 +25998,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="212"/>
       <c r="B18" s="242" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C18" s="242"/>
       <c r="D18" s="238"/>
@@ -26060,11 +26031,11 @@
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="212"/>
       <c r="B21" s="229" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C21" s="244"/>
       <c r="D21" s="245" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E21" s="245"/>
       <c r="F21" s="245"/>
@@ -26084,10 +26055,10 @@
       <c r="B23" s="221"/>
       <c r="C23" s="221"/>
       <c r="D23" s="247" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="E23" s="248" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F23" s="249"/>
       <c r="G23" s="219"/>
@@ -26104,14 +26075,14 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="212"/>
       <c r="B25" s="221" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="C25" s="251" t="str">
         <f aca="false">Admin!B24</f>
         <v>2027-28</v>
       </c>
       <c r="D25" s="252" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E25" s="241" t="n">
         <f aca="false">E18</f>
@@ -26123,7 +26094,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="212"/>
       <c r="B26" s="221" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C26" s="221"/>
       <c r="D26" s="253" t="n">
@@ -26140,7 +26111,7 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="212"/>
       <c r="B27" s="221" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C27" s="221"/>
       <c r="D27" s="253" t="n">
@@ -26166,7 +26137,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="212"/>
       <c r="B29" s="254" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C29" s="255"/>
       <c r="D29" s="238"/>
@@ -26177,7 +26148,7 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="212"/>
       <c r="B30" s="256" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C30" s="256"/>
       <c r="D30" s="212"/>
@@ -26188,7 +26159,7 @@
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="212"/>
       <c r="B31" s="259" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="C31" s="259"/>
       <c r="D31" s="260"/>
@@ -26199,7 +26170,7 @@
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="212"/>
       <c r="B32" s="261" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C32" s="259"/>
       <c r="D32" s="260"/>
@@ -26210,7 +26181,7 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="212"/>
       <c r="B33" s="255" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="C33" s="255"/>
       <c r="D33" s="260"/>
@@ -26221,7 +26192,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="212"/>
       <c r="B34" s="255" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C34" s="255"/>
       <c r="D34" s="260"/>
@@ -26232,7 +26203,7 @@
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="212"/>
       <c r="B35" s="255" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C35" s="255"/>
       <c r="D35" s="260"/>
@@ -26307,39 +26278,39 @@
     <row r="2" s="273" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="268"/>
       <c r="B2" s="269" t="s">
+        <v>346</v>
+      </c>
+      <c r="C2" s="270" t="s">
+        <v>347</v>
+      </c>
+      <c r="D2" s="270" t="s">
+        <v>348</v>
+      </c>
+      <c r="E2" s="270" t="s">
         <v>349</v>
       </c>
-      <c r="C2" s="270" t="s">
+      <c r="F2" s="270" t="s">
         <v>350</v>
       </c>
-      <c r="D2" s="270" t="s">
+      <c r="G2" s="270" t="s">
         <v>351</v>
       </c>
-      <c r="E2" s="270" t="s">
+      <c r="H2" s="270" t="s">
         <v>352</v>
       </c>
-      <c r="F2" s="270" t="s">
+      <c r="I2" s="270" t="s">
         <v>353</v>
-      </c>
-      <c r="G2" s="270" t="s">
-        <v>354</v>
-      </c>
-      <c r="H2" s="270" t="s">
-        <v>355</v>
-      </c>
-      <c r="I2" s="270" t="s">
-        <v>356</v>
       </c>
       <c r="J2" s="271"/>
       <c r="K2" s="269" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="L2" s="272"/>
     </row>
     <row r="3" s="273" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="268"/>
       <c r="B3" s="274" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="C3" s="274"/>
       <c r="D3" s="275"/>
@@ -26388,7 +26359,7 @@
       </c>
       <c r="J4" s="159"/>
       <c r="K4" s="279" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="L4" s="165"/>
     </row>
@@ -26542,7 +26513,7 @@
       </c>
       <c r="J8" s="159"/>
       <c r="K8" s="279" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="L8" s="165"/>
     </row>
@@ -26894,7 +26865,7 @@
       <c r="F1" s="288"/>
       <c r="G1" s="288"/>
       <c r="H1" s="289" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="I1" s="289"/>
       <c r="J1" s="289"/>
@@ -26902,7 +26873,7 @@
       <c r="L1" s="289"/>
       <c r="M1" s="288"/>
       <c r="N1" s="289" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="O1" s="289"/>
       <c r="P1" s="289"/>
@@ -26910,7 +26881,7 @@
       <c r="R1" s="289"/>
       <c r="S1" s="288"/>
       <c r="T1" s="289" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="U1" s="289"/>
       <c r="V1" s="289"/>
@@ -26930,63 +26901,63 @@
     <row r="2" s="303" customFormat="true" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="293"/>
       <c r="B2" s="294" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="C2" s="295"/>
       <c r="D2" s="296" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E2" s="297"/>
       <c r="F2" s="296" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="G2" s="297"/>
       <c r="H2" s="298" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="I2" s="297"/>
       <c r="J2" s="296" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="K2" s="297"/>
       <c r="L2" s="296" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="M2" s="297"/>
       <c r="N2" s="298" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="O2" s="297"/>
       <c r="P2" s="296" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="Q2" s="297"/>
       <c r="R2" s="296" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="S2" s="297"/>
       <c r="T2" s="298" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="U2" s="297"/>
       <c r="V2" s="296" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="W2" s="297"/>
       <c r="X2" s="299" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="Y2" s="300"/>
       <c r="Z2" s="296" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="AA2" s="297"/>
       <c r="AB2" s="296" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="AC2" s="301"/>
       <c r="AD2" s="302" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="AE2" s="302"/>
       <c r="AF2" s="302"/>
@@ -27024,7 +26995,7 @@
       <c r="AB3" s="306"/>
       <c r="AC3" s="165"/>
       <c r="AD3" s="310" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="AE3" s="310"/>
       <c r="AF3" s="310"/>
@@ -27034,7 +27005,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="277"/>
       <c r="B4" s="311" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C4" s="311"/>
       <c r="D4" s="311"/>
@@ -27414,7 +27385,7 @@
       <c r="AB11" s="178"/>
       <c r="AC11" s="165"/>
       <c r="AD11" s="310" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="AE11" s="310"/>
       <c r="AF11" s="310"/>
@@ -27644,7 +27615,7 @@
       <c r="AB15" s="178"/>
       <c r="AC15" s="165"/>
       <c r="AD15" s="310" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="AE15" s="310"/>
       <c r="AF15" s="310"/>
@@ -27874,7 +27845,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="165"/>
       <c r="AD19" s="310" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="AE19" s="310"/>
       <c r="AF19" s="310"/>
@@ -28104,7 +28075,7 @@
       <c r="AB23" s="178"/>
       <c r="AC23" s="165"/>
       <c r="AD23" s="310" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="AE23" s="310"/>
       <c r="AF23" s="310"/>
@@ -28412,7 +28383,7 @@
       </c>
       <c r="AC28" s="165"/>
       <c r="AD28" s="310" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="AE28" s="310"/>
       <c r="AF28" s="310"/>
@@ -28630,10 +28601,10 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="159"/>
       <c r="B2" s="331" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C2" s="162" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D2" s="163" t="n">
         <f aca="false">Admin!B5</f>
@@ -28753,7 +28724,7 @@
     <row r="5" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="179"/>
       <c r="B5" s="333" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C5" s="171" t="n">
         <f aca="false">SUM(D5:O5)</f>
@@ -28830,7 +28801,7 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="159"/>
       <c r="B7" s="335" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C7" s="171" t="n">
         <f aca="false">SUM(D7:O7)</f>
@@ -28907,7 +28878,7 @@
     <row r="9" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="179"/>
       <c r="B9" s="334" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C9" s="171" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -28984,7 +28955,7 @@
     <row r="11" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="179"/>
       <c r="B11" s="333" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C11" s="171" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -29061,7 +29032,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="159"/>
       <c r="B13" s="334" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C13" s="171" t="n">
         <f aca="false">SUM(D13:O13)</f>
@@ -29138,7 +29109,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="159"/>
       <c r="B15" s="333" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C15" s="171" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -29197,7 +29168,7 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="159"/>
       <c r="B16" s="335" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C16" s="171" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -29256,7 +29227,7 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="159"/>
       <c r="B17" s="336" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C17" s="171" t="n">
         <f aca="false">SUM(D17:O17)</f>
@@ -29333,10 +29304,10 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="159"/>
       <c r="B19" s="338" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C19" s="162" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D19" s="163" t="n">
         <f aca="false">D2</f>
@@ -29469,7 +29440,7 @@
     <row r="22" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="179"/>
       <c r="B22" s="333" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C22" s="171" t="n">
         <f aca="false">SUM(D22:O22)</f>
@@ -29546,7 +29517,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="159"/>
       <c r="B24" s="335" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C24" s="171" t="n">
         <f aca="false">SUM(D24:O24)</f>
@@ -29623,7 +29594,7 @@
     <row r="26" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="179"/>
       <c r="B26" s="334" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C26" s="171" t="n">
         <f aca="false">SUM(D26:O26)</f>
@@ -29700,7 +29671,7 @@
     <row r="28" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="179"/>
       <c r="B28" s="333" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C28" s="171" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -29777,7 +29748,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="159"/>
       <c r="B30" s="334" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C30" s="171" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -29854,7 +29825,7 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="159"/>
       <c r="B32" s="333" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C32" s="171" t="n">
         <f aca="false">SUM(D32:O32)</f>
@@ -29913,7 +29884,7 @@
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="159"/>
       <c r="B33" s="335" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="C33" s="171" t="n">
         <f aca="false">SUM(D33:O33)</f>
@@ -29972,7 +29943,7 @@
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="159"/>
       <c r="B34" s="336" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">SUM(D34:O34)</f>
@@ -30049,7 +30020,7 @@
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="159"/>
       <c r="B36" s="339" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C36" s="339"/>
       <c r="D36" s="159"/>
@@ -30069,7 +30040,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="159"/>
       <c r="B37" s="170" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C37" s="340" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
@@ -30092,7 +30063,7 @@
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="159"/>
       <c r="B38" s="170" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C38" s="340" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
@@ -30115,7 +30086,7 @@
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="159"/>
       <c r="B39" s="170" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C39" s="340" t="n">
         <f aca="false">C34+C37-C38</f>
@@ -30138,7 +30109,7 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="159"/>
       <c r="B40" s="183" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C40" s="340" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
@@ -30161,7 +30132,7 @@
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="159"/>
       <c r="B41" s="183" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C41" s="340" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
@@ -30184,7 +30155,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="159"/>
       <c r="B42" s="183" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C42" s="340" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
@@ -30207,7 +30178,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="159"/>
       <c r="B43" s="183" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C43" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
@@ -30230,7 +30201,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="159"/>
       <c r="B44" s="183" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C44" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
@@ -30253,7 +30224,7 @@
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="159"/>
       <c r="B45" s="183" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C45" s="340" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
@@ -30276,7 +30247,7 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="159"/>
       <c r="B46" s="183" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C46" s="342" t="n">
         <f aca="false">C42+C43+C44+C45</f>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="437">
   <si>
     <r>
       <rPr>
@@ -592,7 +592,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Any other business income not included in box 9</t>
+    <t xml:space="preserve">Any other business income not included in box 8</t>
   </si>
   <si>
     <t xml:space="preserve">by your business</t>
@@ -630,11 +630,11 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> to see which expenses are allowed for tax purposes. If your annual turnover was below the VAT threshold shown above</t>
+      <t xml:space="preserve"> to see which expenses are allowed for tax purposes. If your annual turnover was below £30,000</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">you may just put your total expenses in box 20, rather than filling in the whole section.</t>
+    <t xml:space="preserve">you may just put your total expenses in box 19, rather than filling in the whole section.</t>
   </si>
   <si>
     <t xml:space="preserve">Cost of goods bought for re-sale or goods used</t>
@@ -723,7 +723,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">total of boxes 11 to 19</t>
+      <t xml:space="preserve">total of boxes 10 to 18</t>
     </r>
   </si>
   <si>
@@ -772,10 +772,10 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">expenses (box 9 + box 10 minus box 20)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">income (box 9 + box 10 minus box 20 is negative)</t>
+    <t xml:space="preserve">expenses (box 8 + box 9 minus box 19)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">income (box 8 + box 9 minus box 19 is negative)</t>
   </si>
   <si>
     <t xml:space="preserve">Tax allowances for vehicles and equipment (capital allowances)</t>
@@ -915,17 +915,17 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">up to the amount in box 28</t>
+      <t xml:space="preserve">up to the amount in box 27</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">Net business profit for tax purposes (if box 21 + box 26 +</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Any other business income not included in boxes 9 or 10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">box 27 minus boxes 22 to 25) is positive)</t>
+    <t xml:space="preserve">Net business profit for tax purposes (if box 20 + box 25 +</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Any other business income not included in boxes 8 or 9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">box 26 minus boxes 21 to 24) is positive)</t>
   </si>
   <si>
     <t xml:space="preserve"> - for example, Business Start-up Allowance</t>
@@ -937,13 +937,13 @@
     <t xml:space="preserve">Total taxable profits from this business</t>
   </si>
   <si>
-    <t xml:space="preserve">Net business loss for tax purposes (if boxes 22 to 25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">if box 28 + box 30 minus box 29 is positive</t>
-  </si>
-  <si>
-    <t xml:space="preserve">minus (box 21 + box 26 + box 27) is positive)</t>
+    <t xml:space="preserve">Net business loss for tax purposes (if boxes 21 to 24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if box 27 + box 29 minus box 28 is positive</t>
+  </si>
+  <si>
+    <t xml:space="preserve">minus (box 20 + box 25 + box 26) is positive)</t>
   </si>
   <si>
     <t xml:space="preserve">Losses, Class 4 NICs and deductions</t>
@@ -956,7 +956,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">If you have made a loss for tax purposes (box 32), read page SESN 7 of the </t>
+      <t xml:space="preserve">If you have made a loss for tax purposes (box 29), read page SESN 7 of the </t>
     </r>
     <r>
       <rPr>
@@ -975,26 +975,17 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve"> and fill in boxes 33 to 35 as appropriate.</t>
+      <t xml:space="preserve"> and fill in boxes 30 to 32 as appropriate.</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">Loss from this tax year set-off against other income</t>
   </si>
   <si>
+    <t xml:space="preserve">If you are exempt from paying Class 4 NICs, put 'X' in the</t>
+  </si>
+  <si>
     <t xml:space="preserve">for </t>
-  </si>
-  <si>
-    <t xml:space="preserve">choose to pay Class 2 NICs voluntarily, put 'X' in the box</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loss to be carried back to previous year(s) and set-off</t>
-  </si>
-  <si>
-    <t xml:space="preserve">If you are exempt from paying Class 4 NICs, put 'X' in the</t>
-  </si>
-  <si>
-    <t xml:space="preserve">against income (or capital gains)</t>
   </si>
   <si>
     <r>
@@ -1016,6 +1007,42 @@
       </rPr>
       <t xml:space="preserve">read page SESN 10 of the notes</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss to be carried back to previous year(s) and set-off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">If you have been given a </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Class 4 NICs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">against income (or capital gains)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">deferment certificate, put 'X' in the box - </t>
+    </r>
+    <r>
+      <rPr>
+        <i val="true"/>
+        <sz val="8"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">read page SESN 10</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">of the notes</t>
   </si>
   <si>
     <t xml:space="preserve">Total loss to carry forward after all other set-offs</t>
@@ -7959,7 +7986,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="345" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="346"/>
@@ -7982,7 +8009,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="349" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E2" s="349"/>
       <c r="F2" s="349"/>
@@ -7993,7 +8020,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="351" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="K2" s="351"/>
       <c r="L2" s="352" t="str">
@@ -8039,7 +8066,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="356" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J4" s="356"/>
       <c r="K4" s="356"/>
@@ -8059,7 +8086,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="356" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E5" s="356"/>
       <c r="F5" s="356"/>
@@ -8068,7 +8095,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="356" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J5" s="356"/>
       <c r="K5" s="356"/>
@@ -8093,7 +8120,7 @@
       <c r="G6" s="353"/>
       <c r="H6" s="63"/>
       <c r="I6" s="356" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J6" s="356"/>
       <c r="K6" s="356"/>
@@ -8103,7 +8130,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="353" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8113,14 +8140,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="356" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="E7" s="356"/>
       <c r="F7" s="356"/>
       <c r="G7" s="353"/>
       <c r="H7" s="63"/>
       <c r="I7" s="356" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J7" s="356"/>
       <c r="K7" s="356"/>
@@ -8130,7 +8157,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="353" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8145,7 +8172,7 @@
       <c r="G8" s="359"/>
       <c r="H8" s="63"/>
       <c r="I8" s="356" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="J8" s="356"/>
       <c r="K8" s="356"/>
@@ -8155,7 +8182,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="353" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8170,18 +8197,18 @@
       <c r="G9" s="353"/>
       <c r="H9" s="63"/>
       <c r="I9" s="356" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J9" s="356"/>
       <c r="K9" s="356"/>
       <c r="L9" s="360" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="M9" s="360" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="N9" s="361" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="O9" s="353"/>
     </row>
@@ -8211,16 +8238,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="349" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="E11" s="349"/>
       <c r="F11" s="349"/>
       <c r="G11" s="353" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="362" t="n">
@@ -8250,7 +8277,7 @@
       <c r="G12" s="353"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="362" t="n">
@@ -8272,7 +8299,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="356" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="E13" s="356"/>
       <c r="F13" s="356"/>
@@ -8281,7 +8308,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="362" t="n">
@@ -8303,7 +8330,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="356" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -8312,7 +8339,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="349" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J14" s="349"/>
       <c r="K14" s="349"/>
@@ -8331,7 +8358,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="356" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E15" s="356"/>
       <c r="F15" s="356"/>
@@ -8354,7 +8381,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="356" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E16" s="356"/>
       <c r="F16" s="356"/>
@@ -8363,22 +8390,18 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="356" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="J16" s="356"/>
       <c r="K16" s="356"/>
       <c r="L16" s="363" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>419</v>
-      </c>
-      <c r="N16" s="359" t="n">
-        <v>6845</v>
-      </c>
-      <c r="O16" s="353" t="s">
-        <v>33</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N16" s="63"/>
+      <c r="O16" s="63"/>
     </row>
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="63"/>
@@ -8387,7 +8410,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="356" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E17" s="356"/>
       <c r="F17" s="356"/>
@@ -8429,24 +8452,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="349" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E19" s="349"/>
       <c r="F19" s="353" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="G19" s="353" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="365" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="J19" s="365"/>
       <c r="K19" s="365"/>
       <c r="L19" s="63"/>
       <c r="M19" s="366" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8483,7 +8506,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="356" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="E21" s="356"/>
       <c r="F21" s="359" t="n">
@@ -8508,7 +8531,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="359" t="n">
@@ -8519,13 +8542,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="365" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="J22" s="365"/>
       <c r="K22" s="365"/>
       <c r="L22" s="63"/>
       <c r="M22" s="366" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8533,7 +8556,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="355" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8558,11 +8581,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="355" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="349" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="E24" s="349"/>
       <c r="F24" s="63"/>
@@ -8600,7 +8623,7 @@
       <c r="B26" s="369"/>
       <c r="C26" s="63"/>
       <c r="D26" s="356" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="E26" s="356"/>
       <c r="F26" s="359" t="n">
@@ -8621,7 +8644,7 @@
       <c r="B27" s="369"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="357" t="n">
@@ -9633,7 +9656,7 @@
     </row>
     <row r="33" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="96" t="str">
-        <f aca="false">IF(D38&gt;Admin!F26,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
+        <f aca="false">IF(D38&gt;67000,"SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £"&amp;Admin!F26&amp;" VAT threshold","Business income - if your annual turnover was below £"&amp;Admin!F26&amp;" VAT threshold")</f>
         <v>SELF-EMPLOYMENT FULL RETURN REQUIRED AS TURNOVER EXCEEDS £90000 VAT threshold</v>
       </c>
       <c r="B33" s="96"/>
@@ -9686,7 +9709,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="75" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B35" s="63"/>
       <c r="C35" s="64" t="s">
@@ -9701,7 +9724,7 @@
       <c r="J35" s="64"/>
       <c r="K35" s="64"/>
       <c r="L35" s="75" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="M35" s="63"/>
       <c r="N35" s="64" t="s">
@@ -9951,7 +9974,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="75" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B44" s="63"/>
       <c r="C44" s="64" t="s">
@@ -9966,7 +9989,7 @@
       <c r="J44" s="64"/>
       <c r="K44" s="64"/>
       <c r="L44" s="75" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="M44" s="63"/>
       <c r="N44" s="64" t="s">
@@ -10014,7 +10037,7 @@
         <v>33</v>
       </c>
       <c r="D46" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B17," ")</f>
         <v>20136.6666666667</v>
       </c>
       <c r="E46" s="98"/>
@@ -10036,7 +10059,7 @@
         <v>33</v>
       </c>
       <c r="O46" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B28," ")</f>
         <v>6925</v>
       </c>
       <c r="P46" s="98"/>
@@ -10081,7 +10104,7 @@
     </row>
     <row r="48" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="75" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B48" s="63"/>
       <c r="C48" s="64" t="s">
@@ -10096,7 +10119,7 @@
       <c r="J48" s="64"/>
       <c r="K48" s="64"/>
       <c r="L48" s="75" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M48" s="63"/>
       <c r="N48" s="64" t="s">
@@ -10171,7 +10194,7 @@
         <v>33</v>
       </c>
       <c r="D51" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
         <v>7984.25</v>
       </c>
       <c r="E51" s="98"/>
@@ -10193,7 +10216,7 @@
         <v>33</v>
       </c>
       <c r="O51" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
         <v>3900</v>
       </c>
       <c r="P51" s="98"/>
@@ -10238,7 +10261,7 @@
     </row>
     <row r="53" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="75" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
@@ -10253,7 +10276,7 @@
       <c r="J53" s="64"/>
       <c r="K53" s="64"/>
       <c r="L53" s="75" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M53" s="63"/>
       <c r="N53" s="64" t="s">
@@ -10301,7 +10324,7 @@
         <v>33</v>
       </c>
       <c r="D55" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B21," ")</f>
         <v>92735.7333333333</v>
       </c>
       <c r="E55" s="98"/>
@@ -10323,7 +10346,7 @@
         <v>33</v>
       </c>
       <c r="O55" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B24," ")</f>
         <v>3035</v>
       </c>
       <c r="P55" s="98"/>
@@ -10368,7 +10391,7 @@
     </row>
     <row r="57" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="75" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B57" s="63"/>
       <c r="C57" s="64" t="s">
@@ -10383,7 +10406,7 @@
       <c r="J57" s="64"/>
       <c r="K57" s="64"/>
       <c r="L57" s="75" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="M57" s="63"/>
       <c r="N57" s="64" t="s">
@@ -10458,7 +10481,7 @@
         <v>33</v>
       </c>
       <c r="D60" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B22," ")</f>
         <v>13200</v>
       </c>
       <c r="E60" s="98"/>
@@ -10480,7 +10503,7 @@
         <v>33</v>
       </c>
       <c r="O60" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
         <v>6903.66666666666</v>
       </c>
       <c r="P60" s="98"/>
@@ -10525,7 +10548,7 @@
     </row>
     <row r="62" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="75" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
@@ -10540,7 +10563,7 @@
       <c r="J62" s="64"/>
       <c r="K62" s="64"/>
       <c r="L62" s="75" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="M62" s="63"/>
       <c r="N62" s="64" t="s">
@@ -10588,7 +10611,7 @@
         <v>33</v>
       </c>
       <c r="D64" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23," ")</f>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;30000,'Profit &amp; Loss Account'!B23," ")</f>
         <v>950</v>
       </c>
       <c r="E64" s="98"/>
@@ -10707,7 +10730,7 @@
     </row>
     <row r="68" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="75" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
@@ -10722,7 +10745,7 @@
       <c r="J68" s="64"/>
       <c r="K68" s="64"/>
       <c r="L68" s="75" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M68" s="63"/>
       <c r="N68" s="64" t="s">
@@ -11005,7 +11028,7 @@
     </row>
     <row r="78" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="75" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B78" s="63"/>
       <c r="C78" s="64" t="s">
@@ -11020,7 +11043,7 @@
       <c r="J78" s="64"/>
       <c r="K78" s="64"/>
       <c r="L78" s="75" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M78" s="63"/>
       <c r="N78" s="64" t="s">
@@ -11135,7 +11158,7 @@
     </row>
     <row r="82" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="75" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B82" s="63"/>
       <c r="C82" s="64" t="s">
@@ -11150,7 +11173,7 @@
       <c r="J82" s="63"/>
       <c r="K82" s="63"/>
       <c r="L82" s="75" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M82" s="63"/>
       <c r="N82" s="64" t="s">
@@ -11400,7 +11423,7 @@
     </row>
     <row r="91" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="75" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B91" s="63"/>
       <c r="C91" s="64" t="s">
@@ -11415,7 +11438,7 @@
       <c r="J91" s="64"/>
       <c r="K91" s="64"/>
       <c r="L91" s="75" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M91" s="63"/>
       <c r="N91" s="64" t="s">
@@ -11559,7 +11582,7 @@
     </row>
     <row r="96" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="75" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
@@ -11574,7 +11597,7 @@
       <c r="J96" s="64"/>
       <c r="K96" s="64"/>
       <c r="L96" s="75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="M96" s="63"/>
       <c r="N96" s="64" t="s">
@@ -11772,7 +11795,7 @@
     </row>
     <row r="103" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="75" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B103" s="63"/>
       <c r="C103" s="64" t="s">
@@ -11787,7 +11810,7 @@
       <c r="J103" s="64"/>
       <c r="K103" s="64"/>
       <c r="L103" s="75" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="M103" s="63"/>
       <c r="N103" s="64" t="s">
@@ -12010,7 +12033,7 @@
     </row>
     <row r="111" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="75" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B111" s="63"/>
       <c r="C111" s="64" t="s">
@@ -12025,12 +12048,11 @@
       <c r="J111" s="64"/>
       <c r="K111" s="64"/>
       <c r="L111" s="75" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M111" s="63"/>
-      <c r="N111" s="64" t="str">
-        <f aca="false">"If your total profits for "&amp;Admin!G2&amp;" are less than £"&amp;TEXT(Admin!N16,"#,##0")&amp;" and you"</f>
-        <v>If your total profits for 2026-27 are less than £6,845 and you</v>
+      <c r="N111" s="64" t="s">
+        <v>107</v>
       </c>
       <c r="O111" s="63"/>
       <c r="P111" s="63"/>
@@ -12046,7 +12068,7 @@
       <c r="A112" s="106"/>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D112" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -12062,7 +12084,7 @@
       <c r="L112" s="64"/>
       <c r="M112" s="63"/>
       <c r="N112" s="64" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O112" s="110"/>
       <c r="P112" s="110"/>
@@ -12159,11 +12181,11 @@
     </row>
     <row r="116" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="75" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -12174,19 +12196,24 @@
       <c r="J116" s="64"/>
       <c r="K116" s="64"/>
       <c r="L116" s="75" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M116" s="63"/>
       <c r="N116" s="64" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="O116" s="63"/>
       <c r="P116" s="63"/>
       <c r="Q116" s="63"/>
-      <c r="R116" s="115"/>
+      <c r="R116" s="115" t="str">
+        <f aca="false">Admin!G2</f>
+        <v>2026-27</v>
+      </c>
       <c r="S116" s="115"/>
       <c r="T116" s="115"/>
-      <c r="U116" s="64"/>
+      <c r="U116" s="64" t="s">
+        <v>112</v>
+      </c>
       <c r="V116" s="63"/>
       <c r="W116" s="82"/>
     </row>
@@ -12194,7 +12221,7 @@
       <c r="A117" s="106"/>
       <c r="B117" s="63"/>
       <c r="C117" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D117" s="64"/>
       <c r="E117" s="64"/>
@@ -12207,7 +12234,7 @@
       <c r="L117" s="64"/>
       <c r="M117" s="63"/>
       <c r="N117" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O117" s="63"/>
       <c r="P117" s="63"/>
@@ -12233,7 +12260,9 @@
       <c r="K118" s="64"/>
       <c r="L118" s="64"/>
       <c r="M118" s="63"/>
-      <c r="N118" s="92"/>
+      <c r="N118" s="92" t="s">
+        <v>115</v>
+      </c>
       <c r="O118" s="63"/>
       <c r="P118" s="63"/>
       <c r="Q118" s="63"/>
@@ -12304,11 +12333,11 @@
     </row>
     <row r="121" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="75" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B121" s="63"/>
       <c r="C121" s="64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D121" s="64"/>
       <c r="E121" s="64"/>
@@ -12319,11 +12348,11 @@
       <c r="J121" s="64"/>
       <c r="K121" s="64"/>
       <c r="L121" s="75" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M121" s="63"/>
       <c r="N121" s="64" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="O121" s="63"/>
       <c r="P121" s="63"/>
@@ -12339,7 +12368,7 @@
       <c r="A122" s="106"/>
       <c r="B122" s="63"/>
       <c r="C122" s="90" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D122" s="64"/>
       <c r="E122" s="64"/>
@@ -12352,7 +12381,7 @@
       <c r="L122" s="64"/>
       <c r="M122" s="63"/>
       <c r="N122" s="64" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="O122" s="63"/>
       <c r="P122" s="63"/>
@@ -12575,7 +12604,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -12593,7 +12622,7 @@
       <c r="L1" s="121"/>
       <c r="M1" s="121"/>
       <c r="N1" s="122" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="O1" s="122"/>
       <c r="P1" s="122"/>
@@ -12954,7 +12983,7 @@
       </c>
       <c r="M14" s="63"/>
       <c r="N14" s="64" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="O14" s="64"/>
       <c r="P14" s="64"/>
@@ -12984,7 +13013,7 @@
       <c r="L15" s="63"/>
       <c r="M15" s="63"/>
       <c r="N15" s="80" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="O15" s="64"/>
       <c r="P15" s="64"/>
@@ -13011,7 +13040,7 @@
       <c r="L16" s="63"/>
       <c r="M16" s="63"/>
       <c r="N16" s="64" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="O16" s="64"/>
       <c r="P16" s="64"/>
@@ -13468,7 +13497,7 @@
       </c>
       <c r="B32" s="63"/>
       <c r="C32" s="80" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -13516,7 +13545,7 @@
       <c r="L33" s="63"/>
       <c r="M33" s="63"/>
       <c r="N33" s="64" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="O33" s="64"/>
       <c r="P33" s="64"/>
@@ -13543,7 +13572,7 @@
       <c r="L34" s="63"/>
       <c r="M34" s="63"/>
       <c r="N34" s="90" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="O34" s="90"/>
       <c r="P34" s="64"/>
@@ -13850,7 +13879,7 @@
       <c r="L45" s="63"/>
       <c r="M45" s="63"/>
       <c r="N45" s="64" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="O45" s="64"/>
       <c r="P45" s="64"/>
@@ -13967,7 +13996,7 @@
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="103" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B50" s="103"/>
       <c r="C50" s="103"/>
@@ -14038,7 +14067,7 @@
       </c>
       <c r="M52" s="63"/>
       <c r="N52" s="64" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="64"/>
@@ -14176,7 +14205,7 @@
     </row>
     <row r="57" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="103" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B57" s="103"/>
       <c r="C57" s="103"/>
@@ -14203,7 +14232,7 @@
     </row>
     <row r="58" s="105" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="104" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B58" s="104"/>
       <c r="C58" s="104"/>
@@ -14257,7 +14286,7 @@
       <c r="A60" s="79"/>
       <c r="B60" s="63"/>
       <c r="C60" s="130" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="D60" s="63"/>
       <c r="E60" s="63"/>
@@ -14270,7 +14299,7 @@
       <c r="L60" s="63"/>
       <c r="M60" s="63"/>
       <c r="N60" s="130" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="O60" s="63"/>
       <c r="P60" s="63"/>
@@ -14286,7 +14315,7 @@
       <c r="A61" s="79"/>
       <c r="B61" s="63"/>
       <c r="C61" s="64" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="D61" s="64"/>
       <c r="E61" s="64"/>
@@ -14299,7 +14328,7 @@
       <c r="L61" s="64"/>
       <c r="M61" s="64"/>
       <c r="N61" s="64" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="O61" s="64"/>
       <c r="P61" s="64"/>
@@ -14315,7 +14344,7 @@
       <c r="A62" s="79"/>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D62" s="64"/>
       <c r="E62" s="64"/>
@@ -14328,7 +14357,7 @@
       <c r="L62" s="64"/>
       <c r="M62" s="64"/>
       <c r="N62" s="64" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="O62" s="64"/>
       <c r="P62" s="64"/>
@@ -14371,7 +14400,7 @@
       </c>
       <c r="B64" s="63"/>
       <c r="C64" s="64" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D64" s="64"/>
       <c r="E64" s="64"/>
@@ -14496,7 +14525,7 @@
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D68" s="64"/>
       <c r="E68" s="64"/>
@@ -14746,7 +14775,7 @@
       </c>
       <c r="B76" s="63"/>
       <c r="C76" s="64" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D76" s="64"/>
       <c r="E76" s="64"/>
@@ -14996,7 +15025,7 @@
       </c>
       <c r="B84" s="63"/>
       <c r="C84" s="64" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D84" s="64"/>
       <c r="E84" s="64"/>
@@ -15121,7 +15150,7 @@
       </c>
       <c r="B88" s="63"/>
       <c r="C88" s="64" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="D88" s="64"/>
       <c r="E88" s="64"/>
@@ -15246,7 +15275,7 @@
       </c>
       <c r="B92" s="63"/>
       <c r="C92" s="64" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="D92" s="64"/>
       <c r="E92" s="64"/>
@@ -15371,7 +15400,7 @@
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="D96" s="64"/>
       <c r="E96" s="64"/>
@@ -15496,7 +15525,7 @@
       </c>
       <c r="B100" s="63"/>
       <c r="C100" s="64" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D100" s="64"/>
       <c r="E100" s="64"/>
@@ -15621,7 +15650,7 @@
       </c>
       <c r="B104" s="63"/>
       <c r="C104" s="64" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="D104" s="64"/>
       <c r="E104" s="64"/>
@@ -15871,7 +15900,7 @@
       </c>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D112" s="64"/>
       <c r="E112" s="64"/>
@@ -15999,7 +16028,7 @@
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -16124,7 +16153,7 @@
       </c>
       <c r="B120" s="63"/>
       <c r="C120" s="64" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D120" s="64"/>
       <c r="E120" s="64"/>
@@ -16139,7 +16168,7 @@
       </c>
       <c r="M120" s="63"/>
       <c r="N120" s="64" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="O120" s="63"/>
       <c r="P120" s="63"/>
@@ -16306,7 +16335,7 @@
       </c>
       <c r="B126" s="63"/>
       <c r="C126" s="64" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D126" s="64"/>
       <c r="E126" s="64"/>
@@ -16321,7 +16350,7 @@
       </c>
       <c r="M126" s="63"/>
       <c r="N126" s="64" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="O126" s="63"/>
       <c r="P126" s="63"/>
@@ -16337,7 +16366,7 @@
       <c r="A127" s="79"/>
       <c r="B127" s="63"/>
       <c r="C127" s="90" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="D127" s="64"/>
       <c r="E127" s="64"/>
@@ -16350,7 +16379,7 @@
       <c r="L127" s="63"/>
       <c r="M127" s="63"/>
       <c r="N127" s="64" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="O127" s="63"/>
       <c r="P127" s="63"/>
@@ -16488,7 +16517,7 @@
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="104" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B132" s="104"/>
       <c r="C132" s="104"/>
@@ -16515,7 +16544,7 @@
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="104" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="B133" s="104"/>
       <c r="C133" s="104"/>
@@ -16542,7 +16571,7 @@
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="104" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B134" s="104"/>
       <c r="C134" s="104"/>
@@ -16613,7 +16642,7 @@
       </c>
       <c r="M136" s="63"/>
       <c r="N136" s="64" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="O136" s="63"/>
       <c r="P136" s="63"/>
@@ -16750,7 +16779,7 @@
       </c>
       <c r="B141" s="63"/>
       <c r="C141" s="64" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D141" s="64"/>
       <c r="E141" s="64"/>
@@ -16761,7 +16790,7 @@
       </c>
       <c r="H141" s="132"/>
       <c r="I141" s="64" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J141" s="64"/>
       <c r="K141" s="64"/>
@@ -16770,7 +16799,7 @@
       </c>
       <c r="M141" s="63"/>
       <c r="N141" s="64" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="O141" s="63"/>
       <c r="P141" s="63"/>
@@ -16786,7 +16815,7 @@
       <c r="A142" s="106"/>
       <c r="B142" s="63"/>
       <c r="C142" s="64" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D142" s="64"/>
       <c r="E142" s="64"/>
@@ -16912,7 +16941,7 @@
       </c>
       <c r="B146" s="63"/>
       <c r="C146" s="131" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D146" s="64"/>
       <c r="E146" s="64"/>
@@ -16960,7 +16989,7 @@
       </c>
       <c r="M147" s="63"/>
       <c r="N147" s="64" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O147" s="63"/>
       <c r="P147" s="63"/>
@@ -16987,7 +17016,7 @@
       <c r="L148" s="64"/>
       <c r="M148" s="63"/>
       <c r="N148" s="64" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O148" s="63"/>
       <c r="P148" s="63"/>
@@ -17005,7 +17034,7 @@
       </c>
       <c r="B149" s="63"/>
       <c r="C149" s="64" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="D149" s="64"/>
       <c r="E149" s="64"/>
@@ -17081,7 +17110,7 @@
       </c>
       <c r="M151" s="63"/>
       <c r="N151" s="64" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="O151" s="63"/>
       <c r="P151" s="63"/>
@@ -17157,7 +17186,7 @@
       </c>
       <c r="B154" s="63"/>
       <c r="C154" s="64" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="D154" s="64"/>
       <c r="E154" s="64"/>
@@ -17241,7 +17270,7 @@
       </c>
       <c r="M156" s="63"/>
       <c r="N156" s="64" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="O156" s="63"/>
       <c r="P156" s="63"/>
@@ -17259,7 +17288,7 @@
       </c>
       <c r="B157" s="63"/>
       <c r="C157" s="64" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D157" s="64"/>
       <c r="E157" s="64"/>
@@ -17272,7 +17301,7 @@
       <c r="L157" s="63"/>
       <c r="M157" s="63"/>
       <c r="N157" s="64" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="O157" s="63"/>
       <c r="P157" s="63"/>
@@ -17299,7 +17328,7 @@
       <c r="L158" s="63"/>
       <c r="M158" s="63"/>
       <c r="N158" s="64" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O158" s="63"/>
       <c r="P158" s="63"/>
@@ -17407,7 +17436,7 @@
     </row>
     <row r="162" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="103" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="B162" s="103"/>
       <c r="C162" s="103"/>
@@ -17434,7 +17463,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="104" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B163" s="104"/>
       <c r="C163" s="104"/>
@@ -17461,7 +17490,7 @@
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="104" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B164" s="104"/>
       <c r="C164" s="104"/>
@@ -17517,7 +17546,7 @@
       </c>
       <c r="B166" s="63"/>
       <c r="C166" s="64" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="D166" s="64"/>
       <c r="E166" s="64"/>
@@ -17532,7 +17561,7 @@
       </c>
       <c r="M166" s="63"/>
       <c r="N166" s="64" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="O166" s="63"/>
       <c r="P166" s="63"/>
@@ -17559,7 +17588,7 @@
       <c r="L167" s="64"/>
       <c r="M167" s="63"/>
       <c r="N167" s="64" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="O167" s="110"/>
       <c r="P167" s="110"/>
@@ -17674,7 +17703,7 @@
       </c>
       <c r="B171" s="63"/>
       <c r="C171" s="64" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="D171" s="64"/>
       <c r="E171" s="64"/>
@@ -17689,7 +17718,7 @@
       </c>
       <c r="M171" s="63"/>
       <c r="N171" s="64" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="O171" s="63"/>
       <c r="P171" s="63"/>
@@ -17705,7 +17734,7 @@
       <c r="A172" s="106"/>
       <c r="B172" s="63"/>
       <c r="C172" s="64" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="D172" s="64"/>
       <c r="E172" s="64"/>
@@ -17718,7 +17747,7 @@
       <c r="L172" s="64"/>
       <c r="M172" s="63"/>
       <c r="N172" s="64" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="O172" s="63"/>
       <c r="P172" s="63"/>
@@ -17833,7 +17862,7 @@
       </c>
       <c r="B176" s="63"/>
       <c r="C176" s="64" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="D176" s="64"/>
       <c r="E176" s="64"/>
@@ -17848,7 +17877,7 @@
       </c>
       <c r="M176" s="63"/>
       <c r="N176" s="64" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O176" s="63"/>
       <c r="P176" s="63"/>
@@ -17864,7 +17893,7 @@
       <c r="A177" s="79"/>
       <c r="B177" s="63"/>
       <c r="C177" s="64" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="D177" s="63"/>
       <c r="E177" s="63"/>
@@ -17877,7 +17906,7 @@
       <c r="L177" s="63"/>
       <c r="M177" s="63"/>
       <c r="N177" s="64" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="O177" s="63"/>
       <c r="P177" s="63"/>
@@ -17985,7 +18014,7 @@
     </row>
     <row r="181" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="103" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B181" s="103"/>
       <c r="C181" s="103"/>
@@ -18012,7 +18041,7 @@
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="104" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B182" s="104"/>
       <c r="C182" s="104"/>
@@ -18039,7 +18068,7 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="104" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="B183" s="104"/>
       <c r="C183" s="104"/>
@@ -18066,7 +18095,7 @@
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="134" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="B184" s="134"/>
       <c r="C184" s="134"/>
@@ -18120,7 +18149,7 @@
       <c r="A186" s="75"/>
       <c r="B186" s="63"/>
       <c r="C186" s="64" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="D186" s="64"/>
       <c r="E186" s="64"/>
@@ -18135,7 +18164,7 @@
       </c>
       <c r="M186" s="63"/>
       <c r="N186" s="64" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="O186" s="63"/>
       <c r="P186" s="63"/>
@@ -18162,7 +18191,7 @@
       <c r="L187" s="64"/>
       <c r="M187" s="63"/>
       <c r="N187" s="80" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="O187" s="63"/>
       <c r="P187" s="63"/>
@@ -18189,7 +18218,7 @@
       <c r="L188" s="64"/>
       <c r="M188" s="63"/>
       <c r="N188" s="92" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="O188" s="63"/>
       <c r="P188" s="63"/>
@@ -18216,7 +18245,7 @@
       <c r="L189" s="64"/>
       <c r="M189" s="63"/>
       <c r="N189" s="92" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="O189" s="110"/>
       <c r="P189" s="110"/>
@@ -18246,7 +18275,7 @@
         <v>33</v>
       </c>
       <c r="O190" s="137" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P190" s="138"/>
       <c r="Q190" s="138"/>
@@ -18294,7 +18323,7 @@
       </c>
       <c r="B192" s="63"/>
       <c r="C192" s="64" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D192" s="112"/>
       <c r="E192" s="112"/>
@@ -18309,7 +18338,7 @@
       </c>
       <c r="M192" s="63"/>
       <c r="N192" s="64" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="O192" s="63"/>
       <c r="P192" s="63"/>
@@ -18328,7 +18357,7 @@
       <c r="A193" s="79"/>
       <c r="B193" s="63"/>
       <c r="C193" s="64" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="D193" s="64"/>
       <c r="E193" s="64"/>
@@ -18341,7 +18370,7 @@
       <c r="L193" s="64"/>
       <c r="M193" s="64"/>
       <c r="N193" s="80" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O193" s="112"/>
       <c r="P193" s="112"/>
@@ -18357,7 +18386,7 @@
       <c r="A194" s="79"/>
       <c r="B194" s="63"/>
       <c r="C194" s="80" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D194" s="64"/>
       <c r="E194" s="64"/>
@@ -18433,7 +18462,7 @@
       </c>
       <c r="M196" s="63"/>
       <c r="N196" s="64" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="O196" s="63"/>
       <c r="P196" s="63"/>
@@ -18452,7 +18481,7 @@
         <v>33</v>
       </c>
       <c r="D197" s="137" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="E197" s="138"/>
       <c r="F197" s="138"/>
@@ -18470,7 +18499,7 @@
       <c r="L197" s="63"/>
       <c r="M197" s="63"/>
       <c r="N197" s="80" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="O197" s="63"/>
       <c r="P197" s="63"/>
@@ -18511,7 +18540,7 @@
       <c r="A199" s="75"/>
       <c r="B199" s="63"/>
       <c r="C199" s="64" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D199" s="63"/>
       <c r="E199" s="63"/>
@@ -18587,7 +18616,7 @@
       </c>
       <c r="M201" s="63"/>
       <c r="N201" s="64" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="O201" s="63"/>
       <c r="P201" s="63"/>
@@ -18614,7 +18643,7 @@
       <c r="L202" s="63"/>
       <c r="M202" s="63"/>
       <c r="N202" s="64" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="O202" s="63"/>
       <c r="P202" s="63"/>
@@ -18756,7 +18785,7 @@
       <c r="L207" s="63"/>
       <c r="M207" s="63"/>
       <c r="N207" s="64" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="O207" s="63"/>
       <c r="P207" s="63"/>
@@ -18774,7 +18803,7 @@
       </c>
       <c r="B208" s="63"/>
       <c r="C208" s="64" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D208" s="64"/>
       <c r="E208" s="64"/>
@@ -18893,7 +18922,7 @@
     </row>
     <row r="212" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="111" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B212" s="111"/>
       <c r="C212" s="111"/>
@@ -18920,7 +18949,7 @@
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="104" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="B213" s="104"/>
       <c r="C213" s="104"/>
@@ -18947,7 +18976,7 @@
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="104" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B214" s="104"/>
       <c r="C214" s="104"/>
@@ -19003,7 +19032,7 @@
       </c>
       <c r="B216" s="63"/>
       <c r="C216" s="64" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="D216" s="64"/>
       <c r="E216" s="64"/>
@@ -19012,7 +19041,7 @@
         <v>2026-27</v>
       </c>
       <c r="G216" s="64" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="H216" s="64"/>
       <c r="I216" s="64"/>
@@ -19023,7 +19052,7 @@
       </c>
       <c r="M216" s="63"/>
       <c r="N216" s="64" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="O216" s="63"/>
       <c r="P216" s="63"/>
@@ -19050,7 +19079,7 @@
       <c r="L217" s="64"/>
       <c r="M217" s="63"/>
       <c r="N217" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O217" s="63"/>
       <c r="P217" s="63"/>
@@ -19162,7 +19191,7 @@
       </c>
       <c r="B221" s="63"/>
       <c r="C221" s="64" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D221" s="64"/>
       <c r="E221" s="64"/>
@@ -19177,7 +19206,7 @@
       </c>
       <c r="M221" s="63"/>
       <c r="N221" s="64" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="O221" s="63"/>
       <c r="P221" s="63"/>
@@ -19193,7 +19222,7 @@
       <c r="A222" s="79"/>
       <c r="B222" s="63"/>
       <c r="C222" s="64" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D222" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -19209,7 +19238,7 @@
       <c r="L222" s="63"/>
       <c r="M222" s="63"/>
       <c r="N222" s="90" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="O222" s="63"/>
       <c r="P222" s="63"/>
@@ -19317,7 +19346,7 @@
     </row>
     <row r="226" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="148" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B226" s="148"/>
       <c r="C226" s="148"/>
@@ -19373,7 +19402,7 @@
       </c>
       <c r="B228" s="63"/>
       <c r="C228" s="64" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D228" s="64"/>
       <c r="E228" s="64"/>
@@ -19388,7 +19417,7 @@
       </c>
       <c r="M228" s="63"/>
       <c r="N228" s="64" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="O228" s="63"/>
       <c r="P228" s="63"/>
@@ -19404,7 +19433,7 @@
       <c r="A229" s="106"/>
       <c r="B229" s="63"/>
       <c r="C229" s="64" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D229" s="64"/>
       <c r="E229" s="64"/>
@@ -19523,7 +19552,7 @@
     </row>
     <row r="233" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="103" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B233" s="103"/>
       <c r="C233" s="103"/>
@@ -19550,7 +19579,7 @@
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="104" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="B234" s="104"/>
       <c r="C234" s="104"/>
@@ -19577,7 +19606,7 @@
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="104" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B235" s="104"/>
       <c r="C235" s="104"/>
@@ -19631,7 +19660,7 @@
       <c r="A237" s="79"/>
       <c r="B237" s="63"/>
       <c r="C237" s="130" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="D237" s="63"/>
       <c r="E237" s="63"/>
@@ -19644,7 +19673,7 @@
       <c r="L237" s="63"/>
       <c r="M237" s="63"/>
       <c r="N237" s="130" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="O237" s="63"/>
       <c r="P237" s="63"/>
@@ -19687,7 +19716,7 @@
       </c>
       <c r="B239" s="63"/>
       <c r="C239" s="64" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="D239" s="64"/>
       <c r="E239" s="64"/>
@@ -19702,7 +19731,7 @@
       </c>
       <c r="M239" s="63"/>
       <c r="N239" s="64" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="O239" s="63"/>
       <c r="P239" s="63"/>
@@ -19811,7 +19840,7 @@
       </c>
       <c r="B243" s="63"/>
       <c r="C243" s="64" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="D243" s="64"/>
       <c r="E243" s="64"/>
@@ -19826,7 +19855,7 @@
       </c>
       <c r="M243" s="63"/>
       <c r="N243" s="64" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="O243" s="63"/>
       <c r="P243" s="63"/>
@@ -19935,7 +19964,7 @@
       </c>
       <c r="B247" s="63"/>
       <c r="C247" s="64" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D247" s="64"/>
       <c r="E247" s="64"/>
@@ -19950,7 +19979,7 @@
       </c>
       <c r="M247" s="63"/>
       <c r="N247" s="64" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="O247" s="63"/>
       <c r="P247" s="63"/>
@@ -20059,7 +20088,7 @@
       </c>
       <c r="B251" s="63"/>
       <c r="C251" s="64" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="D251" s="64"/>
       <c r="E251" s="64"/>
@@ -20072,7 +20101,7 @@
       <c r="L251" s="63"/>
       <c r="M251" s="63"/>
       <c r="N251" s="130" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="O251" s="112"/>
       <c r="P251" s="112"/>
@@ -20134,7 +20163,7 @@
       </c>
       <c r="M253" s="63"/>
       <c r="N253" s="64" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="O253" s="63"/>
       <c r="P253" s="63"/>
@@ -20177,7 +20206,7 @@
       </c>
       <c r="B255" s="63"/>
       <c r="C255" s="64" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="D255" s="64"/>
       <c r="E255" s="64"/>
@@ -20193,7 +20222,7 @@
         <v>33</v>
       </c>
       <c r="O255" s="150" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P255" s="98"/>
       <c r="Q255" s="98"/>
@@ -20258,7 +20287,7 @@
       <c r="L257" s="63"/>
       <c r="M257" s="63"/>
       <c r="N257" s="130" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="O257" s="63"/>
       <c r="P257" s="63"/>
@@ -20301,7 +20330,7 @@
       </c>
       <c r="B259" s="63"/>
       <c r="C259" s="64" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="D259" s="64"/>
       <c r="E259" s="64"/>
@@ -20316,7 +20345,7 @@
       </c>
       <c r="M259" s="63"/>
       <c r="N259" s="64" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="O259" s="63"/>
       <c r="P259" s="63"/>
@@ -20379,7 +20408,7 @@
         <v>33</v>
       </c>
       <c r="O261" s="137" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P261" s="98"/>
       <c r="Q261" s="98"/>
@@ -20427,7 +20456,7 @@
       </c>
       <c r="B263" s="63"/>
       <c r="C263" s="64" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D263" s="64"/>
       <c r="E263" s="64"/>
@@ -20442,7 +20471,7 @@
       </c>
       <c r="M263" s="63"/>
       <c r="N263" s="64" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="O263" s="63"/>
       <c r="P263" s="63"/>
@@ -20505,7 +20534,7 @@
         <v>33</v>
       </c>
       <c r="O265" s="137" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P265" s="98"/>
       <c r="Q265" s="98"/>
@@ -20553,7 +20582,7 @@
       </c>
       <c r="B267" s="63"/>
       <c r="C267" s="64" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="D267" s="64"/>
       <c r="E267" s="64"/>
@@ -20568,7 +20597,7 @@
       </c>
       <c r="M267" s="63"/>
       <c r="N267" s="64" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="O267" s="63"/>
       <c r="P267" s="63"/>
@@ -20688,7 +20717,7 @@
       </c>
       <c r="M271" s="63"/>
       <c r="N271" s="64" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="O271" s="63"/>
       <c r="P271" s="63"/>
@@ -20800,7 +20829,7 @@
       </c>
       <c r="M275" s="63"/>
       <c r="N275" s="64" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="O275" s="63"/>
       <c r="P275" s="63"/>
@@ -20855,7 +20884,7 @@
         <v>33</v>
       </c>
       <c r="O277" s="137" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="P277" s="98"/>
       <c r="Q277" s="98"/>
@@ -20899,7 +20928,7 @@
     </row>
     <row r="279" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="111" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B279" s="111"/>
       <c r="C279" s="111"/>
@@ -20926,7 +20955,7 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="104" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B280" s="104"/>
       <c r="C280" s="104"/>
@@ -20941,7 +20970,7 @@
         <v>12570</v>
       </c>
       <c r="K280" s="104" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="L280" s="104"/>
       <c r="M280" s="104"/>
@@ -20958,7 +20987,7 @@
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="152" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="B281" s="152"/>
       <c r="C281" s="152"/>
@@ -21014,7 +21043,7 @@
       </c>
       <c r="B283" s="63"/>
       <c r="C283" s="64" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="D283" s="63"/>
       <c r="E283" s="63"/>
@@ -21029,7 +21058,7 @@
       </c>
       <c r="M283" s="63"/>
       <c r="N283" s="64" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="O283" s="63"/>
       <c r="P283" s="63"/>
@@ -21045,7 +21074,7 @@
       <c r="A284" s="79"/>
       <c r="B284" s="63"/>
       <c r="C284" s="64" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="D284" s="63"/>
       <c r="E284" s="63"/>
@@ -21058,7 +21087,7 @@
       <c r="L284" s="63"/>
       <c r="M284" s="63"/>
       <c r="N284" s="90" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="O284" s="63"/>
       <c r="P284" s="63"/>
@@ -21159,7 +21188,7 @@
       </c>
       <c r="B288" s="63"/>
       <c r="C288" s="64" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="D288" s="63"/>
       <c r="E288" s="63"/>
@@ -21186,7 +21215,7 @@
       <c r="A289" s="79"/>
       <c r="B289" s="63"/>
       <c r="C289" s="64" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D289" s="63"/>
       <c r="E289" s="63"/>
@@ -21311,7 +21340,7 @@
     </row>
     <row r="294" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="103" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B294" s="103"/>
       <c r="C294" s="103"/>
@@ -21367,7 +21396,7 @@
       </c>
       <c r="B296" s="63"/>
       <c r="C296" s="64" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="D296" s="63"/>
       <c r="E296" s="63"/>
@@ -22293,10 +22322,10 @@
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="161" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B2" s="162" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C2" s="163" t="n">
         <f aca="false">Admin!B5</f>
@@ -22413,7 +22442,7 @@
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="170" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B5" s="171" t="n">
         <f aca="false">SUM(C5:N5)</f>
@@ -22471,7 +22500,7 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="170" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="B6" s="171" t="n">
         <f aca="false">SUM(C6:N6)</f>
@@ -22529,7 +22558,7 @@
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="170" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B7" s="171" t="n">
         <f aca="false">SUM(C7:N7)</f>
@@ -22587,7 +22616,7 @@
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="170" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="B8" s="171" t="n">
         <f aca="false">SUM(C8:N8)</f>
@@ -22645,7 +22674,7 @@
     </row>
     <row r="9" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="174" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="B9" s="171" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -22720,7 +22749,7 @@
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="170" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B11" s="171" t="n">
         <f aca="false">SUM(C11:N11)</f>
@@ -22795,7 +22824,7 @@
     </row>
     <row r="13" s="177" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="181" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B13" s="178"/>
       <c r="C13" s="178"/>
@@ -22814,7 +22843,7 @@
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="170" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B14" s="171" t="n">
         <f aca="false">SUM(C14:N14)</f>
@@ -22872,7 +22901,7 @@
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="170" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B15" s="171" t="n">
         <f aca="false">SUM(C15:N15)</f>
@@ -22930,7 +22959,7 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="170" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="B16" s="171" t="n">
         <f aca="false">SUM(C16:N16)</f>
@@ -22988,7 +23017,7 @@
     </row>
     <row r="17" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="174" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B17" s="171" t="n">
         <f aca="false">SUM(B14:B16)</f>
@@ -23063,7 +23092,7 @@
     </row>
     <row r="19" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="174" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="B19" s="171" t="n">
         <f aca="false">B9+B11-B17</f>
@@ -23121,7 +23150,7 @@
     </row>
     <row r="20" s="177" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="181" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B20" s="178"/>
       <c r="C20" s="182"/>
@@ -23140,7 +23169,7 @@
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="170" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B21" s="171" t="n">
         <f aca="false">SUM(C21:N21)</f>
@@ -23198,7 +23227,7 @@
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="183" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B22" s="171" t="n">
         <f aca="false">SUM(C22:N22)</f>
@@ -23256,7 +23285,7 @@
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="183" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B23" s="171" t="n">
         <f aca="false">SUM(C23:N23)</f>
@@ -23314,7 +23343,7 @@
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="183" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B24" s="171" t="n">
         <f aca="false">SUM(C24:N24)</f>
@@ -23372,7 +23401,7 @@
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="183" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="B25" s="171" t="n">
         <f aca="false">SUM(C25:N25)</f>
@@ -23430,7 +23459,7 @@
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="183" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B26" s="171" t="n">
         <f aca="false">SUM(C26:N26)</f>
@@ -23488,7 +23517,7 @@
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="183" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B27" s="171" t="n">
         <f aca="false">SUM(C27:N27)</f>
@@ -23546,7 +23575,7 @@
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="183" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B28" s="171" t="n">
         <f aca="false">SUM(C28:N28)</f>
@@ -23604,7 +23633,7 @@
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="183" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B29" s="171" t="n">
         <f aca="false">SUM(C29:N29)</f>
@@ -23662,7 +23691,7 @@
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="183" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B30" s="171" t="n">
         <f aca="false">SUM(C30:N30)</f>
@@ -23720,7 +23749,7 @@
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="183" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B31" s="171" t="n">
         <f aca="false">SUM(C31:N31)</f>
@@ -23778,7 +23807,7 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="183" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B32" s="171" t="n">
         <f aca="false">SUM(C32:N32)</f>
@@ -23836,7 +23865,7 @@
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="170" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B33" s="171" t="n">
         <f aca="false">SUM(C33:N33)</f>
@@ -23894,7 +23923,7 @@
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="170" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B34" s="171" t="n">
         <f aca="false">SUM(C34:N34)</f>
@@ -23952,7 +23981,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="174" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B35" s="171" t="n">
         <f aca="false">SUM(B21:B34)</f>
@@ -24027,7 +24056,7 @@
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="174" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B37" s="171" t="n">
         <f aca="false">B19-B35</f>
@@ -24085,7 +24114,7 @@
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="170" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="B38" s="171" t="n">
         <f aca="false">SUM(C38:N38)</f>
@@ -24143,7 +24172,7 @@
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="174" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="B39" s="171" t="n">
         <f aca="false">B37+B38</f>
@@ -24218,7 +24247,7 @@
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="188" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B41" s="157"/>
       <c r="C41" s="158"/>
@@ -24237,7 +24266,7 @@
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="183" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B42" s="178" t="n">
         <f aca="false">SUM(C42:N42)</f>
@@ -24295,7 +24324,7 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="183" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="B43" s="178" t="n">
         <f aca="false">SUM(C43:N43)</f>
@@ -24353,7 +24382,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="183" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="B44" s="178" t="n">
         <f aca="false">SUM(C44:N44)</f>
@@ -24411,7 +24440,7 @@
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="189" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="B45" s="190" t="n">
         <f aca="false">SUM(C45:N45)</f>
@@ -24469,7 +24498,7 @@
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="183" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B46" s="178" t="n">
         <f aca="false">SUM(C46:N46)</f>
@@ -24601,25 +24630,25 @@
     <row r="2" s="197" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="196"/>
       <c r="B2" s="198" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="C2" s="198" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D2" s="198" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="E2" s="198" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="F2" s="198" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G2" s="198" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="I2" s="196"/>
     </row>
@@ -24648,7 +24677,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="196"/>
       <c r="B5" s="196" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="C5" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -24676,7 +24705,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="196"/>
       <c r="B6" s="196" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="C6" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -24704,7 +24733,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="196"/>
       <c r="B7" s="196" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C7" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -24754,7 +24783,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="196"/>
       <c r="B10" s="203" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="C10" s="196"/>
       <c r="D10" s="196"/>
@@ -24778,7 +24807,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="196"/>
       <c r="B12" s="196" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C12" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -24806,7 +24835,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="196"/>
       <c r="B13" s="196" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C13" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -24834,7 +24863,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="196"/>
       <c r="B14" s="196" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C14" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -24862,7 +24891,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="196"/>
       <c r="B15" s="196" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C15" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -24890,7 +24919,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="196"/>
       <c r="B16" s="196" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C16" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -24918,7 +24947,7 @@
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="196"/>
       <c r="B17" s="196" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="C17" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -24946,7 +24975,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="196"/>
       <c r="B18" s="196" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C18" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -24974,7 +25003,7 @@
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="196"/>
       <c r="B19" s="196" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C19" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -25002,7 +25031,7 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="196"/>
       <c r="B20" s="196" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="C20" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -25030,7 +25059,7 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="196"/>
       <c r="B21" s="196" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C21" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -25058,7 +25087,7 @@
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="196"/>
       <c r="B22" s="196" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C22" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -25097,7 +25126,7 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="196"/>
       <c r="B24" s="196" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C24" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -25125,7 +25154,7 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="196"/>
       <c r="B25" s="196" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C25" s="201" t="n">
         <v>0</v>
@@ -25144,14 +25173,14 @@
         <v>0</v>
       </c>
       <c r="H25" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I25" s="196"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="196"/>
       <c r="B26" s="196" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
@@ -25201,7 +25230,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="196"/>
       <c r="B29" s="203" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="C29" s="204" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
@@ -25273,7 +25302,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="196"/>
       <c r="B34" s="203" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="C34" s="196"/>
       <c r="D34" s="196"/>
@@ -25297,7 +25326,7 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="196"/>
       <c r="B36" s="196" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C36" s="201" t="n">
         <v>0</v>
@@ -25316,14 +25345,14 @@
         <v>0</v>
       </c>
       <c r="H36" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I36" s="196"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="196"/>
       <c r="B37" s="196" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C37" s="201" t="n">
         <v>0</v>
@@ -25342,14 +25371,14 @@
         <v>0</v>
       </c>
       <c r="H37" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I37" s="196"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="196"/>
       <c r="B38" s="196" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C38" s="201" t="n">
         <v>0</v>
@@ -25368,14 +25397,14 @@
         <v>0</v>
       </c>
       <c r="H38" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I38" s="196"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="196"/>
       <c r="B39" s="196" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="C39" s="201" t="n">
         <v>0</v>
@@ -25394,14 +25423,14 @@
         <v>0</v>
       </c>
       <c r="H39" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I39" s="196"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="196"/>
       <c r="B40" s="196" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C40" s="201" t="n">
         <v>0</v>
@@ -25420,14 +25449,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I40" s="196"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="196"/>
       <c r="B41" s="196" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C41" s="201" t="n">
         <v>0</v>
@@ -25446,14 +25475,14 @@
         <v>0</v>
       </c>
       <c r="H41" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I41" s="196"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="196"/>
       <c r="B42" s="196" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="C42" s="201" t="n">
         <v>0</v>
@@ -25472,14 +25501,14 @@
         <v>0</v>
       </c>
       <c r="H42" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I42" s="196"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="196"/>
       <c r="B43" s="196" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="C43" s="201" t="n">
         <v>0</v>
@@ -25498,14 +25527,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I43" s="196"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="196"/>
       <c r="B44" s="196" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="C44" s="201" t="n">
         <v>0</v>
@@ -25524,14 +25553,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I44" s="196"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="196"/>
       <c r="B45" s="196" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="C45" s="201" t="n">
         <v>0</v>
@@ -25550,14 +25579,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I45" s="196"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="196"/>
       <c r="B46" s="196" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="C46" s="201" t="n">
         <v>0</v>
@@ -25576,14 +25605,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I46" s="196"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="196"/>
       <c r="B47" s="196" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="C47" s="201" t="n">
         <v>0</v>
@@ -25602,14 +25631,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I47" s="196"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="196"/>
       <c r="B48" s="196" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="C48" s="201" t="n">
         <v>0</v>
@@ -25628,14 +25657,14 @@
         <v>0</v>
       </c>
       <c r="H48" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I48" s="196"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="196"/>
       <c r="B49" s="196" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="C49" s="201" t="n">
         <v>0</v>
@@ -25654,14 +25683,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I49" s="196"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="196"/>
       <c r="B50" s="196" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C50" s="201" t="n">
         <v>0</v>
@@ -25680,7 +25709,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="196" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="I50" s="196"/>
     </row>
@@ -25751,14 +25780,14 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="212"/>
       <c r="B2" s="216" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C2" s="217" t="str">
         <f aca="false">Admin!L2</f>
         <v>2026-27</v>
       </c>
       <c r="D2" s="218" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E2" s="218"/>
       <c r="F2" s="218"/>
@@ -25785,7 +25814,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="212"/>
       <c r="B5" s="223" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C5" s="223"/>
       <c r="D5" s="223"/>
@@ -25800,7 +25829,7 @@
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="212"/>
       <c r="B6" s="221" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C6" s="221" t="str">
         <f aca="false">C2</f>
@@ -25818,7 +25847,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="212"/>
       <c r="B7" s="223" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C7" s="223"/>
       <c r="D7" s="223"/>
@@ -25833,7 +25862,7 @@
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="212"/>
       <c r="B8" s="221" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C8" s="221" t="n">
         <f aca="false">Admin!N$11</f>
@@ -25855,7 +25884,7 @@
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="212"/>
       <c r="B9" s="221" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C9" s="221" t="n">
         <f aca="false">Admin!M$11</f>
@@ -25876,7 +25905,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="212"/>
       <c r="B10" s="221" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C10" s="221" t="n">
         <f aca="false">Admin!N$13</f>
@@ -25897,7 +25926,7 @@
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="212"/>
       <c r="B11" s="229" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C11" s="230"/>
       <c r="D11" s="231"/>
@@ -25912,7 +25941,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="212"/>
       <c r="B12" s="221" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C12" s="221"/>
       <c r="D12" s="235"/>
@@ -25927,7 +25956,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="212"/>
       <c r="B13" s="236" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C13" s="237" t="n">
         <f aca="false">Admin!B21</f>
@@ -25952,7 +25981,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="212"/>
       <c r="B15" s="240" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C15" s="240"/>
       <c r="D15" s="227" t="n">
@@ -25970,7 +25999,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="212"/>
       <c r="B16" s="240" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C16" s="240"/>
       <c r="D16" s="227" t="n">
@@ -25998,7 +26027,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="212"/>
       <c r="B18" s="242" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C18" s="242"/>
       <c r="D18" s="238"/>
@@ -26031,11 +26060,11 @@
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="212"/>
       <c r="B21" s="229" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C21" s="244"/>
       <c r="D21" s="245" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E21" s="245"/>
       <c r="F21" s="245"/>
@@ -26055,10 +26084,10 @@
       <c r="B23" s="221"/>
       <c r="C23" s="221"/>
       <c r="D23" s="247" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="E23" s="248" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="F23" s="249"/>
       <c r="G23" s="219"/>
@@ -26075,14 +26104,14 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="212"/>
       <c r="B25" s="221" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="C25" s="251" t="str">
         <f aca="false">Admin!B24</f>
         <v>2027-28</v>
       </c>
       <c r="D25" s="252" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E25" s="241" t="n">
         <f aca="false">E18</f>
@@ -26094,7 +26123,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="212"/>
       <c r="B26" s="221" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C26" s="221"/>
       <c r="D26" s="253" t="n">
@@ -26111,7 +26140,7 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="212"/>
       <c r="B27" s="221" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C27" s="221"/>
       <c r="D27" s="253" t="n">
@@ -26137,7 +26166,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="212"/>
       <c r="B29" s="254" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="C29" s="255"/>
       <c r="D29" s="238"/>
@@ -26148,7 +26177,7 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="212"/>
       <c r="B30" s="256" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C30" s="256"/>
       <c r="D30" s="212"/>
@@ -26159,7 +26188,7 @@
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="212"/>
       <c r="B31" s="259" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C31" s="259"/>
       <c r="D31" s="260"/>
@@ -26170,7 +26199,7 @@
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="212"/>
       <c r="B32" s="261" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C32" s="259"/>
       <c r="D32" s="260"/>
@@ -26181,7 +26210,7 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="212"/>
       <c r="B33" s="255" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C33" s="255"/>
       <c r="D33" s="260"/>
@@ -26192,7 +26221,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="212"/>
       <c r="B34" s="255" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C34" s="255"/>
       <c r="D34" s="260"/>
@@ -26203,7 +26232,7 @@
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="212"/>
       <c r="B35" s="255" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C35" s="255"/>
       <c r="D35" s="260"/>
@@ -26278,39 +26307,39 @@
     <row r="2" s="273" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="268"/>
       <c r="B2" s="269" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C2" s="270" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D2" s="270" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E2" s="270" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="F2" s="270" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="G2" s="270" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="H2" s="270" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="I2" s="270" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="J2" s="271"/>
       <c r="K2" s="269" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L2" s="272"/>
     </row>
     <row r="3" s="273" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="268"/>
       <c r="B3" s="274" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C3" s="274"/>
       <c r="D3" s="275"/>
@@ -26359,7 +26388,7 @@
       </c>
       <c r="J4" s="159"/>
       <c r="K4" s="279" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L4" s="165"/>
     </row>
@@ -26513,7 +26542,7 @@
       </c>
       <c r="J8" s="159"/>
       <c r="K8" s="279" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="L8" s="165"/>
     </row>
@@ -26865,7 +26894,7 @@
       <c r="F1" s="288"/>
       <c r="G1" s="288"/>
       <c r="H1" s="289" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="I1" s="289"/>
       <c r="J1" s="289"/>
@@ -26873,7 +26902,7 @@
       <c r="L1" s="289"/>
       <c r="M1" s="288"/>
       <c r="N1" s="289" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="O1" s="289"/>
       <c r="P1" s="289"/>
@@ -26881,7 +26910,7 @@
       <c r="R1" s="289"/>
       <c r="S1" s="288"/>
       <c r="T1" s="289" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="U1" s="289"/>
       <c r="V1" s="289"/>
@@ -26901,63 +26930,63 @@
     <row r="2" s="303" customFormat="true" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="293"/>
       <c r="B2" s="294" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="C2" s="295"/>
       <c r="D2" s="296" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="E2" s="297"/>
       <c r="F2" s="296" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="G2" s="297"/>
       <c r="H2" s="298" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="I2" s="297"/>
       <c r="J2" s="296" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K2" s="297"/>
       <c r="L2" s="296" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M2" s="297"/>
       <c r="N2" s="298" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O2" s="297"/>
       <c r="P2" s="296" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Q2" s="297"/>
       <c r="R2" s="296" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="S2" s="297"/>
       <c r="T2" s="298" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="U2" s="297"/>
       <c r="V2" s="296" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="W2" s="297"/>
       <c r="X2" s="299" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="Y2" s="300"/>
       <c r="Z2" s="296" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AA2" s="297"/>
       <c r="AB2" s="296" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AC2" s="301"/>
       <c r="AD2" s="302" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AE2" s="302"/>
       <c r="AF2" s="302"/>
@@ -26995,7 +27024,7 @@
       <c r="AB3" s="306"/>
       <c r="AC3" s="165"/>
       <c r="AD3" s="310" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AE3" s="310"/>
       <c r="AF3" s="310"/>
@@ -27005,7 +27034,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="277"/>
       <c r="B4" s="311" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C4" s="311"/>
       <c r="D4" s="311"/>
@@ -27385,7 +27414,7 @@
       <c r="AB11" s="178"/>
       <c r="AC11" s="165"/>
       <c r="AD11" s="310" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AE11" s="310"/>
       <c r="AF11" s="310"/>
@@ -27615,7 +27644,7 @@
       <c r="AB15" s="178"/>
       <c r="AC15" s="165"/>
       <c r="AD15" s="310" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="AE15" s="310"/>
       <c r="AF15" s="310"/>
@@ -27845,7 +27874,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="165"/>
       <c r="AD19" s="310" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AE19" s="310"/>
       <c r="AF19" s="310"/>
@@ -28075,7 +28104,7 @@
       <c r="AB23" s="178"/>
       <c r="AC23" s="165"/>
       <c r="AD23" s="310" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AE23" s="310"/>
       <c r="AF23" s="310"/>
@@ -28383,7 +28412,7 @@
       </c>
       <c r="AC28" s="165"/>
       <c r="AD28" s="310" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AE28" s="310"/>
       <c r="AF28" s="310"/>
@@ -28601,10 +28630,10 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="159"/>
       <c r="B2" s="331" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C2" s="162" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D2" s="163" t="n">
         <f aca="false">Admin!B5</f>
@@ -28724,7 +28753,7 @@
     <row r="5" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="179"/>
       <c r="B5" s="333" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C5" s="171" t="n">
         <f aca="false">SUM(D5:O5)</f>
@@ -28801,7 +28830,7 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="159"/>
       <c r="B7" s="335" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C7" s="171" t="n">
         <f aca="false">SUM(D7:O7)</f>
@@ -28878,7 +28907,7 @@
     <row r="9" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="179"/>
       <c r="B9" s="334" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C9" s="171" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -28955,7 +28984,7 @@
     <row r="11" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="179"/>
       <c r="B11" s="333" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C11" s="171" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -29032,7 +29061,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="159"/>
       <c r="B13" s="334" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C13" s="171" t="n">
         <f aca="false">SUM(D13:O13)</f>
@@ -29109,7 +29138,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="159"/>
       <c r="B15" s="333" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C15" s="171" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -29168,7 +29197,7 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="159"/>
       <c r="B16" s="335" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C16" s="171" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -29227,7 +29256,7 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="159"/>
       <c r="B17" s="336" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C17" s="171" t="n">
         <f aca="false">SUM(D17:O17)</f>
@@ -29304,10 +29333,10 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="159"/>
       <c r="B19" s="338" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C19" s="162" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="D19" s="163" t="n">
         <f aca="false">D2</f>
@@ -29440,7 +29469,7 @@
     <row r="22" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="179"/>
       <c r="B22" s="333" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="C22" s="171" t="n">
         <f aca="false">SUM(D22:O22)</f>
@@ -29517,7 +29546,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="159"/>
       <c r="B24" s="335" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C24" s="171" t="n">
         <f aca="false">SUM(D24:O24)</f>
@@ -29594,7 +29623,7 @@
     <row r="26" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="179"/>
       <c r="B26" s="334" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="C26" s="171" t="n">
         <f aca="false">SUM(D26:O26)</f>
@@ -29671,7 +29700,7 @@
     <row r="28" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="179"/>
       <c r="B28" s="333" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="C28" s="171" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -29748,7 +29777,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="159"/>
       <c r="B30" s="334" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C30" s="171" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -29825,7 +29854,7 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="159"/>
       <c r="B32" s="333" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="C32" s="171" t="n">
         <f aca="false">SUM(D32:O32)</f>
@@ -29884,7 +29913,7 @@
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="159"/>
       <c r="B33" s="335" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="C33" s="171" t="n">
         <f aca="false">SUM(D33:O33)</f>
@@ -29943,7 +29972,7 @@
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="159"/>
       <c r="B34" s="336" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">SUM(D34:O34)</f>
@@ -30020,7 +30049,7 @@
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="159"/>
       <c r="B36" s="339" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C36" s="339"/>
       <c r="D36" s="159"/>
@@ -30040,7 +30069,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="159"/>
       <c r="B37" s="170" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C37" s="340" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
@@ -30063,7 +30092,7 @@
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="159"/>
       <c r="B38" s="170" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C38" s="340" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
@@ -30086,7 +30115,7 @@
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="159"/>
       <c r="B39" s="170" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C39" s="340" t="n">
         <f aca="false">C34+C37-C38</f>
@@ -30109,7 +30138,7 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="159"/>
       <c r="B40" s="183" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C40" s="340" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
@@ -30132,7 +30161,7 @@
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="159"/>
       <c r="B41" s="183" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C41" s="340" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
@@ -30155,7 +30184,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="159"/>
       <c r="B42" s="183" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C42" s="340" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
@@ -30178,7 +30207,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="159"/>
       <c r="B43" s="183" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C43" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
@@ -30201,7 +30230,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="159"/>
       <c r="B44" s="183" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C44" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
@@ -30224,7 +30253,7 @@
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="159"/>
       <c r="B45" s="183" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C45" s="340" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
@@ -30247,7 +30276,7 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="159"/>
       <c r="B46" s="183" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C46" s="342" t="n">
         <f aca="false">C42+C43+C44+C45</f>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -8368,13 +8368,13 @@
       <c r="J16" s="356"/>
       <c r="K16" s="356"/>
       <c r="L16" s="363" t="n">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="M16" s="63" t="s">
         <v>419</v>
       </c>
       <c r="N16" s="359" t="n">
-        <v>6845</v>
+        <v>7105</v>
       </c>
       <c r="O16" s="353" t="s">
         <v>33</v>
@@ -12030,7 +12030,7 @@
       <c r="M111" s="63"/>
       <c r="N111" s="64" t="str">
         <f aca="false">"If your total profits for "&amp;Admin!G2&amp;" are less than £"&amp;TEXT(Admin!N16,"#,##0")&amp;" and you"</f>
-        <v>If your total profits for 2026-27 are less than £6,845 and you</v>
+        <v>If your total profits for 2026-27 are less than £7,105 and you</v>
       </c>
       <c r="O111" s="63"/>
       <c r="P111" s="63"/>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="436">
   <si>
     <r>
       <rPr>
@@ -467,6 +467,12 @@
   </si>
   <si>
     <t xml:space="preserve">Calculated no entry required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Copyright (C) 2006-2026 DIY Accounting Limited</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licensed under the PolyForm Internal Use License 1.0.0 with an additional grant for accountants. Free to use, source available: https://spreadsheets.diyaccounting.co.uk</t>
   </si>
   <si>
     <t xml:space="preserve">HM Revenue                  &amp; Customs</t>
@@ -6317,7 +6323,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W59"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="3.66"/>
@@ -7894,6 +7900,16 @@
       <c r="U56" s="36"/>
       <c r="V56" s="36"/>
       <c r="W56" s="37"/>
+    </row>
+    <row r="58" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
+        <v>39</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -7959,7 +7975,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="345" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="346"/>
@@ -7982,7 +7998,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="349" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E2" s="349"/>
       <c r="F2" s="349"/>
@@ -7993,7 +8009,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="351" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="K2" s="351"/>
       <c r="L2" s="352" t="str">
@@ -8030,7 +8046,7 @@
       </c>
       <c r="C4" s="63"/>
       <c r="D4" s="356" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E4" s="356"/>
       <c r="F4" s="356"/>
@@ -8039,7 +8055,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="356" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="J4" s="356"/>
       <c r="K4" s="356"/>
@@ -8059,7 +8075,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="356" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E5" s="356"/>
       <c r="F5" s="356"/>
@@ -8068,7 +8084,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="356" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J5" s="356"/>
       <c r="K5" s="356"/>
@@ -8093,7 +8109,7 @@
       <c r="G6" s="353"/>
       <c r="H6" s="63"/>
       <c r="I6" s="356" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="J6" s="356"/>
       <c r="K6" s="356"/>
@@ -8103,7 +8119,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="353" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8113,14 +8129,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="356" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E7" s="356"/>
       <c r="F7" s="356"/>
       <c r="G7" s="353"/>
       <c r="H7" s="63"/>
       <c r="I7" s="356" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="J7" s="356"/>
       <c r="K7" s="356"/>
@@ -8130,7 +8146,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="353" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8145,7 +8161,7 @@
       <c r="G8" s="359"/>
       <c r="H8" s="63"/>
       <c r="I8" s="356" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J8" s="356"/>
       <c r="K8" s="356"/>
@@ -8155,7 +8171,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="353" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8170,18 +8186,18 @@
       <c r="G9" s="353"/>
       <c r="H9" s="63"/>
       <c r="I9" s="356" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="J9" s="356"/>
       <c r="K9" s="356"/>
       <c r="L9" s="360" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="M9" s="360" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="N9" s="361" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="O9" s="353"/>
     </row>
@@ -8211,16 +8227,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="349" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E11" s="349"/>
       <c r="F11" s="349"/>
       <c r="G11" s="353" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="362" t="n">
@@ -8250,7 +8266,7 @@
       <c r="G12" s="353"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="362" t="n">
@@ -8272,7 +8288,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="356" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E13" s="356"/>
       <c r="F13" s="356"/>
@@ -8281,7 +8297,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="362" t="n">
@@ -8303,7 +8319,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="356" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -8312,7 +8328,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="349" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="J14" s="349"/>
       <c r="K14" s="349"/>
@@ -8331,7 +8347,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="356" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E15" s="356"/>
       <c r="F15" s="356"/>
@@ -8354,7 +8370,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="356" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E16" s="356"/>
       <c r="F16" s="356"/>
@@ -8363,7 +8379,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="356" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="J16" s="356"/>
       <c r="K16" s="356"/>
@@ -8371,7 +8387,7 @@
         <v>3.65</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N16" s="359" t="n">
         <v>7105</v>
@@ -8387,7 +8403,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="356" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E17" s="356"/>
       <c r="F17" s="356"/>
@@ -8429,24 +8445,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="349" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E19" s="349"/>
       <c r="F19" s="353" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G19" s="353" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="365" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="J19" s="365"/>
       <c r="K19" s="365"/>
       <c r="L19" s="63"/>
       <c r="M19" s="366" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8483,7 +8499,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="356" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E21" s="356"/>
       <c r="F21" s="359" t="n">
@@ -8508,7 +8524,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="359" t="n">
@@ -8519,13 +8535,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="365" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="J22" s="365"/>
       <c r="K22" s="365"/>
       <c r="L22" s="63"/>
       <c r="M22" s="366" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8533,7 +8549,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="355" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8558,11 +8574,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="355" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="349" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E24" s="349"/>
       <c r="F24" s="63"/>
@@ -8600,7 +8616,7 @@
       <c r="B26" s="369"/>
       <c r="C26" s="63"/>
       <c r="D26" s="356" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E26" s="356"/>
       <c r="F26" s="359" t="n">
@@ -8621,7 +8637,7 @@
       <c r="B27" s="369"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="357" t="n">
@@ -8727,7 +8743,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -8735,7 +8751,7 @@
       <c r="E1" s="51"/>
       <c r="F1" s="51"/>
       <c r="G1" s="52" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="52"/>
       <c r="I1" s="52"/>
@@ -8745,7 +8761,7 @@
       <c r="M1" s="52"/>
       <c r="N1" s="52"/>
       <c r="O1" s="53" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="P1" s="53"/>
       <c r="Q1" s="53"/>
@@ -8772,7 +8788,7 @@
       <c r="M2" s="52"/>
       <c r="N2" s="52"/>
       <c r="O2" s="54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="P2" s="54"/>
       <c r="Q2" s="55" t="n">
@@ -8783,7 +8799,7 @@
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
       <c r="U2" s="56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V2" s="55" t="n">
         <f aca="false">Admin!B17</f>
@@ -9052,7 +9068,7 @@
       </c>
       <c r="M12" s="63"/>
       <c r="N12" s="64" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="O12" s="64"/>
       <c r="P12" s="64"/>
@@ -9082,7 +9098,7 @@
       <c r="L13" s="63"/>
       <c r="M13" s="63"/>
       <c r="N13" s="80" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="O13" s="64"/>
       <c r="P13" s="64"/>
@@ -9195,7 +9211,7 @@
       </c>
       <c r="M17" s="63"/>
       <c r="N17" s="64" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="O17" s="64"/>
       <c r="P17" s="64"/>
@@ -9225,7 +9241,7 @@
       <c r="L18" s="63"/>
       <c r="M18" s="63"/>
       <c r="N18" s="85" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="O18" s="85"/>
       <c r="P18" s="85"/>
@@ -9367,7 +9383,7 @@
       </c>
       <c r="M23" s="64"/>
       <c r="N23" s="64" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="O23" s="90"/>
       <c r="P23" s="64"/>
@@ -9388,7 +9404,7 @@
       </c>
       <c r="B24" s="63"/>
       <c r="C24" s="64" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D24" s="63"/>
       <c r="E24" s="63"/>
@@ -9417,7 +9433,7 @@
       <c r="A25" s="79"/>
       <c r="B25" s="63"/>
       <c r="C25" s="64" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D25" s="63"/>
       <c r="E25" s="63"/>
@@ -9444,7 +9460,7 @@
       <c r="A26" s="79"/>
       <c r="B26" s="63"/>
       <c r="C26" s="80" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D26" s="81"/>
       <c r="E26" s="81"/>
@@ -9474,7 +9490,7 @@
       <c r="A27" s="79"/>
       <c r="B27" s="63"/>
       <c r="C27" s="80" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D27" s="63"/>
       <c r="E27" s="63"/>
@@ -9514,7 +9530,7 @@
       </c>
       <c r="M28" s="63"/>
       <c r="N28" s="80" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="O28" s="81"/>
       <c r="P28" s="81"/>
@@ -9541,7 +9557,7 @@
       <c r="L29" s="63"/>
       <c r="M29" s="63"/>
       <c r="N29" s="92" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="O29" s="81"/>
       <c r="P29" s="81"/>
@@ -9690,7 +9706,7 @@
       </c>
       <c r="B35" s="63"/>
       <c r="C35" s="64" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D35" s="64"/>
       <c r="E35" s="64"/>
@@ -9705,7 +9721,7 @@
       </c>
       <c r="M35" s="63"/>
       <c r="N35" s="64" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="O35" s="64"/>
       <c r="P35" s="64"/>
@@ -9721,7 +9737,7 @@
       <c r="A36" s="79"/>
       <c r="B36" s="63"/>
       <c r="C36" s="90" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D36" s="63"/>
       <c r="E36" s="63"/>
@@ -9734,7 +9750,7 @@
       <c r="L36" s="63"/>
       <c r="M36" s="63"/>
       <c r="N36" s="90" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="O36" s="63"/>
       <c r="P36" s="63"/>
@@ -9845,7 +9861,7 @@
     </row>
     <row r="40" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="103" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B40" s="103"/>
       <c r="C40" s="103"/>
@@ -9872,7 +9888,7 @@
     </row>
     <row r="41" s="105" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="104" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B41" s="104"/>
       <c r="C41" s="104"/>
@@ -9899,7 +9915,7 @@
     </row>
     <row r="42" s="105" customFormat="true" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="104" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B42" s="104"/>
       <c r="C42" s="104"/>
@@ -9955,7 +9971,7 @@
       </c>
       <c r="B44" s="63"/>
       <c r="C44" s="64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="D44" s="64"/>
       <c r="E44" s="64"/>
@@ -9970,7 +9986,7 @@
       </c>
       <c r="M44" s="63"/>
       <c r="N44" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O44" s="63"/>
       <c r="P44" s="63"/>
@@ -10085,7 +10101,7 @@
       </c>
       <c r="B48" s="63"/>
       <c r="C48" s="64" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D48" s="64"/>
       <c r="E48" s="64"/>
@@ -10100,7 +10116,7 @@
       </c>
       <c r="M48" s="63"/>
       <c r="N48" s="64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O48" s="63"/>
       <c r="P48" s="63"/>
@@ -10116,7 +10132,7 @@
       <c r="A49" s="79"/>
       <c r="B49" s="63"/>
       <c r="C49" s="90" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D49" s="63"/>
       <c r="E49" s="63"/>
@@ -10242,7 +10258,7 @@
       </c>
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D53" s="64"/>
       <c r="E53" s="64"/>
@@ -10257,7 +10273,7 @@
       </c>
       <c r="M53" s="63"/>
       <c r="N53" s="64" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O53" s="63"/>
       <c r="P53" s="63"/>
@@ -10372,7 +10388,7 @@
       </c>
       <c r="B57" s="63"/>
       <c r="C57" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D57" s="64"/>
       <c r="E57" s="64"/>
@@ -10387,7 +10403,7 @@
       </c>
       <c r="M57" s="63"/>
       <c r="N57" s="64" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="O57" s="63"/>
       <c r="P57" s="63"/>
@@ -10414,7 +10430,7 @@
       <c r="L58" s="63"/>
       <c r="M58" s="63"/>
       <c r="N58" s="90" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O58" s="63"/>
       <c r="P58" s="63"/>
@@ -10529,7 +10545,7 @@
       </c>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="D62" s="64"/>
       <c r="E62" s="64"/>
@@ -10544,7 +10560,7 @@
       </c>
       <c r="M62" s="63"/>
       <c r="N62" s="64" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="O62" s="63"/>
       <c r="P62" s="63"/>
@@ -10655,7 +10671,7 @@
     </row>
     <row r="66" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="107" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B66" s="107"/>
       <c r="C66" s="107"/>
@@ -10711,7 +10727,7 @@
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D68" s="64"/>
       <c r="E68" s="64"/>
@@ -10726,7 +10742,7 @@
       </c>
       <c r="M68" s="63"/>
       <c r="N68" s="64" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O68" s="63"/>
       <c r="P68" s="63"/>
@@ -10742,7 +10758,7 @@
       <c r="A69" s="79"/>
       <c r="B69" s="63"/>
       <c r="C69" s="90" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D69" s="64"/>
       <c r="E69" s="64"/>
@@ -10755,7 +10771,7 @@
       <c r="L69" s="63"/>
       <c r="M69" s="63"/>
       <c r="N69" s="90" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="O69" s="63"/>
       <c r="P69" s="63"/>
@@ -10868,7 +10884,7 @@
     </row>
     <row r="73" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="103" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B73" s="103"/>
       <c r="C73" s="103"/>
@@ -10897,7 +10913,7 @@
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="104" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B74" s="104"/>
       <c r="C74" s="104"/>
@@ -10924,7 +10940,7 @@
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="104" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="B75" s="104"/>
       <c r="C75" s="104"/>
@@ -10953,7 +10969,7 @@
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="104" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B76" s="104"/>
       <c r="C76" s="104"/>
@@ -11009,7 +11025,7 @@
       </c>
       <c r="B78" s="63"/>
       <c r="C78" s="64" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D78" s="64"/>
       <c r="E78" s="64"/>
@@ -11024,7 +11040,7 @@
       </c>
       <c r="M78" s="63"/>
       <c r="N78" s="64" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O78" s="63"/>
       <c r="P78" s="63"/>
@@ -11139,7 +11155,7 @@
       </c>
       <c r="B82" s="63"/>
       <c r="C82" s="64" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D82" s="63"/>
       <c r="E82" s="63"/>
@@ -11154,7 +11170,7 @@
       </c>
       <c r="M82" s="63"/>
       <c r="N82" s="64" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="O82" s="63"/>
       <c r="P82" s="63"/>
@@ -11170,7 +11186,7 @@
       <c r="A83" s="79"/>
       <c r="B83" s="63"/>
       <c r="C83" s="64" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D83" s="63"/>
       <c r="E83" s="63"/>
@@ -11183,7 +11199,7 @@
       <c r="L83" s="64"/>
       <c r="M83" s="63"/>
       <c r="N83" s="64" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="O83" s="110"/>
       <c r="P83" s="110"/>
@@ -11294,7 +11310,7 @@
     </row>
     <row r="87" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="111" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B87" s="111"/>
       <c r="C87" s="111"/>
@@ -11321,7 +11337,7 @@
     </row>
     <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="104" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B88" s="104"/>
       <c r="C88" s="104"/>
@@ -11348,7 +11364,7 @@
     </row>
     <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="104" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B89" s="104"/>
       <c r="C89" s="104"/>
@@ -11404,7 +11420,7 @@
       </c>
       <c r="B91" s="63"/>
       <c r="C91" s="64" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D91" s="64"/>
       <c r="E91" s="64"/>
@@ -11419,7 +11435,7 @@
       </c>
       <c r="M91" s="63"/>
       <c r="N91" s="64" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="O91" s="63"/>
       <c r="P91" s="63"/>
@@ -11435,7 +11451,7 @@
       <c r="A92" s="64"/>
       <c r="B92" s="63"/>
       <c r="C92" s="90" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D92" s="64"/>
       <c r="E92" s="64"/>
@@ -11448,7 +11464,7 @@
       <c r="L92" s="64"/>
       <c r="M92" s="63"/>
       <c r="N92" s="64" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O92" s="110"/>
       <c r="P92" s="110"/>
@@ -11563,7 +11579,7 @@
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D96" s="64"/>
       <c r="E96" s="64"/>
@@ -11578,7 +11594,7 @@
       </c>
       <c r="M96" s="63"/>
       <c r="N96" s="64" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="O96" s="63"/>
       <c r="P96" s="63"/>
@@ -11594,7 +11610,7 @@
       <c r="A97" s="106"/>
       <c r="B97" s="63"/>
       <c r="C97" s="64" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D97" s="64"/>
       <c r="E97" s="64"/>
@@ -11607,7 +11623,7 @@
       <c r="L97" s="64"/>
       <c r="M97" s="63"/>
       <c r="N97" s="90" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="O97" s="63"/>
       <c r="P97" s="63"/>
@@ -11720,7 +11736,7 @@
     </row>
     <row r="101" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="103" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B101" s="103"/>
       <c r="C101" s="103"/>
@@ -11776,7 +11792,7 @@
       </c>
       <c r="B103" s="63"/>
       <c r="C103" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D103" s="64"/>
       <c r="E103" s="64"/>
@@ -11791,7 +11807,7 @@
       </c>
       <c r="M103" s="63"/>
       <c r="N103" s="64" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="O103" s="63"/>
       <c r="P103" s="63"/>
@@ -11807,7 +11823,7 @@
       <c r="A104" s="79"/>
       <c r="B104" s="63"/>
       <c r="C104" s="80" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="D104" s="112"/>
       <c r="E104" s="112"/>
@@ -11820,7 +11836,7 @@
       <c r="L104" s="64"/>
       <c r="M104" s="63"/>
       <c r="N104" s="64" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="O104" s="63"/>
       <c r="P104" s="63"/>
@@ -11931,7 +11947,7 @@
     </row>
     <row r="108" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="111" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B108" s="111"/>
       <c r="C108" s="111"/>
@@ -11958,7 +11974,7 @@
     </row>
     <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="104" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B109" s="104"/>
       <c r="C109" s="104"/>
@@ -12014,7 +12030,7 @@
       </c>
       <c r="B111" s="63"/>
       <c r="C111" s="64" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D111" s="64"/>
       <c r="E111" s="64"/>
@@ -12046,7 +12062,7 @@
       <c r="A112" s="106"/>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D112" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -12062,7 +12078,7 @@
       <c r="L112" s="64"/>
       <c r="M112" s="63"/>
       <c r="N112" s="64" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O112" s="110"/>
       <c r="P112" s="110"/>
@@ -12163,7 +12179,7 @@
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -12178,7 +12194,7 @@
       </c>
       <c r="M116" s="63"/>
       <c r="N116" s="64" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="O116" s="63"/>
       <c r="P116" s="63"/>
@@ -12194,7 +12210,7 @@
       <c r="A117" s="106"/>
       <c r="B117" s="63"/>
       <c r="C117" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D117" s="64"/>
       <c r="E117" s="64"/>
@@ -12207,7 +12223,7 @@
       <c r="L117" s="64"/>
       <c r="M117" s="63"/>
       <c r="N117" s="64" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="O117" s="63"/>
       <c r="P117" s="63"/>
@@ -12308,7 +12324,7 @@
       </c>
       <c r="B121" s="63"/>
       <c r="C121" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D121" s="64"/>
       <c r="E121" s="64"/>
@@ -12323,7 +12339,7 @@
       </c>
       <c r="M121" s="63"/>
       <c r="N121" s="64" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="O121" s="63"/>
       <c r="P121" s="63"/>
@@ -12339,7 +12355,7 @@
       <c r="A122" s="106"/>
       <c r="B122" s="63"/>
       <c r="C122" s="90" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D122" s="64"/>
       <c r="E122" s="64"/>
@@ -12352,7 +12368,7 @@
       <c r="L122" s="64"/>
       <c r="M122" s="63"/>
       <c r="N122" s="64" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="O122" s="63"/>
       <c r="P122" s="63"/>
@@ -12575,7 +12591,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="51" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B1" s="51"/>
       <c r="C1" s="51"/>
@@ -12593,7 +12609,7 @@
       <c r="L1" s="121"/>
       <c r="M1" s="121"/>
       <c r="N1" s="122" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O1" s="122"/>
       <c r="P1" s="122"/>
@@ -12620,7 +12636,7 @@
       <c r="L2" s="121"/>
       <c r="M2" s="121"/>
       <c r="N2" s="54" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="O2" s="54"/>
       <c r="P2" s="54"/>
@@ -12632,7 +12648,7 @@
       <c r="S2" s="55"/>
       <c r="T2" s="55"/>
       <c r="U2" s="56" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="V2" s="55" t="n">
         <f aca="false">Admin!B17</f>
@@ -12954,7 +12970,7 @@
       </c>
       <c r="M14" s="63"/>
       <c r="N14" s="64" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="O14" s="64"/>
       <c r="P14" s="64"/>
@@ -12984,7 +13000,7 @@
       <c r="L15" s="63"/>
       <c r="M15" s="63"/>
       <c r="N15" s="80" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O15" s="64"/>
       <c r="P15" s="64"/>
@@ -13011,7 +13027,7 @@
       <c r="L16" s="63"/>
       <c r="M16" s="63"/>
       <c r="N16" s="64" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="O16" s="64"/>
       <c r="P16" s="64"/>
@@ -13468,7 +13484,7 @@
       </c>
       <c r="B32" s="63"/>
       <c r="C32" s="80" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D32" s="64"/>
       <c r="E32" s="64"/>
@@ -13516,7 +13532,7 @@
       <c r="L33" s="63"/>
       <c r="M33" s="63"/>
       <c r="N33" s="64" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="O33" s="64"/>
       <c r="P33" s="64"/>
@@ -13543,7 +13559,7 @@
       <c r="L34" s="63"/>
       <c r="M34" s="63"/>
       <c r="N34" s="90" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O34" s="90"/>
       <c r="P34" s="64"/>
@@ -13850,7 +13866,7 @@
       <c r="L45" s="63"/>
       <c r="M45" s="63"/>
       <c r="N45" s="64" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="O45" s="64"/>
       <c r="P45" s="64"/>
@@ -13967,7 +13983,7 @@
     </row>
     <row r="50" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="103" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B50" s="103"/>
       <c r="C50" s="103"/>
@@ -14023,7 +14039,7 @@
       </c>
       <c r="B52" s="63"/>
       <c r="C52" s="64" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D52" s="64"/>
       <c r="E52" s="64"/>
@@ -14038,7 +14054,7 @@
       </c>
       <c r="M52" s="63"/>
       <c r="N52" s="64" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="O52" s="64"/>
       <c r="P52" s="64"/>
@@ -14054,7 +14070,7 @@
       <c r="A53" s="79"/>
       <c r="B53" s="63"/>
       <c r="C53" s="64" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D53" s="63"/>
       <c r="E53" s="63"/>
@@ -14176,7 +14192,7 @@
     </row>
     <row r="57" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="103" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B57" s="103"/>
       <c r="C57" s="103"/>
@@ -14203,7 +14219,7 @@
     </row>
     <row r="58" s="105" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="104" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B58" s="104"/>
       <c r="C58" s="104"/>
@@ -14257,7 +14273,7 @@
       <c r="A60" s="79"/>
       <c r="B60" s="63"/>
       <c r="C60" s="130" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D60" s="63"/>
       <c r="E60" s="63"/>
@@ -14270,7 +14286,7 @@
       <c r="L60" s="63"/>
       <c r="M60" s="63"/>
       <c r="N60" s="130" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="O60" s="63"/>
       <c r="P60" s="63"/>
@@ -14286,7 +14302,7 @@
       <c r="A61" s="79"/>
       <c r="B61" s="63"/>
       <c r="C61" s="64" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D61" s="64"/>
       <c r="E61" s="64"/>
@@ -14299,7 +14315,7 @@
       <c r="L61" s="64"/>
       <c r="M61" s="64"/>
       <c r="N61" s="64" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="O61" s="64"/>
       <c r="P61" s="64"/>
@@ -14315,7 +14331,7 @@
       <c r="A62" s="79"/>
       <c r="B62" s="63"/>
       <c r="C62" s="64" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="D62" s="64"/>
       <c r="E62" s="64"/>
@@ -14328,7 +14344,7 @@
       <c r="L62" s="64"/>
       <c r="M62" s="64"/>
       <c r="N62" s="64" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="O62" s="64"/>
       <c r="P62" s="64"/>
@@ -14371,7 +14387,7 @@
       </c>
       <c r="B64" s="63"/>
       <c r="C64" s="64" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D64" s="64"/>
       <c r="E64" s="64"/>
@@ -14496,7 +14512,7 @@
       </c>
       <c r="B68" s="63"/>
       <c r="C68" s="64" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D68" s="64"/>
       <c r="E68" s="64"/>
@@ -14621,7 +14637,7 @@
       </c>
       <c r="B72" s="63"/>
       <c r="C72" s="64" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D72" s="64"/>
       <c r="E72" s="64"/>
@@ -14746,7 +14762,7 @@
       </c>
       <c r="B76" s="63"/>
       <c r="C76" s="64" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D76" s="64"/>
       <c r="E76" s="64"/>
@@ -14871,7 +14887,7 @@
       </c>
       <c r="B80" s="63"/>
       <c r="C80" s="64" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D80" s="64"/>
       <c r="E80" s="64"/>
@@ -14996,7 +15012,7 @@
       </c>
       <c r="B84" s="63"/>
       <c r="C84" s="64" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="D84" s="64"/>
       <c r="E84" s="64"/>
@@ -15121,7 +15137,7 @@
       </c>
       <c r="B88" s="63"/>
       <c r="C88" s="64" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D88" s="64"/>
       <c r="E88" s="64"/>
@@ -15246,7 +15262,7 @@
       </c>
       <c r="B92" s="63"/>
       <c r="C92" s="64" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D92" s="64"/>
       <c r="E92" s="64"/>
@@ -15371,7 +15387,7 @@
       </c>
       <c r="B96" s="63"/>
       <c r="C96" s="64" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="D96" s="64"/>
       <c r="E96" s="64"/>
@@ -15496,7 +15512,7 @@
       </c>
       <c r="B100" s="63"/>
       <c r="C100" s="64" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="D100" s="64"/>
       <c r="E100" s="64"/>
@@ -15621,7 +15637,7 @@
       </c>
       <c r="B104" s="63"/>
       <c r="C104" s="64" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D104" s="64"/>
       <c r="E104" s="64"/>
@@ -15746,7 +15762,7 @@
       </c>
       <c r="B108" s="63"/>
       <c r="C108" s="64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D108" s="64"/>
       <c r="E108" s="64"/>
@@ -15871,7 +15887,7 @@
       </c>
       <c r="B112" s="63"/>
       <c r="C112" s="64" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="D112" s="64"/>
       <c r="E112" s="64"/>
@@ -15999,7 +16015,7 @@
       </c>
       <c r="B116" s="63"/>
       <c r="C116" s="64" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D116" s="64"/>
       <c r="E116" s="64"/>
@@ -16124,7 +16140,7 @@
       </c>
       <c r="B120" s="63"/>
       <c r="C120" s="64" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="D120" s="64"/>
       <c r="E120" s="64"/>
@@ -16139,7 +16155,7 @@
       </c>
       <c r="M120" s="63"/>
       <c r="N120" s="64" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O120" s="63"/>
       <c r="P120" s="63"/>
@@ -16250,7 +16266,7 @@
     </row>
     <row r="124" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="107" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B124" s="107"/>
       <c r="C124" s="107"/>
@@ -16306,7 +16322,7 @@
       </c>
       <c r="B126" s="63"/>
       <c r="C126" s="64" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D126" s="64"/>
       <c r="E126" s="64"/>
@@ -16321,7 +16337,7 @@
       </c>
       <c r="M126" s="63"/>
       <c r="N126" s="64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O126" s="63"/>
       <c r="P126" s="63"/>
@@ -16337,7 +16353,7 @@
       <c r="A127" s="79"/>
       <c r="B127" s="63"/>
       <c r="C127" s="90" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="D127" s="64"/>
       <c r="E127" s="64"/>
@@ -16350,7 +16366,7 @@
       <c r="L127" s="63"/>
       <c r="M127" s="63"/>
       <c r="N127" s="64" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O127" s="63"/>
       <c r="P127" s="63"/>
@@ -16461,7 +16477,7 @@
     </row>
     <row r="131" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="103" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B131" s="103"/>
       <c r="C131" s="103"/>
@@ -16488,7 +16504,7 @@
     </row>
     <row r="132" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="104" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B132" s="104"/>
       <c r="C132" s="104"/>
@@ -16515,7 +16531,7 @@
     </row>
     <row r="133" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="104" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B133" s="104"/>
       <c r="C133" s="104"/>
@@ -16542,7 +16558,7 @@
     </row>
     <row r="134" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="104" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B134" s="104"/>
       <c r="C134" s="104"/>
@@ -16598,7 +16614,7 @@
       </c>
       <c r="B136" s="63"/>
       <c r="C136" s="131" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D136" s="64"/>
       <c r="E136" s="64"/>
@@ -16613,7 +16629,7 @@
       </c>
       <c r="M136" s="63"/>
       <c r="N136" s="64" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="O136" s="63"/>
       <c r="P136" s="63"/>
@@ -16750,7 +16766,7 @@
       </c>
       <c r="B141" s="63"/>
       <c r="C141" s="64" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D141" s="64"/>
       <c r="E141" s="64"/>
@@ -16761,7 +16777,7 @@
       </c>
       <c r="H141" s="132"/>
       <c r="I141" s="64" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="J141" s="64"/>
       <c r="K141" s="64"/>
@@ -16770,7 +16786,7 @@
       </c>
       <c r="M141" s="63"/>
       <c r="N141" s="64" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O141" s="63"/>
       <c r="P141" s="63"/>
@@ -16786,7 +16802,7 @@
       <c r="A142" s="106"/>
       <c r="B142" s="63"/>
       <c r="C142" s="64" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="D142" s="64"/>
       <c r="E142" s="64"/>
@@ -16912,7 +16928,7 @@
       </c>
       <c r="B146" s="63"/>
       <c r="C146" s="131" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="D146" s="64"/>
       <c r="E146" s="64"/>
@@ -16960,7 +16976,7 @@
       </c>
       <c r="M147" s="63"/>
       <c r="N147" s="64" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O147" s="63"/>
       <c r="P147" s="63"/>
@@ -16987,7 +17003,7 @@
       <c r="L148" s="64"/>
       <c r="M148" s="63"/>
       <c r="N148" s="64" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="O148" s="63"/>
       <c r="P148" s="63"/>
@@ -17005,7 +17021,7 @@
       </c>
       <c r="B149" s="63"/>
       <c r="C149" s="64" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D149" s="64"/>
       <c r="E149" s="64"/>
@@ -17081,7 +17097,7 @@
       </c>
       <c r="M151" s="63"/>
       <c r="N151" s="64" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O151" s="63"/>
       <c r="P151" s="63"/>
@@ -17157,7 +17173,7 @@
       </c>
       <c r="B154" s="63"/>
       <c r="C154" s="64" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D154" s="64"/>
       <c r="E154" s="64"/>
@@ -17241,7 +17257,7 @@
       </c>
       <c r="M156" s="63"/>
       <c r="N156" s="64" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O156" s="63"/>
       <c r="P156" s="63"/>
@@ -17259,7 +17275,7 @@
       </c>
       <c r="B157" s="63"/>
       <c r="C157" s="64" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D157" s="64"/>
       <c r="E157" s="64"/>
@@ -17272,7 +17288,7 @@
       <c r="L157" s="63"/>
       <c r="M157" s="63"/>
       <c r="N157" s="64" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O157" s="63"/>
       <c r="P157" s="63"/>
@@ -17299,7 +17315,7 @@
       <c r="L158" s="63"/>
       <c r="M158" s="63"/>
       <c r="N158" s="64" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O158" s="63"/>
       <c r="P158" s="63"/>
@@ -17407,7 +17423,7 @@
     </row>
     <row r="162" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="103" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B162" s="103"/>
       <c r="C162" s="103"/>
@@ -17434,7 +17450,7 @@
     </row>
     <row r="163" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="104" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B163" s="104"/>
       <c r="C163" s="104"/>
@@ -17461,7 +17477,7 @@
     </row>
     <row r="164" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="104" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B164" s="104"/>
       <c r="C164" s="104"/>
@@ -17517,7 +17533,7 @@
       </c>
       <c r="B166" s="63"/>
       <c r="C166" s="64" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D166" s="64"/>
       <c r="E166" s="64"/>
@@ -17532,7 +17548,7 @@
       </c>
       <c r="M166" s="63"/>
       <c r="N166" s="64" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O166" s="63"/>
       <c r="P166" s="63"/>
@@ -17559,7 +17575,7 @@
       <c r="L167" s="64"/>
       <c r="M167" s="63"/>
       <c r="N167" s="64" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O167" s="110"/>
       <c r="P167" s="110"/>
@@ -17674,7 +17690,7 @@
       </c>
       <c r="B171" s="63"/>
       <c r="C171" s="64" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D171" s="64"/>
       <c r="E171" s="64"/>
@@ -17689,7 +17705,7 @@
       </c>
       <c r="M171" s="63"/>
       <c r="N171" s="64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O171" s="63"/>
       <c r="P171" s="63"/>
@@ -17705,7 +17721,7 @@
       <c r="A172" s="106"/>
       <c r="B172" s="63"/>
       <c r="C172" s="64" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D172" s="64"/>
       <c r="E172" s="64"/>
@@ -17718,7 +17734,7 @@
       <c r="L172" s="64"/>
       <c r="M172" s="63"/>
       <c r="N172" s="64" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O172" s="63"/>
       <c r="P172" s="63"/>
@@ -17833,7 +17849,7 @@
       </c>
       <c r="B176" s="63"/>
       <c r="C176" s="64" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D176" s="64"/>
       <c r="E176" s="64"/>
@@ -17848,7 +17864,7 @@
       </c>
       <c r="M176" s="63"/>
       <c r="N176" s="64" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O176" s="63"/>
       <c r="P176" s="63"/>
@@ -17864,7 +17880,7 @@
       <c r="A177" s="79"/>
       <c r="B177" s="63"/>
       <c r="C177" s="64" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D177" s="63"/>
       <c r="E177" s="63"/>
@@ -17877,7 +17893,7 @@
       <c r="L177" s="63"/>
       <c r="M177" s="63"/>
       <c r="N177" s="64" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O177" s="63"/>
       <c r="P177" s="63"/>
@@ -17985,7 +18001,7 @@
     </row>
     <row r="181" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="103" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B181" s="103"/>
       <c r="C181" s="103"/>
@@ -18012,7 +18028,7 @@
     </row>
     <row r="182" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="104" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B182" s="104"/>
       <c r="C182" s="104"/>
@@ -18039,7 +18055,7 @@
     </row>
     <row r="183" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="104" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B183" s="104"/>
       <c r="C183" s="104"/>
@@ -18066,7 +18082,7 @@
     </row>
     <row r="184" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="134" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B184" s="134"/>
       <c r="C184" s="134"/>
@@ -18120,7 +18136,7 @@
       <c r="A186" s="75"/>
       <c r="B186" s="63"/>
       <c r="C186" s="64" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="D186" s="64"/>
       <c r="E186" s="64"/>
@@ -18135,7 +18151,7 @@
       </c>
       <c r="M186" s="63"/>
       <c r="N186" s="64" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O186" s="63"/>
       <c r="P186" s="63"/>
@@ -18162,7 +18178,7 @@
       <c r="L187" s="64"/>
       <c r="M187" s="63"/>
       <c r="N187" s="80" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O187" s="63"/>
       <c r="P187" s="63"/>
@@ -18189,7 +18205,7 @@
       <c r="L188" s="64"/>
       <c r="M188" s="63"/>
       <c r="N188" s="92" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O188" s="63"/>
       <c r="P188" s="63"/>
@@ -18216,7 +18232,7 @@
       <c r="L189" s="64"/>
       <c r="M189" s="63"/>
       <c r="N189" s="92" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O189" s="110"/>
       <c r="P189" s="110"/>
@@ -18246,7 +18262,7 @@
         <v>33</v>
       </c>
       <c r="O190" s="137" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P190" s="138"/>
       <c r="Q190" s="138"/>
@@ -18294,7 +18310,7 @@
       </c>
       <c r="B192" s="63"/>
       <c r="C192" s="64" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D192" s="112"/>
       <c r="E192" s="112"/>
@@ -18309,7 +18325,7 @@
       </c>
       <c r="M192" s="63"/>
       <c r="N192" s="64" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O192" s="63"/>
       <c r="P192" s="63"/>
@@ -18328,7 +18344,7 @@
       <c r="A193" s="79"/>
       <c r="B193" s="63"/>
       <c r="C193" s="64" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="D193" s="64"/>
       <c r="E193" s="64"/>
@@ -18341,7 +18357,7 @@
       <c r="L193" s="64"/>
       <c r="M193" s="64"/>
       <c r="N193" s="80" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O193" s="112"/>
       <c r="P193" s="112"/>
@@ -18357,7 +18373,7 @@
       <c r="A194" s="79"/>
       <c r="B194" s="63"/>
       <c r="C194" s="80" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D194" s="64"/>
       <c r="E194" s="64"/>
@@ -18433,7 +18449,7 @@
       </c>
       <c r="M196" s="63"/>
       <c r="N196" s="64" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="O196" s="63"/>
       <c r="P196" s="63"/>
@@ -18452,7 +18468,7 @@
         <v>33</v>
       </c>
       <c r="D197" s="137" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E197" s="138"/>
       <c r="F197" s="138"/>
@@ -18470,7 +18486,7 @@
       <c r="L197" s="63"/>
       <c r="M197" s="63"/>
       <c r="N197" s="80" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O197" s="63"/>
       <c r="P197" s="63"/>
@@ -18511,7 +18527,7 @@
       <c r="A199" s="75"/>
       <c r="B199" s="63"/>
       <c r="C199" s="64" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D199" s="63"/>
       <c r="E199" s="63"/>
@@ -18587,7 +18603,7 @@
       </c>
       <c r="M201" s="63"/>
       <c r="N201" s="64" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="O201" s="63"/>
       <c r="P201" s="63"/>
@@ -18614,7 +18630,7 @@
       <c r="L202" s="63"/>
       <c r="M202" s="63"/>
       <c r="N202" s="64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="O202" s="63"/>
       <c r="P202" s="63"/>
@@ -18729,7 +18745,7 @@
       </c>
       <c r="M206" s="63"/>
       <c r="N206" s="64" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O206" s="63"/>
       <c r="P206" s="63"/>
@@ -18756,7 +18772,7 @@
       <c r="L207" s="63"/>
       <c r="M207" s="63"/>
       <c r="N207" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O207" s="63"/>
       <c r="P207" s="63"/>
@@ -18774,7 +18790,7 @@
       </c>
       <c r="B208" s="63"/>
       <c r="C208" s="64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D208" s="64"/>
       <c r="E208" s="64"/>
@@ -18893,7 +18909,7 @@
     </row>
     <row r="212" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="111" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B212" s="111"/>
       <c r="C212" s="111"/>
@@ -18920,7 +18936,7 @@
     </row>
     <row r="213" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="104" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="B213" s="104"/>
       <c r="C213" s="104"/>
@@ -18947,7 +18963,7 @@
     </row>
     <row r="214" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="104" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B214" s="104"/>
       <c r="C214" s="104"/>
@@ -19003,7 +19019,7 @@
       </c>
       <c r="B216" s="63"/>
       <c r="C216" s="64" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D216" s="64"/>
       <c r="E216" s="64"/>
@@ -19012,7 +19028,7 @@
         <v>2026-27</v>
       </c>
       <c r="G216" s="64" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="H216" s="64"/>
       <c r="I216" s="64"/>
@@ -19023,7 +19039,7 @@
       </c>
       <c r="M216" s="63"/>
       <c r="N216" s="64" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="O216" s="63"/>
       <c r="P216" s="63"/>
@@ -19050,7 +19066,7 @@
       <c r="L217" s="64"/>
       <c r="M217" s="63"/>
       <c r="N217" s="64" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O217" s="63"/>
       <c r="P217" s="63"/>
@@ -19162,7 +19178,7 @@
       </c>
       <c r="B221" s="63"/>
       <c r="C221" s="64" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D221" s="64"/>
       <c r="E221" s="64"/>
@@ -19177,7 +19193,7 @@
       </c>
       <c r="M221" s="63"/>
       <c r="N221" s="64" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="O221" s="63"/>
       <c r="P221" s="63"/>
@@ -19193,7 +19209,7 @@
       <c r="A222" s="79"/>
       <c r="B222" s="63"/>
       <c r="C222" s="64" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D222" s="114" t="str">
         <f aca="false">Admin!G2</f>
@@ -19209,7 +19225,7 @@
       <c r="L222" s="63"/>
       <c r="M222" s="63"/>
       <c r="N222" s="90" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="O222" s="63"/>
       <c r="P222" s="63"/>
@@ -19317,7 +19333,7 @@
     </row>
     <row r="226" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="148" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B226" s="148"/>
       <c r="C226" s="148"/>
@@ -19373,7 +19389,7 @@
       </c>
       <c r="B228" s="63"/>
       <c r="C228" s="64" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D228" s="64"/>
       <c r="E228" s="64"/>
@@ -19388,7 +19404,7 @@
       </c>
       <c r="M228" s="63"/>
       <c r="N228" s="64" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="O228" s="63"/>
       <c r="P228" s="63"/>
@@ -19404,7 +19420,7 @@
       <c r="A229" s="106"/>
       <c r="B229" s="63"/>
       <c r="C229" s="64" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D229" s="64"/>
       <c r="E229" s="64"/>
@@ -19523,7 +19539,7 @@
     </row>
     <row r="233" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="103" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B233" s="103"/>
       <c r="C233" s="103"/>
@@ -19550,7 +19566,7 @@
     </row>
     <row r="234" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="104" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B234" s="104"/>
       <c r="C234" s="104"/>
@@ -19577,7 +19593,7 @@
     </row>
     <row r="235" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="104" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B235" s="104"/>
       <c r="C235" s="104"/>
@@ -19631,7 +19647,7 @@
       <c r="A237" s="79"/>
       <c r="B237" s="63"/>
       <c r="C237" s="130" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="D237" s="63"/>
       <c r="E237" s="63"/>
@@ -19644,7 +19660,7 @@
       <c r="L237" s="63"/>
       <c r="M237" s="63"/>
       <c r="N237" s="130" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="O237" s="63"/>
       <c r="P237" s="63"/>
@@ -19687,7 +19703,7 @@
       </c>
       <c r="B239" s="63"/>
       <c r="C239" s="64" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D239" s="64"/>
       <c r="E239" s="64"/>
@@ -19702,7 +19718,7 @@
       </c>
       <c r="M239" s="63"/>
       <c r="N239" s="64" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="O239" s="63"/>
       <c r="P239" s="63"/>
@@ -19811,7 +19827,7 @@
       </c>
       <c r="B243" s="63"/>
       <c r="C243" s="64" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="D243" s="64"/>
       <c r="E243" s="64"/>
@@ -19826,7 +19842,7 @@
       </c>
       <c r="M243" s="63"/>
       <c r="N243" s="64" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="O243" s="63"/>
       <c r="P243" s="63"/>
@@ -19935,7 +19951,7 @@
       </c>
       <c r="B247" s="63"/>
       <c r="C247" s="64" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="D247" s="64"/>
       <c r="E247" s="64"/>
@@ -19950,7 +19966,7 @@
       </c>
       <c r="M247" s="63"/>
       <c r="N247" s="64" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O247" s="63"/>
       <c r="P247" s="63"/>
@@ -20059,7 +20075,7 @@
       </c>
       <c r="B251" s="63"/>
       <c r="C251" s="64" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D251" s="64"/>
       <c r="E251" s="64"/>
@@ -20072,7 +20088,7 @@
       <c r="L251" s="63"/>
       <c r="M251" s="63"/>
       <c r="N251" s="130" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="O251" s="112"/>
       <c r="P251" s="112"/>
@@ -20134,7 +20150,7 @@
       </c>
       <c r="M253" s="63"/>
       <c r="N253" s="64" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="O253" s="63"/>
       <c r="P253" s="63"/>
@@ -20177,7 +20193,7 @@
       </c>
       <c r="B255" s="63"/>
       <c r="C255" s="64" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D255" s="64"/>
       <c r="E255" s="64"/>
@@ -20193,7 +20209,7 @@
         <v>33</v>
       </c>
       <c r="O255" s="150" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P255" s="98"/>
       <c r="Q255" s="98"/>
@@ -20258,7 +20274,7 @@
       <c r="L257" s="63"/>
       <c r="M257" s="63"/>
       <c r="N257" s="130" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="O257" s="63"/>
       <c r="P257" s="63"/>
@@ -20301,7 +20317,7 @@
       </c>
       <c r="B259" s="63"/>
       <c r="C259" s="64" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D259" s="64"/>
       <c r="E259" s="64"/>
@@ -20316,7 +20332,7 @@
       </c>
       <c r="M259" s="63"/>
       <c r="N259" s="64" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="O259" s="63"/>
       <c r="P259" s="63"/>
@@ -20379,7 +20395,7 @@
         <v>33</v>
       </c>
       <c r="O261" s="137" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P261" s="98"/>
       <c r="Q261" s="98"/>
@@ -20427,7 +20443,7 @@
       </c>
       <c r="B263" s="63"/>
       <c r="C263" s="64" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="D263" s="64"/>
       <c r="E263" s="64"/>
@@ -20442,7 +20458,7 @@
       </c>
       <c r="M263" s="63"/>
       <c r="N263" s="64" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="O263" s="63"/>
       <c r="P263" s="63"/>
@@ -20505,7 +20521,7 @@
         <v>33</v>
       </c>
       <c r="O265" s="137" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P265" s="98"/>
       <c r="Q265" s="98"/>
@@ -20553,7 +20569,7 @@
       </c>
       <c r="B267" s="63"/>
       <c r="C267" s="64" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D267" s="64"/>
       <c r="E267" s="64"/>
@@ -20568,7 +20584,7 @@
       </c>
       <c r="M267" s="63"/>
       <c r="N267" s="64" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O267" s="63"/>
       <c r="P267" s="63"/>
@@ -20688,7 +20704,7 @@
       </c>
       <c r="M271" s="63"/>
       <c r="N271" s="64" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="O271" s="63"/>
       <c r="P271" s="63"/>
@@ -20800,7 +20816,7 @@
       </c>
       <c r="M275" s="63"/>
       <c r="N275" s="64" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O275" s="63"/>
       <c r="P275" s="63"/>
@@ -20855,7 +20871,7 @@
         <v>33</v>
       </c>
       <c r="O277" s="137" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="P277" s="98"/>
       <c r="Q277" s="98"/>
@@ -20899,7 +20915,7 @@
     </row>
     <row r="279" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A279" s="111" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B279" s="111"/>
       <c r="C279" s="111"/>
@@ -20926,7 +20942,7 @@
     </row>
     <row r="280" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A280" s="104" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B280" s="104"/>
       <c r="C280" s="104"/>
@@ -20941,7 +20957,7 @@
         <v>12570</v>
       </c>
       <c r="K280" s="104" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="L280" s="104"/>
       <c r="M280" s="104"/>
@@ -20958,7 +20974,7 @@
     </row>
     <row r="281" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A281" s="152" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B281" s="152"/>
       <c r="C281" s="152"/>
@@ -21014,7 +21030,7 @@
       </c>
       <c r="B283" s="63"/>
       <c r="C283" s="64" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="D283" s="63"/>
       <c r="E283" s="63"/>
@@ -21029,7 +21045,7 @@
       </c>
       <c r="M283" s="63"/>
       <c r="N283" s="64" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="O283" s="63"/>
       <c r="P283" s="63"/>
@@ -21045,7 +21061,7 @@
       <c r="A284" s="79"/>
       <c r="B284" s="63"/>
       <c r="C284" s="64" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="D284" s="63"/>
       <c r="E284" s="63"/>
@@ -21058,7 +21074,7 @@
       <c r="L284" s="63"/>
       <c r="M284" s="63"/>
       <c r="N284" s="90" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="O284" s="63"/>
       <c r="P284" s="63"/>
@@ -21159,7 +21175,7 @@
       </c>
       <c r="B288" s="63"/>
       <c r="C288" s="64" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D288" s="63"/>
       <c r="E288" s="63"/>
@@ -21186,7 +21202,7 @@
       <c r="A289" s="79"/>
       <c r="B289" s="63"/>
       <c r="C289" s="64" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D289" s="63"/>
       <c r="E289" s="63"/>
@@ -21311,7 +21327,7 @@
     </row>
     <row r="294" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A294" s="103" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B294" s="103"/>
       <c r="C294" s="103"/>
@@ -21367,7 +21383,7 @@
       </c>
       <c r="B296" s="63"/>
       <c r="C296" s="64" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D296" s="63"/>
       <c r="E296" s="63"/>
@@ -22293,10 +22309,10 @@
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="161" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B2" s="162" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C2" s="163" t="n">
         <f aca="false">Admin!B5</f>
@@ -22413,7 +22429,7 @@
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="170" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B5" s="171" t="n">
         <f aca="false">SUM(C5:N5)</f>
@@ -22471,7 +22487,7 @@
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="170" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B6" s="171" t="n">
         <f aca="false">SUM(C6:N6)</f>
@@ -22529,7 +22545,7 @@
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="170" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B7" s="171" t="n">
         <f aca="false">SUM(C7:N7)</f>
@@ -22587,7 +22603,7 @@
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="170" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B8" s="171" t="n">
         <f aca="false">SUM(C8:N8)</f>
@@ -22645,7 +22661,7 @@
     </row>
     <row r="9" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="174" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B9" s="171" t="n">
         <f aca="false">SUM(B5:B8)</f>
@@ -22720,7 +22736,7 @@
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="170" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B11" s="171" t="n">
         <f aca="false">SUM(C11:N11)</f>
@@ -22795,7 +22811,7 @@
     </row>
     <row r="13" s="177" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="181" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="B13" s="178"/>
       <c r="C13" s="178"/>
@@ -22814,7 +22830,7 @@
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="170" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B14" s="171" t="n">
         <f aca="false">SUM(C14:N14)</f>
@@ -22872,7 +22888,7 @@
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="170" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B15" s="171" t="n">
         <f aca="false">SUM(C15:N15)</f>
@@ -22930,7 +22946,7 @@
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="170" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B16" s="171" t="n">
         <f aca="false">SUM(C16:N16)</f>
@@ -22988,7 +23004,7 @@
     </row>
     <row r="17" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="174" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B17" s="171" t="n">
         <f aca="false">SUM(B14:B16)</f>
@@ -23063,7 +23079,7 @@
     </row>
     <row r="19" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="174" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B19" s="171" t="n">
         <f aca="false">B9+B11-B17</f>
@@ -23121,7 +23137,7 @@
     </row>
     <row r="20" s="177" customFormat="true" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="181" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B20" s="178"/>
       <c r="C20" s="182"/>
@@ -23140,7 +23156,7 @@
     </row>
     <row r="21" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="170" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B21" s="171" t="n">
         <f aca="false">SUM(C21:N21)</f>
@@ -23198,7 +23214,7 @@
     </row>
     <row r="22" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="183" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B22" s="171" t="n">
         <f aca="false">SUM(C22:N22)</f>
@@ -23256,7 +23272,7 @@
     </row>
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="183" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B23" s="171" t="n">
         <f aca="false">SUM(C23:N23)</f>
@@ -23314,7 +23330,7 @@
     </row>
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="183" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B24" s="171" t="n">
         <f aca="false">SUM(C24:N24)</f>
@@ -23372,7 +23388,7 @@
     </row>
     <row r="25" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="183" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B25" s="171" t="n">
         <f aca="false">SUM(C25:N25)</f>
@@ -23430,7 +23446,7 @@
     </row>
     <row r="26" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="183" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B26" s="171" t="n">
         <f aca="false">SUM(C26:N26)</f>
@@ -23488,7 +23504,7 @@
     </row>
     <row r="27" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="183" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B27" s="171" t="n">
         <f aca="false">SUM(C27:N27)</f>
@@ -23546,7 +23562,7 @@
     </row>
     <row r="28" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="183" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="B28" s="171" t="n">
         <f aca="false">SUM(C28:N28)</f>
@@ -23604,7 +23620,7 @@
     </row>
     <row r="29" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="183" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B29" s="171" t="n">
         <f aca="false">SUM(C29:N29)</f>
@@ -23662,7 +23678,7 @@
     </row>
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="183" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B30" s="171" t="n">
         <f aca="false">SUM(C30:N30)</f>
@@ -23720,7 +23736,7 @@
     </row>
     <row r="31" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="183" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B31" s="171" t="n">
         <f aca="false">SUM(C31:N31)</f>
@@ -23778,7 +23794,7 @@
     </row>
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="183" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B32" s="171" t="n">
         <f aca="false">SUM(C32:N32)</f>
@@ -23836,7 +23852,7 @@
     </row>
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="170" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B33" s="171" t="n">
         <f aca="false">SUM(C33:N33)</f>
@@ -23894,7 +23910,7 @@
     </row>
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="170" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B34" s="171" t="n">
         <f aca="false">SUM(C34:N34)</f>
@@ -23952,7 +23968,7 @@
     </row>
     <row r="35" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="174" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B35" s="171" t="n">
         <f aca="false">SUM(B21:B34)</f>
@@ -24027,7 +24043,7 @@
     </row>
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="174" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B37" s="171" t="n">
         <f aca="false">B19-B35</f>
@@ -24085,7 +24101,7 @@
     </row>
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="170" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B38" s="171" t="n">
         <f aca="false">SUM(C38:N38)</f>
@@ -24143,7 +24159,7 @@
     </row>
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="174" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B39" s="171" t="n">
         <f aca="false">B37+B38</f>
@@ -24218,7 +24234,7 @@
     </row>
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="188" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B41" s="157"/>
       <c r="C41" s="158"/>
@@ -24237,7 +24253,7 @@
     </row>
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="183" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B42" s="178" t="n">
         <f aca="false">SUM(C42:N42)</f>
@@ -24295,7 +24311,7 @@
     </row>
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="183" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B43" s="178" t="n">
         <f aca="false">SUM(C43:N43)</f>
@@ -24353,7 +24369,7 @@
     </row>
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="183" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B44" s="178" t="n">
         <f aca="false">SUM(C44:N44)</f>
@@ -24411,7 +24427,7 @@
     </row>
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="189" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B45" s="190" t="n">
         <f aca="false">SUM(C45:N45)</f>
@@ -24469,7 +24485,7 @@
     </row>
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="183" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="B46" s="178" t="n">
         <f aca="false">SUM(C46:N46)</f>
@@ -24601,25 +24617,25 @@
     <row r="2" s="197" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="196"/>
       <c r="B2" s="198" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C2" s="198" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="D2" s="198" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E2" s="198" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F2" s="198" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G2" s="198" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="I2" s="196"/>
     </row>
@@ -24648,7 +24664,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="196"/>
       <c r="B5" s="196" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C5" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -24676,7 +24692,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="196"/>
       <c r="B6" s="196" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C6" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -24704,7 +24720,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="196"/>
       <c r="B7" s="196" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C7" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -24754,7 +24770,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="196"/>
       <c r="B10" s="203" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C10" s="196"/>
       <c r="D10" s="196"/>
@@ -24778,7 +24794,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="196"/>
       <c r="B12" s="196" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C12" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -24806,7 +24822,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="196"/>
       <c r="B13" s="196" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C13" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -24834,7 +24850,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="196"/>
       <c r="B14" s="196" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C14" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -24862,7 +24878,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="196"/>
       <c r="B15" s="196" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C15" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -24890,7 +24906,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="196"/>
       <c r="B16" s="196" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="C16" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -24918,7 +24934,7 @@
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="196"/>
       <c r="B17" s="196" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C17" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -24946,7 +24962,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="196"/>
       <c r="B18" s="196" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C18" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -24974,7 +24990,7 @@
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="196"/>
       <c r="B19" s="196" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C19" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -25002,7 +25018,7 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="196"/>
       <c r="B20" s="196" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C20" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -25030,7 +25046,7 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="196"/>
       <c r="B21" s="196" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C21" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -25058,7 +25074,7 @@
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="196"/>
       <c r="B22" s="196" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C22" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -25097,7 +25113,7 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="196"/>
       <c r="B24" s="196" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C24" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -25125,7 +25141,7 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="196"/>
       <c r="B25" s="196" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C25" s="201" t="n">
         <v>0</v>
@@ -25144,14 +25160,14 @@
         <v>0</v>
       </c>
       <c r="H25" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I25" s="196"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="196"/>
       <c r="B26" s="196" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C26" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C33:E34)</f>
@@ -25201,7 +25217,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="196"/>
       <c r="B29" s="203" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C29" s="204" t="n">
         <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
@@ -25273,7 +25289,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="196"/>
       <c r="B34" s="203" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C34" s="196"/>
       <c r="D34" s="196"/>
@@ -25297,7 +25313,7 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="196"/>
       <c r="B36" s="196" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C36" s="201" t="n">
         <v>0</v>
@@ -25316,14 +25332,14 @@
         <v>0</v>
       </c>
       <c r="H36" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I36" s="196"/>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="196"/>
       <c r="B37" s="196" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="C37" s="201" t="n">
         <v>0</v>
@@ -25342,14 +25358,14 @@
         <v>0</v>
       </c>
       <c r="H37" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I37" s="196"/>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="196"/>
       <c r="B38" s="196" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C38" s="201" t="n">
         <v>0</v>
@@ -25368,14 +25384,14 @@
         <v>0</v>
       </c>
       <c r="H38" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I38" s="196"/>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="196"/>
       <c r="B39" s="196" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C39" s="201" t="n">
         <v>0</v>
@@ -25394,14 +25410,14 @@
         <v>0</v>
       </c>
       <c r="H39" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I39" s="196"/>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="196"/>
       <c r="B40" s="196" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C40" s="201" t="n">
         <v>0</v>
@@ -25420,14 +25436,14 @@
         <v>0</v>
       </c>
       <c r="H40" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I40" s="196"/>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="196"/>
       <c r="B41" s="196" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C41" s="201" t="n">
         <v>0</v>
@@ -25446,14 +25462,14 @@
         <v>0</v>
       </c>
       <c r="H41" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I41" s="196"/>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="196"/>
       <c r="B42" s="196" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C42" s="201" t="n">
         <v>0</v>
@@ -25472,14 +25488,14 @@
         <v>0</v>
       </c>
       <c r="H42" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I42" s="196"/>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="196"/>
       <c r="B43" s="196" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="C43" s="201" t="n">
         <v>0</v>
@@ -25498,14 +25514,14 @@
         <v>0</v>
       </c>
       <c r="H43" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I43" s="196"/>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="196"/>
       <c r="B44" s="196" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C44" s="201" t="n">
         <v>0</v>
@@ -25524,14 +25540,14 @@
         <v>0</v>
       </c>
       <c r="H44" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I44" s="196"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="196"/>
       <c r="B45" s="196" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C45" s="201" t="n">
         <v>0</v>
@@ -25550,14 +25566,14 @@
         <v>0</v>
       </c>
       <c r="H45" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I45" s="196"/>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="196"/>
       <c r="B46" s="196" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C46" s="201" t="n">
         <v>0</v>
@@ -25576,14 +25592,14 @@
         <v>0</v>
       </c>
       <c r="H46" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I46" s="196"/>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="196"/>
       <c r="B47" s="196" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="C47" s="201" t="n">
         <v>0</v>
@@ -25602,14 +25618,14 @@
         <v>0</v>
       </c>
       <c r="H47" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I47" s="196"/>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="196"/>
       <c r="B48" s="196" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C48" s="201" t="n">
         <v>0</v>
@@ -25628,14 +25644,14 @@
         <v>0</v>
       </c>
       <c r="H48" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I48" s="196"/>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="196"/>
       <c r="B49" s="196" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="C49" s="201" t="n">
         <v>0</v>
@@ -25654,14 +25670,14 @@
         <v>0</v>
       </c>
       <c r="H49" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I49" s="196"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="196"/>
       <c r="B50" s="196" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C50" s="201" t="n">
         <v>0</v>
@@ -25680,7 +25696,7 @@
         <v>0</v>
       </c>
       <c r="H50" s="196" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="I50" s="196"/>
     </row>
@@ -25751,14 +25767,14 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="212"/>
       <c r="B2" s="216" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C2" s="217" t="str">
         <f aca="false">Admin!L2</f>
         <v>2026-27</v>
       </c>
       <c r="D2" s="218" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E2" s="218"/>
       <c r="F2" s="218"/>
@@ -25785,7 +25801,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="212"/>
       <c r="B5" s="223" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C5" s="223"/>
       <c r="D5" s="223"/>
@@ -25800,7 +25816,7 @@
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="212"/>
       <c r="B6" s="221" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C6" s="221" t="str">
         <f aca="false">C2</f>
@@ -25818,7 +25834,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="212"/>
       <c r="B7" s="223" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C7" s="223"/>
       <c r="D7" s="223"/>
@@ -25833,7 +25849,7 @@
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="212"/>
       <c r="B8" s="221" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="C8" s="221" t="n">
         <f aca="false">Admin!N$11</f>
@@ -25855,7 +25871,7 @@
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="212"/>
       <c r="B9" s="221" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C9" s="221" t="n">
         <f aca="false">Admin!M$11</f>
@@ -25876,7 +25892,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="212"/>
       <c r="B10" s="221" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C10" s="221" t="n">
         <f aca="false">Admin!N$13</f>
@@ -25897,7 +25913,7 @@
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="212"/>
       <c r="B11" s="229" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C11" s="230"/>
       <c r="D11" s="231"/>
@@ -25912,7 +25928,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="212"/>
       <c r="B12" s="221" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C12" s="221"/>
       <c r="D12" s="235"/>
@@ -25927,7 +25943,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="212"/>
       <c r="B13" s="236" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="C13" s="237" t="n">
         <f aca="false">Admin!B21</f>
@@ -25952,7 +25968,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="212"/>
       <c r="B15" s="240" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C15" s="240"/>
       <c r="D15" s="227" t="n">
@@ -25970,7 +25986,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="212"/>
       <c r="B16" s="240" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C16" s="240"/>
       <c r="D16" s="227" t="n">
@@ -25998,7 +26014,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="212"/>
       <c r="B18" s="242" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="C18" s="242"/>
       <c r="D18" s="238"/>
@@ -26031,11 +26047,11 @@
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="212"/>
       <c r="B21" s="229" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="C21" s="244"/>
       <c r="D21" s="245" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="E21" s="245"/>
       <c r="F21" s="245"/>
@@ -26055,10 +26071,10 @@
       <c r="B23" s="221"/>
       <c r="C23" s="221"/>
       <c r="D23" s="247" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E23" s="248" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F23" s="249"/>
       <c r="G23" s="219"/>
@@ -26075,14 +26091,14 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="212"/>
       <c r="B25" s="221" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C25" s="251" t="str">
         <f aca="false">Admin!B24</f>
         <v>2027-28</v>
       </c>
       <c r="D25" s="252" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E25" s="241" t="n">
         <f aca="false">E18</f>
@@ -26094,7 +26110,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="212"/>
       <c r="B26" s="221" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C26" s="221"/>
       <c r="D26" s="253" t="n">
@@ -26111,7 +26127,7 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="212"/>
       <c r="B27" s="221" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C27" s="221"/>
       <c r="D27" s="253" t="n">
@@ -26137,7 +26153,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="212"/>
       <c r="B29" s="254" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C29" s="255"/>
       <c r="D29" s="238"/>
@@ -26148,7 +26164,7 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="212"/>
       <c r="B30" s="256" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C30" s="256"/>
       <c r="D30" s="212"/>
@@ -26159,7 +26175,7 @@
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="212"/>
       <c r="B31" s="259" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C31" s="259"/>
       <c r="D31" s="260"/>
@@ -26170,7 +26186,7 @@
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="212"/>
       <c r="B32" s="261" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C32" s="259"/>
       <c r="D32" s="260"/>
@@ -26181,7 +26197,7 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="212"/>
       <c r="B33" s="255" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C33" s="255"/>
       <c r="D33" s="260"/>
@@ -26192,7 +26208,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="212"/>
       <c r="B34" s="255" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C34" s="255"/>
       <c r="D34" s="260"/>
@@ -26203,7 +26219,7 @@
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="212"/>
       <c r="B35" s="255" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C35" s="255"/>
       <c r="D35" s="260"/>
@@ -26278,39 +26294,39 @@
     <row r="2" s="273" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="268"/>
       <c r="B2" s="269" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="C2" s="270" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="D2" s="270" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E2" s="270" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="F2" s="270" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="G2" s="270" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="H2" s="270" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="I2" s="270" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="J2" s="271"/>
       <c r="K2" s="269" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="L2" s="272"/>
     </row>
     <row r="3" s="273" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="268"/>
       <c r="B3" s="274" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C3" s="274"/>
       <c r="D3" s="275"/>
@@ -26359,7 +26375,7 @@
       </c>
       <c r="J4" s="159"/>
       <c r="K4" s="279" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="L4" s="165"/>
     </row>
@@ -26513,7 +26529,7 @@
       </c>
       <c r="J8" s="159"/>
       <c r="K8" s="279" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="L8" s="165"/>
     </row>
@@ -26865,7 +26881,7 @@
       <c r="F1" s="288"/>
       <c r="G1" s="288"/>
       <c r="H1" s="289" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="I1" s="289"/>
       <c r="J1" s="289"/>
@@ -26873,7 +26889,7 @@
       <c r="L1" s="289"/>
       <c r="M1" s="288"/>
       <c r="N1" s="289" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="O1" s="289"/>
       <c r="P1" s="289"/>
@@ -26881,7 +26897,7 @@
       <c r="R1" s="289"/>
       <c r="S1" s="288"/>
       <c r="T1" s="289" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="U1" s="289"/>
       <c r="V1" s="289"/>
@@ -26901,63 +26917,63 @@
     <row r="2" s="303" customFormat="true" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="293"/>
       <c r="B2" s="294" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C2" s="295"/>
       <c r="D2" s="296" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E2" s="297"/>
       <c r="F2" s="296" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="G2" s="297"/>
       <c r="H2" s="298" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="I2" s="297"/>
       <c r="J2" s="296" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="K2" s="297"/>
       <c r="L2" s="296" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M2" s="297"/>
       <c r="N2" s="298" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="O2" s="297"/>
       <c r="P2" s="296" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="Q2" s="297"/>
       <c r="R2" s="296" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="S2" s="297"/>
       <c r="T2" s="298" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="U2" s="297"/>
       <c r="V2" s="296" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="W2" s="297"/>
       <c r="X2" s="299" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="Y2" s="300"/>
       <c r="Z2" s="296" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AA2" s="297"/>
       <c r="AB2" s="296" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AC2" s="301"/>
       <c r="AD2" s="302" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AE2" s="302"/>
       <c r="AF2" s="302"/>
@@ -26995,7 +27011,7 @@
       <c r="AB3" s="306"/>
       <c r="AC3" s="165"/>
       <c r="AD3" s="310" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AE3" s="310"/>
       <c r="AF3" s="310"/>
@@ -27005,7 +27021,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="277"/>
       <c r="B4" s="311" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="C4" s="311"/>
       <c r="D4" s="311"/>
@@ -27385,7 +27401,7 @@
       <c r="AB11" s="178"/>
       <c r="AC11" s="165"/>
       <c r="AD11" s="310" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AE11" s="310"/>
       <c r="AF11" s="310"/>
@@ -27615,7 +27631,7 @@
       <c r="AB15" s="178"/>
       <c r="AC15" s="165"/>
       <c r="AD15" s="310" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="AE15" s="310"/>
       <c r="AF15" s="310"/>
@@ -27845,7 +27861,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="165"/>
       <c r="AD19" s="310" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="AE19" s="310"/>
       <c r="AF19" s="310"/>
@@ -28075,7 +28091,7 @@
       <c r="AB23" s="178"/>
       <c r="AC23" s="165"/>
       <c r="AD23" s="310" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AE23" s="310"/>
       <c r="AF23" s="310"/>
@@ -28383,7 +28399,7 @@
       </c>
       <c r="AC28" s="165"/>
       <c r="AD28" s="310" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AE28" s="310"/>
       <c r="AF28" s="310"/>
@@ -28601,10 +28617,10 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="159"/>
       <c r="B2" s="331" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C2" s="162" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D2" s="163" t="n">
         <f aca="false">Admin!B5</f>
@@ -28724,7 +28740,7 @@
     <row r="5" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="179"/>
       <c r="B5" s="333" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C5" s="171" t="n">
         <f aca="false">SUM(D5:O5)</f>
@@ -28801,7 +28817,7 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="159"/>
       <c r="B7" s="335" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C7" s="171" t="n">
         <f aca="false">SUM(D7:O7)</f>
@@ -28878,7 +28894,7 @@
     <row r="9" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="179"/>
       <c r="B9" s="334" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C9" s="171" t="n">
         <f aca="false">SUM(D9:O9)</f>
@@ -28955,7 +28971,7 @@
     <row r="11" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="179"/>
       <c r="B11" s="333" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C11" s="171" t="n">
         <f aca="false">SUM(D11:O11)</f>
@@ -29032,7 +29048,7 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="159"/>
       <c r="B13" s="334" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C13" s="171" t="n">
         <f aca="false">SUM(D13:O13)</f>
@@ -29109,7 +29125,7 @@
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="159"/>
       <c r="B15" s="333" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C15" s="171" t="n">
         <f aca="false">SUM(D15:O15)</f>
@@ -29168,7 +29184,7 @@
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="159"/>
       <c r="B16" s="335" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C16" s="171" t="n">
         <f aca="false">SUM(D16:O16)</f>
@@ -29227,7 +29243,7 @@
     <row r="17" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="159"/>
       <c r="B17" s="336" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C17" s="171" t="n">
         <f aca="false">SUM(D17:O17)</f>
@@ -29304,10 +29320,10 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="159"/>
       <c r="B19" s="338" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C19" s="162" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="D19" s="163" t="n">
         <f aca="false">D2</f>
@@ -29440,7 +29456,7 @@
     <row r="22" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="179"/>
       <c r="B22" s="333" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="C22" s="171" t="n">
         <f aca="false">SUM(D22:O22)</f>
@@ -29517,7 +29533,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="159"/>
       <c r="B24" s="335" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="C24" s="171" t="n">
         <f aca="false">SUM(D24:O24)</f>
@@ -29594,7 +29610,7 @@
     <row r="26" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="179"/>
       <c r="B26" s="334" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="C26" s="171" t="n">
         <f aca="false">SUM(D26:O26)</f>
@@ -29671,7 +29687,7 @@
     <row r="28" s="177" customFormat="true" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="179"/>
       <c r="B28" s="333" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C28" s="171" t="n">
         <f aca="false">SUM(D28:O28)</f>
@@ -29748,7 +29764,7 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="159"/>
       <c r="B30" s="334" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C30" s="171" t="n">
         <f aca="false">SUM(D30:O30)</f>
@@ -29825,7 +29841,7 @@
     <row r="32" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="159"/>
       <c r="B32" s="333" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C32" s="171" t="n">
         <f aca="false">SUM(D32:O32)</f>
@@ -29884,7 +29900,7 @@
     <row r="33" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="159"/>
       <c r="B33" s="335" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C33" s="171" t="n">
         <f aca="false">SUM(D33:O33)</f>
@@ -29943,7 +29959,7 @@
     <row r="34" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="159"/>
       <c r="B34" s="336" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">SUM(D34:O34)</f>
@@ -30020,7 +30036,7 @@
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="159"/>
       <c r="B36" s="339" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="C36" s="339"/>
       <c r="D36" s="159"/>
@@ -30040,7 +30056,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="159"/>
       <c r="B37" s="170" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C37" s="340" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
@@ -30063,7 +30079,7 @@
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="159"/>
       <c r="B38" s="170" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="C38" s="340" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
@@ -30086,7 +30102,7 @@
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="159"/>
       <c r="B39" s="170" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C39" s="340" t="n">
         <f aca="false">C34+C37-C38</f>
@@ -30109,7 +30125,7 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="159"/>
       <c r="B40" s="183" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C40" s="340" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
@@ -30132,7 +30148,7 @@
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="159"/>
       <c r="B41" s="183" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C41" s="340" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
@@ -30155,7 +30171,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="159"/>
       <c r="B42" s="183" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C42" s="340" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
@@ -30178,7 +30194,7 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="159"/>
       <c r="B43" s="183" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C43" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
@@ -30201,7 +30217,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="159"/>
       <c r="B44" s="183" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C44" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
@@ -30224,7 +30240,7 @@
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="159"/>
       <c r="B45" s="183" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C45" s="340" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
@@ -30247,7 +30263,7 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="159"/>
       <c r="B46" s="183" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C46" s="342" t="n">
         <f aca="false">C42+C43+C44+C45</f>

--- a/examples/se-latest/Financialaccounts.xlsx
+++ b/examples/se-latest/Financialaccounts.xlsx
@@ -208,7 +208,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="436">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="799" uniqueCount="439">
   <si>
     <r>
       <rPr>
@@ -1576,7 +1576,7 @@
     <t xml:space="preserve">Travel Hotel &amp; Subsistence</t>
   </si>
   <si>
-    <t xml:space="preserve">Advertising &amp; Promotion</t>
+    <t xml:space="preserve">Advertising Promotion &amp; Entertainment</t>
   </si>
   <si>
     <t xml:space="preserve">Legal &amp; Professional Fees</t>
@@ -1624,6 +1624,9 @@
     <t xml:space="preserve">Financial Health Check</t>
   </si>
   <si>
+    <t xml:space="preserve">Business Entertainment (memo)</t>
+  </si>
+  <si>
     <t xml:space="preserve">VitalTax summary</t>
   </si>
   <si>
@@ -1696,19 +1699,25 @@
     <t xml:space="preserve">Business entertainment</t>
   </si>
   <si>
-    <t xml:space="preserve">Not captured in DIY Accounting</t>
-  </si>
-  <si>
     <t xml:space="preserve">Total allowable expenses </t>
   </si>
   <si>
+    <t xml:space="preserve">Enter the % of this category that is private use or otherwise disallowable</t>
+  </si>
+  <si>
     <t xml:space="preserve">Travel </t>
   </si>
   <si>
+    <t xml:space="preserve">Wholly disallowable</t>
+  </si>
+  <si>
     <t xml:space="preserve">Financial charges </t>
   </si>
   <si>
     <t xml:space="preserve">Bad debt </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reads the depreciation charge automatically</t>
   </si>
   <si>
     <t xml:space="preserve">TAXATION CALCULATION </t>
@@ -4836,6 +4845,11 @@
             <v>1330.83333333333</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="2">
         <row r="1">
@@ -4874,6 +4888,11 @@
           </cell>
           <cell r="AA1">
             <v>95.8333333333333</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -4916,6 +4935,11 @@
             <v>120.833333333333</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="4">
         <row r="1">
@@ -4954,6 +4978,11 @@
           </cell>
           <cell r="AA1">
             <v>95.8333333333333</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -4996,6 +5025,11 @@
             <v>135.833333333333</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>291.666666666667</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="6">
         <row r="1">
@@ -5034,6 +5068,11 @@
           </cell>
           <cell r="AA1">
             <v>95.8333333333333</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -5076,6 +5115,11 @@
             <v>425.833333333333</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="8">
         <row r="1">
@@ -5114,6 +5158,11 @@
           </cell>
           <cell r="AA1">
             <v>95.8333333333333</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -5156,6 +5205,11 @@
             <v>532.5</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="10">
         <row r="1">
@@ -5194,6 +5248,11 @@
           </cell>
           <cell r="AA1">
             <v>95.8333333333333</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -5236,6 +5295,11 @@
             <v>110.833333333333</v>
           </cell>
         </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
+          </cell>
+        </row>
       </sheetData>
       <sheetData sheetId="12">
         <row r="1">
@@ -5274,6 +5338,11 @@
           </cell>
           <cell r="AA1">
             <v>95.8333333333333</v>
+          </cell>
+        </row>
+        <row r="1">
+          <cell r="AC1">
+            <v>0</v>
           </cell>
         </row>
       </sheetData>
@@ -7975,7 +8044,7 @@
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="63"/>
       <c r="B1" s="345" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C1" s="63"/>
       <c r="D1" s="346"/>
@@ -7998,7 +8067,7 @@
       </c>
       <c r="C2" s="63"/>
       <c r="D2" s="349" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="E2" s="349"/>
       <c r="F2" s="349"/>
@@ -8009,7 +8078,7 @@
       <c r="H2" s="63"/>
       <c r="I2" s="63"/>
       <c r="J2" s="351" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="K2" s="351"/>
       <c r="L2" s="352" t="str">
@@ -8055,7 +8124,7 @@
       </c>
       <c r="H4" s="63"/>
       <c r="I4" s="356" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="J4" s="356"/>
       <c r="K4" s="356"/>
@@ -8075,7 +8144,7 @@
       </c>
       <c r="C5" s="63"/>
       <c r="D5" s="356" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E5" s="356"/>
       <c r="F5" s="356"/>
@@ -8084,7 +8153,7 @@
       </c>
       <c r="H5" s="63"/>
       <c r="I5" s="356" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="J5" s="356"/>
       <c r="K5" s="356"/>
@@ -8109,7 +8178,7 @@
       <c r="G6" s="353"/>
       <c r="H6" s="63"/>
       <c r="I6" s="356" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="J6" s="356"/>
       <c r="K6" s="356"/>
@@ -8119,7 +8188,7 @@
         <v>0.2</v>
       </c>
       <c r="O6" s="353" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8129,14 +8198,14 @@
       </c>
       <c r="C7" s="63"/>
       <c r="D7" s="356" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E7" s="356"/>
       <c r="F7" s="356"/>
       <c r="G7" s="353"/>
       <c r="H7" s="63"/>
       <c r="I7" s="356" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="J7" s="356"/>
       <c r="K7" s="356"/>
@@ -8146,7 +8215,7 @@
         <v>0.4</v>
       </c>
       <c r="O7" s="353" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8161,7 +8230,7 @@
       <c r="G8" s="359"/>
       <c r="H8" s="63"/>
       <c r="I8" s="356" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J8" s="356"/>
       <c r="K8" s="356"/>
@@ -8171,7 +8240,7 @@
         <v>0.45</v>
       </c>
       <c r="O8" s="353" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8186,18 +8255,18 @@
       <c r="G9" s="353"/>
       <c r="H9" s="63"/>
       <c r="I9" s="356" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="J9" s="356"/>
       <c r="K9" s="356"/>
       <c r="L9" s="360" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="M9" s="360" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="N9" s="361" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="O9" s="353"/>
     </row>
@@ -8227,16 +8296,16 @@
       </c>
       <c r="C11" s="63"/>
       <c r="D11" s="349" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E11" s="349"/>
       <c r="F11" s="349"/>
       <c r="G11" s="353" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="H11" s="63"/>
       <c r="I11" s="63" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="J11" s="63"/>
       <c r="K11" s="362" t="n">
@@ -8266,7 +8335,7 @@
       <c r="G12" s="353"/>
       <c r="H12" s="63"/>
       <c r="I12" s="63" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="J12" s="63"/>
       <c r="K12" s="362" t="n">
@@ -8288,7 +8357,7 @@
       </c>
       <c r="C13" s="63"/>
       <c r="D13" s="356" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E13" s="356"/>
       <c r="F13" s="356"/>
@@ -8297,7 +8366,7 @@
       </c>
       <c r="H13" s="63"/>
       <c r="I13" s="63" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="J13" s="63"/>
       <c r="K13" s="362" t="n">
@@ -8319,7 +8388,7 @@
       </c>
       <c r="C14" s="63"/>
       <c r="D14" s="356" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E14" s="356"/>
       <c r="F14" s="356"/>
@@ -8328,7 +8397,7 @@
       </c>
       <c r="H14" s="63"/>
       <c r="I14" s="349" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="J14" s="349"/>
       <c r="K14" s="349"/>
@@ -8347,7 +8416,7 @@
       </c>
       <c r="C15" s="63"/>
       <c r="D15" s="356" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E15" s="356"/>
       <c r="F15" s="356"/>
@@ -8370,7 +8439,7 @@
       </c>
       <c r="C16" s="63"/>
       <c r="D16" s="356" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E16" s="356"/>
       <c r="F16" s="356"/>
@@ -8379,7 +8448,7 @@
       </c>
       <c r="H16" s="63"/>
       <c r="I16" s="356" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="J16" s="356"/>
       <c r="K16" s="356"/>
@@ -8387,7 +8456,7 @@
         <v>3.65</v>
       </c>
       <c r="M16" s="63" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N16" s="359" t="n">
         <v>7105</v>
@@ -8403,7 +8472,7 @@
       </c>
       <c r="C17" s="63"/>
       <c r="D17" s="356" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E17" s="356"/>
       <c r="F17" s="356"/>
@@ -8445,24 +8514,24 @@
       </c>
       <c r="C19" s="63"/>
       <c r="D19" s="349" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E19" s="349"/>
       <c r="F19" s="353" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="G19" s="353" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="H19" s="63"/>
       <c r="I19" s="365" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J19" s="365"/>
       <c r="K19" s="365"/>
       <c r="L19" s="63"/>
       <c r="M19" s="366" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="N19" s="63"/>
       <c r="O19" s="63"/>
@@ -8499,7 +8568,7 @@
       </c>
       <c r="C21" s="63"/>
       <c r="D21" s="356" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="E21" s="356"/>
       <c r="F21" s="359" t="n">
@@ -8524,7 +8593,7 @@
       </c>
       <c r="C22" s="63"/>
       <c r="D22" s="63" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="E22" s="63"/>
       <c r="F22" s="359" t="n">
@@ -8535,13 +8604,13 @@
       </c>
       <c r="H22" s="63"/>
       <c r="I22" s="365" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="J22" s="365"/>
       <c r="K22" s="365"/>
       <c r="L22" s="63"/>
       <c r="M22" s="366" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="N22" s="63"/>
       <c r="O22" s="63"/>
@@ -8549,7 +8618,7 @@
     <row r="23" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="63"/>
       <c r="B23" s="355" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="C23" s="63"/>
       <c r="D23" s="63"/>
@@ -8574,11 +8643,11 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="63"/>
       <c r="B24" s="355" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="C24" s="63"/>
       <c r="D24" s="349" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="E24" s="349"/>
       <c r="F24" s="63"/>
@@ -8616,7 +8685,7 @@
       <c r="B26" s="369"/>
       <c r="C26" s="63"/>
       <c r="D26" s="356" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="E26" s="356"/>
       <c r="F26" s="359" t="n">
@@ -8637,7 +8706,7 @@
       <c r="B27" s="369"/>
       <c r="C27" s="63"/>
       <c r="D27" s="63" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="E27" s="63"/>
       <c r="F27" s="357" t="n">
@@ -10030,8 +10099,8 @@
         <v>33</v>
       </c>
       <c r="D46" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17," ")</f>
-        <v>20136.6666666667</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B17-'SE Full'!O66-'SE Full'!O70," ")</f>
+        <v>19667.2666666667</v>
       </c>
       <c r="E46" s="98"/>
       <c r="F46" s="98"/>
@@ -10052,8 +10121,8 @@
         <v>33</v>
       </c>
       <c r="O46" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28," ")</f>
-        <v>6925</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B28-'SE Full'!O110," ")</f>
+        <v>6094</v>
       </c>
       <c r="P46" s="98"/>
       <c r="Q46" s="98"/>
@@ -10187,8 +10256,8 @@
         <v>33</v>
       </c>
       <c r="D51" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26," ")</f>
-        <v>7984.25</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B25+'Profit &amp; Loss Account'!B26-'SE Full'!O78," ")</f>
+        <v>5988.1875</v>
       </c>
       <c r="E51" s="98"/>
       <c r="F51" s="98"/>
@@ -10209,8 +10278,8 @@
         <v>33</v>
       </c>
       <c r="O51" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31," ")</f>
-        <v>3900</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B30+'Profit &amp; Loss Account'!B31-'SE Full'!O98-'SE Full'!O102," ")</f>
+        <v>3510</v>
       </c>
       <c r="P51" s="98"/>
       <c r="Q51" s="98"/>
@@ -10317,8 +10386,8 @@
         <v>33</v>
       </c>
       <c r="D55" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21," ")</f>
-        <v>92735.7333333333</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B21-'SE Full'!O74," ")</f>
+        <v>89026.304</v>
       </c>
       <c r="E55" s="98"/>
       <c r="F55" s="98"/>
@@ -10339,8 +10408,8 @@
         <v>33</v>
       </c>
       <c r="O55" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24," ")</f>
-        <v>3035</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B24-'SE Full'!O90," ")</f>
+        <v>2822.55</v>
       </c>
       <c r="P55" s="98"/>
       <c r="Q55" s="98"/>
@@ -10474,8 +10543,8 @@
         <v>33</v>
       </c>
       <c r="D60" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22," ")</f>
-        <v>13200</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B22-'SE Full'!O82," ")</f>
+        <v>12540</v>
       </c>
       <c r="E60" s="98"/>
       <c r="F60" s="98"/>
@@ -10496,8 +10565,8 @@
         <v>33</v>
       </c>
       <c r="O60" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33," ")</f>
-        <v>6903.66666666666</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B27+'Profit &amp; Loss Account'!B29+'Profit &amp; Loss Account'!B32+'Profit &amp; Loss Account'!B33-'SE Full'!O94-'SE Full'!O106-'SE Full'!O118," ")</f>
+        <v>6189.21666666666</v>
       </c>
       <c r="P60" s="98"/>
       <c r="Q60" s="98"/>
@@ -10604,8 +10673,8 @@
         <v>33</v>
       </c>
       <c r="D64" s="98" t="n">
-        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23," ")</f>
-        <v>950</v>
+        <f aca="false">IF('Profit &amp; Loss Account'!B9&gt;Admin!F26,'Profit &amp; Loss Account'!B23-'SE Full'!O86," ")</f>
+        <v>893</v>
       </c>
       <c r="E64" s="98"/>
       <c r="F64" s="98"/>
@@ -10626,8 +10695,8 @@
         <v>33</v>
       </c>
       <c r="O64" s="98" t="n">
-        <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'Profit &amp; Loss Account'!B34</f>
-        <v>155770.316666667</v>
+        <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35-'SE Full'!O122</f>
+        <v>146730.524833333</v>
       </c>
       <c r="P64" s="98"/>
       <c r="Q64" s="98"/>
@@ -10816,7 +10885,7 @@
       </c>
       <c r="D71" s="98" t="n">
         <f aca="false">IF((D38+O38-O64)&gt;=0,D38+O38-O64,0)</f>
-        <v>183429.683333333</v>
+        <v>192469.475166666</v>
       </c>
       <c r="E71" s="98"/>
       <c r="F71" s="98"/>
@@ -11668,7 +11737,7 @@
       </c>
       <c r="D99" s="98" t="n">
         <f aca="false">IF((D71+O85+D94-O71-D80-D85-O80)&gt;0,D71+O85+D94-O71-D80-D85-O80,0)</f>
-        <v>119429.683333333</v>
+        <v>128469.475166666</v>
       </c>
       <c r="E99" s="98"/>
       <c r="F99" s="98"/>
@@ -11881,7 +11950,7 @@
       </c>
       <c r="D106" s="98" t="n">
         <f aca="false">IF((D99+O99-O94)&gt;0,D99+O99-O94,0)</f>
-        <v>121513.016666666</v>
+        <v>130552.8085</v>
       </c>
       <c r="E106" s="98"/>
       <c r="F106" s="98"/>
@@ -14465,7 +14534,10 @@
       <c r="N66" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O66" s="98"/>
+      <c r="O66" s="98" t="n">
+        <f aca="false">VitalTax!G36</f>
+        <v>269.4</v>
+      </c>
       <c r="P66" s="98"/>
       <c r="Q66" s="98"/>
       <c r="R66" s="99" t="s">
@@ -14590,7 +14662,10 @@
       <c r="N70" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O70" s="98"/>
+      <c r="O70" s="98" t="n">
+        <f aca="false">VitalTax!G37</f>
+        <v>200</v>
+      </c>
       <c r="P70" s="98"/>
       <c r="Q70" s="98"/>
       <c r="R70" s="99" t="s">
@@ -14715,7 +14790,10 @@
       <c r="N74" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O74" s="98"/>
+      <c r="O74" s="98" t="n">
+        <f aca="false">VitalTax!G38</f>
+        <v>3709.42933333333</v>
+      </c>
       <c r="P74" s="98"/>
       <c r="Q74" s="98"/>
       <c r="R74" s="99" t="s">
@@ -14840,7 +14918,10 @@
       <c r="N78" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O78" s="98"/>
+      <c r="O78" s="98" t="n">
+        <f aca="false">VitalTax!G39</f>
+        <v>1996.0625</v>
+      </c>
       <c r="P78" s="98"/>
       <c r="Q78" s="98"/>
       <c r="R78" s="99" t="s">
@@ -14965,7 +15046,10 @@
       <c r="N82" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O82" s="98"/>
+      <c r="O82" s="98" t="n">
+        <f aca="false">VitalTax!G40</f>
+        <v>660</v>
+      </c>
       <c r="P82" s="98"/>
       <c r="Q82" s="98"/>
       <c r="R82" s="99" t="s">
@@ -15090,7 +15174,10 @@
       <c r="N86" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O86" s="98"/>
+      <c r="O86" s="98" t="n">
+        <f aca="false">VitalTax!G41</f>
+        <v>57</v>
+      </c>
       <c r="P86" s="98"/>
       <c r="Q86" s="98"/>
       <c r="R86" s="99" t="s">
@@ -15215,7 +15302,10 @@
       <c r="N90" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O90" s="98"/>
+      <c r="O90" s="98" t="n">
+        <f aca="false">VitalTax!G42</f>
+        <v>212.45</v>
+      </c>
       <c r="P90" s="98"/>
       <c r="Q90" s="98"/>
       <c r="R90" s="99" t="s">
@@ -15320,7 +15410,7 @@
       </c>
       <c r="D94" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B27</f>
-        <v>3800</v>
+        <v>4091.66666666667</v>
       </c>
       <c r="E94" s="98"/>
       <c r="F94" s="98"/>
@@ -15340,7 +15430,10 @@
       <c r="N94" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O94" s="98"/>
+      <c r="O94" s="98" t="n">
+        <f aca="false">VitalTax!G43+VitalTax!G44</f>
+        <v>619.000000000001</v>
+      </c>
       <c r="P94" s="98"/>
       <c r="Q94" s="98"/>
       <c r="R94" s="99" t="s">
@@ -15465,7 +15558,10 @@
       <c r="N98" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O98" s="98"/>
+      <c r="O98" s="98" t="n">
+        <f aca="false">VitalTax!G45</f>
+        <v>0</v>
+      </c>
       <c r="P98" s="98"/>
       <c r="Q98" s="98"/>
       <c r="R98" s="99" t="s">
@@ -15590,7 +15686,10 @@
       <c r="N102" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O102" s="98"/>
+      <c r="O102" s="98" t="n">
+        <f aca="false">VitalTax!G46</f>
+        <v>390</v>
+      </c>
       <c r="P102" s="98"/>
       <c r="Q102" s="98"/>
       <c r="R102" s="99" t="s">
@@ -15715,7 +15814,10 @@
       <c r="N106" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O106" s="98"/>
+      <c r="O106" s="98" t="n">
+        <f aca="false">VitalTax!G47</f>
+        <v>-33</v>
+      </c>
       <c r="P106" s="98"/>
       <c r="Q106" s="98"/>
       <c r="R106" s="99" t="s">
@@ -15840,7 +15942,10 @@
       <c r="N110" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O110" s="98"/>
+      <c r="O110" s="98" t="n">
+        <f aca="false">VitalTax!G48</f>
+        <v>831</v>
+      </c>
       <c r="P110" s="98"/>
       <c r="Q110" s="98"/>
       <c r="R110" s="99" t="s">
@@ -16093,7 +16198,10 @@
       <c r="N118" s="97" t="s">
         <v>33</v>
       </c>
-      <c r="O118" s="98"/>
+      <c r="O118" s="98" t="n">
+        <f aca="false">VitalTax!G50</f>
+        <v>420.116666666666</v>
+      </c>
       <c r="P118" s="98"/>
       <c r="Q118" s="98"/>
       <c r="R118" s="99" t="s">
@@ -16200,7 +16308,7 @@
       </c>
       <c r="D122" s="98" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B17+'Profit &amp; Loss Account'!B35</f>
-        <v>169510.316666667</v>
+        <v>169801.983333333</v>
       </c>
       <c r="E122" s="98"/>
       <c r="F122" s="98"/>
@@ -16221,8 +16329,8 @@
         <v>33</v>
       </c>
       <c r="O122" s="98" t="n">
-        <f aca="false">'Profit &amp; Loss Account'!B34</f>
-        <v>13740</v>
+        <f aca="false">O66+O70+O74+O78+O82+O86+O90+O94+O98+O102+O106+O110+O114+O118</f>
+        <v>23071.4585</v>
       </c>
       <c r="P122" s="98"/>
       <c r="Q122" s="98"/>
@@ -16411,7 +16519,7 @@
       </c>
       <c r="D129" s="98" t="n">
         <f aca="false">IF((D55+O55-D122)&gt;=0,D55+O55-D122,0)</f>
-        <v>169689.683333333</v>
+        <v>169398.016666666</v>
       </c>
       <c r="E129" s="98"/>
       <c r="F129" s="98"/>
@@ -17779,7 +17887,7 @@
       </c>
       <c r="D174" s="98" t="n">
         <f aca="false">O122+O160+D169</f>
-        <v>13740</v>
+        <v>23071.4585</v>
       </c>
       <c r="E174" s="98"/>
       <c r="F174" s="98"/>
@@ -17801,7 +17909,7 @@
       </c>
       <c r="O174" s="98" t="n">
         <f aca="false">IF((D129+D174-O169)&gt;0,(D129+D174-O169),IF((-O129+D174-O169)&gt;0,(-O129+D174-O169),0))</f>
-        <v>119429.683333333</v>
+        <v>128469.475166666</v>
       </c>
       <c r="P174" s="98"/>
       <c r="Q174" s="98"/>
@@ -18390,7 +18498,7 @@
       </c>
       <c r="O194" s="98" t="n">
         <f aca="false">O174</f>
-        <v>119429.683333333</v>
+        <v>128469.475166666</v>
       </c>
       <c r="P194" s="98"/>
       <c r="Q194" s="98"/>
@@ -18865,7 +18973,7 @@
       </c>
       <c r="O210" s="98" t="n">
         <f aca="false">O194-O199+O204</f>
-        <v>121513.016666666</v>
+        <v>130552.8085</v>
       </c>
       <c r="P210" s="98"/>
       <c r="Q210" s="98"/>
@@ -22280,7 +22388,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O47"/>
+  <dimension ref="A1:O49"/>
   <sheetFormatPr defaultColWidth="9.15625" defaultRowHeight="12" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="154" width="25.82"/>
@@ -23508,54 +23616,54 @@
       </c>
       <c r="B27" s="171" t="n">
         <f aca="false">SUM(C27:N27)</f>
-        <v>3800</v>
+        <v>4091.66666666667</v>
       </c>
       <c r="C27" s="172" t="n">
-        <f aca="false">[3]Apr!$Y$1</f>
+        <f aca="false">[3]Apr!$Y$1+[3]Apr!$AC$1</f>
         <v>0</v>
       </c>
       <c r="D27" s="172" t="n">
-        <f aca="false">[3]May!$Y$1</f>
+        <f aca="false">[3]May!$Y$1+[3]May!$AC$1</f>
         <v>500</v>
       </c>
       <c r="E27" s="173" t="n">
-        <f aca="false">[3]Jun!$Y$1</f>
+        <f aca="false">[3]Jun!$Y$1+[3]Jun!$AC$1</f>
         <v>0</v>
       </c>
       <c r="F27" s="172" t="n">
-        <f aca="false">[3]Jul!$Y$1</f>
+        <f aca="false">[3]Jul!$Y$1+[3]Jul!$AC$1</f>
         <v>400</v>
       </c>
       <c r="G27" s="172" t="n">
-        <f aca="false">[3]Aug!$Y$1</f>
-        <v>0</v>
+        <f aca="false">[3]Aug!$Y$1+[3]Aug!$AC$1</f>
+        <v>291.666666666667</v>
       </c>
       <c r="H27" s="173" t="n">
-        <f aca="false">[3]Sep!$Y$1</f>
+        <f aca="false">[3]Sep!$Y$1+[3]Sep!$AC$1</f>
         <v>0</v>
       </c>
       <c r="I27" s="172" t="n">
-        <f aca="false">[3]Oct!$Y$1</f>
+        <f aca="false">[3]Oct!$Y$1+[3]Oct!$AC$1</f>
         <v>2500</v>
       </c>
       <c r="J27" s="172" t="n">
-        <f aca="false">[3]Nov!$Y$1</f>
+        <f aca="false">[3]Nov!$Y$1+[3]Nov!$AC$1</f>
         <v>0</v>
       </c>
       <c r="K27" s="173" t="n">
-        <f aca="false">[3]Dec!$Y$1</f>
+        <f aca="false">[3]Dec!$Y$1+[3]Dec!$AC$1</f>
         <v>0</v>
       </c>
       <c r="L27" s="172" t="n">
-        <f aca="false">[3]Jan!$Y$1</f>
+        <f aca="false">[3]Jan!$Y$1+[3]Jan!$AC$1</f>
         <v>400</v>
       </c>
       <c r="M27" s="172" t="n">
-        <f aca="false">[3]Feb!$Y$1</f>
+        <f aca="false">[3]Feb!$Y$1+[3]Feb!$AC$1</f>
         <v>0</v>
       </c>
       <c r="N27" s="172" t="n">
-        <f aca="false">[3]Mar!$Y$1</f>
+        <f aca="false">[3]Mar!$Y$1+[3]Mar!$AC$1</f>
         <v>0</v>
       </c>
       <c r="O27" s="165"/>
@@ -23972,7 +24080,7 @@
       </c>
       <c r="B35" s="171" t="n">
         <f aca="false">SUM(B21:B34)</f>
-        <v>149373.65</v>
+        <v>149665.316666667</v>
       </c>
       <c r="C35" s="171" t="n">
         <f aca="false">SUM(C21:C34)</f>
@@ -23992,7 +24100,7 @@
       </c>
       <c r="G35" s="171" t="n">
         <f aca="false">SUM(G21:G34)</f>
-        <v>11474.45</v>
+        <v>11766.1166666667</v>
       </c>
       <c r="H35" s="171" t="n">
         <f aca="false">SUM(H21:H34)</f>
@@ -24047,7 +24155,7 @@
       </c>
       <c r="B37" s="171" t="n">
         <f aca="false">B19-B35</f>
-        <v>171773.016666666</v>
+        <v>171481.35</v>
       </c>
       <c r="C37" s="171" t="n">
         <f aca="false">C19-C35</f>
@@ -24067,7 +24175,7 @@
       </c>
       <c r="G37" s="171" t="n">
         <f aca="false">G19-G35</f>
-        <v>17854.7166666666</v>
+        <v>17563.05</v>
       </c>
       <c r="H37" s="171" t="n">
         <f aca="false">H19-H35</f>
@@ -24163,7 +24271,7 @@
       </c>
       <c r="B39" s="171" t="n">
         <f aca="false">B37+B38</f>
-        <v>171773.016666666</v>
+        <v>171481.35</v>
       </c>
       <c r="C39" s="171" t="n">
         <f aca="false">C37+C38</f>
@@ -24183,7 +24291,7 @@
       </c>
       <c r="G39" s="171" t="n">
         <f aca="false">G37+G38</f>
-        <v>17854.7166666666</v>
+        <v>17563.05</v>
       </c>
       <c r="H39" s="171" t="n">
         <f aca="false">H37+H38</f>
@@ -24373,55 +24481,55 @@
       </c>
       <c r="B44" s="178" t="n">
         <f aca="false">SUM(C44:N44)</f>
-        <v>44133.3103333331</v>
+        <v>43952.4769999998</v>
       </c>
       <c r="C44" s="178" t="n">
         <f aca="false">IF(C9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="D44" s="178" t="n">
         <f aca="false">IF(D9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="E44" s="178" t="n">
         <f aca="false">IF(E9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="F44" s="178" t="n">
         <f aca="false">IF(F9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="G44" s="178" t="n">
         <f aca="false">IF(G9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="H44" s="178" t="n">
         <f aca="false">IF(H9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="I44" s="178" t="n">
         <f aca="false">IF(I9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="J44" s="178" t="n">
         <f aca="false">IF(J9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="K44" s="178" t="n">
         <f aca="false">IF(K9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="L44" s="178" t="n">
         <f aca="false">IF(L9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="M44" s="178" t="n">
         <f aca="false">IF(M9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="N44" s="178" t="n">
         <f aca="false">IF(N9&gt;0,'Profit Forecast'!C$46/12,0)</f>
-        <v>3677.77586111109</v>
+        <v>3662.70641666665</v>
       </c>
       <c r="O44" s="165"/>
     </row>
@@ -24431,55 +24539,55 @@
       </c>
       <c r="B45" s="190" t="n">
         <f aca="false">SUM(C45:N45)</f>
-        <v>100639.706333333</v>
+        <v>100528.873</v>
       </c>
       <c r="C45" s="191" t="n">
         <f aca="false">C39-C42-C44</f>
-        <v>10405.2741388889</v>
+        <v>10420.3435833333</v>
       </c>
       <c r="D45" s="192" t="n">
         <f aca="false">D39-D42-D44</f>
-        <v>10424.5241388889</v>
+        <v>10439.5935833333</v>
       </c>
       <c r="E45" s="192" t="n">
         <f aca="false">E39-E42-E44</f>
-        <v>6358.52413888887</v>
+        <v>6373.59358333332</v>
       </c>
       <c r="F45" s="192" t="n">
         <f aca="false">F39-F42-F44</f>
-        <v>5418.27413888888</v>
+        <v>5433.34358333332</v>
       </c>
       <c r="G45" s="192" t="n">
         <f aca="false">G39-G42-G44</f>
-        <v>13176.9408055555</v>
+        <v>12900.3435833333</v>
       </c>
       <c r="H45" s="192" t="n">
         <f aca="false">H39-H42-H44</f>
-        <v>9505.19080555555</v>
+        <v>9520.26024999999</v>
       </c>
       <c r="I45" s="192" t="n">
         <f aca="false">I39-I42-I44</f>
-        <v>7625.77413888888</v>
+        <v>7640.84358333332</v>
       </c>
       <c r="J45" s="192" t="n">
         <f aca="false">J39-J42-J44</f>
-        <v>10467.5241388889</v>
+        <v>10482.5935833333</v>
       </c>
       <c r="K45" s="192" t="n">
         <f aca="false">K39-K42-K44</f>
-        <v>6119.52413888887</v>
+        <v>6134.59358333332</v>
       </c>
       <c r="L45" s="192" t="n">
         <f aca="false">L39-L42-L44</f>
-        <v>9605.27413888888</v>
+        <v>9620.34358333332</v>
       </c>
       <c r="M45" s="192" t="n">
         <f aca="false">M39-M42-M44</f>
-        <v>11802.0241388889</v>
+        <v>11817.0935833333</v>
       </c>
       <c r="N45" s="192" t="n">
         <f aca="false">N39-N42-N44</f>
-        <v>-269.142527777791</v>
+        <v>-254.073083333347</v>
       </c>
       <c r="O45" s="165"/>
     </row>
@@ -24557,6 +24665,64 @@
       <c r="M47" s="194"/>
       <c r="N47" s="194"/>
       <c r="O47" s="187"/>
+    </row>
+    <row r="49" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="183" t="s">
+        <v>291</v>
+      </c>
+      <c r="B49" s="171" t="n">
+        <f aca="false">SUM(C49:N49)</f>
+        <v>291.666666666667</v>
+      </c>
+      <c r="C49" s="172" t="n">
+        <f aca="false">[3]Apr!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="D49" s="172" t="n">
+        <f aca="false">[3]May!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="E49" s="173" t="n">
+        <f aca="false">[3]Jun!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="F49" s="172" t="n">
+        <f aca="false">[3]Jul!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="G49" s="172" t="n">
+        <f aca="false">[3]Aug!$AC$1</f>
+        <v>291.666666666667</v>
+      </c>
+      <c r="H49" s="173" t="n">
+        <f aca="false">[3]Sep!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="I49" s="172" t="n">
+        <f aca="false">[3]Oct!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="J49" s="172" t="n">
+        <f aca="false">[3]Nov!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="K49" s="173" t="n">
+        <f aca="false">[3]Dec!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="L49" s="172" t="n">
+        <f aca="false">[3]Jan!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="M49" s="172" t="n">
+        <f aca="false">[3]Feb!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="N49" s="173" t="n">
+        <f aca="false">[3]Mar!$AC$1</f>
+        <v>0</v>
+      </c>
+      <c r="O49" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -24617,25 +24783,25 @@
     <row r="2" s="197" customFormat="true" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="196"/>
       <c r="B2" s="198" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C2" s="198" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="D2" s="198" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E2" s="198" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F2" s="198" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="G2" s="198" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H2" s="198" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I2" s="196"/>
     </row>
@@ -24664,7 +24830,7 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="196"/>
       <c r="B5" s="196" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C5" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C5:E7)</f>
@@ -24692,7 +24858,7 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="196"/>
       <c r="B6" s="196" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C6" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C8:E8)+SUM('Profit &amp; Loss Account'!C11:E11)+SUM('Profit &amp; Loss Account'!C38:E38)</f>
@@ -24720,7 +24886,7 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="196"/>
       <c r="B7" s="196" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C7" s="200" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C14:E14)+SUM('Profit &amp; Loss Account'!C16:E16)</f>
@@ -24770,7 +24936,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="196"/>
       <c r="B10" s="203" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="C10" s="196"/>
       <c r="D10" s="196"/>
@@ -24794,7 +24960,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="196"/>
       <c r="B12" s="196" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C12" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C21:E21)</f>
@@ -24822,7 +24988,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="196"/>
       <c r="B13" s="196" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C13" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C22:E22)</f>
@@ -24850,7 +25016,7 @@
     <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="196"/>
       <c r="B14" s="196" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C14" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C23:E23)</f>
@@ -24878,7 +25044,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="196"/>
       <c r="B15" s="196" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C15" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C24:E24)</f>
@@ -24906,7 +25072,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="196"/>
       <c r="B16" s="196" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C16" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C31:E31)</f>
@@ -24934,7 +25100,7 @@
     <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="196"/>
       <c r="B17" s="196" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C17" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C25:E26)</f>
@@ -24962,7 +25128,7 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="196"/>
       <c r="B18" s="196" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C18" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C27:E27)</f>
@@ -24970,7 +25136,7 @@
       </c>
       <c r="D18" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!F27:H27)</f>
-        <v>400</v>
+        <v>691.666666666667</v>
       </c>
       <c r="E18" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!I27:K27)</f>
@@ -24982,7 +25148,7 @@
       </c>
       <c r="G18" s="201" t="n">
         <f aca="false">SUM(C18:F18)</f>
-        <v>3800</v>
+        <v>4091.66666666667</v>
       </c>
       <c r="H18" s="196"/>
       <c r="I18" s="196"/>
@@ -24990,7 +25156,7 @@
     <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="196"/>
       <c r="B19" s="196" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C19" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C28:E28)</f>
@@ -25018,7 +25184,7 @@
     <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="196"/>
       <c r="B20" s="196" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="C20" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C29:E29)</f>
@@ -25046,7 +25212,7 @@
     <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="196"/>
       <c r="B21" s="196" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C21" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C30:E30)</f>
@@ -25074,7 +25240,7 @@
     <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="196"/>
       <c r="B22" s="196" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C22" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C32:E32)</f>
@@ -25113,7 +25279,7 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="196"/>
       <c r="B24" s="196" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C24" s="201" t="n">
         <f aca="false">SUM('Profit &amp; Loss Account'!C15:E15)</f>
@@ -25141,27 +25307,29 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="196"/>
       <c r="B25" s="196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C25" s="201" t="n">
+        <f aca="false">SUM('Profit &amp; Loss Account'!C49:E49)</f>
         <v>0</v>
       </c>
       <c r="D25" s="201" t="n">
-        <v>0</v>
+        <f aca="false">SUM('Profit &amp; Loss Account'!F49:H49)</f>
+        <v>291.666666666667</v>
       </c>
       <c r="E25" s="201" t="n">
+        <f aca="false">SUM('Profit &amp; Loss Account'!I49:K49)</f>
         <v>0</v>
       </c>
       <c r="F25" s="201" t="n">
+        <f aca="false">SUM('Profit &amp; Loss Account'!L49:N49)</f>
         <v>0</v>
       </c>
       <c r="G25" s="201" t="n">
         <f aca="false">SUM(C25:F25)</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="196" t="s">
-        <v>315</v>
-      </c>
+        <v>291.666666666667</v>
+      </c>
+      <c r="H25" s="196"/>
       <c r="I25" s="196"/>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -25220,24 +25388,24 @@
         <v>316</v>
       </c>
       <c r="C29" s="204" t="n">
-        <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C25,C26)</f>
+        <f aca="false">SUM(C7,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C24,C26)</f>
         <v>43378.35</v>
       </c>
       <c r="D29" s="204" t="n">
-        <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D25,D26)</f>
-        <v>41149.6</v>
+        <f aca="false">SUM(D7,D12,D13,D14,D15,D16,D17,D18,D19,D20,D21,D22,D24,D26)</f>
+        <v>41441.2666666667</v>
       </c>
       <c r="E29" s="204" t="n">
-        <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E25,E26)</f>
+        <f aca="false">SUM(E7,E12,E13,E14,E15,E16,E17,E18,E19,E20,E21,E22,E24,E26)</f>
         <v>45153.85</v>
       </c>
       <c r="F29" s="204" t="n">
-        <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F25,F26)</f>
+        <f aca="false">SUM(F7,F12,F13,F14,F15,F16,F17,F18,F19,F20,F21,F22,F24,F26)</f>
         <v>39828.5166666667</v>
       </c>
       <c r="G29" s="204" t="n">
-        <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G25,G26)</f>
-        <v>169510.316666667</v>
+        <f aca="false">SUM(G7,G12,G13,G14,G15,G16,G17,G18,G19,G20,G21,G22,G24,G26)</f>
+        <v>169801.983333333</v>
       </c>
       <c r="H29" s="205"/>
       <c r="I29" s="196"/>
@@ -25313,252 +25481,308 @@
     <row r="36" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="196"/>
       <c r="B36" s="196" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="C36" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C7*$I$36</f>
+        <v>45.65</v>
       </c>
       <c r="D36" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D7*$I$36</f>
+        <v>52.05</v>
       </c>
       <c r="E36" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E7*$I$36</f>
+        <v>43.65</v>
       </c>
       <c r="F36" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F7*$I$36</f>
+        <v>128.05</v>
       </c>
       <c r="G36" s="201" t="n">
         <f aca="false">SUM(C36:F36)</f>
-        <v>0</v>
+        <v>269.4</v>
       </c>
       <c r="H36" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I36" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I36" s="196" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="196"/>
       <c r="B37" s="196" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C37" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C24*$I$37</f>
+        <v>125</v>
       </c>
       <c r="D37" s="201" t="n">
+        <f aca="false">D24*$I$37</f>
         <v>0</v>
       </c>
       <c r="E37" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E24*$I$37</f>
+        <v>75</v>
       </c>
       <c r="F37" s="201" t="n">
+        <f aca="false">F24*$I$37</f>
         <v>0</v>
       </c>
       <c r="G37" s="201" t="n">
         <f aca="false">SUM(C37:F37)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H37" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I37" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I37" s="196" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="196"/>
       <c r="B38" s="196" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C38" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C12*$I$38</f>
+        <v>879.024</v>
       </c>
       <c r="D38" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D12*$I$38</f>
+        <v>905.690666666667</v>
       </c>
       <c r="E38" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E12*$I$38</f>
+        <v>1045.69066666667</v>
       </c>
       <c r="F38" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F12*$I$38</f>
+        <v>879.024</v>
       </c>
       <c r="G38" s="201" t="n">
         <f aca="false">SUM(C38:F38)</f>
-        <v>0</v>
+        <v>3709.42933333333</v>
       </c>
       <c r="H38" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I38" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I38" s="196" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="196"/>
       <c r="B39" s="196" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C39" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C17*$I$39</f>
+        <v>515.5625</v>
       </c>
       <c r="D39" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D17*$I$39</f>
+        <v>467.625</v>
       </c>
       <c r="E39" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E17*$I$39</f>
+        <v>493.3125</v>
       </c>
       <c r="F39" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F17*$I$39</f>
+        <v>519.5625</v>
       </c>
       <c r="G39" s="201" t="n">
         <f aca="false">SUM(C39:F39)</f>
-        <v>0</v>
+        <v>1996.0625</v>
       </c>
       <c r="H39" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I39" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I39" s="196" t="n">
+        <v>0.25</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="196"/>
       <c r="B40" s="196" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C40" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C13*$I$40</f>
+        <v>165</v>
       </c>
       <c r="D40" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D13*$I$40</f>
+        <v>162.5</v>
       </c>
       <c r="E40" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E13*$I$40</f>
+        <v>167.5</v>
       </c>
       <c r="F40" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F13*$I$40</f>
+        <v>165</v>
       </c>
       <c r="G40" s="201" t="n">
         <f aca="false">SUM(C40:F40)</f>
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="H40" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I40" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I40" s="196" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="196"/>
       <c r="B41" s="196" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C41" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C14*$I$41</f>
+        <v>6</v>
       </c>
       <c r="D41" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D14*$I$41</f>
+        <v>21</v>
       </c>
       <c r="E41" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E14*$I$41</f>
+        <v>4.8</v>
       </c>
       <c r="F41" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F14*$I$41</f>
+        <v>25.2</v>
       </c>
       <c r="G41" s="201" t="n">
         <f aca="false">SUM(C41:F41)</f>
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="H41" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I41" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I41" s="196" t="n">
+        <v>0.06</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="196"/>
       <c r="B42" s="196" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C42" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C15*$I$42</f>
+        <v>51.275</v>
       </c>
       <c r="D42" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D15*$I$42</f>
+        <v>48.825</v>
       </c>
       <c r="E42" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E15*$I$42</f>
+        <v>56.875</v>
       </c>
       <c r="F42" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F15*$I$42</f>
+        <v>55.475</v>
       </c>
       <c r="G42" s="201" t="n">
         <f aca="false">SUM(C42:F42)</f>
-        <v>0</v>
+        <v>212.45</v>
       </c>
       <c r="H42" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I42" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I42" s="196" t="n">
+        <v>0.07</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="196"/>
       <c r="B43" s="196" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C43" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C18*$I$43</f>
+        <v>40</v>
       </c>
       <c r="D43" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D18*$I$43</f>
+        <v>55.3333333333334</v>
       </c>
       <c r="E43" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E18*$I$43</f>
+        <v>200</v>
       </c>
       <c r="F43" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F18*$I$43</f>
+        <v>32</v>
       </c>
       <c r="G43" s="201" t="n">
         <f aca="false">SUM(C43:F43)</f>
-        <v>0</v>
+        <v>327.333333333333</v>
       </c>
       <c r="H43" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I43" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I43" s="196" t="n">
+        <v>0.08</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="196"/>
       <c r="B44" s="196" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C44" s="201" t="n">
+        <f aca="false">C25</f>
         <v>0</v>
       </c>
       <c r="D44" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D25</f>
+        <v>291.666666666667</v>
       </c>
       <c r="E44" s="201" t="n">
+        <f aca="false">E25</f>
         <v>0</v>
       </c>
       <c r="F44" s="201" t="n">
+        <f aca="false">F25</f>
         <v>0</v>
       </c>
       <c r="G44" s="201" t="n">
         <f aca="false">SUM(C44:F44)</f>
-        <v>0</v>
+        <v>291.666666666667</v>
       </c>
       <c r="H44" s="196" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="I44" s="196"/>
     </row>
     <row r="45" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="196"/>
       <c r="B45" s="196" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C45" s="201" t="n">
+        <f aca="false">C21*$I$45</f>
         <v>0</v>
       </c>
       <c r="D45" s="201" t="n">
+        <f aca="false">D21*$I$45</f>
         <v>0</v>
       </c>
       <c r="E45" s="201" t="n">
+        <f aca="false">E21*$I$45</f>
         <v>0</v>
       </c>
       <c r="F45" s="201" t="n">
+        <f aca="false">F21*$I$45</f>
         <v>0</v>
       </c>
       <c r="G45" s="201" t="n">
@@ -25566,87 +25790,107 @@
         <v>0</v>
       </c>
       <c r="H45" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I45" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I45" s="196" t="n">
+        <v>0.09</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="196"/>
       <c r="B46" s="196" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C46" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C16*$I$46</f>
+        <v>227.5</v>
       </c>
       <c r="D46" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D16*$I$46</f>
+        <v>130.8</v>
       </c>
       <c r="E46" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E16*$I$46</f>
+        <v>19.2</v>
       </c>
       <c r="F46" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F16*$I$46</f>
+        <v>12.5</v>
       </c>
       <c r="G46" s="201" t="n">
         <f aca="false">SUM(C46:F46)</f>
-        <v>0</v>
+        <v>390</v>
       </c>
       <c r="H46" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I46" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I46" s="196" t="n">
+        <v>0.1</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="196"/>
       <c r="B47" s="196" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C47" s="201" t="n">
+        <f aca="false">C20*$I$47</f>
         <v>0</v>
       </c>
       <c r="D47" s="201" t="n">
+        <f aca="false">D20*$I$47</f>
         <v>0</v>
       </c>
       <c r="E47" s="201" t="n">
+        <f aca="false">E20*$I$47</f>
         <v>0</v>
       </c>
       <c r="F47" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F20*$I$47</f>
+        <v>-33</v>
       </c>
       <c r="G47" s="201" t="n">
         <f aca="false">SUM(C47:F47)</f>
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="H47" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I47" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I47" s="196" t="n">
+        <v>0.11</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="196"/>
       <c r="B48" s="196" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C48" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C19*$I$48</f>
+        <v>115</v>
       </c>
       <c r="D48" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D19*$I$48</f>
+        <v>506.8</v>
       </c>
       <c r="E48" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E19*$I$48</f>
+        <v>106.7</v>
       </c>
       <c r="F48" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F19*$I$48</f>
+        <v>102.5</v>
       </c>
       <c r="G48" s="201" t="n">
         <f aca="false">SUM(C48:F48)</f>
-        <v>0</v>
+        <v>831</v>
       </c>
       <c r="H48" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I48" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I48" s="196" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="196"/>
@@ -25654,51 +25898,61 @@
         <v>282</v>
       </c>
       <c r="C49" s="201" t="n">
-        <v>0</v>
+        <f aca="false">SUM('Profit &amp; Loss Account'!C34:E34)</f>
+        <v>3435</v>
       </c>
       <c r="D49" s="201" t="n">
-        <v>0</v>
+        <f aca="false">SUM('Profit &amp; Loss Account'!F34:H34)</f>
+        <v>3435</v>
       </c>
       <c r="E49" s="201" t="n">
-        <v>0</v>
+        <f aca="false">SUM('Profit &amp; Loss Account'!I34:K34)</f>
+        <v>3435</v>
       </c>
       <c r="F49" s="201" t="n">
-        <v>0</v>
+        <f aca="false">SUM('Profit &amp; Loss Account'!L34:N34)</f>
+        <v>3435</v>
       </c>
       <c r="G49" s="201" t="n">
         <f aca="false">SUM(C49:F49)</f>
-        <v>0</v>
+        <v>13740</v>
       </c>
       <c r="H49" s="196" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="I49" s="196"/>
     </row>
     <row r="50" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="196"/>
       <c r="B50" s="196" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C50" s="201" t="n">
-        <v>0</v>
+        <f aca="false">C22*$I$50</f>
+        <v>201.175</v>
       </c>
       <c r="D50" s="201" t="n">
-        <v>0</v>
+        <f aca="false">D22*$I$50</f>
+        <v>42.575</v>
       </c>
       <c r="E50" s="201" t="n">
-        <v>0</v>
+        <f aca="false">E22*$I$50</f>
+        <v>137.041666666667</v>
       </c>
       <c r="F50" s="201" t="n">
-        <v>0</v>
+        <f aca="false">F22*$I$50</f>
+        <v>39.325</v>
       </c>
       <c r="G50" s="201" t="n">
         <f aca="false">SUM(C50:F50)</f>
-        <v>0</v>
+        <v>420.116666666666</v>
       </c>
       <c r="H50" s="196" t="s">
-        <v>315</v>
-      </c>
-      <c r="I50" s="196"/>
+        <v>317</v>
+      </c>
+      <c r="I50" s="196" t="n">
+        <v>0.13</v>
+      </c>
     </row>
     <row r="51" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="196"/>
@@ -25767,14 +26021,14 @@
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="212"/>
       <c r="B2" s="216" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="C2" s="217" t="str">
         <f aca="false">Admin!L2</f>
         <v>2026-27</v>
       </c>
       <c r="D2" s="218" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="E2" s="218"/>
       <c r="F2" s="218"/>
@@ -25801,13 +26055,13 @@
     <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="212"/>
       <c r="B5" s="223" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C5" s="223"/>
       <c r="D5" s="223"/>
       <c r="E5" s="224" t="n">
         <f aca="false">'SE Full'!O210</f>
-        <v>121513.016666666</v>
+        <v>130552.8085</v>
       </c>
       <c r="F5" s="215"/>
       <c r="G5" s="219"/>
@@ -25816,7 +26070,7 @@
     <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="212"/>
       <c r="B6" s="221" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="C6" s="221" t="str">
         <f aca="false">C2</f>
@@ -25825,7 +26079,7 @@
       <c r="D6" s="226"/>
       <c r="E6" s="219" t="n">
         <f aca="false">IF(E5&lt;=0,0,MAX(0,Admin!N$4-MAX(0,E5-Admin!N$5)/2))</f>
-        <v>1813.49166666687</v>
+        <v>0</v>
       </c>
       <c r="F6" s="215"/>
       <c r="G6" s="219"/>
@@ -25834,13 +26088,13 @@
     <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="212"/>
       <c r="B7" s="223" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="C7" s="223"/>
       <c r="D7" s="223"/>
       <c r="E7" s="224" t="n">
         <f aca="false">IF((E5&gt;E6),(E5-E6),0)</f>
-        <v>119699.524999999</v>
+        <v>130552.8085</v>
       </c>
       <c r="F7" s="215"/>
       <c r="G7" s="219"/>
@@ -25849,7 +26103,7 @@
     <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="212"/>
       <c r="B8" s="221" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="C8" s="221" t="n">
         <f aca="false">Admin!N$11</f>
@@ -25871,7 +26125,7 @@
     <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="212"/>
       <c r="B9" s="221" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C9" s="221" t="n">
         <f aca="false">Admin!M$11</f>
@@ -25883,7 +26137,7 @@
       </c>
       <c r="E9" s="214" t="n">
         <f aca="false">IF(E7&gt;C9,(MIN(E7,C10)-C9)*D9,0)</f>
-        <v>32799.8099999998</v>
+        <v>34976</v>
       </c>
       <c r="F9" s="215"/>
       <c r="G9" s="219"/>
@@ -25892,7 +26146,7 @@
     <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="212"/>
       <c r="B10" s="221" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="C10" s="221" t="n">
         <f aca="false">Admin!N$13</f>
@@ -25904,7 +26158,7 @@
       </c>
       <c r="E10" s="214" t="n">
         <f aca="false">IF(E7&gt;C10,(E7-C10)*D10,0)</f>
-        <v>0</v>
+        <v>2435.76382499982</v>
       </c>
       <c r="F10" s="215"/>
       <c r="G10" s="219"/>
@@ -25913,13 +26167,13 @@
     <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="212"/>
       <c r="B11" s="229" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="C11" s="230"/>
       <c r="D11" s="231"/>
       <c r="E11" s="232" t="n">
         <f aca="false">SUM(E8:E10)</f>
-        <v>40339.8099999998</v>
+        <v>44951.7638249998</v>
       </c>
       <c r="F11" s="233"/>
       <c r="G11" s="234"/>
@@ -25928,7 +26182,7 @@
     <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="212"/>
       <c r="B12" s="221" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="C12" s="221"/>
       <c r="D12" s="235"/>
@@ -25943,7 +26197,7 @@
     <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="212"/>
       <c r="B13" s="236" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C13" s="237" t="n">
         <f aca="false">Admin!B21</f>
@@ -25968,7 +26222,7 @@
     <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="212"/>
       <c r="B15" s="240" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C15" s="240"/>
       <c r="D15" s="227" t="n">
@@ -25986,7 +26240,7 @@
     <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="212"/>
       <c r="B16" s="240" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="C16" s="240"/>
       <c r="D16" s="227" t="n">
@@ -25995,7 +26249,7 @@
       </c>
       <c r="E16" s="241" t="n">
         <f aca="false">IF((E5&gt;Admin!N$23),((E5-Admin!N$23)*D16),0)</f>
-        <v>1424.86033333333</v>
+        <v>1605.65616999999</v>
       </c>
       <c r="F16" s="215"/>
       <c r="G16" s="234"/>
@@ -26014,13 +26268,13 @@
     <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="212"/>
       <c r="B18" s="242" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="C18" s="242"/>
       <c r="D18" s="238"/>
       <c r="E18" s="232" t="n">
         <f aca="false">SUM(E11:E17)</f>
-        <v>44026.6703333331</v>
+        <v>48819.4199949998</v>
       </c>
       <c r="F18" s="215"/>
       <c r="G18" s="219"/>
@@ -26047,11 +26301,11 @@
     <row r="21" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="212"/>
       <c r="B21" s="229" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C21" s="244"/>
       <c r="D21" s="245" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="E21" s="245"/>
       <c r="F21" s="245"/>
@@ -26071,10 +26325,10 @@
       <c r="B23" s="221"/>
       <c r="C23" s="221"/>
       <c r="D23" s="247" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E23" s="248" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="F23" s="249"/>
       <c r="G23" s="219"/>
@@ -26091,18 +26345,18 @@
     <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="212"/>
       <c r="B25" s="221" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C25" s="251" t="str">
         <f aca="false">Admin!B24</f>
         <v>2027-28</v>
       </c>
       <c r="D25" s="252" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="E25" s="241" t="n">
         <f aca="false">E18</f>
-        <v>44026.6703333331</v>
+        <v>48819.4199949998</v>
       </c>
       <c r="F25" s="215"/>
       <c r="G25" s="219"/>
@@ -26110,7 +26364,7 @@
     <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="212"/>
       <c r="B26" s="221" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C26" s="221"/>
       <c r="D26" s="253" t="n">
@@ -26119,7 +26373,7 @@
       </c>
       <c r="E26" s="224" t="n">
         <f aca="false">E25/2</f>
-        <v>22013.3351666665</v>
+        <v>24409.7099974999</v>
       </c>
       <c r="F26" s="215"/>
       <c r="G26" s="219"/>
@@ -26127,7 +26381,7 @@
     <row r="27" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="212"/>
       <c r="B27" s="221" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C27" s="221"/>
       <c r="D27" s="253" t="n">
@@ -26136,7 +26390,7 @@
       </c>
       <c r="E27" s="224" t="n">
         <f aca="false">E25/2</f>
-        <v>22013.3351666665</v>
+        <v>24409.7099974999</v>
       </c>
       <c r="F27" s="215"/>
       <c r="G27" s="219"/>
@@ -26153,7 +26407,7 @@
     <row r="29" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="212"/>
       <c r="B29" s="254" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="C29" s="255"/>
       <c r="D29" s="238"/>
@@ -26164,7 +26418,7 @@
     <row r="30" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="212"/>
       <c r="B30" s="256" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C30" s="256"/>
       <c r="D30" s="212"/>
@@ -26175,7 +26429,7 @@
     <row r="31" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="212"/>
       <c r="B31" s="259" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C31" s="259"/>
       <c r="D31" s="260"/>
@@ -26186,7 +26440,7 @@
     <row r="32" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="212"/>
       <c r="B32" s="261" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="C32" s="259"/>
       <c r="D32" s="260"/>
@@ -26197,7 +26451,7 @@
     <row r="33" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="212"/>
       <c r="B33" s="255" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="C33" s="255"/>
       <c r="D33" s="260"/>
@@ -26208,7 +26462,7 @@
     <row r="34" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="212"/>
       <c r="B34" s="255" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="C34" s="255"/>
       <c r="D34" s="260"/>
@@ -26219,7 +26473,7 @@
     <row r="35" customFormat="false" ht="12.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="212"/>
       <c r="B35" s="255" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="C35" s="255"/>
       <c r="D35" s="260"/>
@@ -26294,39 +26548,39 @@
     <row r="2" s="273" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="268"/>
       <c r="B2" s="269" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="C2" s="270" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D2" s="270" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E2" s="270" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F2" s="270" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="G2" s="270" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="H2" s="270" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="I2" s="270" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="J2" s="271"/>
       <c r="K2" s="269" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="L2" s="272"/>
     </row>
     <row r="3" s="273" customFormat="true" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="268"/>
       <c r="B3" s="274" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="C3" s="274"/>
       <c r="D3" s="275"/>
@@ -26375,7 +26629,7 @@
       </c>
       <c r="J4" s="159"/>
       <c r="K4" s="279" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="L4" s="165"/>
     </row>
@@ -26529,7 +26783,7 @@
       </c>
       <c r="J8" s="159"/>
       <c r="K8" s="279" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="L8" s="165"/>
     </row>
@@ -26881,7 +27135,7 @@
       <c r="F1" s="288"/>
       <c r="G1" s="288"/>
       <c r="H1" s="289" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="I1" s="289"/>
       <c r="J1" s="289"/>
@@ -26889,7 +27143,7 @@
       <c r="L1" s="289"/>
       <c r="M1" s="288"/>
       <c r="N1" s="289" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="O1" s="289"/>
       <c r="P1" s="289"/>
@@ -26897,7 +27151,7 @@
       <c r="R1" s="289"/>
       <c r="S1" s="288"/>
       <c r="T1" s="289" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="U1" s="289"/>
       <c r="V1" s="289"/>
@@ -26917,63 +27171,63 @@
     <row r="2" s="303" customFormat="true" ht="32.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="293"/>
       <c r="B2" s="294" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="C2" s="295"/>
       <c r="D2" s="296" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E2" s="297"/>
       <c r="F2" s="296" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G2" s="297"/>
       <c r="H2" s="298" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="I2" s="297"/>
       <c r="J2" s="296" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="K2" s="297"/>
       <c r="L2" s="296" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="M2" s="297"/>
       <c r="N2" s="298" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="O2" s="297"/>
       <c r="P2" s="296" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="Q2" s="297"/>
       <c r="R2" s="296" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="S2" s="297"/>
       <c r="T2" s="298" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="U2" s="297"/>
       <c r="V2" s="296" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="W2" s="297"/>
       <c r="X2" s="299" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="Y2" s="300"/>
       <c r="Z2" s="296" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AA2" s="297"/>
       <c r="AB2" s="296" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="AC2" s="301"/>
       <c r="AD2" s="302" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="AE2" s="302"/>
       <c r="AF2" s="302"/>
@@ -27011,7 +27265,7 @@
       <c r="AB3" s="306"/>
       <c r="AC3" s="165"/>
       <c r="AD3" s="310" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="AE3" s="310"/>
       <c r="AF3" s="310"/>
@@ -27021,7 +27275,7 @@
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="277"/>
       <c r="B4" s="311" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C4" s="311"/>
       <c r="D4" s="311"/>
@@ -27401,7 +27655,7 @@
       <c r="AB11" s="178"/>
       <c r="AC11" s="165"/>
       <c r="AD11" s="310" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AE11" s="310"/>
       <c r="AF11" s="310"/>
@@ -27631,7 +27885,7 @@
       <c r="AB15" s="178"/>
       <c r="AC15" s="165"/>
       <c r="AD15" s="310" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AE15" s="310"/>
       <c r="AF15" s="310"/>
@@ -27861,7 +28115,7 @@
       <c r="AB19" s="178"/>
       <c r="AC19" s="165"/>
       <c r="AD19" s="310" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AE19" s="310"/>
       <c r="AF19" s="310"/>
@@ -28091,7 +28345,7 @@
       <c r="AB23" s="178"/>
       <c r="AC23" s="165"/>
       <c r="AD23" s="310" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AE23" s="310"/>
       <c r="AF23" s="310"/>
@@ -28399,7 +28653,7 @@
       </c>
       <c r="AC28" s="165"/>
       <c r="AD28" s="310" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AE28" s="310"/>
       <c r="AF28" s="310"/>
@@ -28617,7 +28871,7 @@
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="159"/>
       <c r="B2" s="331" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C2" s="162" t="s">
         <v>255</v>
@@ -28817,7 +29071,7 @@
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="159"/>
       <c r="B7" s="335" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C7" s="171" t="n">
         <f aca="false">SUM(D7:O7)</f>
@@ -29048,11 +29302,11 @@
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="159"/>
       <c r="B13" s="334" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C13" s="171" t="n">
         <f aca="false">SUM(D13:O13)</f>
-        <v>149373.65</v>
+        <v>149665.316666667</v>
       </c>
       <c r="D13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!C35</f>
@@ -29072,7 +29326,7 @@
       </c>
       <c r="H13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!G35</f>
-        <v>11474.45</v>
+        <v>11766.1166666667</v>
       </c>
       <c r="I13" s="171" t="n">
         <f aca="false">'Profit &amp; Loss Account'!H35</f>
@@ -29129,7 +29383,7 @@
       </c>
       <c r="C15" s="171" t="n">
         <f aca="false">SUM(D15:O15)</f>
-        <v>171773.016666666</v>
+        <v>171481.35</v>
       </c>
       <c r="D15" s="171" t="n">
         <f aca="false">D11-D13</f>
@@ -29149,7 +29403,7 @@
       </c>
       <c r="H15" s="171" t="n">
         <f aca="false">H11-H13</f>
-        <v>17854.7166666666</v>
+        <v>17563.05</v>
       </c>
       <c r="I15" s="171" t="n">
         <f aca="false">I11-I13</f>
@@ -29247,7 +29501,7 @@
       </c>
       <c r="C17" s="171" t="n">
         <f aca="false">SUM(D17:O17)</f>
-        <v>171773.016666666</v>
+        <v>171481.35</v>
       </c>
       <c r="D17" s="171" t="n">
         <f aca="false">D15+D16</f>
@@ -29267,7 +29521,7 @@
       </c>
       <c r="H17" s="171" t="n">
         <f aca="false">H15+H16</f>
-        <v>17854.7166666666</v>
+        <v>17563.05</v>
       </c>
       <c r="I17" s="171" t="n">
         <f aca="false">I15+I16</f>
@@ -29320,7 +29574,7 @@
     <row r="19" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="159"/>
       <c r="B19" s="338" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C19" s="162" t="s">
         <v>255</v>
@@ -29533,7 +29787,7 @@
     <row r="24" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="159"/>
       <c r="B24" s="335" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="C24" s="171" t="n">
         <f aca="false">SUM(D24:O24)</f>
@@ -29764,11 +30018,11 @@
     <row r="30" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="159"/>
       <c r="B30" s="334" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C30" s="171" t="n">
         <f aca="false">SUM(D30:O30)</f>
-        <v>149373.65</v>
+        <v>149665.316666667</v>
       </c>
       <c r="D30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(D5&gt;0,D13,C13/C21),0)</f>
@@ -29788,7 +30042,7 @@
       </c>
       <c r="H30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(H5&gt;0,H13,C13/C21),0)</f>
-        <v>11474.45</v>
+        <v>11766.1166666667</v>
       </c>
       <c r="I30" s="171" t="n">
         <f aca="false">IF(C5&gt;0,IF(I5&gt;0,I13,C13/C21),0)</f>
@@ -29845,7 +30099,7 @@
       </c>
       <c r="C32" s="171" t="n">
         <f aca="false">SUM(D32:O32)</f>
-        <v>171773.016666666</v>
+        <v>171481.35</v>
       </c>
       <c r="D32" s="171" t="n">
         <f aca="false">D28-D30</f>
@@ -29865,7 +30119,7 @@
       </c>
       <c r="H32" s="171" t="n">
         <f aca="false">H28-H30</f>
-        <v>17854.7166666666</v>
+        <v>17563.05</v>
       </c>
       <c r="I32" s="171" t="n">
         <f aca="false">I28-I30</f>
@@ -29963,7 +30217,7 @@
       </c>
       <c r="C34" s="171" t="n">
         <f aca="false">SUM(D34:O34)</f>
-        <v>171773.016666666</v>
+        <v>171481.35</v>
       </c>
       <c r="D34" s="171" t="n">
         <f aca="false">D32+D33</f>
@@ -29983,7 +30237,7 @@
       </c>
       <c r="H34" s="171" t="n">
         <f aca="false">H32+H33</f>
-        <v>17854.7166666666</v>
+        <v>17563.05</v>
       </c>
       <c r="I34" s="171" t="n">
         <f aca="false">I32+I33</f>
@@ -30036,7 +30290,7 @@
     <row r="36" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="159"/>
       <c r="B36" s="339" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C36" s="339"/>
       <c r="D36" s="159"/>
@@ -30056,7 +30310,7 @@
     <row r="37" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="159"/>
       <c r="B37" s="170" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C37" s="340" t="n">
         <f aca="false">'Profit &amp; Loss Account'!B33+'Profit &amp; Loss Account'!B34</f>
@@ -30079,7 +30333,7 @@
     <row r="38" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="159"/>
       <c r="B38" s="170" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C38" s="340" t="n">
         <f aca="false">[1]Schedule!$Q$1+[1]Schedule!$R$1+[1]Schedule!$Y$1-[1]Schedule!$Z$1</f>
@@ -30102,11 +30356,11 @@
     <row r="39" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="159"/>
       <c r="B39" s="170" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="C39" s="340" t="n">
         <f aca="false">C34+C37-C38</f>
-        <v>121685.016666666</v>
+        <v>121393.35</v>
       </c>
       <c r="D39" s="159"/>
       <c r="E39" s="159"/>
@@ -30125,11 +30379,11 @@
     <row r="40" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="159"/>
       <c r="B40" s="183" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C40" s="340" t="n">
         <f aca="false">IF(C39&lt;=0,0,MAX(0,Admin!N$4-MAX(0,C39-Admin!N$5)/2))</f>
-        <v>1727.49166666687</v>
+        <v>1873.3250000002</v>
       </c>
       <c r="D40" s="159"/>
       <c r="E40" s="159"/>
@@ -30148,11 +30402,11 @@
     <row r="41" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="159"/>
       <c r="B41" s="183" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="C41" s="340" t="n">
         <f aca="false">IF((C39&gt;C40),(C39-C40),0)</f>
-        <v>119957.524999999</v>
+        <v>119520.024999999</v>
       </c>
       <c r="D41" s="159"/>
       <c r="E41" s="159"/>
@@ -30171,7 +30425,7 @@
     <row r="42" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="159"/>
       <c r="B42" s="183" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C42" s="340" t="n">
         <f aca="false">IF((C41&gt;0),(IF((C41&lt;Admin!M$11),C41*Admin!N$6,Admin!M$11*Admin!N$6)),0)</f>
@@ -30194,11 +30448,11 @@
     <row r="43" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="159"/>
       <c r="B43" s="183" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C43" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!M$11,(MIN(C41,Admin!N$13)-Admin!M$11)*Admin!N$7,0)</f>
-        <v>32903.0099999998</v>
+        <v>32728.0099999998</v>
       </c>
       <c r="D43" s="159"/>
       <c r="E43" s="159"/>
@@ -30217,7 +30471,7 @@
     <row r="44" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="159"/>
       <c r="B44" s="183" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C44" s="340" t="n">
         <f aca="false">IF(C41&gt;Admin!N$13,(C41-Admin!N$13)*Admin!N$8,0)</f>
@@ -30240,11 +30494,11 @@
     <row r="45" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="159"/>
       <c r="B45" s="183" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C45" s="340" t="n">
         <f aca="false">IF(C39&gt;Admin!N$20,IF(C39&lt;Admin!N$23,(C39-Admin!N$20)*Admin!L$20,(Admin!N$23-Admin!N$20)*Admin!L$20),0)+IF(C39&gt;Admin!N$23,(C39-Admin!N$23)*Admin!L$23,0)</f>
-        <v>3690.30033333333</v>
+        <v>3684.46699999999</v>
       </c>
       <c r="D45" s="159"/>
       <c r="E45" s="159"/>
@@ -30263,11 +30517,11 @@
     <row r="46" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="159"/>
       <c r="B46" s="183" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C46" s="342" t="n">
         <f aca="false">C42+C43+C44+C45</f>
-        <v>44133.3103333331</v>
+        <v>43952.4769999998</v>
       </c>
       <c r="D46" s="159"/>
       <c r="E46" s="159"/>
